--- a/Design/config/HeroConfig.xlsx
+++ b/Design/config/HeroConfig.xlsx
@@ -5994,17 +5994,17 @@
         <v>77</v>
       </c>
       <c r="G5" s="5">
+        <v>74</v>
+      </c>
+      <c r="H5" s="5">
         <v>78</v>
-      </c>
-      <c r="H5" s="5">
-        <v>82</v>
       </c>
       <c r="I5" s="5">
         <v>99</v>
       </c>
       <c r="J5" s="5">
         <f>SUM(E5:I5)</f>
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="K5" s="5">
         <v>330</v>
@@ -6074,17 +6074,17 @@
         <v>98</v>
       </c>
       <c r="G6" s="5">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="H6" s="5">
+        <v>22</v>
+      </c>
+      <c r="I6" s="5">
         <v>45</v>
-      </c>
-      <c r="I6" s="5">
-        <v>70</v>
       </c>
       <c r="J6" s="5">
         <f>SUM(E6:I6)</f>
-        <v>353</v>
+        <v>287</v>
       </c>
       <c r="K6" s="5">
         <v>310</v>
@@ -6105,7 +6105,7 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5">
         <f>MAX(25, INT(POWER(2.2,J6/45)))</f>
-        <v>485</v>
+        <v>152</v>
       </c>
       <c r="S6" s="5">
         <v>0</v>
@@ -6158,14 +6158,14 @@
         <v>77</v>
       </c>
       <c r="H7" s="5">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="I7" s="5">
         <v>94</v>
       </c>
       <c r="J7" s="5">
         <f>SUM(E7:I7)</f>
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="K7" s="5">
         <v>260</v>
@@ -6186,7 +6186,7 @@
       <c r="Q7" s="5"/>
       <c r="R7" s="5">
         <f>MAX(25, INT(POWER(2.2,J7/45)))</f>
-        <v>2229</v>
+        <v>1775</v>
       </c>
       <c r="S7" s="5">
         <v>0</v>
@@ -6321,17 +6321,17 @@
         <v>82</v>
       </c>
       <c r="G9" s="5">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H9" s="5">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="I9" s="5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J9" s="5">
         <f>SUM(E9:I9)</f>
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="K9" s="5">
         <v>335</v>
@@ -6352,7 +6352,7 @@
       <c r="Q9" s="5"/>
       <c r="R9" s="5">
         <f>MAX(25, INT(POWER(2.2,J9/45)))</f>
-        <v>286</v>
+        <v>135</v>
       </c>
       <c r="S9" s="5">
         <v>0</v>
@@ -6402,17 +6402,17 @@
         <v>78</v>
       </c>
       <c r="G10" s="5">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H10" s="5">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="I10" s="5">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="J10" s="5">
         <f>SUM(E10:I10)</f>
-        <v>362</v>
+        <v>331</v>
       </c>
       <c r="K10" s="5">
         <v>330</v>
@@ -6433,7 +6433,7 @@
       <c r="Q10" s="5"/>
       <c r="R10" s="5">
         <f>MAX(25, INT(POWER(2.2,J10/45)))</f>
-        <v>568</v>
+        <v>330</v>
       </c>
       <c r="S10" s="5">
         <v>0</v>
@@ -6483,7 +6483,7 @@
         <v>65</v>
       </c>
       <c r="G11" s="5">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H11" s="5">
         <v>75</v>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="J11" s="5">
         <f>SUM(E11:I11)</f>
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K11" s="5">
         <v>240</v>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="R11" s="5">
         <f>MAX(25, INT(POWER(2.2,J11/45)))</f>
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="S11" s="5">
         <v>0</v>
@@ -12530,14 +12530,14 @@
         <v>76</v>
       </c>
       <c r="H88" s="5">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="I88" s="5">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="J88" s="5">
         <f>SUM(E88:I88)</f>
-        <v>413</v>
+        <v>339</v>
       </c>
       <c r="K88" s="5">
         <v>180</v>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="R88" s="5">
         <f>MAX(25, INT(POWER(2.2,J88/45)))</f>
-        <v>1388</v>
+        <v>379</v>
       </c>
       <c r="S88" s="5">
         <v>0</v>
@@ -19774,14 +19774,14 @@
         <v>53</v>
       </c>
       <c r="H180" s="5">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="I180" s="5">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J180" s="5">
         <f>SUM(E180:I180)</f>
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="K180" s="5">
         <v>330</v>
@@ -19802,7 +19802,7 @@
       <c r="Q180" s="5"/>
       <c r="R180" s="5">
         <f>MAX(25, INT(POWER(2.2,J180/45)))</f>
-        <v>468</v>
+        <v>341</v>
       </c>
       <c r="S180" s="5">
         <v>0</v>
@@ -21849,17 +21849,17 @@
         <v>85</v>
       </c>
       <c r="G207" s="5">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="H207" s="5">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I207" s="5">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J207" s="5">
         <f>SUM(E207:I207)</f>
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="K207" s="5">
         <v>300</v>
@@ -21880,7 +21880,7 @@
       <c r="Q207" s="5"/>
       <c r="R207" s="5">
         <f>MAX(25, INT(POWER(2.2,J207/45)))</f>
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="S207" s="5">
         <v>0</v>
@@ -22922,17 +22922,17 @@
         <v>91</v>
       </c>
       <c r="G221" s="5">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H221" s="5">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="I221" s="5">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J221" s="5">
         <f>SUM(E221:I221)</f>
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="K221" s="5">
         <v>300</v>
@@ -22953,7 +22953,7 @@
       <c r="Q221" s="5"/>
       <c r="R221" s="5">
         <f>MAX(25, INT(POWER(2.2,J221/45)))</f>
-        <v>599</v>
+        <v>407</v>
       </c>
       <c r="S221" s="5">
         <v>0</v>
@@ -24456,17 +24456,17 @@
         <v>83</v>
       </c>
       <c r="G241" s="5">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H241" s="5">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="I241" s="5">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="J241" s="5">
         <f>SUM(E241:I241)</f>
-        <v>390</v>
+        <v>358</v>
       </c>
       <c r="K241" s="5">
         <v>290</v>
@@ -24487,7 +24487,7 @@
       <c r="Q241" s="5"/>
       <c r="R241" s="5">
         <f>MAX(25, INT(POWER(2.2,J241/45)))</f>
-        <v>928</v>
+        <v>529</v>
       </c>
       <c r="S241" s="5">
         <v>0</v>
@@ -24612,17 +24612,17 @@
         <v>65</v>
       </c>
       <c r="G243" s="5">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H243" s="5">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="I243" s="5">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="J243" s="5">
         <f>SUM(E243:I243)</f>
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="K243" s="5">
         <v>280</v>
@@ -24645,7 +24645,7 @@
       <c r="Q243" s="5"/>
       <c r="R243" s="5">
         <f>MAX(25, INT(POWER(2.2,J243/45)))</f>
-        <v>896</v>
+        <v>821</v>
       </c>
       <c r="S243" s="5">
         <v>0</v>
@@ -29857,14 +29857,14 @@
         <v>84</v>
       </c>
       <c r="H311" s="5">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="I311" s="5">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="J311" s="5">
         <f>SUM(E311:I311)</f>
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="K311" s="5">
         <v>280</v>
@@ -29883,7 +29883,7 @@
       <c r="Q311" s="5"/>
       <c r="R311" s="5">
         <f>MAX(25, INT(POWER(2.2,J311/45)))</f>
-        <v>1388</v>
+        <v>928</v>
       </c>
       <c r="S311" s="5">
         <v>0</v>
@@ -30335,14 +30335,14 @@
         <v>90</v>
       </c>
       <c r="H317" s="5">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="I317" s="5">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J317" s="5">
         <f>SUM(E317:I317)</f>
-        <v>444</v>
+        <v>416</v>
       </c>
       <c r="K317" s="5">
         <v>295</v>
@@ -30361,7 +30361,7 @@
       <c r="Q317" s="5"/>
       <c r="R317" s="5">
         <f>MAX(25, INT(POWER(2.2,J317/45)))</f>
-        <v>2390</v>
+        <v>1463</v>
       </c>
       <c r="S317" s="5">
         <v>0</v>
@@ -30411,17 +30411,17 @@
         <v>85</v>
       </c>
       <c r="G318" s="5">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H318" s="5">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="I318" s="5">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="J318" s="5">
         <f>SUM(E318:I318)</f>
-        <v>387</v>
+        <v>354</v>
       </c>
       <c r="K318" s="5">
         <v>300</v>
@@ -30440,7 +30440,7 @@
       <c r="Q318" s="5"/>
       <c r="R318" s="5">
         <f>MAX(25, INT(POWER(2.2,J318/45)))</f>
-        <v>880</v>
+        <v>493</v>
       </c>
       <c r="S318" s="5">
         <v>0</v>
@@ -30572,17 +30572,17 @@
         <v>87</v>
       </c>
       <c r="G320" s="5">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="H320" s="5">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="I320" s="5">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="J320" s="5">
         <f>SUM(E320:I320)</f>
-        <v>385</v>
+        <v>321</v>
       </c>
       <c r="K320" s="5">
         <v>305</v>
@@ -30601,7 +30601,7 @@
       <c r="Q320" s="5"/>
       <c r="R320" s="5">
         <f>MAX(25, INT(POWER(2.2,J320/45)))</f>
-        <v>850</v>
+        <v>277</v>
       </c>
       <c r="S320" s="5">
         <v>0</v>
@@ -30650,17 +30650,17 @@
         <v>81</v>
       </c>
       <c r="G321" s="5">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="H321" s="5">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="I321" s="5">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J321" s="5">
         <f>SUM(E321:I321)</f>
-        <v>367</v>
+        <v>323</v>
       </c>
       <c r="K321" s="5">
         <v>215</v>
@@ -30683,7 +30683,7 @@
       </c>
       <c r="R321" s="5">
         <f>MAX(25, INT(POWER(2.2,J321/45)))</f>
-        <v>620</v>
+        <v>286</v>
       </c>
       <c r="S321" s="5">
         <v>0</v>
@@ -30805,23 +30805,23 @@
         <v>271</v>
       </c>
       <c r="E323" s="5">
+        <v>12</v>
+      </c>
+      <c r="F323" s="5">
+        <v>15</v>
+      </c>
+      <c r="G323" s="5">
         <v>27</v>
-      </c>
-      <c r="F323" s="5">
-        <v>41</v>
-      </c>
-      <c r="G323" s="5">
-        <v>35</v>
       </c>
       <c r="H323" s="5">
         <v>40</v>
       </c>
       <c r="I323" s="5">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="J323" s="5">
         <f>SUM(E323:I323)</f>
-        <v>203</v>
+        <v>146</v>
       </c>
       <c r="K323" s="5">
         <v>360</v>
@@ -30842,7 +30842,7 @@
       <c r="Q323" s="5"/>
       <c r="R323" s="5">
         <f>MAX(25, INT(POWER(2.2,J323/45)))</f>
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="S323" s="5">
         <v>0</v>
@@ -30975,14 +30975,14 @@
         <v>98</v>
       </c>
       <c r="H325" s="5">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I325" s="5">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J325" s="5">
         <f>SUM(E325:I325)</f>
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K325" s="5">
         <v>220</v>
@@ -31003,7 +31003,7 @@
       <c r="Q325" s="5"/>
       <c r="R325" s="5">
         <f>MAX(25, INT(POWER(2.2,J325/45)))</f>
-        <v>2078</v>
+        <v>2190</v>
       </c>
       <c r="S325" s="5">
         <v>0</v>
@@ -31056,14 +31056,14 @@
         <v>69</v>
       </c>
       <c r="H326" s="5">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="I326" s="5">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="J326" s="5">
         <f>SUM(E326:I326)</f>
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="K326" s="5">
         <v>320</v>
@@ -31082,7 +31082,7 @@
       <c r="Q326" s="5"/>
       <c r="R326" s="5">
         <f>MAX(25, INT(POWER(2.2,J326/45)))</f>
-        <v>713</v>
+        <v>452</v>
       </c>
       <c r="S326" s="5">
         <v>0</v>
@@ -31132,17 +31132,17 @@
         <v>88</v>
       </c>
       <c r="G327" s="5">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="H327" s="5">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I327" s="5">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="J327" s="5">
         <f>SUM(E327:I327)</f>
-        <v>309</v>
+        <v>224</v>
       </c>
       <c r="K327" s="5">
         <v>380</v>
@@ -31161,7 +31161,7 @@
       <c r="Q327" s="5"/>
       <c r="R327" s="5">
         <f>MAX(25, INT(POWER(2.2,J327/45)))</f>
-        <v>224</v>
+        <v>50</v>
       </c>
       <c r="S327" s="5">
         <v>0</v>
@@ -31217,11 +31217,11 @@
         <v>65</v>
       </c>
       <c r="I328" s="5">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="J328" s="5">
         <f>SUM(E328:I328)</f>
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="K328" s="5">
         <v>240</v>
@@ -31244,7 +31244,7 @@
       </c>
       <c r="R328" s="5">
         <f>MAX(25, INT(POWER(2.2,J328/45)))</f>
-        <v>665</v>
+        <v>588</v>
       </c>
       <c r="S328" s="5">
         <v>0</v>
@@ -31293,17 +31293,17 @@
         <v>75</v>
       </c>
       <c r="G329" s="5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H329" s="5">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="I329" s="5">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="J329" s="5">
         <f>SUM(E329:I329)</f>
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="K329" s="5">
         <v>340</v>
@@ -31322,7 +31322,7 @@
       <c r="Q329" s="5"/>
       <c r="R329" s="5">
         <f>MAX(25, INT(POWER(2.2,J329/45)))</f>
-        <v>460</v>
+        <v>224</v>
       </c>
       <c r="S329" s="5">
         <v>0</v>
@@ -31457,11 +31457,11 @@
         <v>80</v>
       </c>
       <c r="I331" s="5">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J331" s="5">
         <f>SUM(E331:I331)</f>
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="K331" s="5">
         <v>235</v>
@@ -31482,7 +31482,7 @@
       <c r="Q331" s="5"/>
       <c r="R331" s="5">
         <f>MAX(25, INT(POWER(2.2,J331/45)))</f>
-        <v>452</v>
+        <v>429</v>
       </c>
       <c r="S331" s="5">
         <v>0</v>
@@ -32098,14 +32098,14 @@
         <v>88</v>
       </c>
       <c r="H339" s="5">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="I339" s="5">
         <v>65</v>
       </c>
       <c r="J339" s="5">
         <f>SUM(E339:I339)</f>
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="K339" s="5">
         <v>235</v>
@@ -32126,7 +32126,7 @@
       <c r="Q339" s="5"/>
       <c r="R339" s="5">
         <f>MAX(25, INT(POWER(2.2,J339/45)))</f>
-        <v>689</v>
+        <v>599</v>
       </c>
       <c r="S339" s="5">
         <v>0</v>
@@ -32260,14 +32260,14 @@
         <v>85</v>
       </c>
       <c r="H341" s="5">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="I341" s="5">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J341" s="5">
         <f>SUM(E341:I341)</f>
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K341" s="5">
         <v>240</v>
@@ -32288,7 +32288,7 @@
       <c r="Q341" s="5"/>
       <c r="R341" s="5">
         <f>MAX(25, INT(POWER(2.2,J341/45)))</f>
-        <v>752</v>
+        <v>765</v>
       </c>
       <c r="S341" s="5">
         <v>0</v>
@@ -32336,17 +32336,17 @@
         <v>42</v>
       </c>
       <c r="G342" s="5">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H342" s="5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I342" s="5">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="J342" s="5">
         <f>SUM(E342:I342)</f>
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="K342" s="5">
         <v>250</v>
@@ -32367,7 +32367,7 @@
       <c r="Q342" s="5"/>
       <c r="R342" s="5">
         <f>MAX(25, INT(POWER(2.2,J342/45)))</f>
-        <v>701</v>
+        <v>665</v>
       </c>
       <c r="S342" s="5">
         <v>0</v>
@@ -32501,14 +32501,14 @@
         <v>80</v>
       </c>
       <c r="H344" s="5">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I344" s="5">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J344" s="5">
         <f>SUM(E344:I344)</f>
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="K344" s="5">
         <v>290</v>
@@ -32527,7 +32527,7 @@
       <c r="Q344" s="5"/>
       <c r="R344" s="5">
         <f>MAX(25, INT(POWER(2.2,J344/45)))</f>
-        <v>835</v>
+        <v>1049</v>
       </c>
       <c r="S344" s="5">
         <v>0</v>
@@ -32580,14 +32580,14 @@
         <v>75</v>
       </c>
       <c r="H345" s="5">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="I345" s="5">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="J345" s="5">
         <f>SUM(E345:I345)</f>
-        <v>383</v>
+        <v>345</v>
       </c>
       <c r="K345" s="5">
         <v>300</v>
@@ -32606,7 +32606,7 @@
       <c r="Q345" s="5"/>
       <c r="R345" s="5">
         <f>MAX(25, INT(POWER(2.2,J345/45)))</f>
-        <v>821</v>
+        <v>421</v>
       </c>
       <c r="S345" s="5">
         <v>0</v>

--- a/Design/config/HeroConfig.xlsx
+++ b/Design/config/HeroConfig.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2305" uniqueCount="988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2305" uniqueCount="990">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -3771,6 +3771,14 @@
   </si>
   <si>
     <t>死亡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>弓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刀</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3961,7 +3969,323 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="179">
+  <dxfs count="219">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -6720,7 +7044,7 @@
         <v>1</v>
       </c>
       <c r="T14" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U14" s="5"/>
       <c r="V14" s="5"/>
@@ -6796,7 +7120,7 @@
         <v>1</v>
       </c>
       <c r="T15" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
@@ -6868,7 +7192,7 @@
         <v>1</v>
       </c>
       <c r="T16" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U16" s="5"/>
       <c r="V16" s="5"/>
@@ -6940,7 +7264,7 @@
         <v>1</v>
       </c>
       <c r="T17" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U17" s="5"/>
       <c r="V17" s="5"/>
@@ -8123,7 +8447,7 @@
         <v>3</v>
       </c>
       <c r="T32" s="5" t="s">
-        <v>292</v>
+        <v>988</v>
       </c>
       <c r="U32" s="5"/>
       <c r="V32" s="5"/>
@@ -9774,7 +10098,7 @@
         <v>1</v>
       </c>
       <c r="T53" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U53" s="5"/>
       <c r="V53" s="5"/>
@@ -9846,7 +10170,7 @@
         <v>1</v>
       </c>
       <c r="T54" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U54" s="5"/>
       <c r="V54" s="5"/>
@@ -9918,7 +10242,7 @@
         <v>1</v>
       </c>
       <c r="T55" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U55" s="5"/>
       <c r="V55" s="5"/>
@@ -9990,7 +10314,7 @@
         <v>1</v>
       </c>
       <c r="T56" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U56" s="5"/>
       <c r="V56" s="5"/>
@@ -10062,7 +10386,7 @@
         <v>1</v>
       </c>
       <c r="T57" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U57" s="5"/>
       <c r="V57" s="5"/>
@@ -10134,7 +10458,7 @@
         <v>1</v>
       </c>
       <c r="T58" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U58" s="5"/>
       <c r="V58" s="5"/>
@@ -10206,7 +10530,7 @@
         <v>1</v>
       </c>
       <c r="T59" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U59" s="5"/>
       <c r="V59" s="5"/>
@@ -10278,7 +10602,7 @@
         <v>1</v>
       </c>
       <c r="T60" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U60" s="5"/>
       <c r="V60" s="5"/>
@@ -10350,7 +10674,7 @@
         <v>1</v>
       </c>
       <c r="T61" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U61" s="5"/>
       <c r="V61" s="5"/>
@@ -10422,7 +10746,7 @@
         <v>1</v>
       </c>
       <c r="T62" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U62" s="5"/>
       <c r="V62" s="5"/>
@@ -10494,7 +10818,7 @@
         <v>1</v>
       </c>
       <c r="T63" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U63" s="5"/>
       <c r="V63" s="5"/>
@@ -10566,7 +10890,7 @@
         <v>1</v>
       </c>
       <c r="T64" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U64" s="5"/>
       <c r="V64" s="5"/>
@@ -10638,7 +10962,7 @@
         <v>1</v>
       </c>
       <c r="T65" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U65" s="5"/>
       <c r="V65" s="5"/>
@@ -10710,7 +11034,7 @@
         <v>1</v>
       </c>
       <c r="T66" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U66" s="5"/>
       <c r="V66" s="5"/>
@@ -10782,7 +11106,7 @@
         <v>1</v>
       </c>
       <c r="T67" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U67" s="5"/>
       <c r="V67" s="5"/>
@@ -10854,7 +11178,7 @@
         <v>1</v>
       </c>
       <c r="T68" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U68" s="5"/>
       <c r="V68" s="5"/>
@@ -10926,7 +11250,7 @@
         <v>1</v>
       </c>
       <c r="T69" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U69" s="5"/>
       <c r="V69" s="5"/>
@@ -10998,7 +11322,7 @@
         <v>1</v>
       </c>
       <c r="T70" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U70" s="5"/>
       <c r="V70" s="5"/>
@@ -11070,7 +11394,7 @@
         <v>1</v>
       </c>
       <c r="T71" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U71" s="5"/>
       <c r="V71" s="5"/>
@@ -11142,7 +11466,7 @@
         <v>1</v>
       </c>
       <c r="T72" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U72" s="5"/>
       <c r="V72" s="5"/>
@@ -11214,7 +11538,7 @@
         <v>1</v>
       </c>
       <c r="T73" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U73" s="5"/>
       <c r="V73" s="5"/>
@@ -11286,7 +11610,7 @@
         <v>1</v>
       </c>
       <c r="T74" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U74" s="5"/>
       <c r="V74" s="5"/>
@@ -11358,7 +11682,7 @@
         <v>1</v>
       </c>
       <c r="T75" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U75" s="5"/>
       <c r="V75" s="5"/>
@@ -11430,7 +11754,7 @@
         <v>1</v>
       </c>
       <c r="T76" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U76" s="5"/>
       <c r="V76" s="5"/>
@@ -11502,7 +11826,7 @@
         <v>1</v>
       </c>
       <c r="T77" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U77" s="5"/>
       <c r="V77" s="5"/>
@@ -11574,7 +11898,7 @@
         <v>1</v>
       </c>
       <c r="T78" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U78" s="5"/>
       <c r="V78" s="5"/>
@@ -11646,7 +11970,7 @@
         <v>1</v>
       </c>
       <c r="T79" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U79" s="5"/>
       <c r="V79" s="5"/>
@@ -11718,7 +12042,7 @@
         <v>1</v>
       </c>
       <c r="T80" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U80" s="5"/>
       <c r="V80" s="5"/>
@@ -11790,7 +12114,7 @@
         <v>1</v>
       </c>
       <c r="T81" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U81" s="5"/>
       <c r="V81" s="5"/>
@@ -11862,7 +12186,7 @@
         <v>1</v>
       </c>
       <c r="T82" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U82" s="5"/>
       <c r="V82" s="5"/>
@@ -11934,7 +12258,7 @@
         <v>1</v>
       </c>
       <c r="T83" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U83" s="5"/>
       <c r="V83" s="5"/>
@@ -12006,7 +12330,7 @@
         <v>1</v>
       </c>
       <c r="T84" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U84" s="5"/>
       <c r="V84" s="5"/>
@@ -12078,7 +12402,7 @@
         <v>1</v>
       </c>
       <c r="T85" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U85" s="5"/>
       <c r="V85" s="5"/>
@@ -12150,7 +12474,7 @@
         <v>1</v>
       </c>
       <c r="T86" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U86" s="5"/>
       <c r="V86" s="5"/>
@@ -14845,7 +15169,7 @@
         <v>1</v>
       </c>
       <c r="T120" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U120" s="5"/>
       <c r="V120" s="5"/>
@@ -14917,7 +15241,7 @@
         <v>1</v>
       </c>
       <c r="T121" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U121" s="5"/>
       <c r="V121" s="5"/>
@@ -14989,7 +15313,7 @@
         <v>1</v>
       </c>
       <c r="T122" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U122" s="5"/>
       <c r="V122" s="5"/>
@@ -15061,7 +15385,7 @@
         <v>1</v>
       </c>
       <c r="T123" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U123" s="5"/>
       <c r="V123" s="5"/>
@@ -15133,7 +15457,7 @@
         <v>1</v>
       </c>
       <c r="T124" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U124" s="5"/>
       <c r="V124" s="5"/>
@@ -15205,7 +15529,7 @@
         <v>1</v>
       </c>
       <c r="T125" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U125" s="5"/>
       <c r="V125" s="5"/>
@@ -15277,7 +15601,7 @@
         <v>1</v>
       </c>
       <c r="T126" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U126" s="5"/>
       <c r="V126" s="5"/>
@@ -15349,7 +15673,7 @@
         <v>1</v>
       </c>
       <c r="T127" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U127" s="5"/>
       <c r="V127" s="5"/>
@@ -15421,7 +15745,7 @@
         <v>1</v>
       </c>
       <c r="T128" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U128" s="5"/>
       <c r="V128" s="5"/>
@@ -15493,7 +15817,7 @@
         <v>1</v>
       </c>
       <c r="T129" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U129" s="5"/>
       <c r="V129" s="5"/>
@@ -15565,7 +15889,7 @@
         <v>1</v>
       </c>
       <c r="T130" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U130" s="5"/>
       <c r="V130" s="5"/>
@@ -15637,7 +15961,7 @@
         <v>1</v>
       </c>
       <c r="T131" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U131" s="5"/>
       <c r="V131" s="5"/>
@@ -15709,7 +16033,7 @@
         <v>1</v>
       </c>
       <c r="T132" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U132" s="5"/>
       <c r="V132" s="5"/>
@@ -15781,7 +16105,7 @@
         <v>1</v>
       </c>
       <c r="T133" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U133" s="5"/>
       <c r="V133" s="5"/>
@@ -15853,7 +16177,7 @@
         <v>1</v>
       </c>
       <c r="T134" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U134" s="5"/>
       <c r="V134" s="5"/>
@@ -15925,7 +16249,7 @@
         <v>1</v>
       </c>
       <c r="T135" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U135" s="5"/>
       <c r="V135" s="5"/>
@@ -15997,7 +16321,7 @@
         <v>1</v>
       </c>
       <c r="T136" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U136" s="5"/>
       <c r="V136" s="5"/>
@@ -16069,7 +16393,7 @@
         <v>1</v>
       </c>
       <c r="T137" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U137" s="5"/>
       <c r="V137" s="5"/>
@@ -16141,7 +16465,7 @@
         <v>1</v>
       </c>
       <c r="T138" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U138" s="5"/>
       <c r="V138" s="5"/>
@@ -16960,7 +17284,7 @@
         <v>1</v>
       </c>
       <c r="T149" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U149" s="5"/>
       <c r="V149" s="5"/>
@@ -17032,7 +17356,7 @@
         <v>1</v>
       </c>
       <c r="T150" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U150" s="5"/>
       <c r="V150" s="5"/>
@@ -17104,7 +17428,7 @@
         <v>1</v>
       </c>
       <c r="T151" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U151" s="5"/>
       <c r="V151" s="5"/>
@@ -17176,7 +17500,7 @@
         <v>1</v>
       </c>
       <c r="T152" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U152" s="5"/>
       <c r="V152" s="5"/>
@@ -17248,7 +17572,7 @@
         <v>1</v>
       </c>
       <c r="T153" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U153" s="5"/>
       <c r="V153" s="5"/>
@@ -17320,7 +17644,7 @@
         <v>1</v>
       </c>
       <c r="T154" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U154" s="5"/>
       <c r="V154" s="5"/>
@@ -17392,7 +17716,7 @@
         <v>1</v>
       </c>
       <c r="T155" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U155" s="5"/>
       <c r="V155" s="5"/>
@@ -17464,7 +17788,7 @@
         <v>1</v>
       </c>
       <c r="T156" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U156" s="5"/>
       <c r="V156" s="5"/>
@@ -17536,7 +17860,7 @@
         <v>1</v>
       </c>
       <c r="T157" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U157" s="5"/>
       <c r="V157" s="5"/>
@@ -17608,7 +17932,7 @@
         <v>1</v>
       </c>
       <c r="T158" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U158" s="5"/>
       <c r="V158" s="5"/>
@@ -17680,7 +18004,7 @@
         <v>1</v>
       </c>
       <c r="T159" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U159" s="5"/>
       <c r="V159" s="5"/>
@@ -17752,7 +18076,7 @@
         <v>1</v>
       </c>
       <c r="T160" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U160" s="5"/>
       <c r="V160" s="5"/>
@@ -17824,7 +18148,7 @@
         <v>1</v>
       </c>
       <c r="T161" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U161" s="5"/>
       <c r="V161" s="5"/>
@@ -17896,7 +18220,7 @@
         <v>1</v>
       </c>
       <c r="T162" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U162" s="5"/>
       <c r="V162" s="5"/>
@@ -17968,7 +18292,7 @@
         <v>1</v>
       </c>
       <c r="T163" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U163" s="5"/>
       <c r="V163" s="5"/>
@@ -18040,7 +18364,7 @@
         <v>1</v>
       </c>
       <c r="T164" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U164" s="5"/>
       <c r="V164" s="5"/>
@@ -18112,7 +18436,7 @@
         <v>1</v>
       </c>
       <c r="T165" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U165" s="5"/>
       <c r="V165" s="5"/>
@@ -18184,7 +18508,7 @@
         <v>1</v>
       </c>
       <c r="T166" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U166" s="5"/>
       <c r="V166" s="5"/>
@@ -18260,7 +18584,7 @@
         <v>1</v>
       </c>
       <c r="T167" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U167" s="5"/>
       <c r="V167" s="5"/>
@@ -18336,7 +18660,7 @@
         <v>1</v>
       </c>
       <c r="T168" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U168" s="5"/>
       <c r="V168" s="5"/>
@@ -18412,7 +18736,7 @@
         <v>1</v>
       </c>
       <c r="T169" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U169" s="5"/>
       <c r="V169" s="5"/>
@@ -18488,7 +18812,7 @@
         <v>1</v>
       </c>
       <c r="T170" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U170" s="5"/>
       <c r="V170" s="5"/>
@@ -18564,7 +18888,7 @@
         <v>1</v>
       </c>
       <c r="T171" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U171" s="5"/>
       <c r="V171" s="5"/>
@@ -18640,7 +18964,7 @@
         <v>1</v>
       </c>
       <c r="T172" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U172" s="5"/>
       <c r="V172" s="5"/>
@@ -18716,7 +19040,7 @@
         <v>1</v>
       </c>
       <c r="T173" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U173" s="5"/>
       <c r="V173" s="5"/>
@@ -19738,7 +20062,7 @@
         <v>1</v>
       </c>
       <c r="T186" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U186" s="5"/>
       <c r="V186" s="5"/>
@@ -19814,7 +20138,7 @@
         <v>1</v>
       </c>
       <c r="T187" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U187" s="5"/>
       <c r="V187" s="5"/>
@@ -19886,7 +20210,7 @@
         <v>1</v>
       </c>
       <c r="T188" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U188" s="5"/>
       <c r="V188" s="5"/>
@@ -19958,7 +20282,7 @@
         <v>1</v>
       </c>
       <c r="T189" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U189" s="5"/>
       <c r="V189" s="5"/>
@@ -20030,7 +20354,7 @@
         <v>1</v>
       </c>
       <c r="T190" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U190" s="5"/>
       <c r="V190" s="5"/>
@@ -20102,7 +20426,7 @@
         <v>1</v>
       </c>
       <c r="T191" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U191" s="5"/>
       <c r="V191" s="5"/>
@@ -20174,7 +20498,7 @@
         <v>1</v>
       </c>
       <c r="T192" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U192" s="5"/>
       <c r="V192" s="5"/>
@@ -20246,7 +20570,7 @@
         <v>1</v>
       </c>
       <c r="T193" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U193" s="5"/>
       <c r="V193" s="5"/>
@@ -20318,7 +20642,7 @@
         <v>1</v>
       </c>
       <c r="T194" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U194" s="5"/>
       <c r="V194" s="5"/>
@@ -20390,7 +20714,7 @@
         <v>1</v>
       </c>
       <c r="T195" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U195" s="5"/>
       <c r="V195" s="5"/>
@@ -20462,7 +20786,7 @@
         <v>1</v>
       </c>
       <c r="T196" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U196" s="5"/>
       <c r="V196" s="5"/>
@@ -20534,7 +20858,7 @@
         <v>1</v>
       </c>
       <c r="T197" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U197" s="5"/>
       <c r="V197" s="5"/>
@@ -20606,7 +20930,7 @@
         <v>1</v>
       </c>
       <c r="T198" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U198" s="5"/>
       <c r="V198" s="5"/>
@@ -20678,7 +21002,7 @@
         <v>1</v>
       </c>
       <c r="T199" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U199" s="5"/>
       <c r="V199" s="5"/>
@@ -20750,7 +21074,7 @@
         <v>1</v>
       </c>
       <c r="T200" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U200" s="5"/>
       <c r="V200" s="5"/>
@@ -20822,7 +21146,7 @@
         <v>1</v>
       </c>
       <c r="T201" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U201" s="5"/>
       <c r="V201" s="5"/>
@@ -20894,7 +21218,7 @@
         <v>1</v>
       </c>
       <c r="T202" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U202" s="5"/>
       <c r="V202" s="5"/>
@@ -20966,7 +21290,7 @@
         <v>1</v>
       </c>
       <c r="T203" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U203" s="5"/>
       <c r="V203" s="5"/>
@@ -21038,7 +21362,7 @@
         <v>1</v>
       </c>
       <c r="T204" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U204" s="5"/>
       <c r="V204" s="5"/>
@@ -21418,7 +21742,7 @@
         <v>1</v>
       </c>
       <c r="T209" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U209" s="5"/>
       <c r="V209" s="5"/>
@@ -21494,7 +21818,7 @@
         <v>1</v>
       </c>
       <c r="T210" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U210" s="5"/>
       <c r="V210" s="5"/>
@@ -21566,7 +21890,7 @@
         <v>1</v>
       </c>
       <c r="T211" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U211" s="5"/>
       <c r="V211" s="5"/>
@@ -21638,7 +21962,7 @@
         <v>1</v>
       </c>
       <c r="T212" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U212" s="5"/>
       <c r="V212" s="5"/>
@@ -21710,7 +22034,7 @@
         <v>1</v>
       </c>
       <c r="T213" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U213" s="5"/>
       <c r="V213" s="5"/>
@@ -21782,7 +22106,7 @@
         <v>1</v>
       </c>
       <c r="T214" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U214" s="5"/>
       <c r="V214" s="5"/>
@@ -21854,7 +22178,7 @@
         <v>1</v>
       </c>
       <c r="T215" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U215" s="5"/>
       <c r="V215" s="5"/>
@@ -21926,7 +22250,7 @@
         <v>1</v>
       </c>
       <c r="T216" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U216" s="5"/>
       <c r="V216" s="5"/>
@@ -21998,7 +22322,7 @@
         <v>1</v>
       </c>
       <c r="T217" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U217" s="5"/>
       <c r="V217" s="5"/>
@@ -22070,7 +22394,7 @@
         <v>1</v>
       </c>
       <c r="T218" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U218" s="5"/>
       <c r="V218" s="5"/>
@@ -22455,7 +22779,7 @@
         <v>1</v>
       </c>
       <c r="T223" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U223" s="5"/>
       <c r="V223" s="5"/>
@@ -22531,7 +22855,7 @@
         <v>1</v>
       </c>
       <c r="T224" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U224" s="5"/>
       <c r="V224" s="5"/>
@@ -22607,7 +22931,7 @@
         <v>1</v>
       </c>
       <c r="T225" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U225" s="5"/>
       <c r="V225" s="5"/>
@@ -22683,7 +23007,7 @@
         <v>1</v>
       </c>
       <c r="T226" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U226" s="5"/>
       <c r="V226" s="5"/>
@@ -22755,7 +23079,7 @@
         <v>1</v>
       </c>
       <c r="T227" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U227" s="5"/>
       <c r="V227" s="5"/>
@@ -22827,7 +23151,7 @@
         <v>1</v>
       </c>
       <c r="T228" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U228" s="5"/>
       <c r="V228" s="5"/>
@@ -22899,7 +23223,7 @@
         <v>1</v>
       </c>
       <c r="T229" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U229" s="5"/>
       <c r="V229" s="5"/>
@@ -22971,7 +23295,7 @@
         <v>1</v>
       </c>
       <c r="T230" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U230" s="5"/>
       <c r="V230" s="5"/>
@@ -23043,7 +23367,7 @@
         <v>1</v>
       </c>
       <c r="T231" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U231" s="5"/>
       <c r="V231" s="5"/>
@@ -23115,7 +23439,7 @@
         <v>1</v>
       </c>
       <c r="T232" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U232" s="5"/>
       <c r="V232" s="5"/>
@@ -23187,7 +23511,7 @@
         <v>1</v>
       </c>
       <c r="T233" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U233" s="5"/>
       <c r="V233" s="5"/>
@@ -23259,7 +23583,7 @@
         <v>1</v>
       </c>
       <c r="T234" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U234" s="5"/>
       <c r="V234" s="5"/>
@@ -23331,7 +23655,7 @@
         <v>1</v>
       </c>
       <c r="T235" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U235" s="5"/>
       <c r="V235" s="5"/>
@@ -23404,7 +23728,7 @@
         <v>1</v>
       </c>
       <c r="T236" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U236" s="5"/>
       <c r="V236" s="5"/>
@@ -23476,7 +23800,7 @@
         <v>1</v>
       </c>
       <c r="T237" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U237" s="5"/>
       <c r="V237" s="5"/>
@@ -23548,7 +23872,7 @@
         <v>1</v>
       </c>
       <c r="T238" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U238" s="5"/>
       <c r="V238" s="5"/>
@@ -24535,7 +24859,7 @@
         <v>1</v>
       </c>
       <c r="T251" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U251" s="5"/>
       <c r="V251" s="5"/>
@@ -24607,7 +24931,7 @@
         <v>1</v>
       </c>
       <c r="T252" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U252" s="5"/>
       <c r="V252" s="5"/>
@@ -24679,7 +25003,7 @@
         <v>1</v>
       </c>
       <c r="T253" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U253" s="5"/>
       <c r="V253" s="5"/>
@@ -24751,7 +25075,7 @@
         <v>1</v>
       </c>
       <c r="T254" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U254" s="5"/>
       <c r="V254" s="5"/>
@@ -24823,7 +25147,7 @@
         <v>1</v>
       </c>
       <c r="T255" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U255" s="5"/>
       <c r="V255" s="5"/>
@@ -24895,7 +25219,7 @@
         <v>1</v>
       </c>
       <c r="T256" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U256" s="5"/>
       <c r="V256" s="5"/>
@@ -24967,7 +25291,7 @@
         <v>1</v>
       </c>
       <c r="T257" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U257" s="5"/>
       <c r="V257" s="5"/>
@@ -25039,7 +25363,7 @@
         <v>1</v>
       </c>
       <c r="T258" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U258" s="5"/>
       <c r="V258" s="5"/>
@@ -25111,7 +25435,7 @@
         <v>1</v>
       </c>
       <c r="T259" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U259" s="5"/>
       <c r="V259" s="5"/>
@@ -25183,7 +25507,7 @@
         <v>1</v>
       </c>
       <c r="T260" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U260" s="5"/>
       <c r="V260" s="5"/>
@@ -25255,7 +25579,7 @@
         <v>1</v>
       </c>
       <c r="T261" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U261" s="5"/>
       <c r="V261" s="5"/>
@@ -25327,7 +25651,7 @@
         <v>1</v>
       </c>
       <c r="T262" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U262" s="5"/>
       <c r="V262" s="5"/>
@@ -25399,7 +25723,7 @@
         <v>1</v>
       </c>
       <c r="T263" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U263" s="5"/>
       <c r="V263" s="5"/>
@@ -25475,7 +25799,7 @@
         <v>1</v>
       </c>
       <c r="T264" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U264" s="5"/>
       <c r="V264" s="5"/>
@@ -25551,7 +25875,7 @@
         <v>1</v>
       </c>
       <c r="T265" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U265" s="5"/>
       <c r="V265" s="5"/>
@@ -25627,7 +25951,7 @@
         <v>1</v>
       </c>
       <c r="T266" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U266" s="5"/>
       <c r="V266" s="5"/>
@@ -25778,7 +26102,7 @@
         <v>1</v>
       </c>
       <c r="T268" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U268" s="5"/>
       <c r="V268" s="5"/>
@@ -25854,7 +26178,7 @@
         <v>1</v>
       </c>
       <c r="T269" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U269" s="5"/>
       <c r="V269" s="5"/>
@@ -25930,7 +26254,7 @@
         <v>1</v>
       </c>
       <c r="T270" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U270" s="5"/>
       <c r="V270" s="5"/>
@@ -26006,7 +26330,7 @@
         <v>1</v>
       </c>
       <c r="T271" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U271" s="5"/>
       <c r="V271" s="5"/>
@@ -26082,7 +26406,7 @@
         <v>1</v>
       </c>
       <c r="T272" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U272" s="5"/>
       <c r="V272" s="5"/>
@@ -26158,7 +26482,7 @@
         <v>1</v>
       </c>
       <c r="T273" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U273" s="5"/>
       <c r="V273" s="5"/>
@@ -26310,7 +26634,7 @@
         <v>1</v>
       </c>
       <c r="T275" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U275" s="5"/>
       <c r="V275" s="5"/>
@@ -26382,7 +26706,7 @@
         <v>1</v>
       </c>
       <c r="T276" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U276" s="5"/>
       <c r="V276" s="5"/>
@@ -26454,7 +26778,7 @@
         <v>1</v>
       </c>
       <c r="T277" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U277" s="5"/>
       <c r="V277" s="5"/>
@@ -26526,7 +26850,7 @@
         <v>1</v>
       </c>
       <c r="T278" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U278" s="5"/>
       <c r="V278" s="5"/>
@@ -26598,7 +26922,7 @@
         <v>1</v>
       </c>
       <c r="T279" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U279" s="5"/>
       <c r="V279" s="5"/>
@@ -26670,7 +26994,7 @@
         <v>1</v>
       </c>
       <c r="T280" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U280" s="5"/>
       <c r="V280" s="5"/>
@@ -26742,7 +27066,7 @@
         <v>1</v>
       </c>
       <c r="T281" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U281" s="5"/>
       <c r="V281" s="5"/>
@@ -26818,7 +27142,7 @@
         <v>1</v>
       </c>
       <c r="T282" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U282" s="5"/>
       <c r="V282" s="5"/>
@@ -26890,7 +27214,7 @@
         <v>1</v>
       </c>
       <c r="T283" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U283" s="5"/>
       <c r="V283" s="5"/>
@@ -26962,7 +27286,7 @@
         <v>1</v>
       </c>
       <c r="T284" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U284" s="5"/>
       <c r="V284" s="5"/>
@@ -27034,7 +27358,7 @@
         <v>1</v>
       </c>
       <c r="T285" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U285" s="5"/>
       <c r="V285" s="5"/>
@@ -27106,7 +27430,7 @@
         <v>1</v>
       </c>
       <c r="T286" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U286" s="5"/>
       <c r="V286" s="5"/>
@@ -27178,7 +27502,7 @@
         <v>1</v>
       </c>
       <c r="T287" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U287" s="5"/>
       <c r="V287" s="5"/>
@@ -27250,7 +27574,7 @@
         <v>1</v>
       </c>
       <c r="T288" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U288" s="5"/>
       <c r="V288" s="5"/>
@@ -27322,7 +27646,7 @@
         <v>1</v>
       </c>
       <c r="T289" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U289" s="5"/>
       <c r="V289" s="5"/>
@@ -27394,7 +27718,7 @@
         <v>1</v>
       </c>
       <c r="T290" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U290" s="5"/>
       <c r="V290" s="5"/>
@@ -27466,7 +27790,7 @@
         <v>1</v>
       </c>
       <c r="T291" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U291" s="5"/>
       <c r="V291" s="5"/>
@@ -27610,7 +27934,7 @@
         <v>1</v>
       </c>
       <c r="T293" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U293" s="5"/>
       <c r="V293" s="5"/>
@@ -27682,7 +28006,7 @@
         <v>1</v>
       </c>
       <c r="T294" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U294" s="5"/>
       <c r="V294" s="5"/>
@@ -27754,7 +28078,7 @@
         <v>1</v>
       </c>
       <c r="T295" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U295" s="5"/>
       <c r="V295" s="5"/>
@@ -27826,7 +28150,7 @@
         <v>1</v>
       </c>
       <c r="T296" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U296" s="5"/>
       <c r="V296" s="5"/>
@@ -27898,7 +28222,7 @@
         <v>1</v>
       </c>
       <c r="T297" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U297" s="5"/>
       <c r="V297" s="5"/>
@@ -27970,7 +28294,7 @@
         <v>1</v>
       </c>
       <c r="T298" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U298" s="5"/>
       <c r="V298" s="5"/>
@@ -28042,7 +28366,7 @@
         <v>1</v>
       </c>
       <c r="T299" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U299" s="5"/>
       <c r="V299" s="5"/>
@@ -28118,7 +28442,7 @@
         <v>1</v>
       </c>
       <c r="T300" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U300" s="5"/>
       <c r="V300" s="5"/>
@@ -28350,7 +28674,7 @@
         <v>1</v>
       </c>
       <c r="T303" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U303" s="5"/>
       <c r="V303" s="5"/>
@@ -28426,7 +28750,7 @@
         <v>1</v>
       </c>
       <c r="T304" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U304" s="5"/>
       <c r="V304" s="5"/>
@@ -30001,7 +30325,7 @@
         <v>87</v>
       </c>
       <c r="J325" s="5">
-        <f t="shared" ref="J325:J388" si="16">SUM(E325:I325)</f>
+        <f t="shared" ref="J325:J351" si="16">SUM(E325:I325)</f>
         <v>439</v>
       </c>
       <c r="K325" s="5">
@@ -31884,7 +32208,7 @@
         <v>1</v>
       </c>
       <c r="T349" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U349" s="5"/>
       <c r="V349" s="5"/>
@@ -32034,7 +32358,7 @@
         <v>1</v>
       </c>
       <c r="T351" s="5" t="s">
-        <v>296</v>
+        <v>989</v>
       </c>
       <c r="U351" s="5"/>
       <c r="V351" s="5"/>
@@ -32064,635 +32388,731 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H323:I328 E308:I309 H312:I319 E312:G351 E281:I299 H181:I181 E5:I14 E166:F166 F167 F168:I168 E119:F119 E169:F169 E170:I170 E172:I172 E171:F171 E176:G177 E180:G181 E182:F182 E173:F175 E178:F179 E183:I274 E120:I165 H19:I88 E19:G118">
-    <cfRule type="cellIs" dxfId="178" priority="335" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="218" priority="375" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H93:I118 H89:I90">
-    <cfRule type="cellIs" dxfId="177" priority="333" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="217" priority="373" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H330:I330">
-    <cfRule type="cellIs" dxfId="176" priority="331" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="216" priority="371" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H329:I329">
-    <cfRule type="cellIs" dxfId="175" priority="329" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="215" priority="369" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H332:I332">
-    <cfRule type="cellIs" dxfId="174" priority="327" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="214" priority="367" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H333:I333">
-    <cfRule type="cellIs" dxfId="173" priority="322" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="213" priority="362" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H340:I340">
-    <cfRule type="cellIs" dxfId="172" priority="320" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="212" priority="360" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H341:I341">
-    <cfRule type="cellIs" dxfId="171" priority="318" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="211" priority="358" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H342:I342">
-    <cfRule type="cellIs" dxfId="170" priority="316" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="210" priority="356" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H343:I343">
-    <cfRule type="cellIs" dxfId="169" priority="311" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="209" priority="351" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H344:I344">
-    <cfRule type="cellIs" dxfId="168" priority="307" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="208" priority="347" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H345:I345">
-    <cfRule type="cellIs" dxfId="167" priority="303" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="207" priority="343" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H320:I320">
-    <cfRule type="cellIs" dxfId="166" priority="298" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="206" priority="338" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H321:I321">
-    <cfRule type="cellIs" dxfId="165" priority="297" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="205" priority="337" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H346:I346">
-    <cfRule type="cellIs" dxfId="164" priority="296" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="204" priority="336" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H347:I347">
-    <cfRule type="cellIs" dxfId="163" priority="295" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="203" priority="335" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H348:I348">
-    <cfRule type="cellIs" dxfId="162" priority="294" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="202" priority="334" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H334:I334">
-    <cfRule type="cellIs" dxfId="161" priority="293" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="201" priority="333" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H335:I335">
-    <cfRule type="cellIs" dxfId="160" priority="288" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="200" priority="328" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H336:I336">
-    <cfRule type="cellIs" dxfId="159" priority="287" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="199" priority="327" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H337:I337">
-    <cfRule type="cellIs" dxfId="158" priority="286" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="198" priority="326" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H338:I338">
-    <cfRule type="cellIs" dxfId="157" priority="285" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="197" priority="325" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H339:I339">
-    <cfRule type="cellIs" dxfId="156" priority="284" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="196" priority="324" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H322:I322">
-    <cfRule type="cellIs" dxfId="155" priority="277" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="195" priority="317" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H177:I177">
-    <cfRule type="cellIs" dxfId="154" priority="270" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="194" priority="310" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H91:I91">
-    <cfRule type="cellIs" dxfId="153" priority="269" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="193" priority="309" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H349:I349">
-    <cfRule type="cellIs" dxfId="152" priority="260" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="192" priority="300" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H331:I331">
-    <cfRule type="cellIs" dxfId="151" priority="256" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="191" priority="296" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H350:I350">
-    <cfRule type="cellIs" dxfId="150" priority="251" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="190" priority="291" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H351:I351">
-    <cfRule type="cellIs" dxfId="149" priority="241" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="189" priority="281" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H180:I180">
-    <cfRule type="cellIs" dxfId="148" priority="238" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="188" priority="278" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H92:I92">
-    <cfRule type="cellIs" dxfId="147" priority="234" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="187" priority="274" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T1:T14 T308:T309 T312:T1048576 T299 T281 T206:T209 T220:T246 T263:T274 T88:T123 T145:T186 T19:T86">
-    <cfRule type="cellIs" dxfId="146" priority="222" operator="equal">
+  <conditionalFormatting sqref="T308:T309 T312:T348 T206:T208 T220:T222 T267 T88:T119 T1:T17 T19:T86 T145:T185 T239:T246 T274 T350 T352:T1048576">
+    <cfRule type="cellIs" dxfId="186" priority="262" operator="equal">
       <formula>"炮"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="145" priority="223" operator="equal">
+    <cfRule type="cellIs" dxfId="185" priority="263" operator="equal">
       <formula>"弩"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="224" operator="equal">
+    <cfRule type="cellIs" dxfId="184" priority="264" operator="equal">
       <formula>"弓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="143" priority="225" operator="equal">
+    <cfRule type="cellIs" dxfId="183" priority="265" operator="equal">
       <formula>"医"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="226" operator="equal">
+    <cfRule type="cellIs" dxfId="182" priority="266" operator="equal">
       <formula>"乐"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="227" operator="equal">
+    <cfRule type="cellIs" dxfId="181" priority="267" operator="equal">
       <formula>"鼓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="228" operator="equal">
+    <cfRule type="cellIs" dxfId="180" priority="268" operator="equal">
       <formula>"相"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="229" operator="equal">
+    <cfRule type="cellIs" dxfId="179" priority="269" operator="equal">
       <formula>"扇"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="230" operator="equal">
+    <cfRule type="cellIs" dxfId="178" priority="270" operator="equal">
       <formula>"谋"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="231" operator="equal">
+    <cfRule type="cellIs" dxfId="177" priority="271" operator="equal">
       <formula>"帅"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T300:T307">
-    <cfRule type="cellIs" dxfId="136" priority="197" operator="equal">
+  <conditionalFormatting sqref="T301:T302 T305:T307">
+    <cfRule type="cellIs" dxfId="176" priority="237" operator="equal">
       <formula>"炮"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="198" operator="equal">
+    <cfRule type="cellIs" dxfId="175" priority="238" operator="equal">
       <formula>"弩"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="134" priority="199" operator="equal">
+    <cfRule type="cellIs" dxfId="174" priority="239" operator="equal">
       <formula>"弓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="200" operator="equal">
+    <cfRule type="cellIs" dxfId="173" priority="240" operator="equal">
       <formula>"医"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="201" operator="equal">
+    <cfRule type="cellIs" dxfId="172" priority="241" operator="equal">
       <formula>"乐"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="202" operator="equal">
+    <cfRule type="cellIs" dxfId="171" priority="242" operator="equal">
       <formula>"鼓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="203" operator="equal">
+    <cfRule type="cellIs" dxfId="170" priority="243" operator="equal">
       <formula>"相"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="204" operator="equal">
+    <cfRule type="cellIs" dxfId="169" priority="244" operator="equal">
       <formula>"扇"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="128" priority="205" operator="equal">
+    <cfRule type="cellIs" dxfId="168" priority="245" operator="equal">
       <formula>"谋"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="206" operator="equal">
+    <cfRule type="cellIs" dxfId="167" priority="246" operator="equal">
       <formula>"帅"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T310">
-    <cfRule type="cellIs" dxfId="126" priority="184" operator="equal">
+    <cfRule type="cellIs" dxfId="166" priority="224" operator="equal">
       <formula>"炮"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="185" operator="equal">
+    <cfRule type="cellIs" dxfId="165" priority="225" operator="equal">
       <formula>"弩"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="186" operator="equal">
+    <cfRule type="cellIs" dxfId="164" priority="226" operator="equal">
       <formula>"弓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="187" operator="equal">
+    <cfRule type="cellIs" dxfId="163" priority="227" operator="equal">
       <formula>"医"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="188" operator="equal">
+    <cfRule type="cellIs" dxfId="162" priority="228" operator="equal">
       <formula>"乐"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="189" operator="equal">
+    <cfRule type="cellIs" dxfId="161" priority="229" operator="equal">
       <formula>"鼓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="190" operator="equal">
+    <cfRule type="cellIs" dxfId="160" priority="230" operator="equal">
       <formula>"相"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="191" operator="equal">
+    <cfRule type="cellIs" dxfId="159" priority="231" operator="equal">
       <formula>"扇"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="192" operator="equal">
+    <cfRule type="cellIs" dxfId="158" priority="232" operator="equal">
       <formula>"谋"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="193" operator="equal">
+    <cfRule type="cellIs" dxfId="157" priority="233" operator="equal">
       <formula>"帅"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T311">
-    <cfRule type="cellIs" dxfId="116" priority="171" operator="equal">
+    <cfRule type="cellIs" dxfId="156" priority="211" operator="equal">
       <formula>"炮"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="172" operator="equal">
+    <cfRule type="cellIs" dxfId="155" priority="212" operator="equal">
       <formula>"弩"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="173" operator="equal">
+    <cfRule type="cellIs" dxfId="154" priority="213" operator="equal">
       <formula>"弓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="174" operator="equal">
+    <cfRule type="cellIs" dxfId="153" priority="214" operator="equal">
       <formula>"医"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="175" operator="equal">
+    <cfRule type="cellIs" dxfId="152" priority="215" operator="equal">
       <formula>"乐"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="176" operator="equal">
+    <cfRule type="cellIs" dxfId="151" priority="216" operator="equal">
       <formula>"鼓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="177" operator="equal">
+    <cfRule type="cellIs" dxfId="150" priority="217" operator="equal">
       <formula>"相"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="178" operator="equal">
+    <cfRule type="cellIs" dxfId="149" priority="218" operator="equal">
       <formula>"扇"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="179" operator="equal">
+    <cfRule type="cellIs" dxfId="148" priority="219" operator="equal">
       <formula>"谋"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="180" operator="equal">
+    <cfRule type="cellIs" dxfId="147" priority="220" operator="equal">
       <formula>"帅"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T282:T298">
-    <cfRule type="cellIs" dxfId="106" priority="158" operator="equal">
+  <conditionalFormatting sqref="T292">
+    <cfRule type="cellIs" dxfId="146" priority="198" operator="equal">
       <formula>"炮"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="159" operator="equal">
+    <cfRule type="cellIs" dxfId="145" priority="199" operator="equal">
       <formula>"弩"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="160" operator="equal">
+    <cfRule type="cellIs" dxfId="144" priority="200" operator="equal">
       <formula>"弓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="161" operator="equal">
+    <cfRule type="cellIs" dxfId="143" priority="201" operator="equal">
       <formula>"医"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="162" operator="equal">
+    <cfRule type="cellIs" dxfId="142" priority="202" operator="equal">
       <formula>"乐"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="163" operator="equal">
+    <cfRule type="cellIs" dxfId="141" priority="203" operator="equal">
       <formula>"鼓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="164" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="204" operator="equal">
       <formula>"相"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="165" operator="equal">
+    <cfRule type="cellIs" dxfId="139" priority="205" operator="equal">
       <formula>"扇"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="166" operator="equal">
+    <cfRule type="cellIs" dxfId="138" priority="206" operator="equal">
       <formula>"谋"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="167" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="207" operator="equal">
       <formula>"帅"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E275:I280">
-    <cfRule type="cellIs" dxfId="96" priority="157" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="136" priority="197" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T275:T280">
-    <cfRule type="cellIs" dxfId="95" priority="144" operator="equal">
+  <conditionalFormatting sqref="T219">
+    <cfRule type="cellIs" dxfId="125" priority="171" operator="equal">
       <formula>"炮"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="145" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="172" operator="equal">
       <formula>"弩"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="146" operator="equal">
+    <cfRule type="cellIs" dxfId="123" priority="173" operator="equal">
       <formula>"弓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="147" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="174" operator="equal">
       <formula>"医"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="148" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="175" operator="equal">
       <formula>"乐"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="149" operator="equal">
+    <cfRule type="cellIs" dxfId="120" priority="176" operator="equal">
       <formula>"鼓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="150" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="177" operator="equal">
       <formula>"相"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="151" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="178" operator="equal">
       <formula>"扇"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="152" operator="equal">
+    <cfRule type="cellIs" dxfId="117" priority="179" operator="equal">
       <formula>"谋"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="153" operator="equal">
-      <formula>"帅"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T210:T219">
-    <cfRule type="cellIs" dxfId="85" priority="131" operator="equal">
-      <formula>"炮"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="132" operator="equal">
-      <formula>"弩"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="133" operator="equal">
-      <formula>"弓"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="134" operator="equal">
-      <formula>"医"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="135" operator="equal">
-      <formula>"乐"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="136" operator="equal">
-      <formula>"鼓"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="137" operator="equal">
-      <formula>"相"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="138" operator="equal">
-      <formula>"扇"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="139" operator="equal">
-      <formula>"谋"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="140" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="180" operator="equal">
       <formula>"帅"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G166">
-    <cfRule type="cellIs" dxfId="75" priority="115" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="115" priority="155" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H166:I166">
-    <cfRule type="cellIs" dxfId="74" priority="114" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="114" priority="154" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G167:I167">
-    <cfRule type="cellIs" dxfId="73" priority="113" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="113" priority="153" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E167:E168">
-    <cfRule type="cellIs" dxfId="72" priority="112" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="112" priority="152" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G119:I119">
-    <cfRule type="cellIs" dxfId="71" priority="111" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="111" priority="151" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G169:I169">
-    <cfRule type="cellIs" dxfId="70" priority="110" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="110" priority="150" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G171:I171">
-    <cfRule type="cellIs" dxfId="69" priority="109" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="109" priority="149" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G173:I173">
-    <cfRule type="cellIs" dxfId="68" priority="108" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="108" priority="148" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G174:I174">
-    <cfRule type="cellIs" dxfId="67" priority="107" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="107" priority="147" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G178:I178">
-    <cfRule type="cellIs" dxfId="66" priority="95" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="106" priority="135" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H176:I176">
-    <cfRule type="cellIs" dxfId="65" priority="94" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="105" priority="134" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G182:I182">
-    <cfRule type="cellIs" dxfId="64" priority="93" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="104" priority="133" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G175:I175">
-    <cfRule type="cellIs" dxfId="63" priority="92" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="103" priority="132" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G179:I179">
-    <cfRule type="cellIs" dxfId="62" priority="91" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="102" priority="131" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T187:T205">
-    <cfRule type="cellIs" dxfId="61" priority="78" operator="equal">
+  <conditionalFormatting sqref="T205">
+    <cfRule type="cellIs" dxfId="101" priority="118" operator="equal">
       <formula>"炮"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="79" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="119" operator="equal">
       <formula>"弩"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="80" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="120" operator="equal">
       <formula>"弓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="81" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="121" operator="equal">
       <formula>"医"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="82" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="122" operator="equal">
       <formula>"乐"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="83" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="123" operator="equal">
       <formula>"鼓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="84" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="124" operator="equal">
       <formula>"相"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="85" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="125" operator="equal">
       <formula>"扇"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="86" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="126" operator="equal">
       <formula>"谋"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="87" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="127" operator="equal">
       <formula>"帅"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T247:T262">
-    <cfRule type="cellIs" dxfId="51" priority="68" operator="equal">
+  <conditionalFormatting sqref="T247:T250">
+    <cfRule type="cellIs" dxfId="91" priority="108" operator="equal">
       <formula>"炮"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="69" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="109" operator="equal">
       <formula>"弩"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="70" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="110" operator="equal">
       <formula>"弓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="71" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="111" operator="equal">
       <formula>"医"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="72" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="112" operator="equal">
       <formula>"乐"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="73" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="113" operator="equal">
       <formula>"鼓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="74" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="114" operator="equal">
       <formula>"相"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="75" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="115" operator="equal">
       <formula>"扇"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="76" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="116" operator="equal">
       <formula>"谋"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="117" operator="equal">
       <formula>"帅"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15:I17">
-    <cfRule type="cellIs" dxfId="41" priority="66" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="81" priority="106" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T15:T17">
-    <cfRule type="cellIs" dxfId="40" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="94" operator="equal">
       <formula>"炮"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="95" operator="equal">
       <formula>"弩"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="96" operator="equal">
       <formula>"弓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="97" operator="equal">
       <formula>"医"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="98" operator="equal">
       <formula>"乐"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="59" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="99" operator="equal">
       <formula>"鼓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="100" operator="equal">
       <formula>"相"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="61" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="101" operator="equal">
       <formula>"扇"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="102" operator="equal">
       <formula>"谋"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="103" operator="equal">
       <formula>"帅"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:I18">
-    <cfRule type="cellIs" dxfId="30" priority="52" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="70" priority="92" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T18">
-    <cfRule type="cellIs" dxfId="29" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="80" operator="equal">
       <formula>"炮"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="81" operator="equal">
       <formula>"弩"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="82" operator="equal">
       <formula>"弓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="83" operator="equal">
       <formula>"医"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="84" operator="equal">
       <formula>"乐"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="85" operator="equal">
       <formula>"鼓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="86" operator="equal">
       <formula>"相"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="87" operator="equal">
       <formula>"扇"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="88" operator="equal">
       <formula>"谋"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="89" operator="equal">
       <formula>"帅"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T87">
-    <cfRule type="cellIs" dxfId="19" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="54" operator="equal">
       <formula>"炮"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="55" operator="equal">
       <formula>"弩"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="56" operator="equal">
       <formula>"弓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="57" operator="equal">
       <formula>"医"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="58" operator="equal">
       <formula>"乐"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="59" operator="equal">
       <formula>"鼓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="60" operator="equal">
       <formula>"相"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="61" operator="equal">
       <formula>"扇"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="62" operator="equal">
       <formula>"谋"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="63" operator="equal">
       <formula>"帅"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T124:T144">
+  <conditionalFormatting sqref="T139:T144">
+    <cfRule type="cellIs" dxfId="49" priority="41" operator="equal">
+      <formula>"炮"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="48" priority="42" operator="equal">
+      <formula>"弩"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="47" priority="43" operator="equal">
+      <formula>"弓"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="44" operator="equal">
+      <formula>"医"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="45" operator="equal">
+      <formula>"乐"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="44" priority="46" operator="equal">
+      <formula>"鼓"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="47" operator="equal">
+      <formula>"相"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="48" operator="equal">
+      <formula>"扇"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="41" priority="49" operator="equal">
+      <formula>"谋"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="50" operator="equal">
+      <formula>"帅"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T120:T138">
+    <cfRule type="cellIs" dxfId="39" priority="31" operator="equal">
+      <formula>"炮"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="32" operator="equal">
+      <formula>"弩"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="33" operator="equal">
+      <formula>"弓"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="36" priority="34" operator="equal">
+      <formula>"医"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="35" operator="equal">
+      <formula>"乐"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="36" operator="equal">
+      <formula>"鼓"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="37" operator="equal">
+      <formula>"相"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="38" operator="equal">
+      <formula>"扇"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="39" operator="equal">
+      <formula>"谋"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="40" operator="equal">
+      <formula>"帅"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T209:T218 T186:T204">
+    <cfRule type="cellIs" dxfId="29" priority="21" operator="equal">
+      <formula>"炮"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="22" operator="equal">
+      <formula>"弩"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="23" operator="equal">
+      <formula>"弓"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="24" operator="equal">
+      <formula>"医"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="25" operator="equal">
+      <formula>"乐"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="26" operator="equal">
+      <formula>"鼓"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="27" operator="equal">
+      <formula>"相"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="28" operator="equal">
+      <formula>"扇"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="29" operator="equal">
+      <formula>"谋"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="30" operator="equal">
+      <formula>"帅"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T293:T300 T275:T291 T268:T273 T251:T266 T223:T238">
+    <cfRule type="cellIs" dxfId="19" priority="11" operator="equal">
+      <formula>"炮"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="12" operator="equal">
+      <formula>"弩"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="13" operator="equal">
+      <formula>"弓"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="14" operator="equal">
+      <formula>"医"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="15" operator="equal">
+      <formula>"乐"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
+      <formula>"鼓"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="17" operator="equal">
+      <formula>"相"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="18" operator="equal">
+      <formula>"扇"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="19" operator="equal">
+      <formula>"谋"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="20" operator="equal">
+      <formula>"帅"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T351 T349 T303:T304">
     <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"炮"</formula>
     </cfRule>

--- a/Design/config/HeroConfig.xlsx
+++ b/Design/config/HeroConfig.xlsx
@@ -3969,7 +3969,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="219">
+  <dxfs count="209">
     <dxf>
       <fill>
         <patternFill>
@@ -4871,85 +4871,6 @@
         <i val="0"/>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -6307,7 +6228,7 @@
         <v>99</v>
       </c>
       <c r="J5" s="5">
-        <f t="shared" ref="J5:J68" si="0">SUM(E5:I5)</f>
+        <f>SUM(E5:I5)</f>
         <v>408</v>
       </c>
       <c r="K5" s="5">
@@ -6384,7 +6305,7 @@
         <v>45</v>
       </c>
       <c r="J6" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E6:I6)</f>
         <v>287</v>
       </c>
       <c r="K6" s="5">
@@ -6402,7 +6323,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5">
-        <f t="shared" ref="Q6:Q17" si="1">MAX(25, INT(POWER(2.2,J6/45)))</f>
+        <f>MAX(25, INT(POWER(2.2,J6/45)))</f>
         <v>152</v>
       </c>
       <c r="R6" s="5">
@@ -6462,7 +6383,7 @@
         <v>94</v>
       </c>
       <c r="J7" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E7:I7)</f>
         <v>427</v>
       </c>
       <c r="K7" s="5">
@@ -6480,7 +6401,7 @@
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5">
-        <f t="shared" si="1"/>
+        <f>MAX(25, INT(POWER(2.2,J7/45)))</f>
         <v>1775</v>
       </c>
       <c r="R7" s="5">
@@ -6540,7 +6461,7 @@
         <v>84</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E8:I8)</f>
         <v>411</v>
       </c>
       <c r="K8" s="5">
@@ -6555,12 +6476,12 @@
       <c r="N8" s="5">
         <v>17</v>
       </c>
-      <c r="O8" s="5">
-        <v>15</v>
+      <c r="O8">
+        <v>30</v>
       </c>
       <c r="P8" s="5"/>
       <c r="Q8" s="5">
-        <f t="shared" si="1"/>
+        <f>MAX(25, INT(POWER(2.2,J8/45)))</f>
         <v>1341</v>
       </c>
       <c r="R8" s="5">
@@ -6622,7 +6543,7 @@
         <v>60</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E9:I9)</f>
         <v>280</v>
       </c>
       <c r="K9" s="5">
@@ -6640,7 +6561,7 @@
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5">
-        <f t="shared" si="1"/>
+        <f>MAX(25, INT(POWER(2.2,J9/45)))</f>
         <v>135</v>
       </c>
       <c r="R9" s="5">
@@ -6700,7 +6621,7 @@
         <v>66</v>
       </c>
       <c r="J10" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E10:I10)</f>
         <v>331</v>
       </c>
       <c r="K10" s="5">
@@ -6718,7 +6639,7 @@
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5">
-        <f t="shared" si="1"/>
+        <f>MAX(25, INT(POWER(2.2,J10/45)))</f>
         <v>330</v>
       </c>
       <c r="R10" s="5">
@@ -6778,7 +6699,7 @@
         <v>70</v>
       </c>
       <c r="J11" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E11:I11)</f>
         <v>352</v>
       </c>
       <c r="K11" s="5">
@@ -6793,14 +6714,14 @@
       <c r="N11" s="5">
         <v>17</v>
       </c>
-      <c r="O11" s="5">
-        <v>22</v>
+      <c r="O11">
+        <v>40</v>
       </c>
       <c r="P11" s="5">
         <v>1.5</v>
       </c>
       <c r="Q11" s="5">
-        <f t="shared" si="1"/>
+        <f>MAX(25, INT(POWER(2.2,J11/45)))</f>
         <v>476</v>
       </c>
       <c r="R11" s="5">
@@ -6859,7 +6780,7 @@
         <v>82</v>
       </c>
       <c r="J12" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E12:I12)</f>
         <v>362</v>
       </c>
       <c r="K12" s="5">
@@ -6874,12 +6795,12 @@
       <c r="N12" s="5">
         <v>17</v>
       </c>
-      <c r="O12" s="5">
-        <v>35</v>
+      <c r="O12">
+        <v>58</v>
       </c>
       <c r="P12" s="5"/>
       <c r="Q12" s="5">
-        <f t="shared" si="1"/>
+        <f>MAX(25, INT(POWER(2.2,J12/45)))</f>
         <v>568</v>
       </c>
       <c r="R12" s="5">
@@ -6939,7 +6860,7 @@
         <v>78</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E13:I13)</f>
         <v>382</v>
       </c>
       <c r="K13" s="5">
@@ -6957,7 +6878,7 @@
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
       <c r="Q13" s="5">
-        <f t="shared" si="1"/>
+        <f>MAX(25, INT(POWER(2.2,J13/45)))</f>
         <v>806</v>
       </c>
       <c r="R13" s="5">
@@ -7016,7 +6937,7 @@
         <v>61</v>
       </c>
       <c r="J14" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E14:I14)</f>
         <v>275</v>
       </c>
       <c r="K14" s="5">
@@ -7034,7 +6955,7 @@
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
       <c r="Q14" s="5">
-        <f t="shared" si="1"/>
+        <f>MAX(25, INT(POWER(2.2,J14/45)))</f>
         <v>123</v>
       </c>
       <c r="R14" s="5">
@@ -7092,7 +7013,7 @@
         <v>85</v>
       </c>
       <c r="J15" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E15:I15)</f>
         <v>309</v>
       </c>
       <c r="K15" s="5">
@@ -7110,7 +7031,7 @@
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
       <c r="Q15" s="5">
-        <f t="shared" si="1"/>
+        <f>MAX(25, INT(POWER(2.2,J15/45)))</f>
         <v>224</v>
       </c>
       <c r="R15" s="5">
@@ -7164,7 +7085,7 @@
         <v>23</v>
       </c>
       <c r="J16" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E16:I16)</f>
         <v>193</v>
       </c>
       <c r="K16" s="5">
@@ -7182,7 +7103,7 @@
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
       <c r="Q16" s="5">
-        <f t="shared" si="1"/>
+        <f>MAX(25, INT(POWER(2.2,J16/45)))</f>
         <v>29</v>
       </c>
       <c r="R16" s="5">
@@ -7236,7 +7157,7 @@
         <v>69</v>
       </c>
       <c r="J17" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E17:I17)</f>
         <v>332</v>
       </c>
       <c r="K17" s="5">
@@ -7254,7 +7175,7 @@
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
       <c r="Q17" s="5">
-        <f t="shared" si="1"/>
+        <f>MAX(25, INT(POWER(2.2,J17/45)))</f>
         <v>335</v>
       </c>
       <c r="R17" s="5">
@@ -7308,7 +7229,7 @@
         <v>96</v>
       </c>
       <c r="J18" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E18:I18)</f>
         <v>460</v>
       </c>
       <c r="K18" s="5">
@@ -7381,7 +7302,7 @@
         <v>82</v>
       </c>
       <c r="J19" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E19:I19)</f>
         <v>373</v>
       </c>
       <c r="K19" s="5">
@@ -7396,12 +7317,12 @@
       <c r="N19" s="5">
         <v>17</v>
       </c>
-      <c r="O19" s="5">
-        <v>15</v>
+      <c r="O19">
+        <v>30</v>
       </c>
       <c r="P19" s="5"/>
       <c r="Q19" s="5">
-        <f t="shared" ref="Q19:Q50" si="2">MAX(25, INT(POWER(2.2,J19/45)))</f>
+        <f>MAX(25, INT(POWER(2.2,J19/45)))</f>
         <v>689</v>
       </c>
       <c r="R19" s="5">
@@ -7461,7 +7382,7 @@
         <v>80</v>
       </c>
       <c r="J20" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E20:I20)</f>
         <v>387</v>
       </c>
       <c r="K20" s="5">
@@ -7479,7 +7400,7 @@
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J20/45)))</f>
         <v>880</v>
       </c>
       <c r="R20" s="5">
@@ -7539,7 +7460,7 @@
         <v>93</v>
       </c>
       <c r="J21" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E21:I21)</f>
         <v>402</v>
       </c>
       <c r="K21" s="5">
@@ -7554,12 +7475,12 @@
       <c r="N21" s="5">
         <v>17</v>
       </c>
-      <c r="O21" s="5">
-        <v>18</v>
+      <c r="O21">
+        <v>36</v>
       </c>
       <c r="P21" s="5"/>
       <c r="Q21" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J21/45)))</f>
         <v>1145</v>
       </c>
       <c r="R21" s="5">
@@ -7619,7 +7540,7 @@
         <v>59</v>
       </c>
       <c r="J22" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E22:I22)</f>
         <v>276</v>
       </c>
       <c r="K22" s="5">
@@ -7637,7 +7558,7 @@
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J22/45)))</f>
         <v>125</v>
       </c>
       <c r="R22" s="5">
@@ -7697,7 +7618,7 @@
         <v>80</v>
       </c>
       <c r="J23" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E23:I23)</f>
         <v>353</v>
       </c>
       <c r="K23" s="5">
@@ -7712,14 +7633,14 @@
       <c r="N23" s="5">
         <v>17</v>
       </c>
-      <c r="O23" s="5">
-        <v>22</v>
+      <c r="O23">
+        <v>40</v>
       </c>
       <c r="P23" s="5">
         <v>1.5</v>
       </c>
       <c r="Q23" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J23/45)))</f>
         <v>485</v>
       </c>
       <c r="R23" s="5">
@@ -7779,7 +7700,7 @@
         <v>78</v>
       </c>
       <c r="J24" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E24:I24)</f>
         <v>313</v>
       </c>
       <c r="K24" s="5">
@@ -7797,7 +7718,7 @@
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
       <c r="Q24" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J24/45)))</f>
         <v>240</v>
       </c>
       <c r="R24" s="5">
@@ -7857,7 +7778,7 @@
         <v>71</v>
       </c>
       <c r="J25" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E25:I25)</f>
         <v>394</v>
       </c>
       <c r="K25" s="5">
@@ -7872,14 +7793,14 @@
       <c r="N25" s="5">
         <v>17</v>
       </c>
-      <c r="O25" s="5">
-        <v>22</v>
+      <c r="O25">
+        <v>40</v>
       </c>
       <c r="P25" s="5">
         <v>1.5</v>
       </c>
       <c r="Q25" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J25/45)))</f>
         <v>995</v>
       </c>
       <c r="R25" s="5">
@@ -7939,7 +7860,7 @@
         <v>73</v>
       </c>
       <c r="J26" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E26:I26)</f>
         <v>373</v>
       </c>
       <c r="K26" s="5">
@@ -7954,12 +7875,12 @@
       <c r="N26" s="5">
         <v>17</v>
       </c>
-      <c r="O26" s="5">
-        <v>15</v>
+      <c r="O26">
+        <v>30</v>
       </c>
       <c r="P26" s="5"/>
       <c r="Q26" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J26/45)))</f>
         <v>689</v>
       </c>
       <c r="R26" s="5">
@@ -8021,7 +7942,7 @@
         <v>51</v>
       </c>
       <c r="J27" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E27:I27)</f>
         <v>329</v>
       </c>
       <c r="K27" s="5">
@@ -8039,7 +7960,7 @@
       <c r="O27" s="5"/>
       <c r="P27" s="5"/>
       <c r="Q27" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J27/45)))</f>
         <v>318</v>
       </c>
       <c r="R27" s="5">
@@ -8101,7 +8022,7 @@
         <v>76</v>
       </c>
       <c r="J28" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E28:I28)</f>
         <v>360</v>
       </c>
       <c r="K28" s="5">
@@ -8119,7 +8040,7 @@
       <c r="O28" s="5"/>
       <c r="P28" s="5"/>
       <c r="Q28" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J28/45)))</f>
         <v>548</v>
       </c>
       <c r="R28" s="5">
@@ -8179,7 +8100,7 @@
         <v>54</v>
       </c>
       <c r="J29" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E29:I29)</f>
         <v>298</v>
       </c>
       <c r="K29" s="5">
@@ -8197,7 +8118,7 @@
       <c r="O29" s="5"/>
       <c r="P29" s="5"/>
       <c r="Q29" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J29/45)))</f>
         <v>185</v>
       </c>
       <c r="R29" s="5">
@@ -8257,7 +8178,7 @@
         <v>63</v>
       </c>
       <c r="J30" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E30:I30)</f>
         <v>326</v>
       </c>
       <c r="K30" s="5">
@@ -8275,7 +8196,7 @@
       <c r="O30" s="5"/>
       <c r="P30" s="5"/>
       <c r="Q30" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J30/45)))</f>
         <v>302</v>
       </c>
       <c r="R30" s="5">
@@ -8335,7 +8256,7 @@
         <v>78</v>
       </c>
       <c r="J31" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E31:I31)</f>
         <v>380</v>
       </c>
       <c r="K31" s="5">
@@ -8353,7 +8274,7 @@
       <c r="O31" s="5"/>
       <c r="P31" s="5"/>
       <c r="Q31" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J31/45)))</f>
         <v>779</v>
       </c>
       <c r="R31" s="5">
@@ -8415,7 +8336,7 @@
         <v>67</v>
       </c>
       <c r="J32" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E32:I32)</f>
         <v>327</v>
       </c>
       <c r="K32" s="5">
@@ -8430,14 +8351,14 @@
       <c r="N32" s="5">
         <v>17</v>
       </c>
-      <c r="O32" s="5">
-        <v>22</v>
+      <c r="O32">
+        <v>40</v>
       </c>
       <c r="P32" s="5">
         <v>1.5</v>
       </c>
       <c r="Q32" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J32/45)))</f>
         <v>307</v>
       </c>
       <c r="R32" s="5">
@@ -8495,7 +8416,7 @@
         <v>69</v>
       </c>
       <c r="J33" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E33:I33)</f>
         <v>368</v>
       </c>
       <c r="K33" s="5">
@@ -8513,7 +8434,7 @@
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
       <c r="Q33" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J33/45)))</f>
         <v>631</v>
       </c>
       <c r="R33" s="5">
@@ -8573,7 +8494,7 @@
         <v>56</v>
       </c>
       <c r="J34" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E34:I34)</f>
         <v>339</v>
       </c>
       <c r="K34" s="5">
@@ -8588,12 +8509,12 @@
       <c r="N34" s="5">
         <v>17</v>
       </c>
-      <c r="O34" s="5">
-        <v>15</v>
+      <c r="O34">
+        <v>30</v>
       </c>
       <c r="P34" s="5"/>
       <c r="Q34" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J34/45)))</f>
         <v>379</v>
       </c>
       <c r="R34" s="5">
@@ -8655,7 +8576,7 @@
         <v>43</v>
       </c>
       <c r="J35" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E35:I35)</f>
         <v>220</v>
       </c>
       <c r="K35" s="5">
@@ -8670,12 +8591,12 @@
       <c r="N35" s="5">
         <v>17</v>
       </c>
-      <c r="O35" s="5">
-        <v>18</v>
+      <c r="O35">
+        <v>36</v>
       </c>
       <c r="P35" s="5"/>
       <c r="Q35" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J35/45)))</f>
         <v>47</v>
       </c>
       <c r="R35" s="5">
@@ -8734,7 +8655,7 @@
         <v>45</v>
       </c>
       <c r="J36" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E36:I36)</f>
         <v>271</v>
       </c>
       <c r="K36" s="5">
@@ -8752,7 +8673,7 @@
       <c r="O36" s="5"/>
       <c r="P36" s="5"/>
       <c r="Q36" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J36/45)))</f>
         <v>115</v>
       </c>
       <c r="R36" s="5">
@@ -8811,7 +8732,7 @@
         <v>73</v>
       </c>
       <c r="J37" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E37:I37)</f>
         <v>355</v>
       </c>
       <c r="K37" s="5">
@@ -8826,12 +8747,12 @@
       <c r="N37" s="5">
         <v>17</v>
       </c>
-      <c r="O37" s="5">
-        <v>15</v>
+      <c r="O37">
+        <v>30</v>
       </c>
       <c r="P37" s="5"/>
       <c r="Q37" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J37/45)))</f>
         <v>502</v>
       </c>
       <c r="R37" s="5">
@@ -8893,7 +8814,7 @@
         <v>65</v>
       </c>
       <c r="J38" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E38:I38)</f>
         <v>365</v>
       </c>
       <c r="K38" s="5">
@@ -8911,7 +8832,7 @@
       <c r="O38" s="5"/>
       <c r="P38" s="5"/>
       <c r="Q38" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J38/45)))</f>
         <v>599</v>
       </c>
       <c r="R38" s="5">
@@ -8973,7 +8894,7 @@
         <v>77</v>
       </c>
       <c r="J39" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E39:I39)</f>
         <v>396</v>
       </c>
       <c r="K39" s="5">
@@ -8991,7 +8912,7 @@
       <c r="O39" s="5"/>
       <c r="P39" s="5"/>
       <c r="Q39" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J39/45)))</f>
         <v>1031</v>
       </c>
       <c r="R39" s="5">
@@ -9051,7 +8972,7 @@
         <v>74</v>
       </c>
       <c r="J40" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E40:I40)</f>
         <v>345</v>
       </c>
       <c r="K40" s="5">
@@ -9066,12 +8987,12 @@
       <c r="N40" s="5">
         <v>17</v>
       </c>
-      <c r="O40" s="5">
-        <v>15</v>
+      <c r="O40">
+        <v>30</v>
       </c>
       <c r="P40" s="5"/>
       <c r="Q40" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J40/45)))</f>
         <v>421</v>
       </c>
       <c r="R40" s="5">
@@ -9131,7 +9052,7 @@
         <v>69</v>
       </c>
       <c r="J41" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E41:I41)</f>
         <v>350</v>
       </c>
       <c r="K41" s="5">
@@ -9146,14 +9067,14 @@
       <c r="N41" s="5">
         <v>17</v>
       </c>
-      <c r="O41" s="5">
-        <v>13</v>
+      <c r="O41">
+        <v>26</v>
       </c>
       <c r="P41" s="5">
         <v>2.5</v>
       </c>
       <c r="Q41" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J41/45)))</f>
         <v>460</v>
       </c>
       <c r="R41" s="5">
@@ -9211,7 +9132,7 @@
         <v>42</v>
       </c>
       <c r="J42" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E42:I42)</f>
         <v>312</v>
       </c>
       <c r="K42" s="5">
@@ -9226,14 +9147,14 @@
       <c r="N42" s="5">
         <v>17</v>
       </c>
-      <c r="O42" s="5">
-        <v>13</v>
+      <c r="O42">
+        <v>26</v>
       </c>
       <c r="P42" s="5">
         <v>2.5</v>
       </c>
       <c r="Q42" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J42/45)))</f>
         <v>236</v>
       </c>
       <c r="R42" s="5">
@@ -9289,7 +9210,7 @@
         <v>71</v>
       </c>
       <c r="J43" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E43:I43)</f>
         <v>312</v>
       </c>
       <c r="K43" s="5">
@@ -9307,7 +9228,7 @@
       <c r="O43" s="5"/>
       <c r="P43" s="5"/>
       <c r="Q43" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J43/45)))</f>
         <v>236</v>
       </c>
       <c r="R43" s="5">
@@ -9367,7 +9288,7 @@
         <v>50</v>
       </c>
       <c r="J44" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E44:I44)</f>
         <v>364</v>
       </c>
       <c r="K44" s="5">
@@ -9385,7 +9306,7 @@
       <c r="O44" s="5"/>
       <c r="P44" s="5"/>
       <c r="Q44" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J44/45)))</f>
         <v>588</v>
       </c>
       <c r="R44" s="5">
@@ -9445,7 +9366,7 @@
         <v>78</v>
       </c>
       <c r="J45" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E45:I45)</f>
         <v>283</v>
       </c>
       <c r="K45" s="5">
@@ -9460,12 +9381,12 @@
       <c r="N45" s="5">
         <v>17</v>
       </c>
-      <c r="O45" s="5">
-        <v>15</v>
+      <c r="O45">
+        <v>30</v>
       </c>
       <c r="P45" s="5"/>
       <c r="Q45" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J45/45)))</f>
         <v>142</v>
       </c>
       <c r="R45" s="5">
@@ -9525,7 +9446,7 @@
         <v>53</v>
       </c>
       <c r="J46" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E46:I46)</f>
         <v>297</v>
       </c>
       <c r="K46" s="5">
@@ -9540,12 +9461,12 @@
       <c r="N46" s="5">
         <v>17</v>
       </c>
-      <c r="O46" s="5">
-        <v>35</v>
+      <c r="O46">
+        <v>58</v>
       </c>
       <c r="P46" s="5"/>
       <c r="Q46" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J46/45)))</f>
         <v>181</v>
       </c>
       <c r="R46" s="5">
@@ -9605,7 +9526,7 @@
         <v>94</v>
       </c>
       <c r="J47" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E47:I47)</f>
         <v>244</v>
       </c>
       <c r="K47" s="5">
@@ -9620,12 +9541,12 @@
       <c r="N47" s="5">
         <v>17</v>
       </c>
-      <c r="O47" s="5">
-        <v>35</v>
+      <c r="O47">
+        <v>58</v>
       </c>
       <c r="P47" s="5"/>
       <c r="Q47" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J47/45)))</f>
         <v>71</v>
       </c>
       <c r="R47" s="5">
@@ -9684,7 +9605,7 @@
         <v>70</v>
       </c>
       <c r="J48" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E48:I48)</f>
         <v>323</v>
       </c>
       <c r="K48" s="5">
@@ -9699,12 +9620,12 @@
       <c r="N48" s="5">
         <v>17</v>
       </c>
-      <c r="O48" s="5">
-        <v>15</v>
+      <c r="O48">
+        <v>30</v>
       </c>
       <c r="P48" s="5"/>
       <c r="Q48" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J48/45)))</f>
         <v>286</v>
       </c>
       <c r="R48" s="5">
@@ -9763,7 +9684,7 @@
         <v>84</v>
       </c>
       <c r="J49" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E49:I49)</f>
         <v>374</v>
       </c>
       <c r="K49" s="5">
@@ -9781,7 +9702,7 @@
       <c r="O49" s="5"/>
       <c r="P49" s="5"/>
       <c r="Q49" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J49/45)))</f>
         <v>701</v>
       </c>
       <c r="R49" s="5">
@@ -9840,7 +9761,7 @@
         <v>73</v>
       </c>
       <c r="J50" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E50:I50)</f>
         <v>385</v>
       </c>
       <c r="K50" s="5">
@@ -9858,7 +9779,7 @@
       <c r="O50" s="5"/>
       <c r="P50" s="5"/>
       <c r="Q50" s="5">
-        <f t="shared" si="2"/>
+        <f>MAX(25, INT(POWER(2.2,J50/45)))</f>
         <v>850</v>
       </c>
       <c r="R50" s="5">
@@ -9916,7 +9837,7 @@
         <v>59</v>
       </c>
       <c r="J51" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E51:I51)</f>
         <v>348</v>
       </c>
       <c r="K51" s="5">
@@ -9934,7 +9855,7 @@
       <c r="O51" s="5"/>
       <c r="P51" s="5"/>
       <c r="Q51" s="5">
-        <f t="shared" ref="Q51:Q86" si="3">MAX(25, INT(POWER(2.2,J51/45)))</f>
+        <f>MAX(25, INT(POWER(2.2,J51/45)))</f>
         <v>444</v>
       </c>
       <c r="R51" s="5">
@@ -9994,7 +9915,7 @@
         <v>76</v>
       </c>
       <c r="J52" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E52:I52)</f>
         <v>346</v>
       </c>
       <c r="K52" s="5">
@@ -10009,12 +9930,12 @@
       <c r="N52" s="5">
         <v>17</v>
       </c>
-      <c r="O52" s="5">
-        <v>18</v>
+      <c r="O52">
+        <v>36</v>
       </c>
       <c r="P52" s="5"/>
       <c r="Q52" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J52/45)))</f>
         <v>429</v>
       </c>
       <c r="R52" s="5">
@@ -10070,7 +9991,7 @@
         <v>75</v>
       </c>
       <c r="J53" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E53:I53)</f>
         <v>385</v>
       </c>
       <c r="K53" s="5">
@@ -10088,7 +10009,7 @@
       <c r="O53" s="5"/>
       <c r="P53" s="5"/>
       <c r="Q53" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J53/45)))</f>
         <v>850</v>
       </c>
       <c r="R53" s="5">
@@ -10142,7 +10063,7 @@
         <v>61</v>
       </c>
       <c r="J54" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E54:I54)</f>
         <v>315</v>
       </c>
       <c r="K54" s="5">
@@ -10160,7 +10081,7 @@
       <c r="O54" s="5"/>
       <c r="P54" s="5"/>
       <c r="Q54" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J54/45)))</f>
         <v>249</v>
       </c>
       <c r="R54" s="5">
@@ -10214,7 +10135,7 @@
         <v>61</v>
       </c>
       <c r="J55" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E55:I55)</f>
         <v>367</v>
       </c>
       <c r="K55" s="5">
@@ -10232,7 +10153,7 @@
       <c r="O55" s="5"/>
       <c r="P55" s="5"/>
       <c r="Q55" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J55/45)))</f>
         <v>620</v>
       </c>
       <c r="R55" s="5">
@@ -10286,7 +10207,7 @@
         <v>75</v>
       </c>
       <c r="J56" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E56:I56)</f>
         <v>383</v>
       </c>
       <c r="K56" s="5">
@@ -10304,7 +10225,7 @@
       <c r="O56" s="5"/>
       <c r="P56" s="5"/>
       <c r="Q56" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J56/45)))</f>
         <v>821</v>
       </c>
       <c r="R56" s="5">
@@ -10358,7 +10279,7 @@
         <v>72</v>
       </c>
       <c r="J57" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E57:I57)</f>
         <v>313</v>
       </c>
       <c r="K57" s="5">
@@ -10376,7 +10297,7 @@
       <c r="O57" s="5"/>
       <c r="P57" s="5"/>
       <c r="Q57" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J57/45)))</f>
         <v>240</v>
       </c>
       <c r="R57" s="5">
@@ -10430,7 +10351,7 @@
         <v>71</v>
       </c>
       <c r="J58" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E58:I58)</f>
         <v>361</v>
       </c>
       <c r="K58" s="5">
@@ -10448,7 +10369,7 @@
       <c r="O58" s="5"/>
       <c r="P58" s="5"/>
       <c r="Q58" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J58/45)))</f>
         <v>558</v>
       </c>
       <c r="R58" s="5">
@@ -10502,7 +10423,7 @@
         <v>81</v>
       </c>
       <c r="J59" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E59:I59)</f>
         <v>354</v>
       </c>
       <c r="K59" s="5">
@@ -10520,7 +10441,7 @@
       <c r="O59" s="5"/>
       <c r="P59" s="5"/>
       <c r="Q59" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J59/45)))</f>
         <v>493</v>
       </c>
       <c r="R59" s="5">
@@ -10574,7 +10495,7 @@
         <v>80</v>
       </c>
       <c r="J60" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E60:I60)</f>
         <v>353</v>
       </c>
       <c r="K60" s="5">
@@ -10592,7 +10513,7 @@
       <c r="O60" s="5"/>
       <c r="P60" s="5"/>
       <c r="Q60" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J60/45)))</f>
         <v>485</v>
       </c>
       <c r="R60" s="5">
@@ -10646,7 +10567,7 @@
         <v>83</v>
       </c>
       <c r="J61" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E61:I61)</f>
         <v>357</v>
       </c>
       <c r="K61" s="5">
@@ -10664,7 +10585,7 @@
       <c r="O61" s="5"/>
       <c r="P61" s="5"/>
       <c r="Q61" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J61/45)))</f>
         <v>520</v>
       </c>
       <c r="R61" s="5">
@@ -10718,7 +10639,7 @@
         <v>66</v>
       </c>
       <c r="J62" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E62:I62)</f>
         <v>306</v>
       </c>
       <c r="K62" s="5">
@@ -10736,7 +10657,7 @@
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
       <c r="Q62" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J62/45)))</f>
         <v>213</v>
       </c>
       <c r="R62" s="5">
@@ -10790,7 +10711,7 @@
         <v>52</v>
       </c>
       <c r="J63" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E63:I63)</f>
         <v>266</v>
       </c>
       <c r="K63" s="5">
@@ -10808,7 +10729,7 @@
       <c r="O63" s="5"/>
       <c r="P63" s="5"/>
       <c r="Q63" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J63/45)))</f>
         <v>105</v>
       </c>
       <c r="R63" s="5">
@@ -10862,7 +10783,7 @@
         <v>76</v>
       </c>
       <c r="J64" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E64:I64)</f>
         <v>335</v>
       </c>
       <c r="K64" s="5">
@@ -10880,7 +10801,7 @@
       <c r="O64" s="5"/>
       <c r="P64" s="5"/>
       <c r="Q64" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J64/45)))</f>
         <v>354</v>
       </c>
       <c r="R64" s="5">
@@ -10934,7 +10855,7 @@
         <v>83</v>
       </c>
       <c r="J65" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E65:I65)</f>
         <v>358</v>
       </c>
       <c r="K65" s="5">
@@ -10952,7 +10873,7 @@
       <c r="O65" s="5"/>
       <c r="P65" s="5"/>
       <c r="Q65" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J65/45)))</f>
         <v>529</v>
       </c>
       <c r="R65" s="5">
@@ -11006,7 +10927,7 @@
         <v>70</v>
       </c>
       <c r="J66" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E66:I66)</f>
         <v>299</v>
       </c>
       <c r="K66" s="5">
@@ -11024,7 +10945,7 @@
       <c r="O66" s="5"/>
       <c r="P66" s="5"/>
       <c r="Q66" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J66/45)))</f>
         <v>188</v>
       </c>
       <c r="R66" s="5">
@@ -11078,7 +10999,7 @@
         <v>76</v>
       </c>
       <c r="J67" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E67:I67)</f>
         <v>333</v>
       </c>
       <c r="K67" s="5">
@@ -11096,7 +11017,7 @@
       <c r="O67" s="5"/>
       <c r="P67" s="5"/>
       <c r="Q67" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J67/45)))</f>
         <v>341</v>
       </c>
       <c r="R67" s="5">
@@ -11150,7 +11071,7 @@
         <v>60</v>
       </c>
       <c r="J68" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(E68:I68)</f>
         <v>297</v>
       </c>
       <c r="K68" s="5">
@@ -11168,7 +11089,7 @@
       <c r="O68" s="5"/>
       <c r="P68" s="5"/>
       <c r="Q68" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J68/45)))</f>
         <v>181</v>
       </c>
       <c r="R68" s="5">
@@ -11222,7 +11143,7 @@
         <v>64</v>
       </c>
       <c r="J69" s="5">
-        <f t="shared" ref="J69:J132" si="4">SUM(E69:I69)</f>
+        <f>SUM(E69:I69)</f>
         <v>311</v>
       </c>
       <c r="K69" s="5">
@@ -11240,7 +11161,7 @@
       <c r="O69" s="5"/>
       <c r="P69" s="5"/>
       <c r="Q69" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J69/45)))</f>
         <v>232</v>
       </c>
       <c r="R69" s="5">
@@ -11294,7 +11215,7 @@
         <v>60</v>
       </c>
       <c r="J70" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E70:I70)</f>
         <v>319</v>
       </c>
       <c r="K70" s="5">
@@ -11312,7 +11233,7 @@
       <c r="O70" s="5"/>
       <c r="P70" s="5"/>
       <c r="Q70" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J70/45)))</f>
         <v>267</v>
       </c>
       <c r="R70" s="5">
@@ -11366,7 +11287,7 @@
         <v>79</v>
       </c>
       <c r="J71" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E71:I71)</f>
         <v>315</v>
       </c>
       <c r="K71" s="5">
@@ -11384,7 +11305,7 @@
       <c r="O71" s="5"/>
       <c r="P71" s="5"/>
       <c r="Q71" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J71/45)))</f>
         <v>249</v>
       </c>
       <c r="R71" s="5">
@@ -11438,7 +11359,7 @@
         <v>63</v>
       </c>
       <c r="J72" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E72:I72)</f>
         <v>299</v>
       </c>
       <c r="K72" s="5">
@@ -11456,7 +11377,7 @@
       <c r="O72" s="5"/>
       <c r="P72" s="5"/>
       <c r="Q72" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J72/45)))</f>
         <v>188</v>
       </c>
       <c r="R72" s="5">
@@ -11510,7 +11431,7 @@
         <v>73</v>
       </c>
       <c r="J73" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E73:I73)</f>
         <v>295</v>
       </c>
       <c r="K73" s="5">
@@ -11528,7 +11449,7 @@
       <c r="O73" s="5"/>
       <c r="P73" s="5"/>
       <c r="Q73" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J73/45)))</f>
         <v>175</v>
       </c>
       <c r="R73" s="5">
@@ -11582,7 +11503,7 @@
         <v>50</v>
       </c>
       <c r="J74" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E74:I74)</f>
         <v>233</v>
       </c>
       <c r="K74" s="5">
@@ -11600,7 +11521,7 @@
       <c r="O74" s="5"/>
       <c r="P74" s="5"/>
       <c r="Q74" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J74/45)))</f>
         <v>59</v>
       </c>
       <c r="R74" s="5">
@@ -11654,7 +11575,7 @@
         <v>14</v>
       </c>
       <c r="J75" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E75:I75)</f>
         <v>218</v>
       </c>
       <c r="K75" s="5">
@@ -11672,7 +11593,7 @@
       <c r="O75" s="5"/>
       <c r="P75" s="5"/>
       <c r="Q75" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J75/45)))</f>
         <v>45</v>
       </c>
       <c r="R75" s="5">
@@ -11726,7 +11647,7 @@
         <v>51</v>
       </c>
       <c r="J76" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E76:I76)</f>
         <v>294</v>
       </c>
       <c r="K76" s="5">
@@ -11744,7 +11665,7 @@
       <c r="O76" s="5"/>
       <c r="P76" s="5"/>
       <c r="Q76" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J76/45)))</f>
         <v>172</v>
       </c>
       <c r="R76" s="5">
@@ -11798,7 +11719,7 @@
         <v>87</v>
       </c>
       <c r="J77" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E77:I77)</f>
         <v>295</v>
       </c>
       <c r="K77" s="5">
@@ -11816,7 +11737,7 @@
       <c r="O77" s="5"/>
       <c r="P77" s="5"/>
       <c r="Q77" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J77/45)))</f>
         <v>175</v>
       </c>
       <c r="R77" s="5">
@@ -11870,7 +11791,7 @@
         <v>68</v>
       </c>
       <c r="J78" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E78:I78)</f>
         <v>278</v>
       </c>
       <c r="K78" s="5">
@@ -11888,7 +11809,7 @@
       <c r="O78" s="5"/>
       <c r="P78" s="5"/>
       <c r="Q78" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J78/45)))</f>
         <v>130</v>
       </c>
       <c r="R78" s="5">
@@ -11942,7 +11863,7 @@
         <v>63</v>
       </c>
       <c r="J79" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E79:I79)</f>
         <v>241</v>
       </c>
       <c r="K79" s="5">
@@ -11960,7 +11881,7 @@
       <c r="O79" s="5"/>
       <c r="P79" s="5"/>
       <c r="Q79" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J79/45)))</f>
         <v>68</v>
       </c>
       <c r="R79" s="5">
@@ -12014,7 +11935,7 @@
         <v>81</v>
       </c>
       <c r="J80" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E80:I80)</f>
         <v>277</v>
       </c>
       <c r="K80" s="5">
@@ -12032,7 +11953,7 @@
       <c r="O80" s="5"/>
       <c r="P80" s="5"/>
       <c r="Q80" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J80/45)))</f>
         <v>128</v>
       </c>
       <c r="R80" s="5">
@@ -12086,7 +12007,7 @@
         <v>44</v>
       </c>
       <c r="J81" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E81:I81)</f>
         <v>228</v>
       </c>
       <c r="K81" s="5">
@@ -12104,7 +12025,7 @@
       <c r="O81" s="5"/>
       <c r="P81" s="5"/>
       <c r="Q81" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J81/45)))</f>
         <v>54</v>
       </c>
       <c r="R81" s="5">
@@ -12158,7 +12079,7 @@
         <v>57</v>
       </c>
       <c r="J82" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E82:I82)</f>
         <v>260</v>
       </c>
       <c r="K82" s="5">
@@ -12176,7 +12097,7 @@
       <c r="O82" s="5"/>
       <c r="P82" s="5"/>
       <c r="Q82" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J82/45)))</f>
         <v>95</v>
       </c>
       <c r="R82" s="5">
@@ -12230,7 +12151,7 @@
         <v>74</v>
       </c>
       <c r="J83" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E83:I83)</f>
         <v>298</v>
       </c>
       <c r="K83" s="5">
@@ -12248,7 +12169,7 @@
       <c r="O83" s="5"/>
       <c r="P83" s="5"/>
       <c r="Q83" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J83/45)))</f>
         <v>185</v>
       </c>
       <c r="R83" s="5">
@@ -12302,7 +12223,7 @@
         <v>37</v>
       </c>
       <c r="J84" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E84:I84)</f>
         <v>207</v>
       </c>
       <c r="K84" s="5">
@@ -12320,7 +12241,7 @@
       <c r="O84" s="5"/>
       <c r="P84" s="5"/>
       <c r="Q84" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J84/45)))</f>
         <v>37</v>
       </c>
       <c r="R84" s="5">
@@ -12374,7 +12295,7 @@
         <v>67</v>
       </c>
       <c r="J85" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E85:I85)</f>
         <v>242</v>
       </c>
       <c r="K85" s="5">
@@ -12392,7 +12313,7 @@
       <c r="O85" s="5"/>
       <c r="P85" s="5"/>
       <c r="Q85" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J85/45)))</f>
         <v>69</v>
       </c>
       <c r="R85" s="5">
@@ -12446,7 +12367,7 @@
         <v>47</v>
       </c>
       <c r="J86" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E86:I86)</f>
         <v>191</v>
       </c>
       <c r="K86" s="5">
@@ -12464,7 +12385,7 @@
       <c r="O86" s="5"/>
       <c r="P86" s="5"/>
       <c r="Q86" s="5">
-        <f t="shared" si="3"/>
+        <f>MAX(25, INT(POWER(2.2,J86/45)))</f>
         <v>28</v>
       </c>
       <c r="R86" s="5">
@@ -12518,7 +12439,7 @@
         <v>93</v>
       </c>
       <c r="J87" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E87:I87)</f>
         <v>397</v>
       </c>
       <c r="K87" s="5">
@@ -12591,7 +12512,7 @@
         <v>58</v>
       </c>
       <c r="J88" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E88:I88)</f>
         <v>339</v>
       </c>
       <c r="K88" s="5">
@@ -12606,14 +12527,14 @@
       <c r="N88" s="5">
         <v>17</v>
       </c>
-      <c r="O88" s="5">
-        <v>22</v>
+      <c r="O88">
+        <v>40</v>
       </c>
       <c r="P88" s="5">
         <v>1.5</v>
       </c>
       <c r="Q88" s="5">
-        <f t="shared" ref="Q88:Q119" si="5">MAX(25, INT(POWER(2.2,J88/45)))</f>
+        <f>MAX(25, INT(POWER(2.2,J88/45)))</f>
         <v>379</v>
       </c>
       <c r="R88" s="5">
@@ -12673,7 +12594,7 @@
         <v>79</v>
       </c>
       <c r="J89" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E89:I89)</f>
         <v>381</v>
       </c>
       <c r="K89" s="5">
@@ -12688,14 +12609,14 @@
       <c r="N89" s="5">
         <v>17</v>
       </c>
-      <c r="O89" s="5">
-        <v>22</v>
+      <c r="O89">
+        <v>40</v>
       </c>
       <c r="P89" s="5">
         <v>1.5</v>
       </c>
       <c r="Q89" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J89/45)))</f>
         <v>792</v>
       </c>
       <c r="R89" s="5">
@@ -12755,7 +12676,7 @@
         <v>80</v>
       </c>
       <c r="J90" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E90:I90)</f>
         <v>372</v>
       </c>
       <c r="K90" s="5">
@@ -12773,7 +12694,7 @@
       <c r="O90" s="5"/>
       <c r="P90" s="5"/>
       <c r="Q90" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J90/45)))</f>
         <v>677</v>
       </c>
       <c r="R90" s="5">
@@ -12833,7 +12754,7 @@
         <v>60</v>
       </c>
       <c r="J91" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E91:I91)</f>
         <v>313</v>
       </c>
       <c r="K91" s="5">
@@ -12851,7 +12772,7 @@
       <c r="O91" s="5"/>
       <c r="P91" s="5"/>
       <c r="Q91" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J91/45)))</f>
         <v>240</v>
       </c>
       <c r="R91" s="5">
@@ -12911,7 +12832,7 @@
         <v>89</v>
       </c>
       <c r="J92" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E92:I92)</f>
         <v>409</v>
       </c>
       <c r="K92" s="5">
@@ -12926,12 +12847,12 @@
       <c r="N92" s="5">
         <v>17</v>
       </c>
-      <c r="O92" s="5">
-        <v>18</v>
+      <c r="O92">
+        <v>36</v>
       </c>
       <c r="P92" s="5"/>
       <c r="Q92" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J92/45)))</f>
         <v>1294</v>
       </c>
       <c r="R92" s="5">
@@ -12993,7 +12914,7 @@
         <v>93</v>
       </c>
       <c r="J93" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E93:I93)</f>
         <v>442</v>
       </c>
       <c r="K93" s="5">
@@ -13008,12 +12929,12 @@
       <c r="N93" s="5">
         <v>17</v>
       </c>
-      <c r="O93" s="5">
-        <v>15</v>
+      <c r="O93">
+        <v>30</v>
       </c>
       <c r="P93" s="5"/>
       <c r="Q93" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J93/45)))</f>
         <v>2308</v>
       </c>
       <c r="R93" s="5">
@@ -13075,7 +12996,7 @@
         <v>74</v>
       </c>
       <c r="J94" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E94:I94)</f>
         <v>329</v>
       </c>
       <c r="K94" s="5">
@@ -13093,7 +13014,7 @@
       <c r="O94" s="5"/>
       <c r="P94" s="5"/>
       <c r="Q94" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J94/45)))</f>
         <v>318</v>
       </c>
       <c r="R94" s="5">
@@ -13151,7 +13072,7 @@
         <v>82</v>
       </c>
       <c r="J95" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E95:I95)</f>
         <v>412</v>
       </c>
       <c r="K95" s="5">
@@ -13169,7 +13090,7 @@
       <c r="O95" s="5"/>
       <c r="P95" s="5"/>
       <c r="Q95" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J95/45)))</f>
         <v>1364</v>
       </c>
       <c r="R95" s="5">
@@ -13231,7 +13152,7 @@
         <v>90</v>
       </c>
       <c r="J96" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E96:I96)</f>
         <v>434</v>
       </c>
       <c r="K96" s="5">
@@ -13246,12 +13167,12 @@
       <c r="N96" s="5">
         <v>17</v>
       </c>
-      <c r="O96" s="5">
-        <v>15</v>
+      <c r="O96">
+        <v>30</v>
       </c>
       <c r="P96" s="5"/>
       <c r="Q96" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J96/45)))</f>
         <v>2006</v>
       </c>
       <c r="R96" s="5">
@@ -13311,7 +13232,7 @@
         <v>79</v>
       </c>
       <c r="J97" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E97:I97)</f>
         <v>294</v>
       </c>
       <c r="K97" s="5">
@@ -13326,12 +13247,12 @@
       <c r="N97" s="5">
         <v>17</v>
       </c>
-      <c r="O97" s="5">
-        <v>18</v>
+      <c r="O97">
+        <v>36</v>
       </c>
       <c r="P97" s="5"/>
       <c r="Q97" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J97/45)))</f>
         <v>172</v>
       </c>
       <c r="R97" s="5">
@@ -13389,7 +13310,7 @@
         <v>90</v>
       </c>
       <c r="J98" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E98:I98)</f>
         <v>367</v>
       </c>
       <c r="K98" s="5">
@@ -13404,12 +13325,12 @@
       <c r="N98" s="5">
         <v>17</v>
       </c>
-      <c r="O98" s="5">
-        <v>15</v>
+      <c r="O98">
+        <v>30</v>
       </c>
       <c r="P98" s="5"/>
       <c r="Q98" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J98/45)))</f>
         <v>620</v>
       </c>
       <c r="R98" s="5">
@@ -13469,7 +13390,7 @@
         <v>70</v>
       </c>
       <c r="J99" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E99:I99)</f>
         <v>347</v>
       </c>
       <c r="K99" s="5">
@@ -13484,14 +13405,14 @@
       <c r="N99" s="5">
         <v>17</v>
       </c>
-      <c r="O99" s="5">
-        <v>22</v>
+      <c r="O99">
+        <v>40</v>
       </c>
       <c r="P99" s="5">
         <v>1.5</v>
       </c>
       <c r="Q99" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J99/45)))</f>
         <v>436</v>
       </c>
       <c r="R99" s="5">
@@ -13549,7 +13470,7 @@
         <v>59</v>
       </c>
       <c r="J100" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E100:I100)</f>
         <v>356</v>
       </c>
       <c r="K100" s="5">
@@ -13567,7 +13488,7 @@
       <c r="O100" s="5"/>
       <c r="P100" s="5"/>
       <c r="Q100" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J100/45)))</f>
         <v>511</v>
       </c>
       <c r="R100" s="5">
@@ -13629,7 +13550,7 @@
         <v>92</v>
       </c>
       <c r="J101" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E101:I101)</f>
         <v>270</v>
       </c>
       <c r="K101" s="5">
@@ -13644,12 +13565,12 @@
       <c r="N101" s="5">
         <v>17</v>
       </c>
-      <c r="O101" s="5">
-        <v>15</v>
+      <c r="O101">
+        <v>30</v>
       </c>
       <c r="P101" s="5"/>
       <c r="Q101" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J101/45)))</f>
         <v>113</v>
       </c>
       <c r="R101" s="5">
@@ -13711,7 +13632,7 @@
         <v>92</v>
       </c>
       <c r="J102" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E102:I102)</f>
         <v>270</v>
       </c>
       <c r="K102" s="5">
@@ -13726,12 +13647,12 @@
       <c r="N102" s="5">
         <v>17</v>
       </c>
-      <c r="O102" s="5">
-        <v>15</v>
+      <c r="O102">
+        <v>30</v>
       </c>
       <c r="P102" s="5"/>
       <c r="Q102" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J102/45)))</f>
         <v>113</v>
       </c>
       <c r="R102" s="5">
@@ -13793,7 +13714,7 @@
         <v>52</v>
       </c>
       <c r="J103" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E103:I103)</f>
         <v>340</v>
       </c>
       <c r="K103" s="5">
@@ -13808,14 +13729,14 @@
       <c r="N103" s="5">
         <v>17</v>
       </c>
-      <c r="O103" s="5">
-        <v>13</v>
+      <c r="O103">
+        <v>26</v>
       </c>
       <c r="P103" s="5">
         <v>2.5</v>
       </c>
       <c r="Q103" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J103/45)))</f>
         <v>386</v>
       </c>
       <c r="R103" s="5">
@@ -13873,7 +13794,7 @@
         <v>60</v>
       </c>
       <c r="J104" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E104:I104)</f>
         <v>315</v>
       </c>
       <c r="K104" s="5">
@@ -13891,7 +13812,7 @@
       <c r="O104" s="5"/>
       <c r="P104" s="5"/>
       <c r="Q104" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J104/45)))</f>
         <v>249</v>
       </c>
       <c r="R104" s="5">
@@ -13950,7 +13871,7 @@
         <v>66</v>
       </c>
       <c r="J105" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E105:I105)</f>
         <v>312</v>
       </c>
       <c r="K105" s="5">
@@ -13965,14 +13886,14 @@
       <c r="N105" s="5">
         <v>17</v>
       </c>
-      <c r="O105" s="5">
-        <v>30</v>
+      <c r="O105">
+        <v>50</v>
       </c>
       <c r="P105" s="5">
         <v>1.5</v>
       </c>
       <c r="Q105" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J105/45)))</f>
         <v>236</v>
       </c>
       <c r="R105" s="5">
@@ -14031,7 +13952,7 @@
         <v>12</v>
       </c>
       <c r="J106" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E106:I106)</f>
         <v>266</v>
       </c>
       <c r="K106" s="5">
@@ -14049,7 +13970,7 @@
       <c r="O106" s="5"/>
       <c r="P106" s="5"/>
       <c r="Q106" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J106/45)))</f>
         <v>105</v>
       </c>
       <c r="R106" s="5">
@@ -14111,7 +14032,7 @@
         <v>64</v>
       </c>
       <c r="J107" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E107:I107)</f>
         <v>289</v>
       </c>
       <c r="K107" s="5">
@@ -14126,14 +14047,14 @@
       <c r="N107" s="5">
         <v>17</v>
       </c>
-      <c r="O107" s="5">
-        <v>22</v>
+      <c r="O107">
+        <v>40</v>
       </c>
       <c r="P107" s="5">
         <v>1.5</v>
       </c>
       <c r="Q107" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J107/45)))</f>
         <v>158</v>
       </c>
       <c r="R107" s="5">
@@ -14193,7 +14114,7 @@
         <v>73</v>
       </c>
       <c r="J108" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E108:I108)</f>
         <v>384</v>
       </c>
       <c r="K108" s="5">
@@ -14211,7 +14132,7 @@
       <c r="O108" s="5"/>
       <c r="P108" s="5"/>
       <c r="Q108" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J108/45)))</f>
         <v>835</v>
       </c>
       <c r="R108" s="5">
@@ -14271,7 +14192,7 @@
         <v>81</v>
       </c>
       <c r="J109" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E109:I109)</f>
         <v>380</v>
       </c>
       <c r="K109" s="5">
@@ -14289,7 +14210,7 @@
       <c r="O109" s="5"/>
       <c r="P109" s="5"/>
       <c r="Q109" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J109/45)))</f>
         <v>779</v>
       </c>
       <c r="R109" s="5">
@@ -14351,7 +14272,7 @@
         <v>79</v>
       </c>
       <c r="J110" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E110:I110)</f>
         <v>300</v>
       </c>
       <c r="K110" s="5">
@@ -14366,12 +14287,12 @@
       <c r="N110" s="5">
         <v>17</v>
       </c>
-      <c r="O110" s="5">
-        <v>18</v>
+      <c r="O110">
+        <v>36</v>
       </c>
       <c r="P110" s="5"/>
       <c r="Q110" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J110/45)))</f>
         <v>191</v>
       </c>
       <c r="R110" s="5">
@@ -14431,7 +14352,7 @@
         <v>76</v>
       </c>
       <c r="J111" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E111:I111)</f>
         <v>309</v>
       </c>
       <c r="K111" s="5">
@@ -14446,12 +14367,12 @@
       <c r="N111" s="5">
         <v>17</v>
       </c>
-      <c r="O111" s="5">
-        <v>15</v>
+      <c r="O111">
+        <v>30</v>
       </c>
       <c r="P111" s="5"/>
       <c r="Q111" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J111/45)))</f>
         <v>224</v>
       </c>
       <c r="R111" s="5">
@@ -14511,7 +14432,7 @@
         <v>65</v>
       </c>
       <c r="J112" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E112:I112)</f>
         <v>359</v>
       </c>
       <c r="K112" s="5">
@@ -14526,12 +14447,12 @@
       <c r="N112" s="5">
         <v>17</v>
       </c>
-      <c r="O112" s="5">
-        <v>35</v>
+      <c r="O112">
+        <v>58</v>
       </c>
       <c r="P112" s="5"/>
       <c r="Q112" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J112/45)))</f>
         <v>539</v>
       </c>
       <c r="R112" s="5">
@@ -14591,7 +14512,7 @@
         <v>71</v>
       </c>
       <c r="J113" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E113:I113)</f>
         <v>333</v>
       </c>
       <c r="K113" s="5">
@@ -14606,12 +14527,12 @@
       <c r="N113" s="5">
         <v>17</v>
       </c>
-      <c r="O113" s="5">
-        <v>15</v>
+      <c r="O113">
+        <v>30</v>
       </c>
       <c r="P113" s="5"/>
       <c r="Q113" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J113/45)))</f>
         <v>341</v>
       </c>
       <c r="R113" s="5">
@@ -14671,7 +14592,7 @@
         <v>67</v>
       </c>
       <c r="J114" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E114:I114)</f>
         <v>329</v>
       </c>
       <c r="K114" s="5">
@@ -14689,7 +14610,7 @@
       <c r="O114" s="5"/>
       <c r="P114" s="5"/>
       <c r="Q114" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J114/45)))</f>
         <v>318</v>
       </c>
       <c r="R114" s="5">
@@ -14749,7 +14670,7 @@
         <v>70</v>
       </c>
       <c r="J115" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E115:I115)</f>
         <v>340</v>
       </c>
       <c r="K115" s="5">
@@ -14767,7 +14688,7 @@
       <c r="O115" s="5"/>
       <c r="P115" s="5"/>
       <c r="Q115" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J115/45)))</f>
         <v>386</v>
       </c>
       <c r="R115" s="5">
@@ -14827,7 +14748,7 @@
         <v>62</v>
       </c>
       <c r="J116" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E116:I116)</f>
         <v>306</v>
       </c>
       <c r="K116" s="5">
@@ -14845,7 +14766,7 @@
       <c r="O116" s="5"/>
       <c r="P116" s="5"/>
       <c r="Q116" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J116/45)))</f>
         <v>213</v>
       </c>
       <c r="R116" s="5">
@@ -14905,7 +14826,7 @@
         <v>73</v>
       </c>
       <c r="J117" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E117:I117)</f>
         <v>344</v>
       </c>
       <c r="K117" s="5">
@@ -14923,7 +14844,7 @@
       <c r="O117" s="5"/>
       <c r="P117" s="5"/>
       <c r="Q117" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J117/45)))</f>
         <v>414</v>
       </c>
       <c r="R117" s="5">
@@ -14983,7 +14904,7 @@
         <v>70</v>
       </c>
       <c r="J118" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E118:I118)</f>
         <v>357</v>
       </c>
       <c r="K118" s="5">
@@ -15001,7 +14922,7 @@
       <c r="O118" s="5"/>
       <c r="P118" s="5"/>
       <c r="Q118" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J118/45)))</f>
         <v>520</v>
       </c>
       <c r="R118" s="5">
@@ -15061,7 +14982,7 @@
         <v>72</v>
       </c>
       <c r="J119" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E119:I119)</f>
         <v>242</v>
       </c>
       <c r="K119" s="5">
@@ -15076,12 +14997,12 @@
       <c r="N119" s="5">
         <v>17</v>
       </c>
-      <c r="O119" s="5">
-        <v>15</v>
+      <c r="O119">
+        <v>30</v>
       </c>
       <c r="P119" s="5"/>
       <c r="Q119" s="5">
-        <f t="shared" si="5"/>
+        <f>MAX(25, INT(POWER(2.2,J119/45)))</f>
         <v>69</v>
       </c>
       <c r="R119" s="5">
@@ -15141,7 +15062,7 @@
         <v>69</v>
       </c>
       <c r="J120" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E120:I120)</f>
         <v>356</v>
       </c>
       <c r="K120" s="5">
@@ -15159,7 +15080,7 @@
       <c r="O120" s="5"/>
       <c r="P120" s="5"/>
       <c r="Q120" s="5">
-        <f t="shared" ref="Q120:Q138" si="6">MAX(25, INT(POWER(2.2,J120/45)))</f>
+        <f>MAX(25, INT(POWER(2.2,J120/45)))</f>
         <v>511</v>
       </c>
       <c r="R120" s="5">
@@ -15213,7 +15134,7 @@
         <v>36</v>
       </c>
       <c r="J121" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E121:I121)</f>
         <v>268</v>
       </c>
       <c r="K121" s="5">
@@ -15231,7 +15152,7 @@
       <c r="O121" s="5"/>
       <c r="P121" s="5"/>
       <c r="Q121" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J121/45)))</f>
         <v>109</v>
       </c>
       <c r="R121" s="5">
@@ -15285,7 +15206,7 @@
         <v>52</v>
       </c>
       <c r="J122" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E122:I122)</f>
         <v>266</v>
       </c>
       <c r="K122" s="5">
@@ -15303,7 +15224,7 @@
       <c r="O122" s="5"/>
       <c r="P122" s="5"/>
       <c r="Q122" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J122/45)))</f>
         <v>105</v>
       </c>
       <c r="R122" s="5">
@@ -15357,7 +15278,7 @@
         <v>73</v>
       </c>
       <c r="J123" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E123:I123)</f>
         <v>340</v>
       </c>
       <c r="K123" s="5">
@@ -15375,7 +15296,7 @@
       <c r="O123" s="5"/>
       <c r="P123" s="5"/>
       <c r="Q123" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J123/45)))</f>
         <v>386</v>
       </c>
       <c r="R123" s="5">
@@ -15429,7 +15350,7 @@
         <v>62</v>
       </c>
       <c r="J124" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E124:I124)</f>
         <v>336</v>
       </c>
       <c r="K124" s="5">
@@ -15447,7 +15368,7 @@
       <c r="O124" s="5"/>
       <c r="P124" s="5"/>
       <c r="Q124" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J124/45)))</f>
         <v>360</v>
       </c>
       <c r="R124" s="5">
@@ -15501,7 +15422,7 @@
         <v>46</v>
       </c>
       <c r="J125" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E125:I125)</f>
         <v>304</v>
       </c>
       <c r="K125" s="5">
@@ -15519,7 +15440,7 @@
       <c r="O125" s="5"/>
       <c r="P125" s="5"/>
       <c r="Q125" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J125/45)))</f>
         <v>205</v>
       </c>
       <c r="R125" s="5">
@@ -15573,7 +15494,7 @@
         <v>41</v>
       </c>
       <c r="J126" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E126:I126)</f>
         <v>238</v>
       </c>
       <c r="K126" s="5">
@@ -15591,7 +15512,7 @@
       <c r="O126" s="5"/>
       <c r="P126" s="5"/>
       <c r="Q126" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J126/45)))</f>
         <v>64</v>
       </c>
       <c r="R126" s="5">
@@ -15645,7 +15566,7 @@
         <v>65</v>
       </c>
       <c r="J127" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E127:I127)</f>
         <v>240</v>
       </c>
       <c r="K127" s="5">
@@ -15663,7 +15584,7 @@
       <c r="O127" s="5"/>
       <c r="P127" s="5"/>
       <c r="Q127" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J127/45)))</f>
         <v>67</v>
       </c>
       <c r="R127" s="5">
@@ -15717,7 +15638,7 @@
         <v>62</v>
       </c>
       <c r="J128" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E128:I128)</f>
         <v>355</v>
       </c>
       <c r="K128" s="5">
@@ -15735,7 +15656,7 @@
       <c r="O128" s="5"/>
       <c r="P128" s="5"/>
       <c r="Q128" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J128/45)))</f>
         <v>502</v>
       </c>
       <c r="R128" s="5">
@@ -15789,7 +15710,7 @@
         <v>78</v>
       </c>
       <c r="J129" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E129:I129)</f>
         <v>362</v>
       </c>
       <c r="K129" s="5">
@@ -15807,7 +15728,7 @@
       <c r="O129" s="5"/>
       <c r="P129" s="5"/>
       <c r="Q129" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J129/45)))</f>
         <v>568</v>
       </c>
       <c r="R129" s="5">
@@ -15861,7 +15782,7 @@
         <v>70</v>
       </c>
       <c r="J130" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E130:I130)</f>
         <v>325</v>
       </c>
       <c r="K130" s="5">
@@ -15879,7 +15800,7 @@
       <c r="O130" s="5"/>
       <c r="P130" s="5"/>
       <c r="Q130" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J130/45)))</f>
         <v>297</v>
       </c>
       <c r="R130" s="5">
@@ -15933,7 +15854,7 @@
         <v>22</v>
       </c>
       <c r="J131" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E131:I131)</f>
         <v>186</v>
       </c>
       <c r="K131" s="5">
@@ -15951,7 +15872,7 @@
       <c r="O131" s="5"/>
       <c r="P131" s="5"/>
       <c r="Q131" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J131/45)))</f>
         <v>26</v>
       </c>
       <c r="R131" s="5">
@@ -16005,7 +15926,7 @@
         <v>74</v>
       </c>
       <c r="J132" s="5">
-        <f t="shared" si="4"/>
+        <f>SUM(E132:I132)</f>
         <v>370</v>
       </c>
       <c r="K132" s="5">
@@ -16023,7 +15944,7 @@
       <c r="O132" s="5"/>
       <c r="P132" s="5"/>
       <c r="Q132" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J132/45)))</f>
         <v>653</v>
       </c>
       <c r="R132" s="5">
@@ -16077,7 +15998,7 @@
         <v>71</v>
       </c>
       <c r="J133" s="5">
-        <f t="shared" ref="J133:J196" si="7">SUM(E133:I133)</f>
+        <f>SUM(E133:I133)</f>
         <v>349</v>
       </c>
       <c r="K133" s="5">
@@ -16095,7 +16016,7 @@
       <c r="O133" s="5"/>
       <c r="P133" s="5"/>
       <c r="Q133" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J133/45)))</f>
         <v>452</v>
       </c>
       <c r="R133" s="5">
@@ -16149,7 +16070,7 @@
         <v>73</v>
       </c>
       <c r="J134" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E134:I134)</f>
         <v>339</v>
       </c>
       <c r="K134" s="5">
@@ -16167,7 +16088,7 @@
       <c r="O134" s="5"/>
       <c r="P134" s="5"/>
       <c r="Q134" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J134/45)))</f>
         <v>379</v>
       </c>
       <c r="R134" s="5">
@@ -16221,7 +16142,7 @@
         <v>53</v>
       </c>
       <c r="J135" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E135:I135)</f>
         <v>253</v>
       </c>
       <c r="K135" s="5">
@@ -16239,7 +16160,7 @@
       <c r="O135" s="5"/>
       <c r="P135" s="5"/>
       <c r="Q135" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J135/45)))</f>
         <v>84</v>
       </c>
       <c r="R135" s="5">
@@ -16293,7 +16214,7 @@
         <v>59</v>
       </c>
       <c r="J136" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E136:I136)</f>
         <v>251</v>
       </c>
       <c r="K136" s="5">
@@ -16311,7 +16232,7 @@
       <c r="O136" s="5"/>
       <c r="P136" s="5"/>
       <c r="Q136" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J136/45)))</f>
         <v>81</v>
       </c>
       <c r="R136" s="5">
@@ -16365,7 +16286,7 @@
         <v>42</v>
       </c>
       <c r="J137" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E137:I137)</f>
         <v>180</v>
       </c>
       <c r="K137" s="5">
@@ -16383,7 +16304,7 @@
       <c r="O137" s="5"/>
       <c r="P137" s="5"/>
       <c r="Q137" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J137/45)))</f>
         <v>25</v>
       </c>
       <c r="R137" s="5">
@@ -16437,7 +16358,7 @@
         <v>81</v>
       </c>
       <c r="J138" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E138:I138)</f>
         <v>274</v>
       </c>
       <c r="K138" s="5">
@@ -16455,7 +16376,7 @@
       <c r="O138" s="5"/>
       <c r="P138" s="5"/>
       <c r="Q138" s="5">
-        <f t="shared" si="6"/>
+        <f>MAX(25, INT(POWER(2.2,J138/45)))</f>
         <v>121</v>
       </c>
       <c r="R138" s="5">
@@ -16509,7 +16430,7 @@
         <v>90</v>
       </c>
       <c r="J139" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E139:I139)</f>
         <v>392</v>
       </c>
       <c r="K139" s="5">
@@ -16580,7 +16501,7 @@
         <v>70</v>
       </c>
       <c r="J140" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E140:I140)</f>
         <v>374</v>
       </c>
       <c r="K140" s="5">
@@ -16598,7 +16519,7 @@
       <c r="O140" s="5"/>
       <c r="P140" s="5"/>
       <c r="Q140" s="5">
-        <f t="shared" ref="Q140:Q173" si="8">MAX(25, INT(POWER(2.2,J140/45)))</f>
+        <f>MAX(25, INT(POWER(2.2,J140/45)))</f>
         <v>701</v>
       </c>
       <c r="R140" s="5">
@@ -16654,7 +16575,7 @@
         <v>53</v>
       </c>
       <c r="J141" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E141:I141)</f>
         <v>298</v>
       </c>
       <c r="K141" s="5">
@@ -16672,7 +16593,7 @@
       <c r="O141" s="5"/>
       <c r="P141" s="5"/>
       <c r="Q141" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J141/45)))</f>
         <v>185</v>
       </c>
       <c r="R141" s="5">
@@ -16728,7 +16649,7 @@
         <v>68</v>
       </c>
       <c r="J142" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E142:I142)</f>
         <v>339</v>
       </c>
       <c r="K142" s="5">
@@ -16746,7 +16667,7 @@
       <c r="O142" s="5"/>
       <c r="P142" s="5"/>
       <c r="Q142" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J142/45)))</f>
         <v>379</v>
       </c>
       <c r="R142" s="5">
@@ -16802,7 +16723,7 @@
         <v>64</v>
       </c>
       <c r="J143" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E143:I143)</f>
         <v>351</v>
       </c>
       <c r="K143" s="5">
@@ -16817,12 +16738,12 @@
       <c r="N143" s="5">
         <v>17</v>
       </c>
-      <c r="O143" s="5">
-        <v>15</v>
+      <c r="O143">
+        <v>30</v>
       </c>
       <c r="P143" s="5"/>
       <c r="Q143" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J143/45)))</f>
         <v>468</v>
       </c>
       <c r="R143" s="5">
@@ -16878,7 +16799,7 @@
         <v>37</v>
       </c>
       <c r="J144" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E144:I144)</f>
         <v>260</v>
       </c>
       <c r="K144" s="5">
@@ -16893,14 +16814,14 @@
       <c r="N144" s="5">
         <v>17</v>
       </c>
-      <c r="O144" s="5">
-        <v>22</v>
+      <c r="O144">
+        <v>40</v>
       </c>
       <c r="P144" s="5">
         <v>1.5</v>
       </c>
       <c r="Q144" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J144/45)))</f>
         <v>95</v>
       </c>
       <c r="R144" s="5">
@@ -16954,7 +16875,7 @@
         <v>23</v>
       </c>
       <c r="J145" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E145:I145)</f>
         <v>228</v>
       </c>
       <c r="K145" s="5">
@@ -16969,12 +16890,12 @@
       <c r="N145" s="5">
         <v>17</v>
       </c>
-      <c r="O145" s="5">
-        <v>15</v>
+      <c r="O145">
+        <v>30</v>
       </c>
       <c r="P145" s="5"/>
       <c r="Q145" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J145/45)))</f>
         <v>54</v>
       </c>
       <c r="R145" s="5">
@@ -17030,7 +16951,7 @@
         <v>62</v>
       </c>
       <c r="J146" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E146:I146)</f>
         <v>341</v>
       </c>
       <c r="K146" s="5">
@@ -17048,7 +16969,7 @@
       <c r="O146" s="5"/>
       <c r="P146" s="5"/>
       <c r="Q146" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J146/45)))</f>
         <v>393</v>
       </c>
       <c r="R146" s="5">
@@ -17102,7 +17023,7 @@
         <v>74</v>
       </c>
       <c r="J147" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E147:I147)</f>
         <v>368</v>
       </c>
       <c r="K147" s="5">
@@ -17117,12 +17038,12 @@
       <c r="N147" s="5">
         <v>17</v>
       </c>
-      <c r="O147" s="5">
-        <v>15</v>
+      <c r="O147">
+        <v>30</v>
       </c>
       <c r="P147" s="5"/>
       <c r="Q147" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J147/45)))</f>
         <v>631</v>
       </c>
       <c r="R147" s="5">
@@ -17178,7 +17099,7 @@
         <v>37</v>
       </c>
       <c r="J148" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E148:I148)</f>
         <v>291</v>
       </c>
       <c r="K148" s="5">
@@ -17193,12 +17114,12 @@
       <c r="N148" s="5">
         <v>17</v>
       </c>
-      <c r="O148" s="5">
-        <v>15</v>
+      <c r="O148">
+        <v>30</v>
       </c>
       <c r="P148" s="5"/>
       <c r="Q148" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J148/45)))</f>
         <v>163</v>
       </c>
       <c r="R148" s="5">
@@ -17256,7 +17177,7 @@
         <v>39</v>
       </c>
       <c r="J149" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E149:I149)</f>
         <v>241</v>
       </c>
       <c r="K149" s="5">
@@ -17274,7 +17195,7 @@
       <c r="O149" s="5"/>
       <c r="P149" s="5"/>
       <c r="Q149" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J149/45)))</f>
         <v>68</v>
       </c>
       <c r="R149" s="5">
@@ -17328,7 +17249,7 @@
         <v>28</v>
       </c>
       <c r="J150" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E150:I150)</f>
         <v>184</v>
       </c>
       <c r="K150" s="5">
@@ -17346,7 +17267,7 @@
       <c r="O150" s="5"/>
       <c r="P150" s="5"/>
       <c r="Q150" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J150/45)))</f>
         <v>25</v>
       </c>
       <c r="R150" s="5">
@@ -17400,7 +17321,7 @@
         <v>29</v>
       </c>
       <c r="J151" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E151:I151)</f>
         <v>190</v>
       </c>
       <c r="K151" s="5">
@@ -17418,7 +17339,7 @@
       <c r="O151" s="5"/>
       <c r="P151" s="5"/>
       <c r="Q151" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J151/45)))</f>
         <v>27</v>
       </c>
       <c r="R151" s="5">
@@ -17472,7 +17393,7 @@
         <v>33</v>
       </c>
       <c r="J152" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E152:I152)</f>
         <v>235</v>
       </c>
       <c r="K152" s="5">
@@ -17490,7 +17411,7 @@
       <c r="O152" s="5"/>
       <c r="P152" s="5"/>
       <c r="Q152" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J152/45)))</f>
         <v>61</v>
       </c>
       <c r="R152" s="5">
@@ -17544,7 +17465,7 @@
         <v>49</v>
       </c>
       <c r="J153" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E153:I153)</f>
         <v>246</v>
       </c>
       <c r="K153" s="5">
@@ -17562,7 +17483,7 @@
       <c r="O153" s="5"/>
       <c r="P153" s="5"/>
       <c r="Q153" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J153/45)))</f>
         <v>74</v>
       </c>
       <c r="R153" s="5">
@@ -17616,7 +17537,7 @@
         <v>71</v>
       </c>
       <c r="J154" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E154:I154)</f>
         <v>352</v>
       </c>
       <c r="K154" s="5">
@@ -17634,7 +17555,7 @@
       <c r="O154" s="5"/>
       <c r="P154" s="5"/>
       <c r="Q154" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J154/45)))</f>
         <v>476</v>
       </c>
       <c r="R154" s="5">
@@ -17688,7 +17609,7 @@
         <v>66</v>
       </c>
       <c r="J155" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E155:I155)</f>
         <v>264</v>
       </c>
       <c r="K155" s="5">
@@ -17706,7 +17627,7 @@
       <c r="O155" s="5"/>
       <c r="P155" s="5"/>
       <c r="Q155" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J155/45)))</f>
         <v>102</v>
       </c>
       <c r="R155" s="5">
@@ -17760,7 +17681,7 @@
         <v>56</v>
       </c>
       <c r="J156" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E156:I156)</f>
         <v>240</v>
       </c>
       <c r="K156" s="5">
@@ -17778,7 +17699,7 @@
       <c r="O156" s="5"/>
       <c r="P156" s="5"/>
       <c r="Q156" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J156/45)))</f>
         <v>67</v>
       </c>
       <c r="R156" s="5">
@@ -17832,7 +17753,7 @@
         <v>62</v>
       </c>
       <c r="J157" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E157:I157)</f>
         <v>313</v>
       </c>
       <c r="K157" s="5">
@@ -17850,7 +17771,7 @@
       <c r="O157" s="5"/>
       <c r="P157" s="5"/>
       <c r="Q157" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J157/45)))</f>
         <v>240</v>
       </c>
       <c r="R157" s="5">
@@ -17904,7 +17825,7 @@
         <v>72</v>
       </c>
       <c r="J158" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E158:I158)</f>
         <v>345</v>
       </c>
       <c r="K158" s="5">
@@ -17922,7 +17843,7 @@
       <c r="O158" s="5"/>
       <c r="P158" s="5"/>
       <c r="Q158" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J158/45)))</f>
         <v>421</v>
       </c>
       <c r="R158" s="5">
@@ -17976,7 +17897,7 @@
         <v>35</v>
       </c>
       <c r="J159" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E159:I159)</f>
         <v>225</v>
       </c>
       <c r="K159" s="5">
@@ -17994,7 +17915,7 @@
       <c r="O159" s="5"/>
       <c r="P159" s="5"/>
       <c r="Q159" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J159/45)))</f>
         <v>51</v>
       </c>
       <c r="R159" s="5">
@@ -18048,7 +17969,7 @@
         <v>44</v>
       </c>
       <c r="J160" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E160:I160)</f>
         <v>233</v>
       </c>
       <c r="K160" s="5">
@@ -18066,7 +17987,7 @@
       <c r="O160" s="5"/>
       <c r="P160" s="5"/>
       <c r="Q160" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J160/45)))</f>
         <v>59</v>
       </c>
       <c r="R160" s="5">
@@ -18120,7 +18041,7 @@
         <v>70</v>
       </c>
       <c r="J161" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E161:I161)</f>
         <v>370</v>
       </c>
       <c r="K161" s="5">
@@ -18138,7 +18059,7 @@
       <c r="O161" s="5"/>
       <c r="P161" s="5"/>
       <c r="Q161" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J161/45)))</f>
         <v>653</v>
       </c>
       <c r="R161" s="5">
@@ -18192,7 +18113,7 @@
         <v>52</v>
       </c>
       <c r="J162" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E162:I162)</f>
         <v>259</v>
       </c>
       <c r="K162" s="5">
@@ -18210,7 +18131,7 @@
       <c r="O162" s="5"/>
       <c r="P162" s="5"/>
       <c r="Q162" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J162/45)))</f>
         <v>93</v>
       </c>
       <c r="R162" s="5">
@@ -18264,7 +18185,7 @@
         <v>49</v>
       </c>
       <c r="J163" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E163:I163)</f>
         <v>248</v>
       </c>
       <c r="K163" s="5">
@@ -18282,7 +18203,7 @@
       <c r="O163" s="5"/>
       <c r="P163" s="5"/>
       <c r="Q163" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J163/45)))</f>
         <v>77</v>
       </c>
       <c r="R163" s="5">
@@ -18336,7 +18257,7 @@
         <v>55</v>
       </c>
       <c r="J164" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E164:I164)</f>
         <v>292</v>
       </c>
       <c r="K164" s="5">
@@ -18354,7 +18275,7 @@
       <c r="O164" s="5"/>
       <c r="P164" s="5"/>
       <c r="Q164" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J164/45)))</f>
         <v>166</v>
       </c>
       <c r="R164" s="5">
@@ -18408,7 +18329,7 @@
         <v>64</v>
       </c>
       <c r="J165" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E165:I165)</f>
         <v>294</v>
       </c>
       <c r="K165" s="5">
@@ -18426,7 +18347,7 @@
       <c r="O165" s="5"/>
       <c r="P165" s="5"/>
       <c r="Q165" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J165/45)))</f>
         <v>172</v>
       </c>
       <c r="R165" s="5">
@@ -18480,7 +18401,7 @@
         <v>60</v>
       </c>
       <c r="J166" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E166:I166)</f>
         <v>289</v>
       </c>
       <c r="K166" s="5">
@@ -18498,7 +18419,7 @@
       <c r="O166" s="5"/>
       <c r="P166" s="5"/>
       <c r="Q166" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J166/45)))</f>
         <v>158</v>
       </c>
       <c r="R166" s="5">
@@ -18556,7 +18477,7 @@
         <v>70</v>
       </c>
       <c r="J167" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E167:I167)</f>
         <v>296</v>
       </c>
       <c r="K167" s="5">
@@ -18574,7 +18495,7 @@
       <c r="O167" s="5"/>
       <c r="P167" s="5"/>
       <c r="Q167" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J167/45)))</f>
         <v>178</v>
       </c>
       <c r="R167" s="5">
@@ -18632,7 +18553,7 @@
         <v>68</v>
       </c>
       <c r="J168" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E168:I168)</f>
         <v>331</v>
       </c>
       <c r="K168" s="5">
@@ -18650,7 +18571,7 @@
       <c r="O168" s="5"/>
       <c r="P168" s="5"/>
       <c r="Q168" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J168/45)))</f>
         <v>330</v>
       </c>
       <c r="R168" s="5">
@@ -18708,7 +18629,7 @@
         <v>70</v>
       </c>
       <c r="J169" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E169:I169)</f>
         <v>306</v>
       </c>
       <c r="K169" s="5">
@@ -18726,7 +18647,7 @@
       <c r="O169" s="5"/>
       <c r="P169" s="5"/>
       <c r="Q169" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J169/45)))</f>
         <v>213</v>
       </c>
       <c r="R169" s="5">
@@ -18784,7 +18705,7 @@
         <v>64</v>
       </c>
       <c r="J170" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E170:I170)</f>
         <v>264</v>
       </c>
       <c r="K170" s="5">
@@ -18802,7 +18723,7 @@
       <c r="O170" s="5"/>
       <c r="P170" s="5"/>
       <c r="Q170" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J170/45)))</f>
         <v>102</v>
       </c>
       <c r="R170" s="5">
@@ -18860,7 +18781,7 @@
         <v>69</v>
       </c>
       <c r="J171" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E171:I171)</f>
         <v>281</v>
       </c>
       <c r="K171" s="5">
@@ -18878,7 +18799,7 @@
       <c r="O171" s="5"/>
       <c r="P171" s="5"/>
       <c r="Q171" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J171/45)))</f>
         <v>137</v>
       </c>
       <c r="R171" s="5">
@@ -18936,7 +18857,7 @@
         <v>39</v>
       </c>
       <c r="J172" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E172:I172)</f>
         <v>243</v>
       </c>
       <c r="K172" s="5">
@@ -18954,7 +18875,7 @@
       <c r="O172" s="5"/>
       <c r="P172" s="5"/>
       <c r="Q172" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J172/45)))</f>
         <v>70</v>
       </c>
       <c r="R172" s="5">
@@ -19012,7 +18933,7 @@
         <v>72</v>
       </c>
       <c r="J173" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E173:I173)</f>
         <v>244</v>
       </c>
       <c r="K173" s="5">
@@ -19030,7 +18951,7 @@
       <c r="O173" s="5"/>
       <c r="P173" s="5"/>
       <c r="Q173" s="5">
-        <f t="shared" si="8"/>
+        <f>MAX(25, INT(POWER(2.2,J173/45)))</f>
         <v>71</v>
       </c>
       <c r="R173" s="5">
@@ -19088,7 +19009,7 @@
         <v>36</v>
       </c>
       <c r="J174" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E174:I174)</f>
         <v>285</v>
       </c>
       <c r="K174" s="5">
@@ -19163,7 +19084,7 @@
         <v>76</v>
       </c>
       <c r="J175" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E175:I175)</f>
         <v>397</v>
       </c>
       <c r="K175" s="5">
@@ -19181,7 +19102,7 @@
       <c r="O175" s="5"/>
       <c r="P175" s="5"/>
       <c r="Q175" s="5">
-        <f t="shared" ref="Q175:Q219" si="9">MAX(25, INT(POWER(2.2,J175/45)))</f>
+        <f>MAX(25, INT(POWER(2.2,J175/45)))</f>
         <v>1049</v>
       </c>
       <c r="R175" s="5">
@@ -19241,7 +19162,7 @@
         <v>40</v>
       </c>
       <c r="J176" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E176:I176)</f>
         <v>270</v>
       </c>
       <c r="K176" s="5">
@@ -19259,7 +19180,7 @@
       <c r="O176" s="5"/>
       <c r="P176" s="5"/>
       <c r="Q176" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J176/45)))</f>
         <v>113</v>
       </c>
       <c r="R176" s="5">
@@ -19321,7 +19242,7 @@
         <v>57</v>
       </c>
       <c r="J177" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E177:I177)</f>
         <v>325</v>
       </c>
       <c r="K177" s="5">
@@ -19339,7 +19260,7 @@
       <c r="O177" s="5"/>
       <c r="P177" s="5"/>
       <c r="Q177" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J177/45)))</f>
         <v>297</v>
       </c>
       <c r="R177" s="5">
@@ -19399,7 +19320,7 @@
         <v>57</v>
       </c>
       <c r="J178" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E178:I178)</f>
         <v>375</v>
       </c>
       <c r="K178" s="5">
@@ -19414,12 +19335,12 @@
       <c r="N178" s="5">
         <v>17</v>
       </c>
-      <c r="O178" s="5">
-        <v>15</v>
+      <c r="O178">
+        <v>30</v>
       </c>
       <c r="P178" s="5"/>
       <c r="Q178" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J178/45)))</f>
         <v>713</v>
       </c>
       <c r="R178" s="5">
@@ -19479,7 +19400,7 @@
         <v>95</v>
       </c>
       <c r="J179" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E179:I179)</f>
         <v>338</v>
       </c>
       <c r="K179" s="5">
@@ -19494,12 +19415,12 @@
       <c r="N179" s="5">
         <v>17</v>
       </c>
-      <c r="O179" s="5">
-        <v>15</v>
+      <c r="O179">
+        <v>30</v>
       </c>
       <c r="P179" s="5"/>
       <c r="Q179" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J179/45)))</f>
         <v>373</v>
       </c>
       <c r="R179" s="5">
@@ -19559,7 +19480,7 @@
         <v>71</v>
       </c>
       <c r="J180" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E180:I180)</f>
         <v>333</v>
       </c>
       <c r="K180" s="5">
@@ -19577,7 +19498,7 @@
       <c r="O180" s="5"/>
       <c r="P180" s="5"/>
       <c r="Q180" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J180/45)))</f>
         <v>341</v>
       </c>
       <c r="R180" s="5">
@@ -19637,7 +19558,7 @@
         <v>68</v>
       </c>
       <c r="J181" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E181:I181)</f>
         <v>338</v>
       </c>
       <c r="K181" s="5">
@@ -19652,14 +19573,14 @@
       <c r="N181" s="5">
         <v>17</v>
       </c>
-      <c r="O181" s="5">
-        <v>13</v>
+      <c r="O181">
+        <v>26</v>
       </c>
       <c r="P181" s="5">
         <v>2.5</v>
       </c>
       <c r="Q181" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J181/45)))</f>
         <v>373</v>
       </c>
       <c r="R181" s="5">
@@ -19717,7 +19638,7 @@
         <v>38</v>
       </c>
       <c r="J182" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E182:I182)</f>
         <v>313</v>
       </c>
       <c r="K182" s="5">
@@ -19732,12 +19653,12 @@
       <c r="N182" s="5">
         <v>17</v>
       </c>
-      <c r="O182" s="5">
-        <v>15</v>
+      <c r="O182">
+        <v>30</v>
       </c>
       <c r="P182" s="5"/>
       <c r="Q182" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J182/45)))</f>
         <v>240</v>
       </c>
       <c r="R182" s="5">
@@ -19797,7 +19718,7 @@
         <v>17</v>
       </c>
       <c r="J183" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E183:I183)</f>
         <v>185</v>
       </c>
       <c r="K183" s="5">
@@ -19815,7 +19736,7 @@
       <c r="O183" s="5"/>
       <c r="P183" s="5"/>
       <c r="Q183" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J183/45)))</f>
         <v>25</v>
       </c>
       <c r="R183" s="5">
@@ -19875,7 +19796,7 @@
         <v>13</v>
       </c>
       <c r="J184" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E184:I184)</f>
         <v>180</v>
       </c>
       <c r="K184" s="5">
@@ -19893,7 +19814,7 @@
       <c r="O184" s="5"/>
       <c r="P184" s="5"/>
       <c r="Q184" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J184/45)))</f>
         <v>25</v>
       </c>
       <c r="R184" s="5">
@@ -19952,7 +19873,7 @@
         <v>70</v>
       </c>
       <c r="J185" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E185:I185)</f>
         <v>380</v>
       </c>
       <c r="K185" s="5">
@@ -19967,12 +19888,12 @@
       <c r="N185" s="5">
         <v>17</v>
       </c>
-      <c r="O185" s="5">
-        <v>15</v>
+      <c r="O185">
+        <v>30</v>
       </c>
       <c r="P185" s="5"/>
       <c r="Q185" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J185/45)))</f>
         <v>779</v>
       </c>
       <c r="R185" s="5">
@@ -20034,7 +19955,7 @@
         <v>29</v>
       </c>
       <c r="J186" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E186:I186)</f>
         <v>175</v>
       </c>
       <c r="K186" s="5">
@@ -20052,7 +19973,7 @@
       <c r="O186" s="5"/>
       <c r="P186" s="5"/>
       <c r="Q186" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J186/45)))</f>
         <v>25</v>
       </c>
       <c r="R186" s="5">
@@ -20110,7 +20031,7 @@
         <v>39</v>
       </c>
       <c r="J187" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E187:I187)</f>
         <v>247</v>
       </c>
       <c r="K187" s="5">
@@ -20128,7 +20049,7 @@
       <c r="O187" s="5"/>
       <c r="P187" s="5"/>
       <c r="Q187" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J187/45)))</f>
         <v>75</v>
       </c>
       <c r="R187" s="5">
@@ -20182,7 +20103,7 @@
         <v>31</v>
       </c>
       <c r="J188" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E188:I188)</f>
         <v>241</v>
       </c>
       <c r="K188" s="5">
@@ -20200,7 +20121,7 @@
       <c r="O188" s="5"/>
       <c r="P188" s="5"/>
       <c r="Q188" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J188/45)))</f>
         <v>68</v>
       </c>
       <c r="R188" s="5">
@@ -20254,7 +20175,7 @@
         <v>42</v>
       </c>
       <c r="J189" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E189:I189)</f>
         <v>298</v>
       </c>
       <c r="K189" s="5">
@@ -20272,7 +20193,7 @@
       <c r="O189" s="5"/>
       <c r="P189" s="5"/>
       <c r="Q189" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J189/45)))</f>
         <v>185</v>
       </c>
       <c r="R189" s="5">
@@ -20326,7 +20247,7 @@
         <v>60</v>
       </c>
       <c r="J190" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E190:I190)</f>
         <v>328</v>
       </c>
       <c r="K190" s="5">
@@ -20344,7 +20265,7 @@
       <c r="O190" s="5"/>
       <c r="P190" s="5"/>
       <c r="Q190" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J190/45)))</f>
         <v>313</v>
       </c>
       <c r="R190" s="5">
@@ -20398,7 +20319,7 @@
         <v>21</v>
       </c>
       <c r="J191" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E191:I191)</f>
         <v>187</v>
       </c>
       <c r="K191" s="5">
@@ -20416,7 +20337,7 @@
       <c r="O191" s="5"/>
       <c r="P191" s="5"/>
       <c r="Q191" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J191/45)))</f>
         <v>26</v>
       </c>
       <c r="R191" s="5">
@@ -20470,7 +20391,7 @@
         <v>59</v>
       </c>
       <c r="J192" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E192:I192)</f>
         <v>317</v>
       </c>
       <c r="K192" s="5">
@@ -20488,7 +20409,7 @@
       <c r="O192" s="5"/>
       <c r="P192" s="5"/>
       <c r="Q192" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J192/45)))</f>
         <v>258</v>
       </c>
       <c r="R192" s="5">
@@ -20542,7 +20463,7 @@
         <v>39</v>
       </c>
       <c r="J193" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E193:I193)</f>
         <v>233</v>
       </c>
       <c r="K193" s="5">
@@ -20560,7 +20481,7 @@
       <c r="O193" s="5"/>
       <c r="P193" s="5"/>
       <c r="Q193" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J193/45)))</f>
         <v>59</v>
       </c>
       <c r="R193" s="5">
@@ -20614,7 +20535,7 @@
         <v>38</v>
       </c>
       <c r="J194" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E194:I194)</f>
         <v>227</v>
       </c>
       <c r="K194" s="5">
@@ -20632,7 +20553,7 @@
       <c r="O194" s="5"/>
       <c r="P194" s="5"/>
       <c r="Q194" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J194/45)))</f>
         <v>53</v>
       </c>
       <c r="R194" s="5">
@@ -20686,7 +20607,7 @@
         <v>36</v>
       </c>
       <c r="J195" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E195:I195)</f>
         <v>225</v>
       </c>
       <c r="K195" s="5">
@@ -20704,7 +20625,7 @@
       <c r="O195" s="5"/>
       <c r="P195" s="5"/>
       <c r="Q195" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J195/45)))</f>
         <v>51</v>
       </c>
       <c r="R195" s="5">
@@ -20758,7 +20679,7 @@
         <v>54</v>
       </c>
       <c r="J196" s="5">
-        <f t="shared" si="7"/>
+        <f>SUM(E196:I196)</f>
         <v>291</v>
       </c>
       <c r="K196" s="5">
@@ -20776,7 +20697,7 @@
       <c r="O196" s="5"/>
       <c r="P196" s="5"/>
       <c r="Q196" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J196/45)))</f>
         <v>163</v>
       </c>
       <c r="R196" s="5">
@@ -20830,7 +20751,7 @@
         <v>73</v>
       </c>
       <c r="J197" s="5">
-        <f t="shared" ref="J197:J260" si="10">SUM(E197:I197)</f>
+        <f>SUM(E197:I197)</f>
         <v>360</v>
       </c>
       <c r="K197" s="5">
@@ -20848,7 +20769,7 @@
       <c r="O197" s="5"/>
       <c r="P197" s="5"/>
       <c r="Q197" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J197/45)))</f>
         <v>548</v>
       </c>
       <c r="R197" s="5">
@@ -20902,7 +20823,7 @@
         <v>58</v>
       </c>
       <c r="J198" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E198:I198)</f>
         <v>234</v>
       </c>
       <c r="K198" s="5">
@@ -20920,7 +20841,7 @@
       <c r="O198" s="5"/>
       <c r="P198" s="5"/>
       <c r="Q198" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J198/45)))</f>
         <v>60</v>
       </c>
       <c r="R198" s="5">
@@ -20974,7 +20895,7 @@
         <v>37</v>
       </c>
       <c r="J199" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E199:I199)</f>
         <v>182</v>
       </c>
       <c r="K199" s="5">
@@ -20992,7 +20913,7 @@
       <c r="O199" s="5"/>
       <c r="P199" s="5"/>
       <c r="Q199" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J199/45)))</f>
         <v>25</v>
       </c>
       <c r="R199" s="5">
@@ -21046,7 +20967,7 @@
         <v>23</v>
       </c>
       <c r="J200" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E200:I200)</f>
         <v>169</v>
       </c>
       <c r="K200" s="5">
@@ -21064,7 +20985,7 @@
       <c r="O200" s="5"/>
       <c r="P200" s="5"/>
       <c r="Q200" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J200/45)))</f>
         <v>25</v>
       </c>
       <c r="R200" s="5">
@@ -21118,7 +21039,7 @@
         <v>69</v>
       </c>
       <c r="J201" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E201:I201)</f>
         <v>328</v>
       </c>
       <c r="K201" s="5">
@@ -21136,7 +21057,7 @@
       <c r="O201" s="5"/>
       <c r="P201" s="5"/>
       <c r="Q201" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J201/45)))</f>
         <v>313</v>
       </c>
       <c r="R201" s="5">
@@ -21190,7 +21111,7 @@
         <v>75</v>
       </c>
       <c r="J202" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E202:I202)</f>
         <v>312</v>
       </c>
       <c r="K202" s="5">
@@ -21208,7 +21129,7 @@
       <c r="O202" s="5"/>
       <c r="P202" s="5"/>
       <c r="Q202" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J202/45)))</f>
         <v>236</v>
       </c>
       <c r="R202" s="5">
@@ -21262,7 +21183,7 @@
         <v>17</v>
       </c>
       <c r="J203" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E203:I203)</f>
         <v>234</v>
       </c>
       <c r="K203" s="5">
@@ -21280,7 +21201,7 @@
       <c r="O203" s="5"/>
       <c r="P203" s="5"/>
       <c r="Q203" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J203/45)))</f>
         <v>60</v>
       </c>
       <c r="R203" s="5">
@@ -21334,7 +21255,7 @@
         <v>73</v>
       </c>
       <c r="J204" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E204:I204)</f>
         <v>253</v>
       </c>
       <c r="K204" s="5">
@@ -21352,7 +21273,7 @@
       <c r="O204" s="5"/>
       <c r="P204" s="5"/>
       <c r="Q204" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J204/45)))</f>
         <v>84</v>
       </c>
       <c r="R204" s="5">
@@ -21406,7 +21327,7 @@
         <v>88</v>
       </c>
       <c r="J205" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E205:I205)</f>
         <v>359</v>
       </c>
       <c r="K205" s="5">
@@ -21424,7 +21345,7 @@
       <c r="O205" s="5"/>
       <c r="P205" s="5"/>
       <c r="Q205" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J205/45)))</f>
         <v>539</v>
       </c>
       <c r="R205" s="5">
@@ -21478,7 +21399,7 @@
         <v>80</v>
       </c>
       <c r="J206" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E206:I206)</f>
         <v>336</v>
       </c>
       <c r="K206" s="5">
@@ -21496,7 +21417,7 @@
       <c r="O206" s="5"/>
       <c r="P206" s="5"/>
       <c r="Q206" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J206/45)))</f>
         <v>360</v>
       </c>
       <c r="R206" s="5">
@@ -21556,7 +21477,7 @@
         <v>71</v>
       </c>
       <c r="J207" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E207:I207)</f>
         <v>342</v>
       </c>
       <c r="K207" s="5">
@@ -21574,7 +21495,7 @@
       <c r="O207" s="5"/>
       <c r="P207" s="5"/>
       <c r="Q207" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J207/45)))</f>
         <v>400</v>
       </c>
       <c r="R207" s="5">
@@ -21636,7 +21557,7 @@
         <v>67</v>
       </c>
       <c r="J208" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E208:I208)</f>
         <v>360</v>
       </c>
       <c r="K208" s="5">
@@ -21654,7 +21575,7 @@
       <c r="O208" s="5"/>
       <c r="P208" s="5"/>
       <c r="Q208" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J208/45)))</f>
         <v>548</v>
       </c>
       <c r="R208" s="5">
@@ -21714,7 +21635,7 @@
         <v>65</v>
       </c>
       <c r="J209" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E209:I209)</f>
         <v>339</v>
       </c>
       <c r="K209" s="5">
@@ -21732,7 +21653,7 @@
       <c r="O209" s="5"/>
       <c r="P209" s="5"/>
       <c r="Q209" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J209/45)))</f>
         <v>379</v>
       </c>
       <c r="R209" s="5">
@@ -21790,7 +21711,7 @@
         <v>54</v>
       </c>
       <c r="J210" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E210:I210)</f>
         <v>283</v>
       </c>
       <c r="K210" s="5">
@@ -21808,7 +21729,7 @@
       <c r="O210" s="5"/>
       <c r="P210" s="5"/>
       <c r="Q210" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J210/45)))</f>
         <v>142</v>
       </c>
       <c r="R210" s="5">
@@ -21862,7 +21783,7 @@
         <v>49</v>
       </c>
       <c r="J211" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E211:I211)</f>
         <v>254</v>
       </c>
       <c r="K211" s="5">
@@ -21880,7 +21801,7 @@
       <c r="O211" s="5"/>
       <c r="P211" s="5"/>
       <c r="Q211" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J211/45)))</f>
         <v>85</v>
       </c>
       <c r="R211" s="5">
@@ -21934,7 +21855,7 @@
         <v>63</v>
       </c>
       <c r="J212" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E212:I212)</f>
         <v>278</v>
       </c>
       <c r="K212" s="5">
@@ -21952,7 +21873,7 @@
       <c r="O212" s="5"/>
       <c r="P212" s="5"/>
       <c r="Q212" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J212/45)))</f>
         <v>130</v>
       </c>
       <c r="R212" s="5">
@@ -22006,7 +21927,7 @@
         <v>35</v>
       </c>
       <c r="J213" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E213:I213)</f>
         <v>211</v>
       </c>
       <c r="K213" s="5">
@@ -22024,7 +21945,7 @@
       <c r="O213" s="5"/>
       <c r="P213" s="5"/>
       <c r="Q213" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J213/45)))</f>
         <v>40</v>
       </c>
       <c r="R213" s="5">
@@ -22078,7 +21999,7 @@
         <v>57</v>
       </c>
       <c r="J214" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E214:I214)</f>
         <v>279</v>
       </c>
       <c r="K214" s="5">
@@ -22096,7 +22017,7 @@
       <c r="O214" s="5"/>
       <c r="P214" s="5"/>
       <c r="Q214" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J214/45)))</f>
         <v>132</v>
       </c>
       <c r="R214" s="5">
@@ -22150,7 +22071,7 @@
         <v>25</v>
       </c>
       <c r="J215" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E215:I215)</f>
         <v>186</v>
       </c>
       <c r="K215" s="5">
@@ -22168,7 +22089,7 @@
       <c r="O215" s="5"/>
       <c r="P215" s="5"/>
       <c r="Q215" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J215/45)))</f>
         <v>26</v>
       </c>
       <c r="R215" s="5">
@@ -22222,7 +22143,7 @@
         <v>49</v>
       </c>
       <c r="J216" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E216:I216)</f>
         <v>261</v>
       </c>
       <c r="K216" s="5">
@@ -22240,7 +22161,7 @@
       <c r="O216" s="5"/>
       <c r="P216" s="5"/>
       <c r="Q216" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J216/45)))</f>
         <v>96</v>
       </c>
       <c r="R216" s="5">
@@ -22294,7 +22215,7 @@
         <v>40</v>
       </c>
       <c r="J217" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E217:I217)</f>
         <v>281</v>
       </c>
       <c r="K217" s="5">
@@ -22312,7 +22233,7 @@
       <c r="O217" s="5"/>
       <c r="P217" s="5"/>
       <c r="Q217" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J217/45)))</f>
         <v>137</v>
       </c>
       <c r="R217" s="5">
@@ -22366,7 +22287,7 @@
         <v>69</v>
       </c>
       <c r="J218" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E218:I218)</f>
         <v>344</v>
       </c>
       <c r="K218" s="5">
@@ -22384,7 +22305,7 @@
       <c r="O218" s="5"/>
       <c r="P218" s="5"/>
       <c r="Q218" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J218/45)))</f>
         <v>414</v>
       </c>
       <c r="R218" s="5">
@@ -22438,7 +22359,7 @@
         <v>80</v>
       </c>
       <c r="J219" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E219:I219)</f>
         <v>377</v>
       </c>
       <c r="K219" s="5">
@@ -22456,7 +22377,7 @@
       <c r="O219" s="5"/>
       <c r="P219" s="5"/>
       <c r="Q219" s="5">
-        <f t="shared" si="9"/>
+        <f>MAX(25, INT(POWER(2.2,J219/45)))</f>
         <v>739</v>
       </c>
       <c r="R219" s="5">
@@ -22512,7 +22433,7 @@
         <v>80</v>
       </c>
       <c r="J220" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E220:I220)</f>
         <v>306</v>
       </c>
       <c r="K220" s="5">
@@ -22587,7 +22508,7 @@
         <v>51</v>
       </c>
       <c r="J221" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E221:I221)</f>
         <v>343</v>
       </c>
       <c r="K221" s="5">
@@ -22605,7 +22526,7 @@
       <c r="O221" s="5"/>
       <c r="P221" s="5"/>
       <c r="Q221" s="5">
-        <f t="shared" ref="Q221:Q238" si="11">MAX(25, INT(POWER(2.2,J221/45)))</f>
+        <f>MAX(25, INT(POWER(2.2,J221/45)))</f>
         <v>407</v>
       </c>
       <c r="R221" s="5">
@@ -22667,7 +22588,7 @@
         <v>75</v>
       </c>
       <c r="J222" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E222:I222)</f>
         <v>372</v>
       </c>
       <c r="K222" s="5">
@@ -22682,14 +22603,14 @@
       <c r="N222" s="5">
         <v>17</v>
       </c>
-      <c r="O222" s="5">
-        <v>22</v>
+      <c r="O222">
+        <v>40</v>
       </c>
       <c r="P222" s="5">
         <v>1.5</v>
       </c>
       <c r="Q222" s="5">
-        <f t="shared" si="11"/>
+        <f>MAX(25, INT(POWER(2.2,J222/45)))</f>
         <v>677</v>
       </c>
       <c r="R222" s="5">
@@ -22751,7 +22672,7 @@
         <v>66</v>
       </c>
       <c r="J223" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E223:I223)</f>
         <v>307</v>
       </c>
       <c r="K223" s="5">
@@ -22769,7 +22690,7 @@
       <c r="O223" s="5"/>
       <c r="P223" s="5"/>
       <c r="Q223" s="5">
-        <f t="shared" si="11"/>
+        <f>MAX(25, INT(POWER(2.2,J223/45)))</f>
         <v>216</v>
       </c>
       <c r="R223" s="5">
@@ -22827,7 +22748,7 @@
         <v>52</v>
       </c>
       <c r="J224" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E224:I224)</f>
         <v>219</v>
       </c>
       <c r="K224" s="5">
@@ -22845,7 +22766,7 @@
       <c r="O224" s="5"/>
       <c r="P224" s="5"/>
       <c r="Q224" s="5">
-        <f t="shared" si="11"/>
+        <f>MAX(25, INT(POWER(2.2,J224/45)))</f>
         <v>46</v>
       </c>
       <c r="R224" s="5">
@@ -22903,7 +22824,7 @@
         <v>31</v>
       </c>
       <c r="J225" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E225:I225)</f>
         <v>258</v>
       </c>
       <c r="K225" s="5">
@@ -22921,7 +22842,7 @@
       <c r="O225" s="5"/>
       <c r="P225" s="5"/>
       <c r="Q225" s="5">
-        <f t="shared" si="11"/>
+        <f>MAX(25, INT(POWER(2.2,J225/45)))</f>
         <v>91</v>
       </c>
       <c r="R225" s="5">
@@ -22979,7 +22900,7 @@
         <v>61</v>
       </c>
       <c r="J226" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E226:I226)</f>
         <v>249</v>
       </c>
       <c r="K226" s="5">
@@ -22997,7 +22918,7 @@
       <c r="O226" s="5"/>
       <c r="P226" s="5"/>
       <c r="Q226" s="5">
-        <f t="shared" si="11"/>
+        <f>MAX(25, INT(POWER(2.2,J226/45)))</f>
         <v>78</v>
       </c>
       <c r="R226" s="5">
@@ -23051,7 +22972,7 @@
         <v>60</v>
       </c>
       <c r="J227" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E227:I227)</f>
         <v>308</v>
       </c>
       <c r="K227" s="5">
@@ -23069,7 +22990,7 @@
       <c r="O227" s="5"/>
       <c r="P227" s="5"/>
       <c r="Q227" s="5">
-        <f t="shared" si="11"/>
+        <f>MAX(25, INT(POWER(2.2,J227/45)))</f>
         <v>220</v>
       </c>
       <c r="R227" s="5">
@@ -23123,7 +23044,7 @@
         <v>54</v>
       </c>
       <c r="J228" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E228:I228)</f>
         <v>238</v>
       </c>
       <c r="K228" s="5">
@@ -23141,7 +23062,7 @@
       <c r="O228" s="5"/>
       <c r="P228" s="5"/>
       <c r="Q228" s="5">
-        <f t="shared" si="11"/>
+        <f>MAX(25, INT(POWER(2.2,J228/45)))</f>
         <v>64</v>
       </c>
       <c r="R228" s="5">
@@ -23195,7 +23116,7 @@
         <v>53</v>
       </c>
       <c r="J229" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E229:I229)</f>
         <v>282</v>
       </c>
       <c r="K229" s="5">
@@ -23213,7 +23134,7 @@
       <c r="O229" s="5"/>
       <c r="P229" s="5"/>
       <c r="Q229" s="5">
-        <f t="shared" si="11"/>
+        <f>MAX(25, INT(POWER(2.2,J229/45)))</f>
         <v>139</v>
       </c>
       <c r="R229" s="5">
@@ -23267,7 +23188,7 @@
         <v>84</v>
       </c>
       <c r="J230" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E230:I230)</f>
         <v>303</v>
       </c>
       <c r="K230" s="5">
@@ -23285,7 +23206,7 @@
       <c r="O230" s="5"/>
       <c r="P230" s="5"/>
       <c r="Q230" s="5">
-        <f t="shared" si="11"/>
+        <f>MAX(25, INT(POWER(2.2,J230/45)))</f>
         <v>202</v>
       </c>
       <c r="R230" s="5">
@@ -23339,7 +23260,7 @@
         <v>48</v>
       </c>
       <c r="J231" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E231:I231)</f>
         <v>285</v>
       </c>
       <c r="K231" s="5">
@@ -23357,7 +23278,7 @@
       <c r="O231" s="5"/>
       <c r="P231" s="5"/>
       <c r="Q231" s="5">
-        <f t="shared" si="11"/>
+        <f>MAX(25, INT(POWER(2.2,J231/45)))</f>
         <v>147</v>
       </c>
       <c r="R231" s="5">
@@ -23411,7 +23332,7 @@
         <v>71</v>
       </c>
       <c r="J232" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E232:I232)</f>
         <v>343</v>
       </c>
       <c r="K232" s="5">
@@ -23429,7 +23350,7 @@
       <c r="O232" s="5"/>
       <c r="P232" s="5"/>
       <c r="Q232" s="5">
-        <f t="shared" si="11"/>
+        <f>MAX(25, INT(POWER(2.2,J232/45)))</f>
         <v>407</v>
       </c>
       <c r="R232" s="5">
@@ -23483,7 +23404,7 @@
         <v>73</v>
       </c>
       <c r="J233" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E233:I233)</f>
         <v>318</v>
       </c>
       <c r="K233" s="5">
@@ -23501,7 +23422,7 @@
       <c r="O233" s="5"/>
       <c r="P233" s="5"/>
       <c r="Q233" s="5">
-        <f t="shared" si="11"/>
+        <f>MAX(25, INT(POWER(2.2,J233/45)))</f>
         <v>262</v>
       </c>
       <c r="R233" s="5">
@@ -23555,7 +23476,7 @@
         <v>69</v>
       </c>
       <c r="J234" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E234:I234)</f>
         <v>255</v>
       </c>
       <c r="K234" s="5">
@@ -23573,7 +23494,7 @@
       <c r="O234" s="5"/>
       <c r="P234" s="5"/>
       <c r="Q234" s="5">
-        <f t="shared" si="11"/>
+        <f>MAX(25, INT(POWER(2.2,J234/45)))</f>
         <v>87</v>
       </c>
       <c r="R234" s="5">
@@ -23627,7 +23548,7 @@
         <v>42</v>
       </c>
       <c r="J235" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E235:I235)</f>
         <v>155</v>
       </c>
       <c r="K235" s="5">
@@ -23645,7 +23566,7 @@
       <c r="O235" s="5"/>
       <c r="P235" s="5"/>
       <c r="Q235" s="5">
-        <f t="shared" si="11"/>
+        <f>MAX(25, INT(POWER(2.2,J235/45)))</f>
         <v>25</v>
       </c>
       <c r="R235" s="5">
@@ -23700,7 +23621,7 @@
         <v>66</v>
       </c>
       <c r="J236" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E236:I236)</f>
         <v>208</v>
       </c>
       <c r="K236" s="5">
@@ -23718,7 +23639,7 @@
       <c r="O236" s="5"/>
       <c r="P236" s="5"/>
       <c r="Q236" s="5">
-        <f t="shared" si="11"/>
+        <f>MAX(25, INT(POWER(2.2,J236/45)))</f>
         <v>38</v>
       </c>
       <c r="R236" s="5">
@@ -23772,7 +23693,7 @@
         <v>44</v>
       </c>
       <c r="J237" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E237:I237)</f>
         <v>157</v>
       </c>
       <c r="K237" s="5">
@@ -23790,7 +23711,7 @@
       <c r="O237" s="5"/>
       <c r="P237" s="5"/>
       <c r="Q237" s="5">
-        <f t="shared" si="11"/>
+        <f>MAX(25, INT(POWER(2.2,J237/45)))</f>
         <v>25</v>
       </c>
       <c r="R237" s="5">
@@ -23844,7 +23765,7 @@
         <v>62</v>
       </c>
       <c r="J238" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E238:I238)</f>
         <v>358</v>
       </c>
       <c r="K238" s="5">
@@ -23862,7 +23783,7 @@
       <c r="O238" s="5"/>
       <c r="P238" s="5"/>
       <c r="Q238" s="5">
-        <f t="shared" si="11"/>
+        <f>MAX(25, INT(POWER(2.2,J238/45)))</f>
         <v>529</v>
       </c>
       <c r="R238" s="5">
@@ -23916,7 +23837,7 @@
         <v>64</v>
       </c>
       <c r="J239" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E239:I239)</f>
         <v>128</v>
       </c>
       <c r="K239" s="5">
@@ -23987,7 +23908,7 @@
         <v>79</v>
       </c>
       <c r="J240" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E240:I240)</f>
         <v>374</v>
       </c>
       <c r="K240" s="5">
@@ -24005,7 +23926,7 @@
       <c r="O240" s="5"/>
       <c r="P240" s="5"/>
       <c r="Q240" s="5">
-        <f t="shared" ref="Q240:Q266" si="12">MAX(25, INT(POWER(2.2,J240/45)))</f>
+        <f>MAX(25, INT(POWER(2.2,J240/45)))</f>
         <v>701</v>
       </c>
       <c r="R240" s="5">
@@ -24061,7 +23982,7 @@
         <v>50</v>
       </c>
       <c r="J241" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E241:I241)</f>
         <v>358</v>
       </c>
       <c r="K241" s="5">
@@ -24079,7 +24000,7 @@
       <c r="O241" s="5"/>
       <c r="P241" s="5"/>
       <c r="Q241" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J241/45)))</f>
         <v>529</v>
       </c>
       <c r="R241" s="5">
@@ -24134,7 +24055,7 @@
         <v>19</v>
       </c>
       <c r="J242" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E242:I242)</f>
         <v>211</v>
       </c>
       <c r="K242" s="5">
@@ -24149,12 +24070,12 @@
       <c r="N242" s="5">
         <v>17</v>
       </c>
-      <c r="O242" s="5">
-        <v>15</v>
+      <c r="O242">
+        <v>30</v>
       </c>
       <c r="P242" s="5"/>
       <c r="Q242" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J242/45)))</f>
         <v>40</v>
       </c>
       <c r="R242" s="5">
@@ -24211,7 +24132,7 @@
         <v>79</v>
       </c>
       <c r="J243" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E243:I243)</f>
         <v>383</v>
       </c>
       <c r="K243" s="5">
@@ -24226,12 +24147,12 @@
       <c r="N243" s="5">
         <v>17</v>
       </c>
-      <c r="O243" s="5">
-        <v>15</v>
+      <c r="O243">
+        <v>30</v>
       </c>
       <c r="P243" s="5"/>
       <c r="Q243" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J243/45)))</f>
         <v>821</v>
       </c>
       <c r="R243" s="5">
@@ -24291,7 +24212,7 @@
         <v>75</v>
       </c>
       <c r="J244" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E244:I244)</f>
         <v>355</v>
       </c>
       <c r="K244" s="5">
@@ -24309,7 +24230,7 @@
       <c r="O244" s="5"/>
       <c r="P244" s="5"/>
       <c r="Q244" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J244/45)))</f>
         <v>502</v>
       </c>
       <c r="R244" s="5">
@@ -24369,7 +24290,7 @@
         <v>78</v>
       </c>
       <c r="J245" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E245:I245)</f>
         <v>333</v>
       </c>
       <c r="K245" s="5">
@@ -24387,7 +24308,7 @@
       <c r="O245" s="5"/>
       <c r="P245" s="5"/>
       <c r="Q245" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J245/45)))</f>
         <v>341</v>
       </c>
       <c r="R245" s="5">
@@ -24447,7 +24368,7 @@
         <v>55</v>
       </c>
       <c r="J246" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E246:I246)</f>
         <v>363</v>
       </c>
       <c r="K246" s="5">
@@ -24462,12 +24383,12 @@
       <c r="N246" s="5">
         <v>17</v>
       </c>
-      <c r="O246" s="5">
-        <v>15</v>
+      <c r="O246">
+        <v>30</v>
       </c>
       <c r="P246" s="5"/>
       <c r="Q246" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J246/45)))</f>
         <v>578</v>
       </c>
       <c r="R246" s="5">
@@ -24527,7 +24448,7 @@
         <v>78</v>
       </c>
       <c r="J247" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E247:I247)</f>
         <v>375</v>
       </c>
       <c r="K247" s="5">
@@ -24545,7 +24466,7 @@
       <c r="O247" s="5"/>
       <c r="P247" s="5"/>
       <c r="Q247" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J247/45)))</f>
         <v>713</v>
       </c>
       <c r="R247" s="5">
@@ -24601,7 +24522,7 @@
         <v>72</v>
       </c>
       <c r="J248" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E248:I248)</f>
         <v>361</v>
       </c>
       <c r="K248" s="5">
@@ -24616,14 +24537,14 @@
       <c r="N248" s="5">
         <v>17</v>
       </c>
-      <c r="O248" s="5">
-        <v>22</v>
+      <c r="O248">
+        <v>40</v>
       </c>
       <c r="P248" s="5">
         <v>1.5</v>
       </c>
       <c r="Q248" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J248/45)))</f>
         <v>558</v>
       </c>
       <c r="R248" s="5">
@@ -24679,7 +24600,7 @@
         <v>78</v>
       </c>
       <c r="J249" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E249:I249)</f>
         <v>382</v>
       </c>
       <c r="K249" s="5">
@@ -24697,7 +24618,7 @@
       <c r="O249" s="5"/>
       <c r="P249" s="5"/>
       <c r="Q249" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J249/45)))</f>
         <v>806</v>
       </c>
       <c r="R249" s="5">
@@ -24753,7 +24674,7 @@
         <v>76</v>
       </c>
       <c r="J250" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E250:I250)</f>
         <v>385</v>
       </c>
       <c r="K250" s="5">
@@ -24768,14 +24689,14 @@
       <c r="N250" s="5">
         <v>17</v>
       </c>
-      <c r="O250" s="5">
-        <v>22</v>
+      <c r="O250">
+        <v>40</v>
       </c>
       <c r="P250" s="5">
         <v>1.5</v>
       </c>
       <c r="Q250" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J250/45)))</f>
         <v>850</v>
       </c>
       <c r="R250" s="5">
@@ -24831,7 +24752,7 @@
         <v>53</v>
       </c>
       <c r="J251" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E251:I251)</f>
         <v>288</v>
       </c>
       <c r="K251" s="5">
@@ -24849,7 +24770,7 @@
       <c r="O251" s="5"/>
       <c r="P251" s="5"/>
       <c r="Q251" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J251/45)))</f>
         <v>155</v>
       </c>
       <c r="R251" s="5">
@@ -24903,7 +24824,7 @@
         <v>52</v>
       </c>
       <c r="J252" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E252:I252)</f>
         <v>305</v>
       </c>
       <c r="K252" s="5">
@@ -24921,7 +24842,7 @@
       <c r="O252" s="5"/>
       <c r="P252" s="5"/>
       <c r="Q252" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J252/45)))</f>
         <v>209</v>
       </c>
       <c r="R252" s="5">
@@ -24975,7 +24896,7 @@
         <v>53</v>
       </c>
       <c r="J253" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E253:I253)</f>
         <v>313</v>
       </c>
       <c r="K253" s="5">
@@ -24993,7 +24914,7 @@
       <c r="O253" s="5"/>
       <c r="P253" s="5"/>
       <c r="Q253" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J253/45)))</f>
         <v>240</v>
       </c>
       <c r="R253" s="5">
@@ -25047,7 +24968,7 @@
         <v>50</v>
       </c>
       <c r="J254" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E254:I254)</f>
         <v>263</v>
       </c>
       <c r="K254" s="5">
@@ -25065,7 +24986,7 @@
       <c r="O254" s="5"/>
       <c r="P254" s="5"/>
       <c r="Q254" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J254/45)))</f>
         <v>100</v>
       </c>
       <c r="R254" s="5">
@@ -25119,7 +25040,7 @@
         <v>55</v>
       </c>
       <c r="J255" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E255:I255)</f>
         <v>285</v>
       </c>
       <c r="K255" s="5">
@@ -25137,7 +25058,7 @@
       <c r="O255" s="5"/>
       <c r="P255" s="5"/>
       <c r="Q255" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J255/45)))</f>
         <v>147</v>
       </c>
       <c r="R255" s="5">
@@ -25191,7 +25112,7 @@
         <v>73</v>
       </c>
       <c r="J256" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E256:I256)</f>
         <v>334</v>
       </c>
       <c r="K256" s="5">
@@ -25209,7 +25130,7 @@
       <c r="O256" s="5"/>
       <c r="P256" s="5"/>
       <c r="Q256" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J256/45)))</f>
         <v>347</v>
       </c>
       <c r="R256" s="5">
@@ -25263,7 +25184,7 @@
         <v>76</v>
       </c>
       <c r="J257" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E257:I257)</f>
         <v>329</v>
       </c>
       <c r="K257" s="5">
@@ -25281,7 +25202,7 @@
       <c r="O257" s="5"/>
       <c r="P257" s="5"/>
       <c r="Q257" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J257/45)))</f>
         <v>318</v>
       </c>
       <c r="R257" s="5">
@@ -25335,7 +25256,7 @@
         <v>77</v>
       </c>
       <c r="J258" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E258:I258)</f>
         <v>371</v>
       </c>
       <c r="K258" s="5">
@@ -25353,7 +25274,7 @@
       <c r="O258" s="5"/>
       <c r="P258" s="5"/>
       <c r="Q258" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J258/45)))</f>
         <v>665</v>
       </c>
       <c r="R258" s="5">
@@ -25407,7 +25328,7 @@
         <v>66</v>
       </c>
       <c r="J259" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E259:I259)</f>
         <v>312</v>
       </c>
       <c r="K259" s="5">
@@ -25425,7 +25346,7 @@
       <c r="O259" s="5"/>
       <c r="P259" s="5"/>
       <c r="Q259" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J259/45)))</f>
         <v>236</v>
       </c>
       <c r="R259" s="5">
@@ -25479,7 +25400,7 @@
         <v>23</v>
       </c>
       <c r="J260" s="5">
-        <f t="shared" si="10"/>
+        <f>SUM(E260:I260)</f>
         <v>281</v>
       </c>
       <c r="K260" s="5">
@@ -25497,7 +25418,7 @@
       <c r="O260" s="5"/>
       <c r="P260" s="5"/>
       <c r="Q260" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J260/45)))</f>
         <v>137</v>
       </c>
       <c r="R260" s="5">
@@ -25551,7 +25472,7 @@
         <v>62</v>
       </c>
       <c r="J261" s="5">
-        <f t="shared" ref="J261:J324" si="13">SUM(E261:I261)</f>
+        <f>SUM(E261:I261)</f>
         <v>316</v>
       </c>
       <c r="K261" s="5">
@@ -25569,7 +25490,7 @@
       <c r="O261" s="5"/>
       <c r="P261" s="5"/>
       <c r="Q261" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J261/45)))</f>
         <v>253</v>
       </c>
       <c r="R261" s="5">
@@ -25623,7 +25544,7 @@
         <v>55</v>
       </c>
       <c r="J262" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E262:I262)</f>
         <v>247</v>
       </c>
       <c r="K262" s="5">
@@ -25641,7 +25562,7 @@
       <c r="O262" s="5"/>
       <c r="P262" s="5"/>
       <c r="Q262" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J262/45)))</f>
         <v>75</v>
       </c>
       <c r="R262" s="5">
@@ -25695,7 +25616,7 @@
         <v>73</v>
       </c>
       <c r="J263" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E263:I263)</f>
         <v>290</v>
       </c>
       <c r="K263" s="5">
@@ -25713,7 +25634,7 @@
       <c r="O263" s="5"/>
       <c r="P263" s="5"/>
       <c r="Q263" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J263/45)))</f>
         <v>160</v>
       </c>
       <c r="R263" s="5">
@@ -25771,7 +25692,7 @@
         <v>75</v>
       </c>
       <c r="J264" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E264:I264)</f>
         <v>244</v>
       </c>
       <c r="K264" s="5">
@@ -25789,7 +25710,7 @@
       <c r="O264" s="5"/>
       <c r="P264" s="5"/>
       <c r="Q264" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J264/45)))</f>
         <v>71</v>
       </c>
       <c r="R264" s="5">
@@ -25847,7 +25768,7 @@
         <v>66</v>
       </c>
       <c r="J265" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E265:I265)</f>
         <v>248</v>
       </c>
       <c r="K265" s="5">
@@ -25865,7 +25786,7 @@
       <c r="O265" s="5"/>
       <c r="P265" s="5"/>
       <c r="Q265" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J265/45)))</f>
         <v>77</v>
       </c>
       <c r="R265" s="5">
@@ -25923,7 +25844,7 @@
         <v>65</v>
       </c>
       <c r="J266" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E266:I266)</f>
         <v>212</v>
       </c>
       <c r="K266" s="5">
@@ -25941,7 +25862,7 @@
       <c r="O266" s="5"/>
       <c r="P266" s="5"/>
       <c r="Q266" s="5">
-        <f t="shared" si="12"/>
+        <f>MAX(25, INT(POWER(2.2,J266/45)))</f>
         <v>41</v>
       </c>
       <c r="R266" s="5">
@@ -25999,7 +25920,7 @@
         <v>75</v>
       </c>
       <c r="J267" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E267:I267)</f>
         <v>304</v>
       </c>
       <c r="K267" s="5">
@@ -26074,7 +25995,7 @@
         <v>58</v>
       </c>
       <c r="J268" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E268:I268)</f>
         <v>277</v>
       </c>
       <c r="K268" s="5">
@@ -26092,7 +26013,7 @@
       <c r="O268" s="5"/>
       <c r="P268" s="5"/>
       <c r="Q268" s="5">
-        <f t="shared" ref="Q268:Q304" si="14">MAX(25, INT(POWER(2.2,J268/45)))</f>
+        <f>MAX(25, INT(POWER(2.2,J268/45)))</f>
         <v>128</v>
       </c>
       <c r="R268" s="5">
@@ -26150,7 +26071,7 @@
         <v>54</v>
       </c>
       <c r="J269" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E269:I269)</f>
         <v>285</v>
       </c>
       <c r="K269" s="5">
@@ -26168,7 +26089,7 @@
       <c r="O269" s="5"/>
       <c r="P269" s="5"/>
       <c r="Q269" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J269/45)))</f>
         <v>147</v>
       </c>
       <c r="R269" s="5">
@@ -26226,7 +26147,7 @@
         <v>40</v>
       </c>
       <c r="J270" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E270:I270)</f>
         <v>243</v>
       </c>
       <c r="K270" s="5">
@@ -26244,7 +26165,7 @@
       <c r="O270" s="5"/>
       <c r="P270" s="5"/>
       <c r="Q270" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J270/45)))</f>
         <v>70</v>
       </c>
       <c r="R270" s="5">
@@ -26302,7 +26223,7 @@
         <v>4</v>
       </c>
       <c r="J271" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E271:I271)</f>
         <v>70</v>
       </c>
       <c r="K271" s="5">
@@ -26320,7 +26241,7 @@
       <c r="O271" s="5"/>
       <c r="P271" s="5"/>
       <c r="Q271" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J271/45)))</f>
         <v>25</v>
       </c>
       <c r="R271" s="5">
@@ -26378,7 +26299,7 @@
         <v>20</v>
       </c>
       <c r="J272" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E272:I272)</f>
         <v>148</v>
       </c>
       <c r="K272" s="5">
@@ -26396,7 +26317,7 @@
       <c r="O272" s="5"/>
       <c r="P272" s="5"/>
       <c r="Q272" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J272/45)))</f>
         <v>25</v>
       </c>
       <c r="R272" s="5">
@@ -26454,7 +26375,7 @@
         <v>70</v>
       </c>
       <c r="J273" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E273:I273)</f>
         <v>286</v>
       </c>
       <c r="K273" s="5">
@@ -26472,7 +26393,7 @@
       <c r="O273" s="5"/>
       <c r="P273" s="5"/>
       <c r="Q273" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J273/45)))</f>
         <v>150</v>
       </c>
       <c r="R273" s="5">
@@ -26530,7 +26451,7 @@
         <v>45</v>
       </c>
       <c r="J274" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E274:I274)</f>
         <v>302</v>
       </c>
       <c r="K274" s="5">
@@ -26548,7 +26469,7 @@
       <c r="O274" s="5"/>
       <c r="P274" s="5"/>
       <c r="Q274" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J274/45)))</f>
         <v>198</v>
       </c>
       <c r="R274" s="5">
@@ -26606,7 +26527,7 @@
         <v>47</v>
       </c>
       <c r="J275" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E275:I275)</f>
         <v>262</v>
       </c>
       <c r="K275" s="5">
@@ -26624,7 +26545,7 @@
       <c r="O275" s="5"/>
       <c r="P275" s="5"/>
       <c r="Q275" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J275/45)))</f>
         <v>98</v>
       </c>
       <c r="R275" s="5">
@@ -26678,7 +26599,7 @@
         <v>55</v>
       </c>
       <c r="J276" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E276:I276)</f>
         <v>315</v>
       </c>
       <c r="K276" s="5">
@@ -26696,7 +26617,7 @@
       <c r="O276" s="5"/>
       <c r="P276" s="5"/>
       <c r="Q276" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J276/45)))</f>
         <v>249</v>
       </c>
       <c r="R276" s="5">
@@ -26750,7 +26671,7 @@
         <v>46</v>
       </c>
       <c r="J277" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E277:I277)</f>
         <v>159</v>
       </c>
       <c r="K277" s="5">
@@ -26768,7 +26689,7 @@
       <c r="O277" s="5"/>
       <c r="P277" s="5"/>
       <c r="Q277" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J277/45)))</f>
         <v>25</v>
       </c>
       <c r="R277" s="5">
@@ -26822,7 +26743,7 @@
         <v>83</v>
       </c>
       <c r="J278" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E278:I278)</f>
         <v>277</v>
       </c>
       <c r="K278" s="5">
@@ -26840,7 +26761,7 @@
       <c r="O278" s="5"/>
       <c r="P278" s="5"/>
       <c r="Q278" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J278/45)))</f>
         <v>128</v>
       </c>
       <c r="R278" s="5">
@@ -26894,7 +26815,7 @@
         <v>49</v>
       </c>
       <c r="J279" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E279:I279)</f>
         <v>220</v>
       </c>
       <c r="K279" s="5">
@@ -26912,7 +26833,7 @@
       <c r="O279" s="5"/>
       <c r="P279" s="5"/>
       <c r="Q279" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J279/45)))</f>
         <v>47</v>
       </c>
       <c r="R279" s="5">
@@ -26966,7 +26887,7 @@
         <v>59</v>
       </c>
       <c r="J280" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E280:I280)</f>
         <v>279</v>
       </c>
       <c r="K280" s="5">
@@ -26984,7 +26905,7 @@
       <c r="O280" s="5"/>
       <c r="P280" s="5"/>
       <c r="Q280" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J280/45)))</f>
         <v>132</v>
       </c>
       <c r="R280" s="5">
@@ -27038,7 +26959,7 @@
         <v>46</v>
       </c>
       <c r="J281" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E281:I281)</f>
         <v>238</v>
       </c>
       <c r="K281" s="5">
@@ -27056,7 +26977,7 @@
       <c r="O281" s="5"/>
       <c r="P281" s="5"/>
       <c r="Q281" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J281/45)))</f>
         <v>64</v>
       </c>
       <c r="R281" s="5">
@@ -27114,7 +27035,7 @@
         <v>32</v>
       </c>
       <c r="J282" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E282:I282)</f>
         <v>246</v>
       </c>
       <c r="K282" s="5">
@@ -27132,7 +27053,7 @@
       <c r="O282" s="5"/>
       <c r="P282" s="5"/>
       <c r="Q282" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J282/45)))</f>
         <v>74</v>
       </c>
       <c r="R282" s="5">
@@ -27186,7 +27107,7 @@
         <v>38</v>
       </c>
       <c r="J283" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E283:I283)</f>
         <v>237</v>
       </c>
       <c r="K283" s="5">
@@ -27204,7 +27125,7 @@
       <c r="O283" s="5"/>
       <c r="P283" s="5"/>
       <c r="Q283" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J283/45)))</f>
         <v>63</v>
       </c>
       <c r="R283" s="5">
@@ -27258,7 +27179,7 @@
         <v>45</v>
       </c>
       <c r="J284" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E284:I284)</f>
         <v>216</v>
       </c>
       <c r="K284" s="5">
@@ -27276,7 +27197,7 @@
       <c r="O284" s="5"/>
       <c r="P284" s="5"/>
       <c r="Q284" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J284/45)))</f>
         <v>44</v>
       </c>
       <c r="R284" s="5">
@@ -27330,7 +27251,7 @@
         <v>15</v>
       </c>
       <c r="J285" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E285:I285)</f>
         <v>194</v>
       </c>
       <c r="K285" s="5">
@@ -27348,7 +27269,7 @@
       <c r="O285" s="5"/>
       <c r="P285" s="5"/>
       <c r="Q285" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J285/45)))</f>
         <v>29</v>
       </c>
       <c r="R285" s="5">
@@ -27402,7 +27323,7 @@
         <v>32</v>
       </c>
       <c r="J286" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E286:I286)</f>
         <v>193</v>
       </c>
       <c r="K286" s="5">
@@ -27420,7 +27341,7 @@
       <c r="O286" s="5"/>
       <c r="P286" s="5"/>
       <c r="Q286" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J286/45)))</f>
         <v>29</v>
       </c>
       <c r="R286" s="5">
@@ -27474,7 +27395,7 @@
         <v>53</v>
       </c>
       <c r="J287" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E287:I287)</f>
         <v>272</v>
       </c>
       <c r="K287" s="5">
@@ -27492,7 +27413,7 @@
       <c r="O287" s="5"/>
       <c r="P287" s="5"/>
       <c r="Q287" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J287/45)))</f>
         <v>117</v>
       </c>
       <c r="R287" s="5">
@@ -27546,7 +27467,7 @@
         <v>56</v>
       </c>
       <c r="J288" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E288:I288)</f>
         <v>262</v>
       </c>
       <c r="K288" s="5">
@@ -27564,7 +27485,7 @@
       <c r="O288" s="5"/>
       <c r="P288" s="5"/>
       <c r="Q288" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J288/45)))</f>
         <v>98</v>
       </c>
       <c r="R288" s="5">
@@ -27618,7 +27539,7 @@
         <v>51</v>
       </c>
       <c r="J289" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E289:I289)</f>
         <v>253</v>
       </c>
       <c r="K289" s="5">
@@ -27636,7 +27557,7 @@
       <c r="O289" s="5"/>
       <c r="P289" s="5"/>
       <c r="Q289" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J289/45)))</f>
         <v>84</v>
       </c>
       <c r="R289" s="5">
@@ -27690,7 +27611,7 @@
         <v>44</v>
       </c>
       <c r="J290" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E290:I290)</f>
         <v>218</v>
       </c>
       <c r="K290" s="5">
@@ -27708,7 +27629,7 @@
       <c r="O290" s="5"/>
       <c r="P290" s="5"/>
       <c r="Q290" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J290/45)))</f>
         <v>45</v>
       </c>
       <c r="R290" s="5">
@@ -27762,7 +27683,7 @@
         <v>62</v>
       </c>
       <c r="J291" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E291:I291)</f>
         <v>359</v>
       </c>
       <c r="K291" s="5">
@@ -27780,7 +27701,7 @@
       <c r="O291" s="5"/>
       <c r="P291" s="5"/>
       <c r="Q291" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J291/45)))</f>
         <v>539</v>
       </c>
       <c r="R291" s="5">
@@ -27834,7 +27755,7 @@
         <v>77</v>
       </c>
       <c r="J292" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E292:I292)</f>
         <v>362</v>
       </c>
       <c r="K292" s="5">
@@ -27852,7 +27773,7 @@
       <c r="O292" s="5"/>
       <c r="P292" s="5"/>
       <c r="Q292" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J292/45)))</f>
         <v>568</v>
       </c>
       <c r="R292" s="5">
@@ -27906,7 +27827,7 @@
         <v>61</v>
       </c>
       <c r="J293" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E293:I293)</f>
         <v>329</v>
       </c>
       <c r="K293" s="5">
@@ -27924,7 +27845,7 @@
       <c r="O293" s="5"/>
       <c r="P293" s="5"/>
       <c r="Q293" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J293/45)))</f>
         <v>318</v>
       </c>
       <c r="R293" s="5">
@@ -27978,7 +27899,7 @@
         <v>62</v>
       </c>
       <c r="J294" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E294:I294)</f>
         <v>293</v>
       </c>
       <c r="K294" s="5">
@@ -27996,7 +27917,7 @@
       <c r="O294" s="5"/>
       <c r="P294" s="5"/>
       <c r="Q294" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J294/45)))</f>
         <v>169</v>
       </c>
       <c r="R294" s="5">
@@ -28050,7 +27971,7 @@
         <v>49</v>
       </c>
       <c r="J295" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E295:I295)</f>
         <v>250</v>
       </c>
       <c r="K295" s="5">
@@ -28068,7 +27989,7 @@
       <c r="O295" s="5"/>
       <c r="P295" s="5"/>
       <c r="Q295" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J295/45)))</f>
         <v>79</v>
       </c>
       <c r="R295" s="5">
@@ -28122,7 +28043,7 @@
         <v>72</v>
       </c>
       <c r="J296" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E296:I296)</f>
         <v>370</v>
       </c>
       <c r="K296" s="5">
@@ -28140,7 +28061,7 @@
       <c r="O296" s="5"/>
       <c r="P296" s="5"/>
       <c r="Q296" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J296/45)))</f>
         <v>653</v>
       </c>
       <c r="R296" s="5">
@@ -28194,7 +28115,7 @@
         <v>63</v>
       </c>
       <c r="J297" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E297:I297)</f>
         <v>313</v>
       </c>
       <c r="K297" s="5">
@@ -28212,7 +28133,7 @@
       <c r="O297" s="5"/>
       <c r="P297" s="5"/>
       <c r="Q297" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J297/45)))</f>
         <v>240</v>
       </c>
       <c r="R297" s="5">
@@ -28266,7 +28187,7 @@
         <v>54</v>
       </c>
       <c r="J298" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E298:I298)</f>
         <v>285</v>
       </c>
       <c r="K298" s="5">
@@ -28284,7 +28205,7 @@
       <c r="O298" s="5"/>
       <c r="P298" s="5"/>
       <c r="Q298" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J298/45)))</f>
         <v>147</v>
       </c>
       <c r="R298" s="5">
@@ -28338,7 +28259,7 @@
         <v>38</v>
       </c>
       <c r="J299" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E299:I299)</f>
         <v>230</v>
       </c>
       <c r="K299" s="5">
@@ -28356,7 +28277,7 @@
       <c r="O299" s="5"/>
       <c r="P299" s="5"/>
       <c r="Q299" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J299/45)))</f>
         <v>56</v>
       </c>
       <c r="R299" s="5">
@@ -28414,7 +28335,7 @@
         <v>42</v>
       </c>
       <c r="J300" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E300:I300)</f>
         <v>267</v>
       </c>
       <c r="K300" s="5">
@@ -28432,7 +28353,7 @@
       <c r="O300" s="5"/>
       <c r="P300" s="5"/>
       <c r="Q300" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J300/45)))</f>
         <v>107</v>
       </c>
       <c r="R300" s="5">
@@ -28490,7 +28411,7 @@
         <v>81</v>
       </c>
       <c r="J301" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E301:I301)</f>
         <v>409</v>
       </c>
       <c r="K301" s="5">
@@ -28508,7 +28429,7 @@
       <c r="O301" s="5"/>
       <c r="P301" s="5"/>
       <c r="Q301" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J301/45)))</f>
         <v>1294</v>
       </c>
       <c r="R301" s="5">
@@ -28570,7 +28491,7 @@
         <v>55</v>
       </c>
       <c r="J302" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E302:I302)</f>
         <v>310</v>
       </c>
       <c r="K302" s="5">
@@ -28588,7 +28509,7 @@
       <c r="O302" s="5"/>
       <c r="P302" s="5"/>
       <c r="Q302" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J302/45)))</f>
         <v>228</v>
       </c>
       <c r="R302" s="5">
@@ -28646,7 +28567,7 @@
         <v>39</v>
       </c>
       <c r="J303" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E303:I303)</f>
         <v>213</v>
       </c>
       <c r="K303" s="5">
@@ -28664,7 +28585,7 @@
       <c r="O303" s="5"/>
       <c r="P303" s="5"/>
       <c r="Q303" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J303/45)))</f>
         <v>41</v>
       </c>
       <c r="R303" s="5">
@@ -28722,7 +28643,7 @@
         <v>53</v>
       </c>
       <c r="J304" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E304:I304)</f>
         <v>298</v>
       </c>
       <c r="K304" s="5">
@@ -28740,7 +28661,7 @@
       <c r="O304" s="5"/>
       <c r="P304" s="5"/>
       <c r="Q304" s="5">
-        <f t="shared" si="14"/>
+        <f>MAX(25, INT(POWER(2.2,J304/45)))</f>
         <v>185</v>
       </c>
       <c r="R304" s="5">
@@ -28798,7 +28719,7 @@
         <v>75</v>
       </c>
       <c r="J305" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E305:I305)</f>
         <v>365</v>
       </c>
       <c r="K305" s="5">
@@ -28871,7 +28792,7 @@
         <v>75</v>
       </c>
       <c r="J306" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E306:I306)</f>
         <v>433</v>
       </c>
       <c r="K306" s="5">
@@ -28887,7 +28808,7 @@
       <c r="O306" s="5"/>
       <c r="P306" s="5"/>
       <c r="Q306" s="5">
-        <f t="shared" ref="Q306:Q351" si="15">MAX(25, INT(POWER(2.2,J306/45)))</f>
+        <f>MAX(25, INT(POWER(2.2,J306/45)))</f>
         <v>1971</v>
       </c>
       <c r="R306" s="5">
@@ -28946,7 +28867,7 @@
         <v>70</v>
       </c>
       <c r="J307" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E307:I307)</f>
         <v>386</v>
       </c>
       <c r="K307" s="5">
@@ -28959,12 +28880,12 @@
       <c r="N307" s="5">
         <v>17</v>
       </c>
-      <c r="O307" s="5">
-        <v>18</v>
+      <c r="O307">
+        <v>36</v>
       </c>
       <c r="P307" s="5"/>
       <c r="Q307" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J307/45)))</f>
         <v>865</v>
       </c>
       <c r="R307" s="5">
@@ -29020,7 +28941,7 @@
         <v>65</v>
       </c>
       <c r="J308" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E308:I308)</f>
         <v>371</v>
       </c>
       <c r="K308" s="5">
@@ -29033,12 +28954,12 @@
       <c r="N308" s="5">
         <v>17</v>
       </c>
-      <c r="O308" s="5">
-        <v>18</v>
+      <c r="O308">
+        <v>36</v>
       </c>
       <c r="P308" s="5"/>
       <c r="Q308" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J308/45)))</f>
         <v>665</v>
       </c>
       <c r="R308" s="5">
@@ -29097,7 +29018,7 @@
         <v>92</v>
       </c>
       <c r="J309" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E309:I309)</f>
         <v>420</v>
       </c>
       <c r="K309" s="5">
@@ -29113,7 +29034,7 @@
       <c r="O309" s="5"/>
       <c r="P309" s="5"/>
       <c r="Q309" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J309/45)))</f>
         <v>1570</v>
       </c>
       <c r="R309" s="5">
@@ -29172,7 +29093,7 @@
         <v>65</v>
       </c>
       <c r="J310" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E310:I310)</f>
         <v>382</v>
       </c>
       <c r="K310" s="5">
@@ -29185,12 +29106,12 @@
       <c r="N310" s="5">
         <v>17</v>
       </c>
-      <c r="O310" s="5">
-        <v>15</v>
+      <c r="O310">
+        <v>30</v>
       </c>
       <c r="P310" s="5"/>
       <c r="Q310" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J310/45)))</f>
         <v>806</v>
       </c>
       <c r="R310" s="5">
@@ -29249,7 +29170,7 @@
         <v>71</v>
       </c>
       <c r="J311" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E311:I311)</f>
         <v>390</v>
       </c>
       <c r="K311" s="5">
@@ -29265,7 +29186,7 @@
       <c r="O311" s="5"/>
       <c r="P311" s="5"/>
       <c r="Q311" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J311/45)))</f>
         <v>928</v>
       </c>
       <c r="R311" s="5">
@@ -29324,7 +29245,7 @@
         <v>78</v>
       </c>
       <c r="J312" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E312:I312)</f>
         <v>366</v>
       </c>
       <c r="K312" s="5">
@@ -29337,12 +29258,12 @@
       <c r="N312" s="5">
         <v>17</v>
       </c>
-      <c r="O312" s="5">
-        <v>18</v>
+      <c r="O312">
+        <v>36</v>
       </c>
       <c r="P312" s="5"/>
       <c r="Q312" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J312/45)))</f>
         <v>609</v>
       </c>
       <c r="R312" s="5">
@@ -29401,7 +29322,7 @@
         <v>75</v>
       </c>
       <c r="J313" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E313:I313)</f>
         <v>368</v>
       </c>
       <c r="K313" s="5">
@@ -29417,7 +29338,7 @@
       <c r="O313" s="5"/>
       <c r="P313" s="5"/>
       <c r="Q313" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J313/45)))</f>
         <v>631</v>
       </c>
       <c r="R313" s="5">
@@ -29476,7 +29397,7 @@
         <v>82</v>
       </c>
       <c r="J314" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E314:I314)</f>
         <v>316</v>
       </c>
       <c r="K314" s="5">
@@ -29489,12 +29410,12 @@
       <c r="N314" s="5">
         <v>17</v>
       </c>
-      <c r="O314" s="5">
-        <v>15</v>
+      <c r="O314">
+        <v>30</v>
       </c>
       <c r="P314" s="5"/>
       <c r="Q314" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J314/45)))</f>
         <v>253</v>
       </c>
       <c r="R314" s="5">
@@ -29553,7 +29474,7 @@
         <v>94</v>
       </c>
       <c r="J315" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E315:I315)</f>
         <v>432</v>
       </c>
       <c r="K315" s="5">
@@ -29569,7 +29490,7 @@
       <c r="O315" s="5"/>
       <c r="P315" s="5"/>
       <c r="Q315" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J315/45)))</f>
         <v>1937</v>
       </c>
       <c r="R315" s="5">
@@ -29629,7 +29550,7 @@
         <v>92</v>
       </c>
       <c r="J316" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E316:I316)</f>
         <v>434</v>
       </c>
       <c r="K316" s="5">
@@ -29642,12 +29563,12 @@
       <c r="N316" s="5">
         <v>17</v>
       </c>
-      <c r="O316" s="5">
-        <v>18</v>
+      <c r="O316">
+        <v>36</v>
       </c>
       <c r="P316" s="5"/>
       <c r="Q316" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J316/45)))</f>
         <v>2006</v>
       </c>
       <c r="R316" s="5">
@@ -29709,7 +29630,7 @@
         <v>79</v>
       </c>
       <c r="J317" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E317:I317)</f>
         <v>416</v>
       </c>
       <c r="K317" s="5">
@@ -29725,7 +29646,7 @@
       <c r="O317" s="5"/>
       <c r="P317" s="5"/>
       <c r="Q317" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J317/45)))</f>
         <v>1463</v>
       </c>
       <c r="R317" s="5">
@@ -29785,7 +29706,7 @@
         <v>73</v>
       </c>
       <c r="J318" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E318:I318)</f>
         <v>354</v>
       </c>
       <c r="K318" s="5">
@@ -29801,7 +29722,7 @@
       <c r="O318" s="5"/>
       <c r="P318" s="5"/>
       <c r="Q318" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J318/45)))</f>
         <v>493</v>
       </c>
       <c r="R318" s="5">
@@ -29860,7 +29781,7 @@
         <v>65</v>
       </c>
       <c r="J319" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E319:I319)</f>
         <v>381</v>
       </c>
       <c r="K319" s="5">
@@ -29873,12 +29794,12 @@
       <c r="N319" s="5">
         <v>17</v>
       </c>
-      <c r="O319" s="5">
-        <v>15</v>
+      <c r="O319">
+        <v>30</v>
       </c>
       <c r="P319" s="5"/>
       <c r="Q319" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J319/45)))</f>
         <v>792</v>
       </c>
       <c r="R319" s="5">
@@ -29940,7 +29861,7 @@
         <v>67</v>
       </c>
       <c r="J320" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E320:I320)</f>
         <v>321</v>
       </c>
       <c r="K320" s="5">
@@ -29956,7 +29877,7 @@
       <c r="O320" s="5"/>
       <c r="P320" s="5"/>
       <c r="Q320" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J320/45)))</f>
         <v>277</v>
       </c>
       <c r="R320" s="5">
@@ -30015,7 +29936,7 @@
         <v>72</v>
       </c>
       <c r="J321" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E321:I321)</f>
         <v>323</v>
       </c>
       <c r="K321" s="5">
@@ -30028,14 +29949,14 @@
       <c r="N321" s="5">
         <v>17</v>
       </c>
-      <c r="O321" s="5">
-        <v>30</v>
+      <c r="O321">
+        <v>50</v>
       </c>
       <c r="P321" s="5">
         <v>1.5</v>
       </c>
       <c r="Q321" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J321/45)))</f>
         <v>286</v>
       </c>
       <c r="R321" s="5">
@@ -30092,7 +30013,7 @@
         <v>70</v>
       </c>
       <c r="J322" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E322:I322)</f>
         <v>333</v>
       </c>
       <c r="K322" s="5">
@@ -30105,14 +30026,14 @@
       <c r="N322" s="5">
         <v>17</v>
       </c>
-      <c r="O322" s="5">
-        <v>13</v>
+      <c r="O322">
+        <v>26</v>
       </c>
       <c r="P322" s="5">
         <v>2.5</v>
       </c>
       <c r="Q322" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J322/45)))</f>
         <v>341</v>
       </c>
       <c r="R322" s="5">
@@ -30170,7 +30091,7 @@
         <v>52</v>
       </c>
       <c r="J323" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E323:I323)</f>
         <v>146</v>
       </c>
       <c r="K323" s="5">
@@ -30183,12 +30104,12 @@
       <c r="N323" s="5">
         <v>17</v>
       </c>
-      <c r="O323" s="5">
-        <v>35</v>
+      <c r="O323">
+        <v>58</v>
       </c>
       <c r="P323" s="5"/>
       <c r="Q323" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J323/45)))</f>
         <v>25</v>
       </c>
       <c r="R323" s="5">
@@ -30247,7 +30168,7 @@
         <v>65</v>
       </c>
       <c r="J324" s="5">
-        <f t="shared" si="13"/>
+        <f>SUM(E324:I324)</f>
         <v>285</v>
       </c>
       <c r="K324" s="5">
@@ -30260,12 +30181,12 @@
       <c r="N324" s="5">
         <v>17</v>
       </c>
-      <c r="O324" s="5">
-        <v>15</v>
+      <c r="O324">
+        <v>30</v>
       </c>
       <c r="P324" s="5"/>
       <c r="Q324" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J324/45)))</f>
         <v>147</v>
       </c>
       <c r="R324" s="5">
@@ -30325,7 +30246,7 @@
         <v>87</v>
       </c>
       <c r="J325" s="5">
-        <f t="shared" ref="J325:J351" si="16">SUM(E325:I325)</f>
+        <f>SUM(E325:I325)</f>
         <v>439</v>
       </c>
       <c r="K325" s="5">
@@ -30338,12 +30259,12 @@
       <c r="N325" s="5">
         <v>17</v>
       </c>
-      <c r="O325" s="5">
-        <v>15</v>
+      <c r="O325">
+        <v>30</v>
       </c>
       <c r="P325" s="5"/>
       <c r="Q325" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J325/45)))</f>
         <v>2190</v>
       </c>
       <c r="R325" s="5">
@@ -30403,7 +30324,7 @@
         <v>68</v>
       </c>
       <c r="J326" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E326:I326)</f>
         <v>349</v>
       </c>
       <c r="K326" s="5">
@@ -30419,7 +30340,7 @@
       <c r="O326" s="5"/>
       <c r="P326" s="5"/>
       <c r="Q326" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J326/45)))</f>
         <v>452</v>
       </c>
       <c r="R326" s="5">
@@ -30479,7 +30400,7 @@
         <v>27</v>
       </c>
       <c r="J327" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E327:I327)</f>
         <v>224</v>
       </c>
       <c r="K327" s="5">
@@ -30495,7 +30416,7 @@
       <c r="O327" s="5"/>
       <c r="P327" s="5"/>
       <c r="Q327" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J327/45)))</f>
         <v>50</v>
       </c>
       <c r="R327" s="5">
@@ -30555,7 +30476,7 @@
         <v>68</v>
       </c>
       <c r="J328" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E328:I328)</f>
         <v>364</v>
       </c>
       <c r="K328" s="5">
@@ -30568,14 +30489,14 @@
       <c r="N328" s="5">
         <v>17</v>
       </c>
-      <c r="O328" s="5">
-        <v>22</v>
+      <c r="O328">
+        <v>40</v>
       </c>
       <c r="P328" s="5">
         <v>1.5</v>
       </c>
       <c r="Q328" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J328/45)))</f>
         <v>588</v>
       </c>
       <c r="R328" s="5">
@@ -30634,7 +30555,7 @@
         <v>52</v>
       </c>
       <c r="J329" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E329:I329)</f>
         <v>309</v>
       </c>
       <c r="K329" s="5">
@@ -30650,7 +30571,7 @@
       <c r="O329" s="5"/>
       <c r="P329" s="5"/>
       <c r="Q329" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J329/45)))</f>
         <v>224</v>
       </c>
       <c r="R329" s="5">
@@ -30710,7 +30631,7 @@
         <v>92</v>
       </c>
       <c r="J330" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E330:I330)</f>
         <v>430</v>
       </c>
       <c r="K330" s="5">
@@ -30726,7 +30647,7 @@
       <c r="O330" s="5"/>
       <c r="P330" s="5"/>
       <c r="Q330" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J330/45)))</f>
         <v>1870</v>
       </c>
       <c r="R330" s="5">
@@ -30786,7 +30707,7 @@
         <v>57</v>
       </c>
       <c r="J331" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E331:I331)</f>
         <v>346</v>
       </c>
       <c r="K331" s="5">
@@ -30799,12 +30720,12 @@
       <c r="N331" s="5">
         <v>17</v>
       </c>
-      <c r="O331" s="5">
-        <v>15</v>
+      <c r="O331">
+        <v>30</v>
       </c>
       <c r="P331" s="5"/>
       <c r="Q331" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J331/45)))</f>
         <v>429</v>
       </c>
       <c r="R331" s="5">
@@ -30864,7 +30785,7 @@
         <v>85</v>
       </c>
       <c r="J332" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E332:I332)</f>
         <v>326</v>
       </c>
       <c r="K332" s="5">
@@ -30877,12 +30798,12 @@
       <c r="N332" s="5">
         <v>17</v>
       </c>
-      <c r="O332" s="5">
-        <v>14</v>
+      <c r="O332">
+        <v>28</v>
       </c>
       <c r="P332" s="5"/>
       <c r="Q332" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J332/45)))</f>
         <v>302</v>
       </c>
       <c r="R332" s="5">
@@ -30942,7 +30863,7 @@
         <v>70</v>
       </c>
       <c r="J333" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E333:I333)</f>
         <v>296</v>
       </c>
       <c r="K333" s="5">
@@ -30955,12 +30876,12 @@
       <c r="N333" s="5">
         <v>17</v>
       </c>
-      <c r="O333" s="5">
-        <v>14</v>
+      <c r="O333">
+        <v>28</v>
       </c>
       <c r="P333" s="5"/>
       <c r="Q333" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J333/45)))</f>
         <v>178</v>
       </c>
       <c r="R333" s="5">
@@ -31020,7 +30941,7 @@
         <v>88</v>
       </c>
       <c r="J334" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E334:I334)</f>
         <v>372</v>
       </c>
       <c r="K334" s="5">
@@ -31033,12 +30954,12 @@
       <c r="N334" s="5">
         <v>17</v>
       </c>
-      <c r="O334" s="5">
-        <v>15</v>
+      <c r="O334">
+        <v>30</v>
       </c>
       <c r="P334" s="5"/>
       <c r="Q334" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J334/45)))</f>
         <v>677</v>
       </c>
       <c r="R334" s="5">
@@ -31100,7 +31021,7 @@
         <v>75</v>
       </c>
       <c r="J335" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E335:I335)</f>
         <v>388</v>
       </c>
       <c r="K335" s="5">
@@ -31116,7 +31037,7 @@
       <c r="O335" s="5"/>
       <c r="P335" s="5"/>
       <c r="Q335" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J335/45)))</f>
         <v>896</v>
       </c>
       <c r="R335" s="5">
@@ -31176,7 +31097,7 @@
         <v>70</v>
       </c>
       <c r="J336" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E336:I336)</f>
         <v>377</v>
       </c>
       <c r="K336" s="5">
@@ -31189,14 +31110,14 @@
       <c r="N336" s="5">
         <v>17</v>
       </c>
-      <c r="O336" s="5">
-        <v>13</v>
+      <c r="O336">
+        <v>26</v>
       </c>
       <c r="P336" s="5">
         <v>2.5</v>
       </c>
       <c r="Q336" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J336/45)))</f>
         <v>739</v>
       </c>
       <c r="R336" s="5">
@@ -31254,7 +31175,7 @@
         <v>78</v>
       </c>
       <c r="J337" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E337:I337)</f>
         <v>359</v>
       </c>
       <c r="K337" s="5">
@@ -31270,7 +31191,7 @@
       <c r="O337" s="5"/>
       <c r="P337" s="5"/>
       <c r="Q337" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J337/45)))</f>
         <v>539</v>
       </c>
       <c r="R337" s="5">
@@ -31328,7 +31249,7 @@
         <v>82</v>
       </c>
       <c r="J338" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E338:I338)</f>
         <v>308</v>
       </c>
       <c r="K338" s="5">
@@ -31341,12 +31262,12 @@
       <c r="N338" s="5">
         <v>17</v>
       </c>
-      <c r="O338" s="5">
-        <v>15</v>
+      <c r="O338">
+        <v>30</v>
       </c>
       <c r="P338" s="5"/>
       <c r="Q338" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J338/45)))</f>
         <v>220</v>
       </c>
       <c r="R338" s="5">
@@ -31406,7 +31327,7 @@
         <v>65</v>
       </c>
       <c r="J339" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E339:I339)</f>
         <v>365</v>
       </c>
       <c r="K339" s="5">
@@ -31419,12 +31340,12 @@
       <c r="N339" s="5">
         <v>17</v>
       </c>
-      <c r="O339" s="5">
-        <v>15</v>
+      <c r="O339">
+        <v>30</v>
       </c>
       <c r="P339" s="5"/>
       <c r="Q339" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J339/45)))</f>
         <v>599</v>
       </c>
       <c r="R339" s="5">
@@ -31484,7 +31405,7 @@
         <v>86</v>
       </c>
       <c r="J340" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E340:I340)</f>
         <v>394</v>
       </c>
       <c r="K340" s="5">
@@ -31497,12 +31418,12 @@
       <c r="N340" s="5">
         <v>17</v>
       </c>
-      <c r="O340" s="5">
-        <v>18</v>
+      <c r="O340">
+        <v>36</v>
       </c>
       <c r="P340" s="5"/>
       <c r="Q340" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J340/45)))</f>
         <v>995</v>
       </c>
       <c r="R340" s="5">
@@ -31562,7 +31483,7 @@
         <v>81</v>
       </c>
       <c r="J341" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E341:I341)</f>
         <v>379</v>
       </c>
       <c r="K341" s="5">
@@ -31575,12 +31496,12 @@
       <c r="N341" s="5">
         <v>17</v>
       </c>
-      <c r="O341" s="5">
-        <v>18</v>
+      <c r="O341">
+        <v>36</v>
       </c>
       <c r="P341" s="5"/>
       <c r="Q341" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J341/45)))</f>
         <v>765</v>
       </c>
       <c r="R341" s="5">
@@ -31638,7 +31559,7 @@
         <v>83</v>
       </c>
       <c r="J342" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E342:I342)</f>
         <v>371</v>
       </c>
       <c r="K342" s="5">
@@ -31651,12 +31572,12 @@
       <c r="N342" s="5">
         <v>17</v>
       </c>
-      <c r="O342" s="5">
-        <v>18</v>
+      <c r="O342">
+        <v>36</v>
       </c>
       <c r="P342" s="5"/>
       <c r="Q342" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J342/45)))</f>
         <v>665</v>
       </c>
       <c r="R342" s="5">
@@ -31716,7 +31637,7 @@
         <v>75</v>
       </c>
       <c r="J343" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E343:I343)</f>
         <v>348</v>
       </c>
       <c r="K343" s="5">
@@ -31729,12 +31650,12 @@
       <c r="N343" s="5">
         <v>17</v>
       </c>
-      <c r="O343" s="5">
-        <v>35</v>
+      <c r="O343">
+        <v>58</v>
       </c>
       <c r="P343" s="5"/>
       <c r="Q343" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J343/45)))</f>
         <v>444</v>
       </c>
       <c r="R343" s="5">
@@ -31794,7 +31715,7 @@
         <v>87</v>
       </c>
       <c r="J344" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E344:I344)</f>
         <v>397</v>
       </c>
       <c r="K344" s="5">
@@ -31810,7 +31731,7 @@
       <c r="O344" s="5"/>
       <c r="P344" s="5"/>
       <c r="Q344" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J344/45)))</f>
         <v>1049</v>
       </c>
       <c r="R344" s="5">
@@ -31870,7 +31791,7 @@
         <v>51</v>
       </c>
       <c r="J345" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E345:I345)</f>
         <v>345</v>
       </c>
       <c r="K345" s="5">
@@ -31886,7 +31807,7 @@
       <c r="O345" s="5"/>
       <c r="P345" s="5"/>
       <c r="Q345" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J345/45)))</f>
         <v>421</v>
       </c>
       <c r="R345" s="5">
@@ -31948,7 +31869,7 @@
         <v>86</v>
       </c>
       <c r="J346" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E346:I346)</f>
         <v>415</v>
       </c>
       <c r="K346" s="5">
@@ -31961,14 +31882,14 @@
       <c r="N346" s="5">
         <v>17</v>
       </c>
-      <c r="O346" s="5">
-        <v>30</v>
+      <c r="O346">
+        <v>50</v>
       </c>
       <c r="P346" s="5">
         <v>1.5</v>
       </c>
       <c r="Q346" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J346/45)))</f>
         <v>1438</v>
       </c>
       <c r="R346" s="5">
@@ -32028,7 +31949,7 @@
         <v>50</v>
       </c>
       <c r="J347" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E347:I347)</f>
         <v>303</v>
       </c>
       <c r="K347" s="5">
@@ -32041,14 +31962,14 @@
       <c r="N347" s="5">
         <v>17</v>
       </c>
-      <c r="O347" s="5">
-        <v>30</v>
+      <c r="O347">
+        <v>50</v>
       </c>
       <c r="P347" s="5">
         <v>1.5</v>
       </c>
       <c r="Q347" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J347/45)))</f>
         <v>202</v>
       </c>
       <c r="R347" s="5">
@@ -32106,7 +32027,7 @@
         <v>76</v>
       </c>
       <c r="J348" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E348:I348)</f>
         <v>382</v>
       </c>
       <c r="K348" s="5">
@@ -32122,7 +32043,7 @@
       <c r="O348" s="5"/>
       <c r="P348" s="5"/>
       <c r="Q348" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J348/45)))</f>
         <v>806</v>
       </c>
       <c r="R348" s="5">
@@ -32182,7 +32103,7 @@
         <v>56</v>
       </c>
       <c r="J349" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E349:I349)</f>
         <v>271</v>
       </c>
       <c r="K349" s="5">
@@ -32198,7 +32119,7 @@
       <c r="O349" s="5"/>
       <c r="P349" s="5"/>
       <c r="Q349" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J349/45)))</f>
         <v>115</v>
       </c>
       <c r="R349" s="5">
@@ -32256,7 +32177,7 @@
         <v>64</v>
       </c>
       <c r="J350" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E350:I350)</f>
         <v>335</v>
       </c>
       <c r="K350" s="5">
@@ -32272,7 +32193,7 @@
       <c r="O350" s="5"/>
       <c r="P350" s="5"/>
       <c r="Q350" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J350/45)))</f>
         <v>354</v>
       </c>
       <c r="R350" s="5">
@@ -32332,7 +32253,7 @@
         <v>70</v>
       </c>
       <c r="J351" s="5">
-        <f t="shared" si="16"/>
+        <f>SUM(E351:I351)</f>
         <v>331</v>
       </c>
       <c r="K351" s="5">
@@ -32348,7 +32269,7 @@
       <c r="O351" s="5"/>
       <c r="P351" s="5"/>
       <c r="Q351" s="5">
-        <f t="shared" si="15"/>
+        <f>MAX(25, INT(POWER(2.2,J351/45)))</f>
         <v>330</v>
       </c>
       <c r="R351" s="5">
@@ -32379,7 +32300,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:Z351">
-    <sortState ref="A5:AA351">
+    <sortState ref="A5:Z351">
       <sortCondition ref="K4:K351"/>
     </sortState>
   </autoFilter>
@@ -32388,327 +32309,327 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H323:I328 E308:I309 H312:I319 E312:G351 E281:I299 H181:I181 E5:I14 E166:F166 F167 F168:I168 E119:F119 E169:F169 E170:I170 E172:I172 E171:F171 E176:G177 E180:G181 E182:F182 E173:F175 E178:F179 E183:I274 E120:I165 H19:I88 E19:G118">
-    <cfRule type="cellIs" dxfId="218" priority="375" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="208" priority="375" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H93:I118 H89:I90">
-    <cfRule type="cellIs" dxfId="217" priority="373" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="207" priority="373" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H330:I330">
-    <cfRule type="cellIs" dxfId="216" priority="371" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="206" priority="371" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H329:I329">
-    <cfRule type="cellIs" dxfId="215" priority="369" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="205" priority="369" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H332:I332">
-    <cfRule type="cellIs" dxfId="214" priority="367" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="204" priority="367" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H333:I333">
-    <cfRule type="cellIs" dxfId="213" priority="362" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="203" priority="362" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H340:I340">
-    <cfRule type="cellIs" dxfId="212" priority="360" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="202" priority="360" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H341:I341">
-    <cfRule type="cellIs" dxfId="211" priority="358" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="201" priority="358" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H342:I342">
-    <cfRule type="cellIs" dxfId="210" priority="356" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="200" priority="356" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H343:I343">
-    <cfRule type="cellIs" dxfId="209" priority="351" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="199" priority="351" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H344:I344">
-    <cfRule type="cellIs" dxfId="208" priority="347" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="198" priority="347" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H345:I345">
-    <cfRule type="cellIs" dxfId="207" priority="343" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="197" priority="343" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H320:I320">
-    <cfRule type="cellIs" dxfId="206" priority="338" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="196" priority="338" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H321:I321">
-    <cfRule type="cellIs" dxfId="205" priority="337" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="195" priority="337" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H346:I346">
-    <cfRule type="cellIs" dxfId="204" priority="336" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="194" priority="336" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H347:I347">
-    <cfRule type="cellIs" dxfId="203" priority="335" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="193" priority="335" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H348:I348">
-    <cfRule type="cellIs" dxfId="202" priority="334" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="192" priority="334" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H334:I334">
-    <cfRule type="cellIs" dxfId="201" priority="333" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="191" priority="333" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H335:I335">
-    <cfRule type="cellIs" dxfId="200" priority="328" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="190" priority="328" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H336:I336">
-    <cfRule type="cellIs" dxfId="199" priority="327" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="189" priority="327" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H337:I337">
-    <cfRule type="cellIs" dxfId="198" priority="326" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="188" priority="326" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H338:I338">
-    <cfRule type="cellIs" dxfId="197" priority="325" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="187" priority="325" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H339:I339">
-    <cfRule type="cellIs" dxfId="196" priority="324" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="186" priority="324" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H322:I322">
-    <cfRule type="cellIs" dxfId="195" priority="317" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="185" priority="317" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H177:I177">
-    <cfRule type="cellIs" dxfId="194" priority="310" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="184" priority="310" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H91:I91">
-    <cfRule type="cellIs" dxfId="193" priority="309" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="183" priority="309" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H349:I349">
-    <cfRule type="cellIs" dxfId="192" priority="300" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="182" priority="300" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H331:I331">
-    <cfRule type="cellIs" dxfId="191" priority="296" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="181" priority="296" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H350:I350">
-    <cfRule type="cellIs" dxfId="190" priority="291" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="180" priority="291" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H351:I351">
-    <cfRule type="cellIs" dxfId="189" priority="281" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="179" priority="281" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H180:I180">
-    <cfRule type="cellIs" dxfId="188" priority="278" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="178" priority="278" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H92:I92">
-    <cfRule type="cellIs" dxfId="187" priority="274" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="177" priority="274" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T308:T309 T312:T348 T206:T208 T220:T222 T267 T88:T119 T1:T17 T19:T86 T145:T185 T239:T246 T274 T350 T352:T1048576">
-    <cfRule type="cellIs" dxfId="186" priority="262" operator="equal">
+    <cfRule type="cellIs" dxfId="176" priority="262" operator="equal">
       <formula>"炮"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="185" priority="263" operator="equal">
+    <cfRule type="cellIs" dxfId="175" priority="263" operator="equal">
       <formula>"弩"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="184" priority="264" operator="equal">
+    <cfRule type="cellIs" dxfId="174" priority="264" operator="equal">
       <formula>"弓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="183" priority="265" operator="equal">
+    <cfRule type="cellIs" dxfId="173" priority="265" operator="equal">
       <formula>"医"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="182" priority="266" operator="equal">
+    <cfRule type="cellIs" dxfId="172" priority="266" operator="equal">
       <formula>"乐"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="181" priority="267" operator="equal">
+    <cfRule type="cellIs" dxfId="171" priority="267" operator="equal">
       <formula>"鼓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="180" priority="268" operator="equal">
+    <cfRule type="cellIs" dxfId="170" priority="268" operator="equal">
       <formula>"相"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="179" priority="269" operator="equal">
+    <cfRule type="cellIs" dxfId="169" priority="269" operator="equal">
       <formula>"扇"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="178" priority="270" operator="equal">
+    <cfRule type="cellIs" dxfId="168" priority="270" operator="equal">
       <formula>"谋"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="177" priority="271" operator="equal">
+    <cfRule type="cellIs" dxfId="167" priority="271" operator="equal">
       <formula>"帅"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T301:T302 T305:T307">
-    <cfRule type="cellIs" dxfId="176" priority="237" operator="equal">
+    <cfRule type="cellIs" dxfId="166" priority="237" operator="equal">
       <formula>"炮"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="175" priority="238" operator="equal">
+    <cfRule type="cellIs" dxfId="165" priority="238" operator="equal">
       <formula>"弩"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="174" priority="239" operator="equal">
+    <cfRule type="cellIs" dxfId="164" priority="239" operator="equal">
       <formula>"弓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="173" priority="240" operator="equal">
+    <cfRule type="cellIs" dxfId="163" priority="240" operator="equal">
       <formula>"医"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="172" priority="241" operator="equal">
+    <cfRule type="cellIs" dxfId="162" priority="241" operator="equal">
       <formula>"乐"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="171" priority="242" operator="equal">
+    <cfRule type="cellIs" dxfId="161" priority="242" operator="equal">
       <formula>"鼓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="170" priority="243" operator="equal">
+    <cfRule type="cellIs" dxfId="160" priority="243" operator="equal">
       <formula>"相"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="244" operator="equal">
+    <cfRule type="cellIs" dxfId="159" priority="244" operator="equal">
       <formula>"扇"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="245" operator="equal">
+    <cfRule type="cellIs" dxfId="158" priority="245" operator="equal">
       <formula>"谋"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="167" priority="246" operator="equal">
+    <cfRule type="cellIs" dxfId="157" priority="246" operator="equal">
       <formula>"帅"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T310">
-    <cfRule type="cellIs" dxfId="166" priority="224" operator="equal">
+    <cfRule type="cellIs" dxfId="156" priority="224" operator="equal">
       <formula>"炮"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="165" priority="225" operator="equal">
+    <cfRule type="cellIs" dxfId="155" priority="225" operator="equal">
       <formula>"弩"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="164" priority="226" operator="equal">
+    <cfRule type="cellIs" dxfId="154" priority="226" operator="equal">
       <formula>"弓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="163" priority="227" operator="equal">
+    <cfRule type="cellIs" dxfId="153" priority="227" operator="equal">
       <formula>"医"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="228" operator="equal">
+    <cfRule type="cellIs" dxfId="152" priority="228" operator="equal">
       <formula>"乐"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="161" priority="229" operator="equal">
+    <cfRule type="cellIs" dxfId="151" priority="229" operator="equal">
       <formula>"鼓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="230" operator="equal">
+    <cfRule type="cellIs" dxfId="150" priority="230" operator="equal">
       <formula>"相"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="159" priority="231" operator="equal">
+    <cfRule type="cellIs" dxfId="149" priority="231" operator="equal">
       <formula>"扇"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="232" operator="equal">
+    <cfRule type="cellIs" dxfId="148" priority="232" operator="equal">
       <formula>"谋"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="233" operator="equal">
+    <cfRule type="cellIs" dxfId="147" priority="233" operator="equal">
       <formula>"帅"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T311">
-    <cfRule type="cellIs" dxfId="156" priority="211" operator="equal">
+    <cfRule type="cellIs" dxfId="146" priority="211" operator="equal">
       <formula>"炮"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="155" priority="212" operator="equal">
+    <cfRule type="cellIs" dxfId="145" priority="212" operator="equal">
       <formula>"弩"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="154" priority="213" operator="equal">
+    <cfRule type="cellIs" dxfId="144" priority="213" operator="equal">
       <formula>"弓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="214" operator="equal">
+    <cfRule type="cellIs" dxfId="143" priority="214" operator="equal">
       <formula>"医"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="152" priority="215" operator="equal">
+    <cfRule type="cellIs" dxfId="142" priority="215" operator="equal">
       <formula>"乐"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="216" operator="equal">
+    <cfRule type="cellIs" dxfId="141" priority="216" operator="equal">
       <formula>"鼓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="150" priority="217" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="217" operator="equal">
       <formula>"相"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="149" priority="218" operator="equal">
+    <cfRule type="cellIs" dxfId="139" priority="218" operator="equal">
       <formula>"扇"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="148" priority="219" operator="equal">
+    <cfRule type="cellIs" dxfId="138" priority="219" operator="equal">
       <formula>"谋"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="220" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="220" operator="equal">
       <formula>"帅"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T292">
-    <cfRule type="cellIs" dxfId="146" priority="198" operator="equal">
+    <cfRule type="cellIs" dxfId="136" priority="198" operator="equal">
       <formula>"炮"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="145" priority="199" operator="equal">
+    <cfRule type="cellIs" dxfId="135" priority="199" operator="equal">
       <formula>"弩"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="200" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="200" operator="equal">
       <formula>"弓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="143" priority="201" operator="equal">
+    <cfRule type="cellIs" dxfId="133" priority="201" operator="equal">
       <formula>"医"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="202" operator="equal">
+    <cfRule type="cellIs" dxfId="132" priority="202" operator="equal">
       <formula>"乐"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="203" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="203" operator="equal">
       <formula>"鼓"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="204" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="204" operator="equal">
       <formula>"相"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="205" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="205" operator="equal">
       <formula>"扇"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="206" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="206" operator="equal">
       <formula>"谋"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="207" operator="equal">
+    <cfRule type="cellIs" dxfId="127" priority="207" operator="equal">
       <formula>"帅"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E275:I280">
-    <cfRule type="cellIs" dxfId="136" priority="197" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="126" priority="197" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Design/config/HeroConfig.xlsx
+++ b/Design/config/HeroConfig.xlsx
@@ -6228,7 +6228,7 @@
         <v>99</v>
       </c>
       <c r="J5" s="5">
-        <f>SUM(E5:I5)</f>
+        <f t="shared" ref="J5:J68" si="0">SUM(E5:I5)</f>
         <v>408</v>
       </c>
       <c r="K5" s="5">
@@ -6305,7 +6305,7 @@
         <v>45</v>
       </c>
       <c r="J6" s="5">
-        <f>SUM(E6:I6)</f>
+        <f t="shared" si="0"/>
         <v>287</v>
       </c>
       <c r="K6" s="5">
@@ -6323,7 +6323,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5">
-        <f>MAX(25, INT(POWER(2.2,J6/45)))</f>
+        <f t="shared" ref="Q6:Q17" si="1">MAX(25, INT(POWER(2.2,J6/45)))</f>
         <v>152</v>
       </c>
       <c r="R6" s="5">
@@ -6383,7 +6383,7 @@
         <v>94</v>
       </c>
       <c r="J7" s="5">
-        <f>SUM(E7:I7)</f>
+        <f t="shared" si="0"/>
         <v>427</v>
       </c>
       <c r="K7" s="5">
@@ -6401,7 +6401,7 @@
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5">
-        <f>MAX(25, INT(POWER(2.2,J7/45)))</f>
+        <f t="shared" si="1"/>
         <v>1775</v>
       </c>
       <c r="R7" s="5">
@@ -6461,7 +6461,7 @@
         <v>84</v>
       </c>
       <c r="J8" s="5">
-        <f>SUM(E8:I8)</f>
+        <f t="shared" si="0"/>
         <v>411</v>
       </c>
       <c r="K8" s="5">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="P8" s="5"/>
       <c r="Q8" s="5">
-        <f>MAX(25, INT(POWER(2.2,J8/45)))</f>
+        <f t="shared" si="1"/>
         <v>1341</v>
       </c>
       <c r="R8" s="5">
@@ -6543,7 +6543,7 @@
         <v>60</v>
       </c>
       <c r="J9" s="5">
-        <f>SUM(E9:I9)</f>
+        <f t="shared" si="0"/>
         <v>280</v>
       </c>
       <c r="K9" s="5">
@@ -6561,7 +6561,7 @@
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5">
-        <f>MAX(25, INT(POWER(2.2,J9/45)))</f>
+        <f t="shared" si="1"/>
         <v>135</v>
       </c>
       <c r="R9" s="5">
@@ -6621,7 +6621,7 @@
         <v>66</v>
       </c>
       <c r="J10" s="5">
-        <f>SUM(E10:I10)</f>
+        <f t="shared" si="0"/>
         <v>331</v>
       </c>
       <c r="K10" s="5">
@@ -6639,7 +6639,7 @@
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5">
-        <f>MAX(25, INT(POWER(2.2,J10/45)))</f>
+        <f t="shared" si="1"/>
         <v>330</v>
       </c>
       <c r="R10" s="5">
@@ -6699,7 +6699,7 @@
         <v>70</v>
       </c>
       <c r="J11" s="5">
-        <f>SUM(E11:I11)</f>
+        <f t="shared" si="0"/>
         <v>352</v>
       </c>
       <c r="K11" s="5">
@@ -6718,10 +6718,10 @@
         <v>40</v>
       </c>
       <c r="P11" s="5">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q11" s="5">
-        <f>MAX(25, INT(POWER(2.2,J11/45)))</f>
+        <f t="shared" si="1"/>
         <v>476</v>
       </c>
       <c r="R11" s="5">
@@ -6780,7 +6780,7 @@
         <v>82</v>
       </c>
       <c r="J12" s="5">
-        <f>SUM(E12:I12)</f>
+        <f t="shared" si="0"/>
         <v>362</v>
       </c>
       <c r="K12" s="5">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P12" s="5"/>
       <c r="Q12" s="5">
-        <f>MAX(25, INT(POWER(2.2,J12/45)))</f>
+        <f t="shared" si="1"/>
         <v>568</v>
       </c>
       <c r="R12" s="5">
@@ -6860,7 +6860,7 @@
         <v>78</v>
       </c>
       <c r="J13" s="5">
-        <f>SUM(E13:I13)</f>
+        <f t="shared" si="0"/>
         <v>382</v>
       </c>
       <c r="K13" s="5">
@@ -6878,7 +6878,7 @@
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
       <c r="Q13" s="5">
-        <f>MAX(25, INT(POWER(2.2,J13/45)))</f>
+        <f t="shared" si="1"/>
         <v>806</v>
       </c>
       <c r="R13" s="5">
@@ -6937,7 +6937,7 @@
         <v>61</v>
       </c>
       <c r="J14" s="5">
-        <f>SUM(E14:I14)</f>
+        <f t="shared" si="0"/>
         <v>275</v>
       </c>
       <c r="K14" s="5">
@@ -6955,7 +6955,7 @@
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
       <c r="Q14" s="5">
-        <f>MAX(25, INT(POWER(2.2,J14/45)))</f>
+        <f t="shared" si="1"/>
         <v>123</v>
       </c>
       <c r="R14" s="5">
@@ -7013,7 +7013,7 @@
         <v>85</v>
       </c>
       <c r="J15" s="5">
-        <f>SUM(E15:I15)</f>
+        <f t="shared" si="0"/>
         <v>309</v>
       </c>
       <c r="K15" s="5">
@@ -7031,7 +7031,7 @@
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
       <c r="Q15" s="5">
-        <f>MAX(25, INT(POWER(2.2,J15/45)))</f>
+        <f t="shared" si="1"/>
         <v>224</v>
       </c>
       <c r="R15" s="5">
@@ -7085,7 +7085,7 @@
         <v>23</v>
       </c>
       <c r="J16" s="5">
-        <f>SUM(E16:I16)</f>
+        <f t="shared" si="0"/>
         <v>193</v>
       </c>
       <c r="K16" s="5">
@@ -7103,7 +7103,7 @@
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
       <c r="Q16" s="5">
-        <f>MAX(25, INT(POWER(2.2,J16/45)))</f>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="R16" s="5">
@@ -7157,7 +7157,7 @@
         <v>69</v>
       </c>
       <c r="J17" s="5">
-        <f>SUM(E17:I17)</f>
+        <f t="shared" si="0"/>
         <v>332</v>
       </c>
       <c r="K17" s="5">
@@ -7175,7 +7175,7 @@
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
       <c r="Q17" s="5">
-        <f>MAX(25, INT(POWER(2.2,J17/45)))</f>
+        <f t="shared" si="1"/>
         <v>335</v>
       </c>
       <c r="R17" s="5">
@@ -7229,7 +7229,7 @@
         <v>96</v>
       </c>
       <c r="J18" s="5">
-        <f>SUM(E18:I18)</f>
+        <f t="shared" si="0"/>
         <v>460</v>
       </c>
       <c r="K18" s="5">
@@ -7302,7 +7302,7 @@
         <v>82</v>
       </c>
       <c r="J19" s="5">
-        <f>SUM(E19:I19)</f>
+        <f t="shared" si="0"/>
         <v>373</v>
       </c>
       <c r="K19" s="5">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="P19" s="5"/>
       <c r="Q19" s="5">
-        <f>MAX(25, INT(POWER(2.2,J19/45)))</f>
+        <f t="shared" ref="Q19:Q50" si="2">MAX(25, INT(POWER(2.2,J19/45)))</f>
         <v>689</v>
       </c>
       <c r="R19" s="5">
@@ -7382,7 +7382,7 @@
         <v>80</v>
       </c>
       <c r="J20" s="5">
-        <f>SUM(E20:I20)</f>
+        <f t="shared" si="0"/>
         <v>387</v>
       </c>
       <c r="K20" s="5">
@@ -7400,7 +7400,7 @@
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5">
-        <f>MAX(25, INT(POWER(2.2,J20/45)))</f>
+        <f t="shared" si="2"/>
         <v>880</v>
       </c>
       <c r="R20" s="5">
@@ -7460,7 +7460,7 @@
         <v>93</v>
       </c>
       <c r="J21" s="5">
-        <f>SUM(E21:I21)</f>
+        <f t="shared" si="0"/>
         <v>402</v>
       </c>
       <c r="K21" s="5">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="P21" s="5"/>
       <c r="Q21" s="5">
-        <f>MAX(25, INT(POWER(2.2,J21/45)))</f>
+        <f t="shared" si="2"/>
         <v>1145</v>
       </c>
       <c r="R21" s="5">
@@ -7540,7 +7540,7 @@
         <v>59</v>
       </c>
       <c r="J22" s="5">
-        <f>SUM(E22:I22)</f>
+        <f t="shared" si="0"/>
         <v>276</v>
       </c>
       <c r="K22" s="5">
@@ -7558,7 +7558,7 @@
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5">
-        <f>MAX(25, INT(POWER(2.2,J22/45)))</f>
+        <f t="shared" si="2"/>
         <v>125</v>
       </c>
       <c r="R22" s="5">
@@ -7618,7 +7618,7 @@
         <v>80</v>
       </c>
       <c r="J23" s="5">
-        <f>SUM(E23:I23)</f>
+        <f t="shared" si="0"/>
         <v>353</v>
       </c>
       <c r="K23" s="5">
@@ -7637,10 +7637,10 @@
         <v>40</v>
       </c>
       <c r="P23" s="5">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q23" s="5">
-        <f>MAX(25, INT(POWER(2.2,J23/45)))</f>
+        <f t="shared" si="2"/>
         <v>485</v>
       </c>
       <c r="R23" s="5">
@@ -7700,7 +7700,7 @@
         <v>78</v>
       </c>
       <c r="J24" s="5">
-        <f>SUM(E24:I24)</f>
+        <f t="shared" si="0"/>
         <v>313</v>
       </c>
       <c r="K24" s="5">
@@ -7718,7 +7718,7 @@
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
       <c r="Q24" s="5">
-        <f>MAX(25, INT(POWER(2.2,J24/45)))</f>
+        <f t="shared" si="2"/>
         <v>240</v>
       </c>
       <c r="R24" s="5">
@@ -7778,7 +7778,7 @@
         <v>71</v>
       </c>
       <c r="J25" s="5">
-        <f>SUM(E25:I25)</f>
+        <f t="shared" si="0"/>
         <v>394</v>
       </c>
       <c r="K25" s="5">
@@ -7797,10 +7797,10 @@
         <v>40</v>
       </c>
       <c r="P25" s="5">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q25" s="5">
-        <f>MAX(25, INT(POWER(2.2,J25/45)))</f>
+        <f t="shared" si="2"/>
         <v>995</v>
       </c>
       <c r="R25" s="5">
@@ -7860,7 +7860,7 @@
         <v>73</v>
       </c>
       <c r="J26" s="5">
-        <f>SUM(E26:I26)</f>
+        <f t="shared" si="0"/>
         <v>373</v>
       </c>
       <c r="K26" s="5">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="P26" s="5"/>
       <c r="Q26" s="5">
-        <f>MAX(25, INT(POWER(2.2,J26/45)))</f>
+        <f t="shared" si="2"/>
         <v>689</v>
       </c>
       <c r="R26" s="5">
@@ -7942,7 +7942,7 @@
         <v>51</v>
       </c>
       <c r="J27" s="5">
-        <f>SUM(E27:I27)</f>
+        <f t="shared" si="0"/>
         <v>329</v>
       </c>
       <c r="K27" s="5">
@@ -7960,7 +7960,7 @@
       <c r="O27" s="5"/>
       <c r="P27" s="5"/>
       <c r="Q27" s="5">
-        <f>MAX(25, INT(POWER(2.2,J27/45)))</f>
+        <f t="shared" si="2"/>
         <v>318</v>
       </c>
       <c r="R27" s="5">
@@ -8022,7 +8022,7 @@
         <v>76</v>
       </c>
       <c r="J28" s="5">
-        <f>SUM(E28:I28)</f>
+        <f t="shared" si="0"/>
         <v>360</v>
       </c>
       <c r="K28" s="5">
@@ -8040,7 +8040,7 @@
       <c r="O28" s="5"/>
       <c r="P28" s="5"/>
       <c r="Q28" s="5">
-        <f>MAX(25, INT(POWER(2.2,J28/45)))</f>
+        <f t="shared" si="2"/>
         <v>548</v>
       </c>
       <c r="R28" s="5">
@@ -8100,7 +8100,7 @@
         <v>54</v>
       </c>
       <c r="J29" s="5">
-        <f>SUM(E29:I29)</f>
+        <f t="shared" si="0"/>
         <v>298</v>
       </c>
       <c r="K29" s="5">
@@ -8118,7 +8118,7 @@
       <c r="O29" s="5"/>
       <c r="P29" s="5"/>
       <c r="Q29" s="5">
-        <f>MAX(25, INT(POWER(2.2,J29/45)))</f>
+        <f t="shared" si="2"/>
         <v>185</v>
       </c>
       <c r="R29" s="5">
@@ -8178,7 +8178,7 @@
         <v>63</v>
       </c>
       <c r="J30" s="5">
-        <f>SUM(E30:I30)</f>
+        <f t="shared" si="0"/>
         <v>326</v>
       </c>
       <c r="K30" s="5">
@@ -8196,7 +8196,7 @@
       <c r="O30" s="5"/>
       <c r="P30" s="5"/>
       <c r="Q30" s="5">
-        <f>MAX(25, INT(POWER(2.2,J30/45)))</f>
+        <f t="shared" si="2"/>
         <v>302</v>
       </c>
       <c r="R30" s="5">
@@ -8256,7 +8256,7 @@
         <v>78</v>
       </c>
       <c r="J31" s="5">
-        <f>SUM(E31:I31)</f>
+        <f t="shared" si="0"/>
         <v>380</v>
       </c>
       <c r="K31" s="5">
@@ -8274,7 +8274,7 @@
       <c r="O31" s="5"/>
       <c r="P31" s="5"/>
       <c r="Q31" s="5">
-        <f>MAX(25, INT(POWER(2.2,J31/45)))</f>
+        <f t="shared" si="2"/>
         <v>779</v>
       </c>
       <c r="R31" s="5">
@@ -8336,7 +8336,7 @@
         <v>67</v>
       </c>
       <c r="J32" s="5">
-        <f>SUM(E32:I32)</f>
+        <f t="shared" si="0"/>
         <v>327</v>
       </c>
       <c r="K32" s="5">
@@ -8355,10 +8355,10 @@
         <v>40</v>
       </c>
       <c r="P32" s="5">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q32" s="5">
-        <f>MAX(25, INT(POWER(2.2,J32/45)))</f>
+        <f t="shared" si="2"/>
         <v>307</v>
       </c>
       <c r="R32" s="5">
@@ -8416,7 +8416,7 @@
         <v>69</v>
       </c>
       <c r="J33" s="5">
-        <f>SUM(E33:I33)</f>
+        <f t="shared" si="0"/>
         <v>368</v>
       </c>
       <c r="K33" s="5">
@@ -8434,7 +8434,7 @@
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
       <c r="Q33" s="5">
-        <f>MAX(25, INT(POWER(2.2,J33/45)))</f>
+        <f t="shared" si="2"/>
         <v>631</v>
       </c>
       <c r="R33" s="5">
@@ -8494,7 +8494,7 @@
         <v>56</v>
       </c>
       <c r="J34" s="5">
-        <f>SUM(E34:I34)</f>
+        <f t="shared" si="0"/>
         <v>339</v>
       </c>
       <c r="K34" s="5">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="P34" s="5"/>
       <c r="Q34" s="5">
-        <f>MAX(25, INT(POWER(2.2,J34/45)))</f>
+        <f t="shared" si="2"/>
         <v>379</v>
       </c>
       <c r="R34" s="5">
@@ -8576,7 +8576,7 @@
         <v>43</v>
       </c>
       <c r="J35" s="5">
-        <f>SUM(E35:I35)</f>
+        <f t="shared" si="0"/>
         <v>220</v>
       </c>
       <c r="K35" s="5">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="P35" s="5"/>
       <c r="Q35" s="5">
-        <f>MAX(25, INT(POWER(2.2,J35/45)))</f>
+        <f t="shared" si="2"/>
         <v>47</v>
       </c>
       <c r="R35" s="5">
@@ -8655,7 +8655,7 @@
         <v>45</v>
       </c>
       <c r="J36" s="5">
-        <f>SUM(E36:I36)</f>
+        <f t="shared" si="0"/>
         <v>271</v>
       </c>
       <c r="K36" s="5">
@@ -8673,7 +8673,7 @@
       <c r="O36" s="5"/>
       <c r="P36" s="5"/>
       <c r="Q36" s="5">
-        <f>MAX(25, INT(POWER(2.2,J36/45)))</f>
+        <f t="shared" si="2"/>
         <v>115</v>
       </c>
       <c r="R36" s="5">
@@ -8732,7 +8732,7 @@
         <v>73</v>
       </c>
       <c r="J37" s="5">
-        <f>SUM(E37:I37)</f>
+        <f t="shared" si="0"/>
         <v>355</v>
       </c>
       <c r="K37" s="5">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="P37" s="5"/>
       <c r="Q37" s="5">
-        <f>MAX(25, INT(POWER(2.2,J37/45)))</f>
+        <f t="shared" si="2"/>
         <v>502</v>
       </c>
       <c r="R37" s="5">
@@ -8814,7 +8814,7 @@
         <v>65</v>
       </c>
       <c r="J38" s="5">
-        <f>SUM(E38:I38)</f>
+        <f t="shared" si="0"/>
         <v>365</v>
       </c>
       <c r="K38" s="5">
@@ -8832,7 +8832,7 @@
       <c r="O38" s="5"/>
       <c r="P38" s="5"/>
       <c r="Q38" s="5">
-        <f>MAX(25, INT(POWER(2.2,J38/45)))</f>
+        <f t="shared" si="2"/>
         <v>599</v>
       </c>
       <c r="R38" s="5">
@@ -8894,7 +8894,7 @@
         <v>77</v>
       </c>
       <c r="J39" s="5">
-        <f>SUM(E39:I39)</f>
+        <f t="shared" si="0"/>
         <v>396</v>
       </c>
       <c r="K39" s="5">
@@ -8912,7 +8912,7 @@
       <c r="O39" s="5"/>
       <c r="P39" s="5"/>
       <c r="Q39" s="5">
-        <f>MAX(25, INT(POWER(2.2,J39/45)))</f>
+        <f t="shared" si="2"/>
         <v>1031</v>
       </c>
       <c r="R39" s="5">
@@ -8972,7 +8972,7 @@
         <v>74</v>
       </c>
       <c r="J40" s="5">
-        <f>SUM(E40:I40)</f>
+        <f t="shared" si="0"/>
         <v>345</v>
       </c>
       <c r="K40" s="5">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="P40" s="5"/>
       <c r="Q40" s="5">
-        <f>MAX(25, INT(POWER(2.2,J40/45)))</f>
+        <f t="shared" si="2"/>
         <v>421</v>
       </c>
       <c r="R40" s="5">
@@ -9052,7 +9052,7 @@
         <v>69</v>
       </c>
       <c r="J41" s="5">
-        <f>SUM(E41:I41)</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="K41" s="5">
@@ -9071,10 +9071,10 @@
         <v>26</v>
       </c>
       <c r="P41" s="5">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="Q41" s="5">
-        <f>MAX(25, INT(POWER(2.2,J41/45)))</f>
+        <f t="shared" si="2"/>
         <v>460</v>
       </c>
       <c r="R41" s="5">
@@ -9132,7 +9132,7 @@
         <v>42</v>
       </c>
       <c r="J42" s="5">
-        <f>SUM(E42:I42)</f>
+        <f t="shared" si="0"/>
         <v>312</v>
       </c>
       <c r="K42" s="5">
@@ -9151,10 +9151,10 @@
         <v>26</v>
       </c>
       <c r="P42" s="5">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="Q42" s="5">
-        <f>MAX(25, INT(POWER(2.2,J42/45)))</f>
+        <f t="shared" si="2"/>
         <v>236</v>
       </c>
       <c r="R42" s="5">
@@ -9210,7 +9210,7 @@
         <v>71</v>
       </c>
       <c r="J43" s="5">
-        <f>SUM(E43:I43)</f>
+        <f t="shared" si="0"/>
         <v>312</v>
       </c>
       <c r="K43" s="5">
@@ -9228,7 +9228,7 @@
       <c r="O43" s="5"/>
       <c r="P43" s="5"/>
       <c r="Q43" s="5">
-        <f>MAX(25, INT(POWER(2.2,J43/45)))</f>
+        <f t="shared" si="2"/>
         <v>236</v>
       </c>
       <c r="R43" s="5">
@@ -9288,7 +9288,7 @@
         <v>50</v>
       </c>
       <c r="J44" s="5">
-        <f>SUM(E44:I44)</f>
+        <f t="shared" si="0"/>
         <v>364</v>
       </c>
       <c r="K44" s="5">
@@ -9306,7 +9306,7 @@
       <c r="O44" s="5"/>
       <c r="P44" s="5"/>
       <c r="Q44" s="5">
-        <f>MAX(25, INT(POWER(2.2,J44/45)))</f>
+        <f t="shared" si="2"/>
         <v>588</v>
       </c>
       <c r="R44" s="5">
@@ -9366,7 +9366,7 @@
         <v>78</v>
       </c>
       <c r="J45" s="5">
-        <f>SUM(E45:I45)</f>
+        <f t="shared" si="0"/>
         <v>283</v>
       </c>
       <c r="K45" s="5">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="P45" s="5"/>
       <c r="Q45" s="5">
-        <f>MAX(25, INT(POWER(2.2,J45/45)))</f>
+        <f t="shared" si="2"/>
         <v>142</v>
       </c>
       <c r="R45" s="5">
@@ -9446,7 +9446,7 @@
         <v>53</v>
       </c>
       <c r="J46" s="5">
-        <f>SUM(E46:I46)</f>
+        <f t="shared" si="0"/>
         <v>297</v>
       </c>
       <c r="K46" s="5">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="P46" s="5"/>
       <c r="Q46" s="5">
-        <f>MAX(25, INT(POWER(2.2,J46/45)))</f>
+        <f t="shared" si="2"/>
         <v>181</v>
       </c>
       <c r="R46" s="5">
@@ -9526,7 +9526,7 @@
         <v>94</v>
       </c>
       <c r="J47" s="5">
-        <f>SUM(E47:I47)</f>
+        <f t="shared" si="0"/>
         <v>244</v>
       </c>
       <c r="K47" s="5">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="P47" s="5"/>
       <c r="Q47" s="5">
-        <f>MAX(25, INT(POWER(2.2,J47/45)))</f>
+        <f t="shared" si="2"/>
         <v>71</v>
       </c>
       <c r="R47" s="5">
@@ -9605,7 +9605,7 @@
         <v>70</v>
       </c>
       <c r="J48" s="5">
-        <f>SUM(E48:I48)</f>
+        <f t="shared" si="0"/>
         <v>323</v>
       </c>
       <c r="K48" s="5">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="P48" s="5"/>
       <c r="Q48" s="5">
-        <f>MAX(25, INT(POWER(2.2,J48/45)))</f>
+        <f t="shared" si="2"/>
         <v>286</v>
       </c>
       <c r="R48" s="5">
@@ -9684,7 +9684,7 @@
         <v>84</v>
       </c>
       <c r="J49" s="5">
-        <f>SUM(E49:I49)</f>
+        <f t="shared" si="0"/>
         <v>374</v>
       </c>
       <c r="K49" s="5">
@@ -9702,7 +9702,7 @@
       <c r="O49" s="5"/>
       <c r="P49" s="5"/>
       <c r="Q49" s="5">
-        <f>MAX(25, INT(POWER(2.2,J49/45)))</f>
+        <f t="shared" si="2"/>
         <v>701</v>
       </c>
       <c r="R49" s="5">
@@ -9761,7 +9761,7 @@
         <v>73</v>
       </c>
       <c r="J50" s="5">
-        <f>SUM(E50:I50)</f>
+        <f t="shared" si="0"/>
         <v>385</v>
       </c>
       <c r="K50" s="5">
@@ -9779,7 +9779,7 @@
       <c r="O50" s="5"/>
       <c r="P50" s="5"/>
       <c r="Q50" s="5">
-        <f>MAX(25, INT(POWER(2.2,J50/45)))</f>
+        <f t="shared" si="2"/>
         <v>850</v>
       </c>
       <c r="R50" s="5">
@@ -9837,7 +9837,7 @@
         <v>59</v>
       </c>
       <c r="J51" s="5">
-        <f>SUM(E51:I51)</f>
+        <f t="shared" si="0"/>
         <v>348</v>
       </c>
       <c r="K51" s="5">
@@ -9855,7 +9855,7 @@
       <c r="O51" s="5"/>
       <c r="P51" s="5"/>
       <c r="Q51" s="5">
-        <f>MAX(25, INT(POWER(2.2,J51/45)))</f>
+        <f t="shared" ref="Q51:Q86" si="3">MAX(25, INT(POWER(2.2,J51/45)))</f>
         <v>444</v>
       </c>
       <c r="R51" s="5">
@@ -9915,7 +9915,7 @@
         <v>76</v>
       </c>
       <c r="J52" s="5">
-        <f>SUM(E52:I52)</f>
+        <f t="shared" si="0"/>
         <v>346</v>
       </c>
       <c r="K52" s="5">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="P52" s="5"/>
       <c r="Q52" s="5">
-        <f>MAX(25, INT(POWER(2.2,J52/45)))</f>
+        <f t="shared" si="3"/>
         <v>429</v>
       </c>
       <c r="R52" s="5">
@@ -9991,7 +9991,7 @@
         <v>75</v>
       </c>
       <c r="J53" s="5">
-        <f>SUM(E53:I53)</f>
+        <f t="shared" si="0"/>
         <v>385</v>
       </c>
       <c r="K53" s="5">
@@ -10009,7 +10009,7 @@
       <c r="O53" s="5"/>
       <c r="P53" s="5"/>
       <c r="Q53" s="5">
-        <f>MAX(25, INT(POWER(2.2,J53/45)))</f>
+        <f t="shared" si="3"/>
         <v>850</v>
       </c>
       <c r="R53" s="5">
@@ -10063,7 +10063,7 @@
         <v>61</v>
       </c>
       <c r="J54" s="5">
-        <f>SUM(E54:I54)</f>
+        <f t="shared" si="0"/>
         <v>315</v>
       </c>
       <c r="K54" s="5">
@@ -10081,7 +10081,7 @@
       <c r="O54" s="5"/>
       <c r="P54" s="5"/>
       <c r="Q54" s="5">
-        <f>MAX(25, INT(POWER(2.2,J54/45)))</f>
+        <f t="shared" si="3"/>
         <v>249</v>
       </c>
       <c r="R54" s="5">
@@ -10135,7 +10135,7 @@
         <v>61</v>
       </c>
       <c r="J55" s="5">
-        <f>SUM(E55:I55)</f>
+        <f t="shared" si="0"/>
         <v>367</v>
       </c>
       <c r="K55" s="5">
@@ -10153,7 +10153,7 @@
       <c r="O55" s="5"/>
       <c r="P55" s="5"/>
       <c r="Q55" s="5">
-        <f>MAX(25, INT(POWER(2.2,J55/45)))</f>
+        <f t="shared" si="3"/>
         <v>620</v>
       </c>
       <c r="R55" s="5">
@@ -10207,7 +10207,7 @@
         <v>75</v>
       </c>
       <c r="J56" s="5">
-        <f>SUM(E56:I56)</f>
+        <f t="shared" si="0"/>
         <v>383</v>
       </c>
       <c r="K56" s="5">
@@ -10225,7 +10225,7 @@
       <c r="O56" s="5"/>
       <c r="P56" s="5"/>
       <c r="Q56" s="5">
-        <f>MAX(25, INT(POWER(2.2,J56/45)))</f>
+        <f t="shared" si="3"/>
         <v>821</v>
       </c>
       <c r="R56" s="5">
@@ -10279,7 +10279,7 @@
         <v>72</v>
       </c>
       <c r="J57" s="5">
-        <f>SUM(E57:I57)</f>
+        <f t="shared" si="0"/>
         <v>313</v>
       </c>
       <c r="K57" s="5">
@@ -10297,7 +10297,7 @@
       <c r="O57" s="5"/>
       <c r="P57" s="5"/>
       <c r="Q57" s="5">
-        <f>MAX(25, INT(POWER(2.2,J57/45)))</f>
+        <f t="shared" si="3"/>
         <v>240</v>
       </c>
       <c r="R57" s="5">
@@ -10351,7 +10351,7 @@
         <v>71</v>
       </c>
       <c r="J58" s="5">
-        <f>SUM(E58:I58)</f>
+        <f t="shared" si="0"/>
         <v>361</v>
       </c>
       <c r="K58" s="5">
@@ -10369,7 +10369,7 @@
       <c r="O58" s="5"/>
       <c r="P58" s="5"/>
       <c r="Q58" s="5">
-        <f>MAX(25, INT(POWER(2.2,J58/45)))</f>
+        <f t="shared" si="3"/>
         <v>558</v>
       </c>
       <c r="R58" s="5">
@@ -10423,7 +10423,7 @@
         <v>81</v>
       </c>
       <c r="J59" s="5">
-        <f>SUM(E59:I59)</f>
+        <f t="shared" si="0"/>
         <v>354</v>
       </c>
       <c r="K59" s="5">
@@ -10441,7 +10441,7 @@
       <c r="O59" s="5"/>
       <c r="P59" s="5"/>
       <c r="Q59" s="5">
-        <f>MAX(25, INT(POWER(2.2,J59/45)))</f>
+        <f t="shared" si="3"/>
         <v>493</v>
       </c>
       <c r="R59" s="5">
@@ -10495,7 +10495,7 @@
         <v>80</v>
       </c>
       <c r="J60" s="5">
-        <f>SUM(E60:I60)</f>
+        <f t="shared" si="0"/>
         <v>353</v>
       </c>
       <c r="K60" s="5">
@@ -10513,7 +10513,7 @@
       <c r="O60" s="5"/>
       <c r="P60" s="5"/>
       <c r="Q60" s="5">
-        <f>MAX(25, INT(POWER(2.2,J60/45)))</f>
+        <f t="shared" si="3"/>
         <v>485</v>
       </c>
       <c r="R60" s="5">
@@ -10567,7 +10567,7 @@
         <v>83</v>
       </c>
       <c r="J61" s="5">
-        <f>SUM(E61:I61)</f>
+        <f t="shared" si="0"/>
         <v>357</v>
       </c>
       <c r="K61" s="5">
@@ -10585,7 +10585,7 @@
       <c r="O61" s="5"/>
       <c r="P61" s="5"/>
       <c r="Q61" s="5">
-        <f>MAX(25, INT(POWER(2.2,J61/45)))</f>
+        <f t="shared" si="3"/>
         <v>520</v>
       </c>
       <c r="R61" s="5">
@@ -10639,7 +10639,7 @@
         <v>66</v>
       </c>
       <c r="J62" s="5">
-        <f>SUM(E62:I62)</f>
+        <f t="shared" si="0"/>
         <v>306</v>
       </c>
       <c r="K62" s="5">
@@ -10657,7 +10657,7 @@
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
       <c r="Q62" s="5">
-        <f>MAX(25, INT(POWER(2.2,J62/45)))</f>
+        <f t="shared" si="3"/>
         <v>213</v>
       </c>
       <c r="R62" s="5">
@@ -10711,7 +10711,7 @@
         <v>52</v>
       </c>
       <c r="J63" s="5">
-        <f>SUM(E63:I63)</f>
+        <f t="shared" si="0"/>
         <v>266</v>
       </c>
       <c r="K63" s="5">
@@ -10729,7 +10729,7 @@
       <c r="O63" s="5"/>
       <c r="P63" s="5"/>
       <c r="Q63" s="5">
-        <f>MAX(25, INT(POWER(2.2,J63/45)))</f>
+        <f t="shared" si="3"/>
         <v>105</v>
       </c>
       <c r="R63" s="5">
@@ -10783,7 +10783,7 @@
         <v>76</v>
       </c>
       <c r="J64" s="5">
-        <f>SUM(E64:I64)</f>
+        <f t="shared" si="0"/>
         <v>335</v>
       </c>
       <c r="K64" s="5">
@@ -10801,7 +10801,7 @@
       <c r="O64" s="5"/>
       <c r="P64" s="5"/>
       <c r="Q64" s="5">
-        <f>MAX(25, INT(POWER(2.2,J64/45)))</f>
+        <f t="shared" si="3"/>
         <v>354</v>
       </c>
       <c r="R64" s="5">
@@ -10855,7 +10855,7 @@
         <v>83</v>
       </c>
       <c r="J65" s="5">
-        <f>SUM(E65:I65)</f>
+        <f t="shared" si="0"/>
         <v>358</v>
       </c>
       <c r="K65" s="5">
@@ -10873,7 +10873,7 @@
       <c r="O65" s="5"/>
       <c r="P65" s="5"/>
       <c r="Q65" s="5">
-        <f>MAX(25, INT(POWER(2.2,J65/45)))</f>
+        <f t="shared" si="3"/>
         <v>529</v>
       </c>
       <c r="R65" s="5">
@@ -10927,7 +10927,7 @@
         <v>70</v>
       </c>
       <c r="J66" s="5">
-        <f>SUM(E66:I66)</f>
+        <f t="shared" si="0"/>
         <v>299</v>
       </c>
       <c r="K66" s="5">
@@ -10945,7 +10945,7 @@
       <c r="O66" s="5"/>
       <c r="P66" s="5"/>
       <c r="Q66" s="5">
-        <f>MAX(25, INT(POWER(2.2,J66/45)))</f>
+        <f t="shared" si="3"/>
         <v>188</v>
       </c>
       <c r="R66" s="5">
@@ -10999,7 +10999,7 @@
         <v>76</v>
       </c>
       <c r="J67" s="5">
-        <f>SUM(E67:I67)</f>
+        <f t="shared" si="0"/>
         <v>333</v>
       </c>
       <c r="K67" s="5">
@@ -11017,7 +11017,7 @@
       <c r="O67" s="5"/>
       <c r="P67" s="5"/>
       <c r="Q67" s="5">
-        <f>MAX(25, INT(POWER(2.2,J67/45)))</f>
+        <f t="shared" si="3"/>
         <v>341</v>
       </c>
       <c r="R67" s="5">
@@ -11071,7 +11071,7 @@
         <v>60</v>
       </c>
       <c r="J68" s="5">
-        <f>SUM(E68:I68)</f>
+        <f t="shared" si="0"/>
         <v>297</v>
       </c>
       <c r="K68" s="5">
@@ -11089,7 +11089,7 @@
       <c r="O68" s="5"/>
       <c r="P68" s="5"/>
       <c r="Q68" s="5">
-        <f>MAX(25, INT(POWER(2.2,J68/45)))</f>
+        <f t="shared" si="3"/>
         <v>181</v>
       </c>
       <c r="R68" s="5">
@@ -11143,7 +11143,7 @@
         <v>64</v>
       </c>
       <c r="J69" s="5">
-        <f>SUM(E69:I69)</f>
+        <f t="shared" ref="J69:J132" si="4">SUM(E69:I69)</f>
         <v>311</v>
       </c>
       <c r="K69" s="5">
@@ -11161,7 +11161,7 @@
       <c r="O69" s="5"/>
       <c r="P69" s="5"/>
       <c r="Q69" s="5">
-        <f>MAX(25, INT(POWER(2.2,J69/45)))</f>
+        <f t="shared" si="3"/>
         <v>232</v>
       </c>
       <c r="R69" s="5">
@@ -11215,7 +11215,7 @@
         <v>60</v>
       </c>
       <c r="J70" s="5">
-        <f>SUM(E70:I70)</f>
+        <f t="shared" si="4"/>
         <v>319</v>
       </c>
       <c r="K70" s="5">
@@ -11233,7 +11233,7 @@
       <c r="O70" s="5"/>
       <c r="P70" s="5"/>
       <c r="Q70" s="5">
-        <f>MAX(25, INT(POWER(2.2,J70/45)))</f>
+        <f t="shared" si="3"/>
         <v>267</v>
       </c>
       <c r="R70" s="5">
@@ -11287,7 +11287,7 @@
         <v>79</v>
       </c>
       <c r="J71" s="5">
-        <f>SUM(E71:I71)</f>
+        <f t="shared" si="4"/>
         <v>315</v>
       </c>
       <c r="K71" s="5">
@@ -11305,7 +11305,7 @@
       <c r="O71" s="5"/>
       <c r="P71" s="5"/>
       <c r="Q71" s="5">
-        <f>MAX(25, INT(POWER(2.2,J71/45)))</f>
+        <f t="shared" si="3"/>
         <v>249</v>
       </c>
       <c r="R71" s="5">
@@ -11359,7 +11359,7 @@
         <v>63</v>
       </c>
       <c r="J72" s="5">
-        <f>SUM(E72:I72)</f>
+        <f t="shared" si="4"/>
         <v>299</v>
       </c>
       <c r="K72" s="5">
@@ -11377,7 +11377,7 @@
       <c r="O72" s="5"/>
       <c r="P72" s="5"/>
       <c r="Q72" s="5">
-        <f>MAX(25, INT(POWER(2.2,J72/45)))</f>
+        <f t="shared" si="3"/>
         <v>188</v>
       </c>
       <c r="R72" s="5">
@@ -11431,7 +11431,7 @@
         <v>73</v>
       </c>
       <c r="J73" s="5">
-        <f>SUM(E73:I73)</f>
+        <f t="shared" si="4"/>
         <v>295</v>
       </c>
       <c r="K73" s="5">
@@ -11449,7 +11449,7 @@
       <c r="O73" s="5"/>
       <c r="P73" s="5"/>
       <c r="Q73" s="5">
-        <f>MAX(25, INT(POWER(2.2,J73/45)))</f>
+        <f t="shared" si="3"/>
         <v>175</v>
       </c>
       <c r="R73" s="5">
@@ -11503,7 +11503,7 @@
         <v>50</v>
       </c>
       <c r="J74" s="5">
-        <f>SUM(E74:I74)</f>
+        <f t="shared" si="4"/>
         <v>233</v>
       </c>
       <c r="K74" s="5">
@@ -11521,7 +11521,7 @@
       <c r="O74" s="5"/>
       <c r="P74" s="5"/>
       <c r="Q74" s="5">
-        <f>MAX(25, INT(POWER(2.2,J74/45)))</f>
+        <f t="shared" si="3"/>
         <v>59</v>
       </c>
       <c r="R74" s="5">
@@ -11575,7 +11575,7 @@
         <v>14</v>
       </c>
       <c r="J75" s="5">
-        <f>SUM(E75:I75)</f>
+        <f t="shared" si="4"/>
         <v>218</v>
       </c>
       <c r="K75" s="5">
@@ -11593,7 +11593,7 @@
       <c r="O75" s="5"/>
       <c r="P75" s="5"/>
       <c r="Q75" s="5">
-        <f>MAX(25, INT(POWER(2.2,J75/45)))</f>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
       <c r="R75" s="5">
@@ -11647,7 +11647,7 @@
         <v>51</v>
       </c>
       <c r="J76" s="5">
-        <f>SUM(E76:I76)</f>
+        <f t="shared" si="4"/>
         <v>294</v>
       </c>
       <c r="K76" s="5">
@@ -11665,7 +11665,7 @@
       <c r="O76" s="5"/>
       <c r="P76" s="5"/>
       <c r="Q76" s="5">
-        <f>MAX(25, INT(POWER(2.2,J76/45)))</f>
+        <f t="shared" si="3"/>
         <v>172</v>
       </c>
       <c r="R76" s="5">
@@ -11719,7 +11719,7 @@
         <v>87</v>
       </c>
       <c r="J77" s="5">
-        <f>SUM(E77:I77)</f>
+        <f t="shared" si="4"/>
         <v>295</v>
       </c>
       <c r="K77" s="5">
@@ -11737,7 +11737,7 @@
       <c r="O77" s="5"/>
       <c r="P77" s="5"/>
       <c r="Q77" s="5">
-        <f>MAX(25, INT(POWER(2.2,J77/45)))</f>
+        <f t="shared" si="3"/>
         <v>175</v>
       </c>
       <c r="R77" s="5">
@@ -11791,7 +11791,7 @@
         <v>68</v>
       </c>
       <c r="J78" s="5">
-        <f>SUM(E78:I78)</f>
+        <f t="shared" si="4"/>
         <v>278</v>
       </c>
       <c r="K78" s="5">
@@ -11809,7 +11809,7 @@
       <c r="O78" s="5"/>
       <c r="P78" s="5"/>
       <c r="Q78" s="5">
-        <f>MAX(25, INT(POWER(2.2,J78/45)))</f>
+        <f t="shared" si="3"/>
         <v>130</v>
       </c>
       <c r="R78" s="5">
@@ -11863,7 +11863,7 @@
         <v>63</v>
       </c>
       <c r="J79" s="5">
-        <f>SUM(E79:I79)</f>
+        <f t="shared" si="4"/>
         <v>241</v>
       </c>
       <c r="K79" s="5">
@@ -11881,7 +11881,7 @@
       <c r="O79" s="5"/>
       <c r="P79" s="5"/>
       <c r="Q79" s="5">
-        <f>MAX(25, INT(POWER(2.2,J79/45)))</f>
+        <f t="shared" si="3"/>
         <v>68</v>
       </c>
       <c r="R79" s="5">
@@ -11935,7 +11935,7 @@
         <v>81</v>
       </c>
       <c r="J80" s="5">
-        <f>SUM(E80:I80)</f>
+        <f t="shared" si="4"/>
         <v>277</v>
       </c>
       <c r="K80" s="5">
@@ -11953,7 +11953,7 @@
       <c r="O80" s="5"/>
       <c r="P80" s="5"/>
       <c r="Q80" s="5">
-        <f>MAX(25, INT(POWER(2.2,J80/45)))</f>
+        <f t="shared" si="3"/>
         <v>128</v>
       </c>
       <c r="R80" s="5">
@@ -12007,7 +12007,7 @@
         <v>44</v>
       </c>
       <c r="J81" s="5">
-        <f>SUM(E81:I81)</f>
+        <f t="shared" si="4"/>
         <v>228</v>
       </c>
       <c r="K81" s="5">
@@ -12025,7 +12025,7 @@
       <c r="O81" s="5"/>
       <c r="P81" s="5"/>
       <c r="Q81" s="5">
-        <f>MAX(25, INT(POWER(2.2,J81/45)))</f>
+        <f t="shared" si="3"/>
         <v>54</v>
       </c>
       <c r="R81" s="5">
@@ -12079,7 +12079,7 @@
         <v>57</v>
       </c>
       <c r="J82" s="5">
-        <f>SUM(E82:I82)</f>
+        <f t="shared" si="4"/>
         <v>260</v>
       </c>
       <c r="K82" s="5">
@@ -12097,7 +12097,7 @@
       <c r="O82" s="5"/>
       <c r="P82" s="5"/>
       <c r="Q82" s="5">
-        <f>MAX(25, INT(POWER(2.2,J82/45)))</f>
+        <f t="shared" si="3"/>
         <v>95</v>
       </c>
       <c r="R82" s="5">
@@ -12151,7 +12151,7 @@
         <v>74</v>
       </c>
       <c r="J83" s="5">
-        <f>SUM(E83:I83)</f>
+        <f t="shared" si="4"/>
         <v>298</v>
       </c>
       <c r="K83" s="5">
@@ -12169,7 +12169,7 @@
       <c r="O83" s="5"/>
       <c r="P83" s="5"/>
       <c r="Q83" s="5">
-        <f>MAX(25, INT(POWER(2.2,J83/45)))</f>
+        <f t="shared" si="3"/>
         <v>185</v>
       </c>
       <c r="R83" s="5">
@@ -12223,7 +12223,7 @@
         <v>37</v>
       </c>
       <c r="J84" s="5">
-        <f>SUM(E84:I84)</f>
+        <f t="shared" si="4"/>
         <v>207</v>
       </c>
       <c r="K84" s="5">
@@ -12241,7 +12241,7 @@
       <c r="O84" s="5"/>
       <c r="P84" s="5"/>
       <c r="Q84" s="5">
-        <f>MAX(25, INT(POWER(2.2,J84/45)))</f>
+        <f t="shared" si="3"/>
         <v>37</v>
       </c>
       <c r="R84" s="5">
@@ -12295,7 +12295,7 @@
         <v>67</v>
       </c>
       <c r="J85" s="5">
-        <f>SUM(E85:I85)</f>
+        <f t="shared" si="4"/>
         <v>242</v>
       </c>
       <c r="K85" s="5">
@@ -12313,7 +12313,7 @@
       <c r="O85" s="5"/>
       <c r="P85" s="5"/>
       <c r="Q85" s="5">
-        <f>MAX(25, INT(POWER(2.2,J85/45)))</f>
+        <f t="shared" si="3"/>
         <v>69</v>
       </c>
       <c r="R85" s="5">
@@ -12367,7 +12367,7 @@
         <v>47</v>
       </c>
       <c r="J86" s="5">
-        <f>SUM(E86:I86)</f>
+        <f t="shared" si="4"/>
         <v>191</v>
       </c>
       <c r="K86" s="5">
@@ -12385,7 +12385,7 @@
       <c r="O86" s="5"/>
       <c r="P86" s="5"/>
       <c r="Q86" s="5">
-        <f>MAX(25, INT(POWER(2.2,J86/45)))</f>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
       <c r="R86" s="5">
@@ -12439,7 +12439,7 @@
         <v>93</v>
       </c>
       <c r="J87" s="5">
-        <f>SUM(E87:I87)</f>
+        <f t="shared" si="4"/>
         <v>397</v>
       </c>
       <c r="K87" s="5">
@@ -12512,7 +12512,7 @@
         <v>58</v>
       </c>
       <c r="J88" s="5">
-        <f>SUM(E88:I88)</f>
+        <f t="shared" si="4"/>
         <v>339</v>
       </c>
       <c r="K88" s="5">
@@ -12531,10 +12531,10 @@
         <v>40</v>
       </c>
       <c r="P88" s="5">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q88" s="5">
-        <f>MAX(25, INT(POWER(2.2,J88/45)))</f>
+        <f t="shared" ref="Q88:Q119" si="5">MAX(25, INT(POWER(2.2,J88/45)))</f>
         <v>379</v>
       </c>
       <c r="R88" s="5">
@@ -12594,7 +12594,7 @@
         <v>79</v>
       </c>
       <c r="J89" s="5">
-        <f>SUM(E89:I89)</f>
+        <f t="shared" si="4"/>
         <v>381</v>
       </c>
       <c r="K89" s="5">
@@ -12613,10 +12613,10 @@
         <v>40</v>
       </c>
       <c r="P89" s="5">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q89" s="5">
-        <f>MAX(25, INT(POWER(2.2,J89/45)))</f>
+        <f t="shared" si="5"/>
         <v>792</v>
       </c>
       <c r="R89" s="5">
@@ -12676,7 +12676,7 @@
         <v>80</v>
       </c>
       <c r="J90" s="5">
-        <f>SUM(E90:I90)</f>
+        <f t="shared" si="4"/>
         <v>372</v>
       </c>
       <c r="K90" s="5">
@@ -12694,7 +12694,7 @@
       <c r="O90" s="5"/>
       <c r="P90" s="5"/>
       <c r="Q90" s="5">
-        <f>MAX(25, INT(POWER(2.2,J90/45)))</f>
+        <f t="shared" si="5"/>
         <v>677</v>
       </c>
       <c r="R90" s="5">
@@ -12754,7 +12754,7 @@
         <v>60</v>
       </c>
       <c r="J91" s="5">
-        <f>SUM(E91:I91)</f>
+        <f t="shared" si="4"/>
         <v>313</v>
       </c>
       <c r="K91" s="5">
@@ -12772,7 +12772,7 @@
       <c r="O91" s="5"/>
       <c r="P91" s="5"/>
       <c r="Q91" s="5">
-        <f>MAX(25, INT(POWER(2.2,J91/45)))</f>
+        <f t="shared" si="5"/>
         <v>240</v>
       </c>
       <c r="R91" s="5">
@@ -12832,7 +12832,7 @@
         <v>89</v>
       </c>
       <c r="J92" s="5">
-        <f>SUM(E92:I92)</f>
+        <f t="shared" si="4"/>
         <v>409</v>
       </c>
       <c r="K92" s="5">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="P92" s="5"/>
       <c r="Q92" s="5">
-        <f>MAX(25, INT(POWER(2.2,J92/45)))</f>
+        <f t="shared" si="5"/>
         <v>1294</v>
       </c>
       <c r="R92" s="5">
@@ -12914,7 +12914,7 @@
         <v>93</v>
       </c>
       <c r="J93" s="5">
-        <f>SUM(E93:I93)</f>
+        <f t="shared" si="4"/>
         <v>442</v>
       </c>
       <c r="K93" s="5">
@@ -12934,7 +12934,7 @@
       </c>
       <c r="P93" s="5"/>
       <c r="Q93" s="5">
-        <f>MAX(25, INT(POWER(2.2,J93/45)))</f>
+        <f t="shared" si="5"/>
         <v>2308</v>
       </c>
       <c r="R93" s="5">
@@ -12996,7 +12996,7 @@
         <v>74</v>
       </c>
       <c r="J94" s="5">
-        <f>SUM(E94:I94)</f>
+        <f t="shared" si="4"/>
         <v>329</v>
       </c>
       <c r="K94" s="5">
@@ -13014,7 +13014,7 @@
       <c r="O94" s="5"/>
       <c r="P94" s="5"/>
       <c r="Q94" s="5">
-        <f>MAX(25, INT(POWER(2.2,J94/45)))</f>
+        <f t="shared" si="5"/>
         <v>318</v>
       </c>
       <c r="R94" s="5">
@@ -13072,7 +13072,7 @@
         <v>82</v>
       </c>
       <c r="J95" s="5">
-        <f>SUM(E95:I95)</f>
+        <f t="shared" si="4"/>
         <v>412</v>
       </c>
       <c r="K95" s="5">
@@ -13090,7 +13090,7 @@
       <c r="O95" s="5"/>
       <c r="P95" s="5"/>
       <c r="Q95" s="5">
-        <f>MAX(25, INT(POWER(2.2,J95/45)))</f>
+        <f t="shared" si="5"/>
         <v>1364</v>
       </c>
       <c r="R95" s="5">
@@ -13152,7 +13152,7 @@
         <v>90</v>
       </c>
       <c r="J96" s="5">
-        <f>SUM(E96:I96)</f>
+        <f t="shared" si="4"/>
         <v>434</v>
       </c>
       <c r="K96" s="5">
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P96" s="5"/>
       <c r="Q96" s="5">
-        <f>MAX(25, INT(POWER(2.2,J96/45)))</f>
+        <f t="shared" si="5"/>
         <v>2006</v>
       </c>
       <c r="R96" s="5">
@@ -13232,7 +13232,7 @@
         <v>79</v>
       </c>
       <c r="J97" s="5">
-        <f>SUM(E97:I97)</f>
+        <f t="shared" si="4"/>
         <v>294</v>
       </c>
       <c r="K97" s="5">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="P97" s="5"/>
       <c r="Q97" s="5">
-        <f>MAX(25, INT(POWER(2.2,J97/45)))</f>
+        <f t="shared" si="5"/>
         <v>172</v>
       </c>
       <c r="R97" s="5">
@@ -13310,7 +13310,7 @@
         <v>90</v>
       </c>
       <c r="J98" s="5">
-        <f>SUM(E98:I98)</f>
+        <f t="shared" si="4"/>
         <v>367</v>
       </c>
       <c r="K98" s="5">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="P98" s="5"/>
       <c r="Q98" s="5">
-        <f>MAX(25, INT(POWER(2.2,J98/45)))</f>
+        <f t="shared" si="5"/>
         <v>620</v>
       </c>
       <c r="R98" s="5">
@@ -13390,7 +13390,7 @@
         <v>70</v>
       </c>
       <c r="J99" s="5">
-        <f>SUM(E99:I99)</f>
+        <f t="shared" si="4"/>
         <v>347</v>
       </c>
       <c r="K99" s="5">
@@ -13409,10 +13409,10 @@
         <v>40</v>
       </c>
       <c r="P99" s="5">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q99" s="5">
-        <f>MAX(25, INT(POWER(2.2,J99/45)))</f>
+        <f t="shared" si="5"/>
         <v>436</v>
       </c>
       <c r="R99" s="5">
@@ -13470,7 +13470,7 @@
         <v>59</v>
       </c>
       <c r="J100" s="5">
-        <f>SUM(E100:I100)</f>
+        <f t="shared" si="4"/>
         <v>356</v>
       </c>
       <c r="K100" s="5">
@@ -13488,7 +13488,7 @@
       <c r="O100" s="5"/>
       <c r="P100" s="5"/>
       <c r="Q100" s="5">
-        <f>MAX(25, INT(POWER(2.2,J100/45)))</f>
+        <f t="shared" si="5"/>
         <v>511</v>
       </c>
       <c r="R100" s="5">
@@ -13550,7 +13550,7 @@
         <v>92</v>
       </c>
       <c r="J101" s="5">
-        <f>SUM(E101:I101)</f>
+        <f t="shared" si="4"/>
         <v>270</v>
       </c>
       <c r="K101" s="5">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="P101" s="5"/>
       <c r="Q101" s="5">
-        <f>MAX(25, INT(POWER(2.2,J101/45)))</f>
+        <f t="shared" si="5"/>
         <v>113</v>
       </c>
       <c r="R101" s="5">
@@ -13632,7 +13632,7 @@
         <v>92</v>
       </c>
       <c r="J102" s="5">
-        <f>SUM(E102:I102)</f>
+        <f t="shared" si="4"/>
         <v>270</v>
       </c>
       <c r="K102" s="5">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="P102" s="5"/>
       <c r="Q102" s="5">
-        <f>MAX(25, INT(POWER(2.2,J102/45)))</f>
+        <f t="shared" si="5"/>
         <v>113</v>
       </c>
       <c r="R102" s="5">
@@ -13714,7 +13714,7 @@
         <v>52</v>
       </c>
       <c r="J103" s="5">
-        <f>SUM(E103:I103)</f>
+        <f t="shared" si="4"/>
         <v>340</v>
       </c>
       <c r="K103" s="5">
@@ -13733,10 +13733,10 @@
         <v>26</v>
       </c>
       <c r="P103" s="5">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="Q103" s="5">
-        <f>MAX(25, INT(POWER(2.2,J103/45)))</f>
+        <f t="shared" si="5"/>
         <v>386</v>
       </c>
       <c r="R103" s="5">
@@ -13794,7 +13794,7 @@
         <v>60</v>
       </c>
       <c r="J104" s="5">
-        <f>SUM(E104:I104)</f>
+        <f t="shared" si="4"/>
         <v>315</v>
       </c>
       <c r="K104" s="5">
@@ -13812,7 +13812,7 @@
       <c r="O104" s="5"/>
       <c r="P104" s="5"/>
       <c r="Q104" s="5">
-        <f>MAX(25, INT(POWER(2.2,J104/45)))</f>
+        <f t="shared" si="5"/>
         <v>249</v>
       </c>
       <c r="R104" s="5">
@@ -13871,7 +13871,7 @@
         <v>66</v>
       </c>
       <c r="J105" s="5">
-        <f>SUM(E105:I105)</f>
+        <f t="shared" si="4"/>
         <v>312</v>
       </c>
       <c r="K105" s="5">
@@ -13890,10 +13890,10 @@
         <v>50</v>
       </c>
       <c r="P105" s="5">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q105" s="5">
-        <f>MAX(25, INT(POWER(2.2,J105/45)))</f>
+        <f t="shared" si="5"/>
         <v>236</v>
       </c>
       <c r="R105" s="5">
@@ -13952,7 +13952,7 @@
         <v>12</v>
       </c>
       <c r="J106" s="5">
-        <f>SUM(E106:I106)</f>
+        <f t="shared" si="4"/>
         <v>266</v>
       </c>
       <c r="K106" s="5">
@@ -13970,7 +13970,7 @@
       <c r="O106" s="5"/>
       <c r="P106" s="5"/>
       <c r="Q106" s="5">
-        <f>MAX(25, INT(POWER(2.2,J106/45)))</f>
+        <f t="shared" si="5"/>
         <v>105</v>
       </c>
       <c r="R106" s="5">
@@ -14032,7 +14032,7 @@
         <v>64</v>
       </c>
       <c r="J107" s="5">
-        <f>SUM(E107:I107)</f>
+        <f t="shared" si="4"/>
         <v>289</v>
       </c>
       <c r="K107" s="5">
@@ -14051,10 +14051,10 @@
         <v>40</v>
       </c>
       <c r="P107" s="5">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q107" s="5">
-        <f>MAX(25, INT(POWER(2.2,J107/45)))</f>
+        <f t="shared" si="5"/>
         <v>158</v>
       </c>
       <c r="R107" s="5">
@@ -14114,7 +14114,7 @@
         <v>73</v>
       </c>
       <c r="J108" s="5">
-        <f>SUM(E108:I108)</f>
+        <f t="shared" si="4"/>
         <v>384</v>
       </c>
       <c r="K108" s="5">
@@ -14132,7 +14132,7 @@
       <c r="O108" s="5"/>
       <c r="P108" s="5"/>
       <c r="Q108" s="5">
-        <f>MAX(25, INT(POWER(2.2,J108/45)))</f>
+        <f t="shared" si="5"/>
         <v>835</v>
       </c>
       <c r="R108" s="5">
@@ -14192,7 +14192,7 @@
         <v>81</v>
       </c>
       <c r="J109" s="5">
-        <f>SUM(E109:I109)</f>
+        <f t="shared" si="4"/>
         <v>380</v>
       </c>
       <c r="K109" s="5">
@@ -14210,7 +14210,7 @@
       <c r="O109" s="5"/>
       <c r="P109" s="5"/>
       <c r="Q109" s="5">
-        <f>MAX(25, INT(POWER(2.2,J109/45)))</f>
+        <f t="shared" si="5"/>
         <v>779</v>
       </c>
       <c r="R109" s="5">
@@ -14272,7 +14272,7 @@
         <v>79</v>
       </c>
       <c r="J110" s="5">
-        <f>SUM(E110:I110)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="K110" s="5">
@@ -14292,7 +14292,7 @@
       </c>
       <c r="P110" s="5"/>
       <c r="Q110" s="5">
-        <f>MAX(25, INT(POWER(2.2,J110/45)))</f>
+        <f t="shared" si="5"/>
         <v>191</v>
       </c>
       <c r="R110" s="5">
@@ -14352,7 +14352,7 @@
         <v>76</v>
       </c>
       <c r="J111" s="5">
-        <f>SUM(E111:I111)</f>
+        <f t="shared" si="4"/>
         <v>309</v>
       </c>
       <c r="K111" s="5">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="P111" s="5"/>
       <c r="Q111" s="5">
-        <f>MAX(25, INT(POWER(2.2,J111/45)))</f>
+        <f t="shared" si="5"/>
         <v>224</v>
       </c>
       <c r="R111" s="5">
@@ -14432,7 +14432,7 @@
         <v>65</v>
       </c>
       <c r="J112" s="5">
-        <f>SUM(E112:I112)</f>
+        <f t="shared" si="4"/>
         <v>359</v>
       </c>
       <c r="K112" s="5">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="P112" s="5"/>
       <c r="Q112" s="5">
-        <f>MAX(25, INT(POWER(2.2,J112/45)))</f>
+        <f t="shared" si="5"/>
         <v>539</v>
       </c>
       <c r="R112" s="5">
@@ -14512,7 +14512,7 @@
         <v>71</v>
       </c>
       <c r="J113" s="5">
-        <f>SUM(E113:I113)</f>
+        <f t="shared" si="4"/>
         <v>333</v>
       </c>
       <c r="K113" s="5">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="P113" s="5"/>
       <c r="Q113" s="5">
-        <f>MAX(25, INT(POWER(2.2,J113/45)))</f>
+        <f t="shared" si="5"/>
         <v>341</v>
       </c>
       <c r="R113" s="5">
@@ -14592,7 +14592,7 @@
         <v>67</v>
       </c>
       <c r="J114" s="5">
-        <f>SUM(E114:I114)</f>
+        <f t="shared" si="4"/>
         <v>329</v>
       </c>
       <c r="K114" s="5">
@@ -14610,7 +14610,7 @@
       <c r="O114" s="5"/>
       <c r="P114" s="5"/>
       <c r="Q114" s="5">
-        <f>MAX(25, INT(POWER(2.2,J114/45)))</f>
+        <f t="shared" si="5"/>
         <v>318</v>
       </c>
       <c r="R114" s="5">
@@ -14670,7 +14670,7 @@
         <v>70</v>
       </c>
       <c r="J115" s="5">
-        <f>SUM(E115:I115)</f>
+        <f t="shared" si="4"/>
         <v>340</v>
       </c>
       <c r="K115" s="5">
@@ -14688,7 +14688,7 @@
       <c r="O115" s="5"/>
       <c r="P115" s="5"/>
       <c r="Q115" s="5">
-        <f>MAX(25, INT(POWER(2.2,J115/45)))</f>
+        <f t="shared" si="5"/>
         <v>386</v>
       </c>
       <c r="R115" s="5">
@@ -14748,7 +14748,7 @@
         <v>62</v>
       </c>
       <c r="J116" s="5">
-        <f>SUM(E116:I116)</f>
+        <f t="shared" si="4"/>
         <v>306</v>
       </c>
       <c r="K116" s="5">
@@ -14766,7 +14766,7 @@
       <c r="O116" s="5"/>
       <c r="P116" s="5"/>
       <c r="Q116" s="5">
-        <f>MAX(25, INT(POWER(2.2,J116/45)))</f>
+        <f t="shared" si="5"/>
         <v>213</v>
       </c>
       <c r="R116" s="5">
@@ -14826,7 +14826,7 @@
         <v>73</v>
       </c>
       <c r="J117" s="5">
-        <f>SUM(E117:I117)</f>
+        <f t="shared" si="4"/>
         <v>344</v>
       </c>
       <c r="K117" s="5">
@@ -14844,7 +14844,7 @@
       <c r="O117" s="5"/>
       <c r="P117" s="5"/>
       <c r="Q117" s="5">
-        <f>MAX(25, INT(POWER(2.2,J117/45)))</f>
+        <f t="shared" si="5"/>
         <v>414</v>
       </c>
       <c r="R117" s="5">
@@ -14904,7 +14904,7 @@
         <v>70</v>
       </c>
       <c r="J118" s="5">
-        <f>SUM(E118:I118)</f>
+        <f t="shared" si="4"/>
         <v>357</v>
       </c>
       <c r="K118" s="5">
@@ -14922,7 +14922,7 @@
       <c r="O118" s="5"/>
       <c r="P118" s="5"/>
       <c r="Q118" s="5">
-        <f>MAX(25, INT(POWER(2.2,J118/45)))</f>
+        <f t="shared" si="5"/>
         <v>520</v>
       </c>
       <c r="R118" s="5">
@@ -14982,7 +14982,7 @@
         <v>72</v>
       </c>
       <c r="J119" s="5">
-        <f>SUM(E119:I119)</f>
+        <f t="shared" si="4"/>
         <v>242</v>
       </c>
       <c r="K119" s="5">
@@ -15002,7 +15002,7 @@
       </c>
       <c r="P119" s="5"/>
       <c r="Q119" s="5">
-        <f>MAX(25, INT(POWER(2.2,J119/45)))</f>
+        <f t="shared" si="5"/>
         <v>69</v>
       </c>
       <c r="R119" s="5">
@@ -15062,7 +15062,7 @@
         <v>69</v>
       </c>
       <c r="J120" s="5">
-        <f>SUM(E120:I120)</f>
+        <f t="shared" si="4"/>
         <v>356</v>
       </c>
       <c r="K120" s="5">
@@ -15080,7 +15080,7 @@
       <c r="O120" s="5"/>
       <c r="P120" s="5"/>
       <c r="Q120" s="5">
-        <f>MAX(25, INT(POWER(2.2,J120/45)))</f>
+        <f t="shared" ref="Q120:Q138" si="6">MAX(25, INT(POWER(2.2,J120/45)))</f>
         <v>511</v>
       </c>
       <c r="R120" s="5">
@@ -15134,7 +15134,7 @@
         <v>36</v>
       </c>
       <c r="J121" s="5">
-        <f>SUM(E121:I121)</f>
+        <f t="shared" si="4"/>
         <v>268</v>
       </c>
       <c r="K121" s="5">
@@ -15152,7 +15152,7 @@
       <c r="O121" s="5"/>
       <c r="P121" s="5"/>
       <c r="Q121" s="5">
-        <f>MAX(25, INT(POWER(2.2,J121/45)))</f>
+        <f t="shared" si="6"/>
         <v>109</v>
       </c>
       <c r="R121" s="5">
@@ -15206,7 +15206,7 @@
         <v>52</v>
       </c>
       <c r="J122" s="5">
-        <f>SUM(E122:I122)</f>
+        <f t="shared" si="4"/>
         <v>266</v>
       </c>
       <c r="K122" s="5">
@@ -15224,7 +15224,7 @@
       <c r="O122" s="5"/>
       <c r="P122" s="5"/>
       <c r="Q122" s="5">
-        <f>MAX(25, INT(POWER(2.2,J122/45)))</f>
+        <f t="shared" si="6"/>
         <v>105</v>
       </c>
       <c r="R122" s="5">
@@ -15278,7 +15278,7 @@
         <v>73</v>
       </c>
       <c r="J123" s="5">
-        <f>SUM(E123:I123)</f>
+        <f t="shared" si="4"/>
         <v>340</v>
       </c>
       <c r="K123" s="5">
@@ -15296,7 +15296,7 @@
       <c r="O123" s="5"/>
       <c r="P123" s="5"/>
       <c r="Q123" s="5">
-        <f>MAX(25, INT(POWER(2.2,J123/45)))</f>
+        <f t="shared" si="6"/>
         <v>386</v>
       </c>
       <c r="R123" s="5">
@@ -15350,7 +15350,7 @@
         <v>62</v>
       </c>
       <c r="J124" s="5">
-        <f>SUM(E124:I124)</f>
+        <f t="shared" si="4"/>
         <v>336</v>
       </c>
       <c r="K124" s="5">
@@ -15368,7 +15368,7 @@
       <c r="O124" s="5"/>
       <c r="P124" s="5"/>
       <c r="Q124" s="5">
-        <f>MAX(25, INT(POWER(2.2,J124/45)))</f>
+        <f t="shared" si="6"/>
         <v>360</v>
       </c>
       <c r="R124" s="5">
@@ -15422,7 +15422,7 @@
         <v>46</v>
       </c>
       <c r="J125" s="5">
-        <f>SUM(E125:I125)</f>
+        <f t="shared" si="4"/>
         <v>304</v>
       </c>
       <c r="K125" s="5">
@@ -15440,7 +15440,7 @@
       <c r="O125" s="5"/>
       <c r="P125" s="5"/>
       <c r="Q125" s="5">
-        <f>MAX(25, INT(POWER(2.2,J125/45)))</f>
+        <f t="shared" si="6"/>
         <v>205</v>
       </c>
       <c r="R125" s="5">
@@ -15494,7 +15494,7 @@
         <v>41</v>
       </c>
       <c r="J126" s="5">
-        <f>SUM(E126:I126)</f>
+        <f t="shared" si="4"/>
         <v>238</v>
       </c>
       <c r="K126" s="5">
@@ -15512,7 +15512,7 @@
       <c r="O126" s="5"/>
       <c r="P126" s="5"/>
       <c r="Q126" s="5">
-        <f>MAX(25, INT(POWER(2.2,J126/45)))</f>
+        <f t="shared" si="6"/>
         <v>64</v>
       </c>
       <c r="R126" s="5">
@@ -15566,7 +15566,7 @@
         <v>65</v>
       </c>
       <c r="J127" s="5">
-        <f>SUM(E127:I127)</f>
+        <f t="shared" si="4"/>
         <v>240</v>
       </c>
       <c r="K127" s="5">
@@ -15584,7 +15584,7 @@
       <c r="O127" s="5"/>
       <c r="P127" s="5"/>
       <c r="Q127" s="5">
-        <f>MAX(25, INT(POWER(2.2,J127/45)))</f>
+        <f t="shared" si="6"/>
         <v>67</v>
       </c>
       <c r="R127" s="5">
@@ -15638,7 +15638,7 @@
         <v>62</v>
       </c>
       <c r="J128" s="5">
-        <f>SUM(E128:I128)</f>
+        <f t="shared" si="4"/>
         <v>355</v>
       </c>
       <c r="K128" s="5">
@@ -15656,7 +15656,7 @@
       <c r="O128" s="5"/>
       <c r="P128" s="5"/>
       <c r="Q128" s="5">
-        <f>MAX(25, INT(POWER(2.2,J128/45)))</f>
+        <f t="shared" si="6"/>
         <v>502</v>
       </c>
       <c r="R128" s="5">
@@ -15710,7 +15710,7 @@
         <v>78</v>
       </c>
       <c r="J129" s="5">
-        <f>SUM(E129:I129)</f>
+        <f t="shared" si="4"/>
         <v>362</v>
       </c>
       <c r="K129" s="5">
@@ -15728,7 +15728,7 @@
       <c r="O129" s="5"/>
       <c r="P129" s="5"/>
       <c r="Q129" s="5">
-        <f>MAX(25, INT(POWER(2.2,J129/45)))</f>
+        <f t="shared" si="6"/>
         <v>568</v>
       </c>
       <c r="R129" s="5">
@@ -15782,7 +15782,7 @@
         <v>70</v>
       </c>
       <c r="J130" s="5">
-        <f>SUM(E130:I130)</f>
+        <f t="shared" si="4"/>
         <v>325</v>
       </c>
       <c r="K130" s="5">
@@ -15800,7 +15800,7 @@
       <c r="O130" s="5"/>
       <c r="P130" s="5"/>
       <c r="Q130" s="5">
-        <f>MAX(25, INT(POWER(2.2,J130/45)))</f>
+        <f t="shared" si="6"/>
         <v>297</v>
       </c>
       <c r="R130" s="5">
@@ -15854,7 +15854,7 @@
         <v>22</v>
       </c>
       <c r="J131" s="5">
-        <f>SUM(E131:I131)</f>
+        <f t="shared" si="4"/>
         <v>186</v>
       </c>
       <c r="K131" s="5">
@@ -15872,7 +15872,7 @@
       <c r="O131" s="5"/>
       <c r="P131" s="5"/>
       <c r="Q131" s="5">
-        <f>MAX(25, INT(POWER(2.2,J131/45)))</f>
+        <f t="shared" si="6"/>
         <v>26</v>
       </c>
       <c r="R131" s="5">
@@ -15926,7 +15926,7 @@
         <v>74</v>
       </c>
       <c r="J132" s="5">
-        <f>SUM(E132:I132)</f>
+        <f t="shared" si="4"/>
         <v>370</v>
       </c>
       <c r="K132" s="5">
@@ -15944,7 +15944,7 @@
       <c r="O132" s="5"/>
       <c r="P132" s="5"/>
       <c r="Q132" s="5">
-        <f>MAX(25, INT(POWER(2.2,J132/45)))</f>
+        <f t="shared" si="6"/>
         <v>653</v>
       </c>
       <c r="R132" s="5">
@@ -15998,7 +15998,7 @@
         <v>71</v>
       </c>
       <c r="J133" s="5">
-        <f>SUM(E133:I133)</f>
+        <f t="shared" ref="J133:J196" si="7">SUM(E133:I133)</f>
         <v>349</v>
       </c>
       <c r="K133" s="5">
@@ -16016,7 +16016,7 @@
       <c r="O133" s="5"/>
       <c r="P133" s="5"/>
       <c r="Q133" s="5">
-        <f>MAX(25, INT(POWER(2.2,J133/45)))</f>
+        <f t="shared" si="6"/>
         <v>452</v>
       </c>
       <c r="R133" s="5">
@@ -16070,7 +16070,7 @@
         <v>73</v>
       </c>
       <c r="J134" s="5">
-        <f>SUM(E134:I134)</f>
+        <f t="shared" si="7"/>
         <v>339</v>
       </c>
       <c r="K134" s="5">
@@ -16088,7 +16088,7 @@
       <c r="O134" s="5"/>
       <c r="P134" s="5"/>
       <c r="Q134" s="5">
-        <f>MAX(25, INT(POWER(2.2,J134/45)))</f>
+        <f t="shared" si="6"/>
         <v>379</v>
       </c>
       <c r="R134" s="5">
@@ -16142,7 +16142,7 @@
         <v>53</v>
       </c>
       <c r="J135" s="5">
-        <f>SUM(E135:I135)</f>
+        <f t="shared" si="7"/>
         <v>253</v>
       </c>
       <c r="K135" s="5">
@@ -16160,7 +16160,7 @@
       <c r="O135" s="5"/>
       <c r="P135" s="5"/>
       <c r="Q135" s="5">
-        <f>MAX(25, INT(POWER(2.2,J135/45)))</f>
+        <f t="shared" si="6"/>
         <v>84</v>
       </c>
       <c r="R135" s="5">
@@ -16214,7 +16214,7 @@
         <v>59</v>
       </c>
       <c r="J136" s="5">
-        <f>SUM(E136:I136)</f>
+        <f t="shared" si="7"/>
         <v>251</v>
       </c>
       <c r="K136" s="5">
@@ -16232,7 +16232,7 @@
       <c r="O136" s="5"/>
       <c r="P136" s="5"/>
       <c r="Q136" s="5">
-        <f>MAX(25, INT(POWER(2.2,J136/45)))</f>
+        <f t="shared" si="6"/>
         <v>81</v>
       </c>
       <c r="R136" s="5">
@@ -16286,7 +16286,7 @@
         <v>42</v>
       </c>
       <c r="J137" s="5">
-        <f>SUM(E137:I137)</f>
+        <f t="shared" si="7"/>
         <v>180</v>
       </c>
       <c r="K137" s="5">
@@ -16304,7 +16304,7 @@
       <c r="O137" s="5"/>
       <c r="P137" s="5"/>
       <c r="Q137" s="5">
-        <f>MAX(25, INT(POWER(2.2,J137/45)))</f>
+        <f t="shared" si="6"/>
         <v>25</v>
       </c>
       <c r="R137" s="5">
@@ -16358,7 +16358,7 @@
         <v>81</v>
       </c>
       <c r="J138" s="5">
-        <f>SUM(E138:I138)</f>
+        <f t="shared" si="7"/>
         <v>274</v>
       </c>
       <c r="K138" s="5">
@@ -16376,7 +16376,7 @@
       <c r="O138" s="5"/>
       <c r="P138" s="5"/>
       <c r="Q138" s="5">
-        <f>MAX(25, INT(POWER(2.2,J138/45)))</f>
+        <f t="shared" si="6"/>
         <v>121</v>
       </c>
       <c r="R138" s="5">
@@ -16430,7 +16430,7 @@
         <v>90</v>
       </c>
       <c r="J139" s="5">
-        <f>SUM(E139:I139)</f>
+        <f t="shared" si="7"/>
         <v>392</v>
       </c>
       <c r="K139" s="5">
@@ -16501,7 +16501,7 @@
         <v>70</v>
       </c>
       <c r="J140" s="5">
-        <f>SUM(E140:I140)</f>
+        <f t="shared" si="7"/>
         <v>374</v>
       </c>
       <c r="K140" s="5">
@@ -16519,7 +16519,7 @@
       <c r="O140" s="5"/>
       <c r="P140" s="5"/>
       <c r="Q140" s="5">
-        <f>MAX(25, INT(POWER(2.2,J140/45)))</f>
+        <f t="shared" ref="Q140:Q173" si="8">MAX(25, INT(POWER(2.2,J140/45)))</f>
         <v>701</v>
       </c>
       <c r="R140" s="5">
@@ -16575,7 +16575,7 @@
         <v>53</v>
       </c>
       <c r="J141" s="5">
-        <f>SUM(E141:I141)</f>
+        <f t="shared" si="7"/>
         <v>298</v>
       </c>
       <c r="K141" s="5">
@@ -16593,7 +16593,7 @@
       <c r="O141" s="5"/>
       <c r="P141" s="5"/>
       <c r="Q141" s="5">
-        <f>MAX(25, INT(POWER(2.2,J141/45)))</f>
+        <f t="shared" si="8"/>
         <v>185</v>
       </c>
       <c r="R141" s="5">
@@ -16649,7 +16649,7 @@
         <v>68</v>
       </c>
       <c r="J142" s="5">
-        <f>SUM(E142:I142)</f>
+        <f t="shared" si="7"/>
         <v>339</v>
       </c>
       <c r="K142" s="5">
@@ -16667,7 +16667,7 @@
       <c r="O142" s="5"/>
       <c r="P142" s="5"/>
       <c r="Q142" s="5">
-        <f>MAX(25, INT(POWER(2.2,J142/45)))</f>
+        <f t="shared" si="8"/>
         <v>379</v>
       </c>
       <c r="R142" s="5">
@@ -16723,7 +16723,7 @@
         <v>64</v>
       </c>
       <c r="J143" s="5">
-        <f>SUM(E143:I143)</f>
+        <f t="shared" si="7"/>
         <v>351</v>
       </c>
       <c r="K143" s="5">
@@ -16743,7 +16743,7 @@
       </c>
       <c r="P143" s="5"/>
       <c r="Q143" s="5">
-        <f>MAX(25, INT(POWER(2.2,J143/45)))</f>
+        <f t="shared" si="8"/>
         <v>468</v>
       </c>
       <c r="R143" s="5">
@@ -16799,7 +16799,7 @@
         <v>37</v>
       </c>
       <c r="J144" s="5">
-        <f>SUM(E144:I144)</f>
+        <f t="shared" si="7"/>
         <v>260</v>
       </c>
       <c r="K144" s="5">
@@ -16818,10 +16818,10 @@
         <v>40</v>
       </c>
       <c r="P144" s="5">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q144" s="5">
-        <f>MAX(25, INT(POWER(2.2,J144/45)))</f>
+        <f t="shared" si="8"/>
         <v>95</v>
       </c>
       <c r="R144" s="5">
@@ -16875,7 +16875,7 @@
         <v>23</v>
       </c>
       <c r="J145" s="5">
-        <f>SUM(E145:I145)</f>
+        <f t="shared" si="7"/>
         <v>228</v>
       </c>
       <c r="K145" s="5">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="P145" s="5"/>
       <c r="Q145" s="5">
-        <f>MAX(25, INT(POWER(2.2,J145/45)))</f>
+        <f t="shared" si="8"/>
         <v>54</v>
       </c>
       <c r="R145" s="5">
@@ -16951,7 +16951,7 @@
         <v>62</v>
       </c>
       <c r="J146" s="5">
-        <f>SUM(E146:I146)</f>
+        <f t="shared" si="7"/>
         <v>341</v>
       </c>
       <c r="K146" s="5">
@@ -16969,7 +16969,7 @@
       <c r="O146" s="5"/>
       <c r="P146" s="5"/>
       <c r="Q146" s="5">
-        <f>MAX(25, INT(POWER(2.2,J146/45)))</f>
+        <f t="shared" si="8"/>
         <v>393</v>
       </c>
       <c r="R146" s="5">
@@ -17023,7 +17023,7 @@
         <v>74</v>
       </c>
       <c r="J147" s="5">
-        <f>SUM(E147:I147)</f>
+        <f t="shared" si="7"/>
         <v>368</v>
       </c>
       <c r="K147" s="5">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="P147" s="5"/>
       <c r="Q147" s="5">
-        <f>MAX(25, INT(POWER(2.2,J147/45)))</f>
+        <f t="shared" si="8"/>
         <v>631</v>
       </c>
       <c r="R147" s="5">
@@ -17099,7 +17099,7 @@
         <v>37</v>
       </c>
       <c r="J148" s="5">
-        <f>SUM(E148:I148)</f>
+        <f t="shared" si="7"/>
         <v>291</v>
       </c>
       <c r="K148" s="5">
@@ -17119,7 +17119,7 @@
       </c>
       <c r="P148" s="5"/>
       <c r="Q148" s="5">
-        <f>MAX(25, INT(POWER(2.2,J148/45)))</f>
+        <f t="shared" si="8"/>
         <v>163</v>
       </c>
       <c r="R148" s="5">
@@ -17177,7 +17177,7 @@
         <v>39</v>
       </c>
       <c r="J149" s="5">
-        <f>SUM(E149:I149)</f>
+        <f t="shared" si="7"/>
         <v>241</v>
       </c>
       <c r="K149" s="5">
@@ -17195,7 +17195,7 @@
       <c r="O149" s="5"/>
       <c r="P149" s="5"/>
       <c r="Q149" s="5">
-        <f>MAX(25, INT(POWER(2.2,J149/45)))</f>
+        <f t="shared" si="8"/>
         <v>68</v>
       </c>
       <c r="R149" s="5">
@@ -17249,7 +17249,7 @@
         <v>28</v>
       </c>
       <c r="J150" s="5">
-        <f>SUM(E150:I150)</f>
+        <f t="shared" si="7"/>
         <v>184</v>
       </c>
       <c r="K150" s="5">
@@ -17267,7 +17267,7 @@
       <c r="O150" s="5"/>
       <c r="P150" s="5"/>
       <c r="Q150" s="5">
-        <f>MAX(25, INT(POWER(2.2,J150/45)))</f>
+        <f t="shared" si="8"/>
         <v>25</v>
       </c>
       <c r="R150" s="5">
@@ -17321,7 +17321,7 @@
         <v>29</v>
       </c>
       <c r="J151" s="5">
-        <f>SUM(E151:I151)</f>
+        <f t="shared" si="7"/>
         <v>190</v>
       </c>
       <c r="K151" s="5">
@@ -17339,7 +17339,7 @@
       <c r="O151" s="5"/>
       <c r="P151" s="5"/>
       <c r="Q151" s="5">
-        <f>MAX(25, INT(POWER(2.2,J151/45)))</f>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
       <c r="R151" s="5">
@@ -17393,7 +17393,7 @@
         <v>33</v>
       </c>
       <c r="J152" s="5">
-        <f>SUM(E152:I152)</f>
+        <f t="shared" si="7"/>
         <v>235</v>
       </c>
       <c r="K152" s="5">
@@ -17411,7 +17411,7 @@
       <c r="O152" s="5"/>
       <c r="P152" s="5"/>
       <c r="Q152" s="5">
-        <f>MAX(25, INT(POWER(2.2,J152/45)))</f>
+        <f t="shared" si="8"/>
         <v>61</v>
       </c>
       <c r="R152" s="5">
@@ -17465,7 +17465,7 @@
         <v>49</v>
       </c>
       <c r="J153" s="5">
-        <f>SUM(E153:I153)</f>
+        <f t="shared" si="7"/>
         <v>246</v>
       </c>
       <c r="K153" s="5">
@@ -17483,7 +17483,7 @@
       <c r="O153" s="5"/>
       <c r="P153" s="5"/>
       <c r="Q153" s="5">
-        <f>MAX(25, INT(POWER(2.2,J153/45)))</f>
+        <f t="shared" si="8"/>
         <v>74</v>
       </c>
       <c r="R153" s="5">
@@ -17537,7 +17537,7 @@
         <v>71</v>
       </c>
       <c r="J154" s="5">
-        <f>SUM(E154:I154)</f>
+        <f t="shared" si="7"/>
         <v>352</v>
       </c>
       <c r="K154" s="5">
@@ -17555,7 +17555,7 @@
       <c r="O154" s="5"/>
       <c r="P154" s="5"/>
       <c r="Q154" s="5">
-        <f>MAX(25, INT(POWER(2.2,J154/45)))</f>
+        <f t="shared" si="8"/>
         <v>476</v>
       </c>
       <c r="R154" s="5">
@@ -17609,7 +17609,7 @@
         <v>66</v>
       </c>
       <c r="J155" s="5">
-        <f>SUM(E155:I155)</f>
+        <f t="shared" si="7"/>
         <v>264</v>
       </c>
       <c r="K155" s="5">
@@ -17627,7 +17627,7 @@
       <c r="O155" s="5"/>
       <c r="P155" s="5"/>
       <c r="Q155" s="5">
-        <f>MAX(25, INT(POWER(2.2,J155/45)))</f>
+        <f t="shared" si="8"/>
         <v>102</v>
       </c>
       <c r="R155" s="5">
@@ -17681,7 +17681,7 @@
         <v>56</v>
       </c>
       <c r="J156" s="5">
-        <f>SUM(E156:I156)</f>
+        <f t="shared" si="7"/>
         <v>240</v>
       </c>
       <c r="K156" s="5">
@@ -17699,7 +17699,7 @@
       <c r="O156" s="5"/>
       <c r="P156" s="5"/>
       <c r="Q156" s="5">
-        <f>MAX(25, INT(POWER(2.2,J156/45)))</f>
+        <f t="shared" si="8"/>
         <v>67</v>
       </c>
       <c r="R156" s="5">
@@ -17753,7 +17753,7 @@
         <v>62</v>
       </c>
       <c r="J157" s="5">
-        <f>SUM(E157:I157)</f>
+        <f t="shared" si="7"/>
         <v>313</v>
       </c>
       <c r="K157" s="5">
@@ -17771,7 +17771,7 @@
       <c r="O157" s="5"/>
       <c r="P157" s="5"/>
       <c r="Q157" s="5">
-        <f>MAX(25, INT(POWER(2.2,J157/45)))</f>
+        <f t="shared" si="8"/>
         <v>240</v>
       </c>
       <c r="R157" s="5">
@@ -17825,7 +17825,7 @@
         <v>72</v>
       </c>
       <c r="J158" s="5">
-        <f>SUM(E158:I158)</f>
+        <f t="shared" si="7"/>
         <v>345</v>
       </c>
       <c r="K158" s="5">
@@ -17843,7 +17843,7 @@
       <c r="O158" s="5"/>
       <c r="P158" s="5"/>
       <c r="Q158" s="5">
-        <f>MAX(25, INT(POWER(2.2,J158/45)))</f>
+        <f t="shared" si="8"/>
         <v>421</v>
       </c>
       <c r="R158" s="5">
@@ -17897,7 +17897,7 @@
         <v>35</v>
       </c>
       <c r="J159" s="5">
-        <f>SUM(E159:I159)</f>
+        <f t="shared" si="7"/>
         <v>225</v>
       </c>
       <c r="K159" s="5">
@@ -17915,7 +17915,7 @@
       <c r="O159" s="5"/>
       <c r="P159" s="5"/>
       <c r="Q159" s="5">
-        <f>MAX(25, INT(POWER(2.2,J159/45)))</f>
+        <f t="shared" si="8"/>
         <v>51</v>
       </c>
       <c r="R159" s="5">
@@ -17969,7 +17969,7 @@
         <v>44</v>
       </c>
       <c r="J160" s="5">
-        <f>SUM(E160:I160)</f>
+        <f t="shared" si="7"/>
         <v>233</v>
       </c>
       <c r="K160" s="5">
@@ -17987,7 +17987,7 @@
       <c r="O160" s="5"/>
       <c r="P160" s="5"/>
       <c r="Q160" s="5">
-        <f>MAX(25, INT(POWER(2.2,J160/45)))</f>
+        <f t="shared" si="8"/>
         <v>59</v>
       </c>
       <c r="R160" s="5">
@@ -18041,7 +18041,7 @@
         <v>70</v>
       </c>
       <c r="J161" s="5">
-        <f>SUM(E161:I161)</f>
+        <f t="shared" si="7"/>
         <v>370</v>
       </c>
       <c r="K161" s="5">
@@ -18059,7 +18059,7 @@
       <c r="O161" s="5"/>
       <c r="P161" s="5"/>
       <c r="Q161" s="5">
-        <f>MAX(25, INT(POWER(2.2,J161/45)))</f>
+        <f t="shared" si="8"/>
         <v>653</v>
       </c>
       <c r="R161" s="5">
@@ -18113,7 +18113,7 @@
         <v>52</v>
       </c>
       <c r="J162" s="5">
-        <f>SUM(E162:I162)</f>
+        <f t="shared" si="7"/>
         <v>259</v>
       </c>
       <c r="K162" s="5">
@@ -18131,7 +18131,7 @@
       <c r="O162" s="5"/>
       <c r="P162" s="5"/>
       <c r="Q162" s="5">
-        <f>MAX(25, INT(POWER(2.2,J162/45)))</f>
+        <f t="shared" si="8"/>
         <v>93</v>
       </c>
       <c r="R162" s="5">
@@ -18185,7 +18185,7 @@
         <v>49</v>
       </c>
       <c r="J163" s="5">
-        <f>SUM(E163:I163)</f>
+        <f t="shared" si="7"/>
         <v>248</v>
       </c>
       <c r="K163" s="5">
@@ -18203,7 +18203,7 @@
       <c r="O163" s="5"/>
       <c r="P163" s="5"/>
       <c r="Q163" s="5">
-        <f>MAX(25, INT(POWER(2.2,J163/45)))</f>
+        <f t="shared" si="8"/>
         <v>77</v>
       </c>
       <c r="R163" s="5">
@@ -18257,7 +18257,7 @@
         <v>55</v>
       </c>
       <c r="J164" s="5">
-        <f>SUM(E164:I164)</f>
+        <f t="shared" si="7"/>
         <v>292</v>
       </c>
       <c r="K164" s="5">
@@ -18275,7 +18275,7 @@
       <c r="O164" s="5"/>
       <c r="P164" s="5"/>
       <c r="Q164" s="5">
-        <f>MAX(25, INT(POWER(2.2,J164/45)))</f>
+        <f t="shared" si="8"/>
         <v>166</v>
       </c>
       <c r="R164" s="5">
@@ -18329,7 +18329,7 @@
         <v>64</v>
       </c>
       <c r="J165" s="5">
-        <f>SUM(E165:I165)</f>
+        <f t="shared" si="7"/>
         <v>294</v>
       </c>
       <c r="K165" s="5">
@@ -18347,7 +18347,7 @@
       <c r="O165" s="5"/>
       <c r="P165" s="5"/>
       <c r="Q165" s="5">
-        <f>MAX(25, INT(POWER(2.2,J165/45)))</f>
+        <f t="shared" si="8"/>
         <v>172</v>
       </c>
       <c r="R165" s="5">
@@ -18401,7 +18401,7 @@
         <v>60</v>
       </c>
       <c r="J166" s="5">
-        <f>SUM(E166:I166)</f>
+        <f t="shared" si="7"/>
         <v>289</v>
       </c>
       <c r="K166" s="5">
@@ -18419,7 +18419,7 @@
       <c r="O166" s="5"/>
       <c r="P166" s="5"/>
       <c r="Q166" s="5">
-        <f>MAX(25, INT(POWER(2.2,J166/45)))</f>
+        <f t="shared" si="8"/>
         <v>158</v>
       </c>
       <c r="R166" s="5">
@@ -18477,7 +18477,7 @@
         <v>70</v>
       </c>
       <c r="J167" s="5">
-        <f>SUM(E167:I167)</f>
+        <f t="shared" si="7"/>
         <v>296</v>
       </c>
       <c r="K167" s="5">
@@ -18495,7 +18495,7 @@
       <c r="O167" s="5"/>
       <c r="P167" s="5"/>
       <c r="Q167" s="5">
-        <f>MAX(25, INT(POWER(2.2,J167/45)))</f>
+        <f t="shared" si="8"/>
         <v>178</v>
       </c>
       <c r="R167" s="5">
@@ -18553,7 +18553,7 @@
         <v>68</v>
       </c>
       <c r="J168" s="5">
-        <f>SUM(E168:I168)</f>
+        <f t="shared" si="7"/>
         <v>331</v>
       </c>
       <c r="K168" s="5">
@@ -18571,7 +18571,7 @@
       <c r="O168" s="5"/>
       <c r="P168" s="5"/>
       <c r="Q168" s="5">
-        <f>MAX(25, INT(POWER(2.2,J168/45)))</f>
+        <f t="shared" si="8"/>
         <v>330</v>
       </c>
       <c r="R168" s="5">
@@ -18629,7 +18629,7 @@
         <v>70</v>
       </c>
       <c r="J169" s="5">
-        <f>SUM(E169:I169)</f>
+        <f t="shared" si="7"/>
         <v>306</v>
       </c>
       <c r="K169" s="5">
@@ -18647,7 +18647,7 @@
       <c r="O169" s="5"/>
       <c r="P169" s="5"/>
       <c r="Q169" s="5">
-        <f>MAX(25, INT(POWER(2.2,J169/45)))</f>
+        <f t="shared" si="8"/>
         <v>213</v>
       </c>
       <c r="R169" s="5">
@@ -18705,7 +18705,7 @@
         <v>64</v>
       </c>
       <c r="J170" s="5">
-        <f>SUM(E170:I170)</f>
+        <f t="shared" si="7"/>
         <v>264</v>
       </c>
       <c r="K170" s="5">
@@ -18723,7 +18723,7 @@
       <c r="O170" s="5"/>
       <c r="P170" s="5"/>
       <c r="Q170" s="5">
-        <f>MAX(25, INT(POWER(2.2,J170/45)))</f>
+        <f t="shared" si="8"/>
         <v>102</v>
       </c>
       <c r="R170" s="5">
@@ -18781,7 +18781,7 @@
         <v>69</v>
       </c>
       <c r="J171" s="5">
-        <f>SUM(E171:I171)</f>
+        <f t="shared" si="7"/>
         <v>281</v>
       </c>
       <c r="K171" s="5">
@@ -18799,7 +18799,7 @@
       <c r="O171" s="5"/>
       <c r="P171" s="5"/>
       <c r="Q171" s="5">
-        <f>MAX(25, INT(POWER(2.2,J171/45)))</f>
+        <f t="shared" si="8"/>
         <v>137</v>
       </c>
       <c r="R171" s="5">
@@ -18857,7 +18857,7 @@
         <v>39</v>
       </c>
       <c r="J172" s="5">
-        <f>SUM(E172:I172)</f>
+        <f t="shared" si="7"/>
         <v>243</v>
       </c>
       <c r="K172" s="5">
@@ -18875,7 +18875,7 @@
       <c r="O172" s="5"/>
       <c r="P172" s="5"/>
       <c r="Q172" s="5">
-        <f>MAX(25, INT(POWER(2.2,J172/45)))</f>
+        <f t="shared" si="8"/>
         <v>70</v>
       </c>
       <c r="R172" s="5">
@@ -18933,7 +18933,7 @@
         <v>72</v>
       </c>
       <c r="J173" s="5">
-        <f>SUM(E173:I173)</f>
+        <f t="shared" si="7"/>
         <v>244</v>
       </c>
       <c r="K173" s="5">
@@ -18951,7 +18951,7 @@
       <c r="O173" s="5"/>
       <c r="P173" s="5"/>
       <c r="Q173" s="5">
-        <f>MAX(25, INT(POWER(2.2,J173/45)))</f>
+        <f t="shared" si="8"/>
         <v>71</v>
       </c>
       <c r="R173" s="5">
@@ -19009,7 +19009,7 @@
         <v>36</v>
       </c>
       <c r="J174" s="5">
-        <f>SUM(E174:I174)</f>
+        <f t="shared" si="7"/>
         <v>285</v>
       </c>
       <c r="K174" s="5">
@@ -19084,7 +19084,7 @@
         <v>76</v>
       </c>
       <c r="J175" s="5">
-        <f>SUM(E175:I175)</f>
+        <f t="shared" si="7"/>
         <v>397</v>
       </c>
       <c r="K175" s="5">
@@ -19102,7 +19102,7 @@
       <c r="O175" s="5"/>
       <c r="P175" s="5"/>
       <c r="Q175" s="5">
-        <f>MAX(25, INT(POWER(2.2,J175/45)))</f>
+        <f t="shared" ref="Q175:Q219" si="9">MAX(25, INT(POWER(2.2,J175/45)))</f>
         <v>1049</v>
       </c>
       <c r="R175" s="5">
@@ -19162,7 +19162,7 @@
         <v>40</v>
       </c>
       <c r="J176" s="5">
-        <f>SUM(E176:I176)</f>
+        <f t="shared" si="7"/>
         <v>270</v>
       </c>
       <c r="K176" s="5">
@@ -19180,7 +19180,7 @@
       <c r="O176" s="5"/>
       <c r="P176" s="5"/>
       <c r="Q176" s="5">
-        <f>MAX(25, INT(POWER(2.2,J176/45)))</f>
+        <f t="shared" si="9"/>
         <v>113</v>
       </c>
       <c r="R176" s="5">
@@ -19242,7 +19242,7 @@
         <v>57</v>
       </c>
       <c r="J177" s="5">
-        <f>SUM(E177:I177)</f>
+        <f t="shared" si="7"/>
         <v>325</v>
       </c>
       <c r="K177" s="5">
@@ -19260,7 +19260,7 @@
       <c r="O177" s="5"/>
       <c r="P177" s="5"/>
       <c r="Q177" s="5">
-        <f>MAX(25, INT(POWER(2.2,J177/45)))</f>
+        <f t="shared" si="9"/>
         <v>297</v>
       </c>
       <c r="R177" s="5">
@@ -19320,7 +19320,7 @@
         <v>57</v>
       </c>
       <c r="J178" s="5">
-        <f>SUM(E178:I178)</f>
+        <f t="shared" si="7"/>
         <v>375</v>
       </c>
       <c r="K178" s="5">
@@ -19340,7 +19340,7 @@
       </c>
       <c r="P178" s="5"/>
       <c r="Q178" s="5">
-        <f>MAX(25, INT(POWER(2.2,J178/45)))</f>
+        <f t="shared" si="9"/>
         <v>713</v>
       </c>
       <c r="R178" s="5">
@@ -19400,7 +19400,7 @@
         <v>95</v>
       </c>
       <c r="J179" s="5">
-        <f>SUM(E179:I179)</f>
+        <f t="shared" si="7"/>
         <v>338</v>
       </c>
       <c r="K179" s="5">
@@ -19420,7 +19420,7 @@
       </c>
       <c r="P179" s="5"/>
       <c r="Q179" s="5">
-        <f>MAX(25, INT(POWER(2.2,J179/45)))</f>
+        <f t="shared" si="9"/>
         <v>373</v>
       </c>
       <c r="R179" s="5">
@@ -19480,7 +19480,7 @@
         <v>71</v>
       </c>
       <c r="J180" s="5">
-        <f>SUM(E180:I180)</f>
+        <f t="shared" si="7"/>
         <v>333</v>
       </c>
       <c r="K180" s="5">
@@ -19498,7 +19498,7 @@
       <c r="O180" s="5"/>
       <c r="P180" s="5"/>
       <c r="Q180" s="5">
-        <f>MAX(25, INT(POWER(2.2,J180/45)))</f>
+        <f t="shared" si="9"/>
         <v>341</v>
       </c>
       <c r="R180" s="5">
@@ -19558,7 +19558,7 @@
         <v>68</v>
       </c>
       <c r="J181" s="5">
-        <f>SUM(E181:I181)</f>
+        <f t="shared" si="7"/>
         <v>338</v>
       </c>
       <c r="K181" s="5">
@@ -19577,10 +19577,10 @@
         <v>26</v>
       </c>
       <c r="P181" s="5">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="Q181" s="5">
-        <f>MAX(25, INT(POWER(2.2,J181/45)))</f>
+        <f t="shared" si="9"/>
         <v>373</v>
       </c>
       <c r="R181" s="5">
@@ -19638,7 +19638,7 @@
         <v>38</v>
       </c>
       <c r="J182" s="5">
-        <f>SUM(E182:I182)</f>
+        <f t="shared" si="7"/>
         <v>313</v>
       </c>
       <c r="K182" s="5">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="P182" s="5"/>
       <c r="Q182" s="5">
-        <f>MAX(25, INT(POWER(2.2,J182/45)))</f>
+        <f t="shared" si="9"/>
         <v>240</v>
       </c>
       <c r="R182" s="5">
@@ -19718,7 +19718,7 @@
         <v>17</v>
       </c>
       <c r="J183" s="5">
-        <f>SUM(E183:I183)</f>
+        <f t="shared" si="7"/>
         <v>185</v>
       </c>
       <c r="K183" s="5">
@@ -19736,7 +19736,7 @@
       <c r="O183" s="5"/>
       <c r="P183" s="5"/>
       <c r="Q183" s="5">
-        <f>MAX(25, INT(POWER(2.2,J183/45)))</f>
+        <f t="shared" si="9"/>
         <v>25</v>
       </c>
       <c r="R183" s="5">
@@ -19796,7 +19796,7 @@
         <v>13</v>
       </c>
       <c r="J184" s="5">
-        <f>SUM(E184:I184)</f>
+        <f t="shared" si="7"/>
         <v>180</v>
       </c>
       <c r="K184" s="5">
@@ -19814,7 +19814,7 @@
       <c r="O184" s="5"/>
       <c r="P184" s="5"/>
       <c r="Q184" s="5">
-        <f>MAX(25, INT(POWER(2.2,J184/45)))</f>
+        <f t="shared" si="9"/>
         <v>25</v>
       </c>
       <c r="R184" s="5">
@@ -19873,7 +19873,7 @@
         <v>70</v>
       </c>
       <c r="J185" s="5">
-        <f>SUM(E185:I185)</f>
+        <f t="shared" si="7"/>
         <v>380</v>
       </c>
       <c r="K185" s="5">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="P185" s="5"/>
       <c r="Q185" s="5">
-        <f>MAX(25, INT(POWER(2.2,J185/45)))</f>
+        <f t="shared" si="9"/>
         <v>779</v>
       </c>
       <c r="R185" s="5">
@@ -19955,7 +19955,7 @@
         <v>29</v>
       </c>
       <c r="J186" s="5">
-        <f>SUM(E186:I186)</f>
+        <f t="shared" si="7"/>
         <v>175</v>
       </c>
       <c r="K186" s="5">
@@ -19973,7 +19973,7 @@
       <c r="O186" s="5"/>
       <c r="P186" s="5"/>
       <c r="Q186" s="5">
-        <f>MAX(25, INT(POWER(2.2,J186/45)))</f>
+        <f t="shared" si="9"/>
         <v>25</v>
       </c>
       <c r="R186" s="5">
@@ -20031,7 +20031,7 @@
         <v>39</v>
       </c>
       <c r="J187" s="5">
-        <f>SUM(E187:I187)</f>
+        <f t="shared" si="7"/>
         <v>247</v>
       </c>
       <c r="K187" s="5">
@@ -20049,7 +20049,7 @@
       <c r="O187" s="5"/>
       <c r="P187" s="5"/>
       <c r="Q187" s="5">
-        <f>MAX(25, INT(POWER(2.2,J187/45)))</f>
+        <f t="shared" si="9"/>
         <v>75</v>
       </c>
       <c r="R187" s="5">
@@ -20103,7 +20103,7 @@
         <v>31</v>
       </c>
       <c r="J188" s="5">
-        <f>SUM(E188:I188)</f>
+        <f t="shared" si="7"/>
         <v>241</v>
       </c>
       <c r="K188" s="5">
@@ -20121,7 +20121,7 @@
       <c r="O188" s="5"/>
       <c r="P188" s="5"/>
       <c r="Q188" s="5">
-        <f>MAX(25, INT(POWER(2.2,J188/45)))</f>
+        <f t="shared" si="9"/>
         <v>68</v>
       </c>
       <c r="R188" s="5">
@@ -20175,7 +20175,7 @@
         <v>42</v>
       </c>
       <c r="J189" s="5">
-        <f>SUM(E189:I189)</f>
+        <f t="shared" si="7"/>
         <v>298</v>
       </c>
       <c r="K189" s="5">
@@ -20193,7 +20193,7 @@
       <c r="O189" s="5"/>
       <c r="P189" s="5"/>
       <c r="Q189" s="5">
-        <f>MAX(25, INT(POWER(2.2,J189/45)))</f>
+        <f t="shared" si="9"/>
         <v>185</v>
       </c>
       <c r="R189" s="5">
@@ -20247,7 +20247,7 @@
         <v>60</v>
       </c>
       <c r="J190" s="5">
-        <f>SUM(E190:I190)</f>
+        <f t="shared" si="7"/>
         <v>328</v>
       </c>
       <c r="K190" s="5">
@@ -20265,7 +20265,7 @@
       <c r="O190" s="5"/>
       <c r="P190" s="5"/>
       <c r="Q190" s="5">
-        <f>MAX(25, INT(POWER(2.2,J190/45)))</f>
+        <f t="shared" si="9"/>
         <v>313</v>
       </c>
       <c r="R190" s="5">
@@ -20319,7 +20319,7 @@
         <v>21</v>
       </c>
       <c r="J191" s="5">
-        <f>SUM(E191:I191)</f>
+        <f t="shared" si="7"/>
         <v>187</v>
       </c>
       <c r="K191" s="5">
@@ -20337,7 +20337,7 @@
       <c r="O191" s="5"/>
       <c r="P191" s="5"/>
       <c r="Q191" s="5">
-        <f>MAX(25, INT(POWER(2.2,J191/45)))</f>
+        <f t="shared" si="9"/>
         <v>26</v>
       </c>
       <c r="R191" s="5">
@@ -20391,7 +20391,7 @@
         <v>59</v>
       </c>
       <c r="J192" s="5">
-        <f>SUM(E192:I192)</f>
+        <f t="shared" si="7"/>
         <v>317</v>
       </c>
       <c r="K192" s="5">
@@ -20409,7 +20409,7 @@
       <c r="O192" s="5"/>
       <c r="P192" s="5"/>
       <c r="Q192" s="5">
-        <f>MAX(25, INT(POWER(2.2,J192/45)))</f>
+        <f t="shared" si="9"/>
         <v>258</v>
       </c>
       <c r="R192" s="5">
@@ -20463,7 +20463,7 @@
         <v>39</v>
       </c>
       <c r="J193" s="5">
-        <f>SUM(E193:I193)</f>
+        <f t="shared" si="7"/>
         <v>233</v>
       </c>
       <c r="K193" s="5">
@@ -20481,7 +20481,7 @@
       <c r="O193" s="5"/>
       <c r="P193" s="5"/>
       <c r="Q193" s="5">
-        <f>MAX(25, INT(POWER(2.2,J193/45)))</f>
+        <f t="shared" si="9"/>
         <v>59</v>
       </c>
       <c r="R193" s="5">
@@ -20535,7 +20535,7 @@
         <v>38</v>
       </c>
       <c r="J194" s="5">
-        <f>SUM(E194:I194)</f>
+        <f t="shared" si="7"/>
         <v>227</v>
       </c>
       <c r="K194" s="5">
@@ -20553,7 +20553,7 @@
       <c r="O194" s="5"/>
       <c r="P194" s="5"/>
       <c r="Q194" s="5">
-        <f>MAX(25, INT(POWER(2.2,J194/45)))</f>
+        <f t="shared" si="9"/>
         <v>53</v>
       </c>
       <c r="R194" s="5">
@@ -20607,7 +20607,7 @@
         <v>36</v>
       </c>
       <c r="J195" s="5">
-        <f>SUM(E195:I195)</f>
+        <f t="shared" si="7"/>
         <v>225</v>
       </c>
       <c r="K195" s="5">
@@ -20625,7 +20625,7 @@
       <c r="O195" s="5"/>
       <c r="P195" s="5"/>
       <c r="Q195" s="5">
-        <f>MAX(25, INT(POWER(2.2,J195/45)))</f>
+        <f t="shared" si="9"/>
         <v>51</v>
       </c>
       <c r="R195" s="5">
@@ -20679,7 +20679,7 @@
         <v>54</v>
       </c>
       <c r="J196" s="5">
-        <f>SUM(E196:I196)</f>
+        <f t="shared" si="7"/>
         <v>291</v>
       </c>
       <c r="K196" s="5">
@@ -20697,7 +20697,7 @@
       <c r="O196" s="5"/>
       <c r="P196" s="5"/>
       <c r="Q196" s="5">
-        <f>MAX(25, INT(POWER(2.2,J196/45)))</f>
+        <f t="shared" si="9"/>
         <v>163</v>
       </c>
       <c r="R196" s="5">
@@ -20751,7 +20751,7 @@
         <v>73</v>
       </c>
       <c r="J197" s="5">
-        <f>SUM(E197:I197)</f>
+        <f t="shared" ref="J197:J260" si="10">SUM(E197:I197)</f>
         <v>360</v>
       </c>
       <c r="K197" s="5">
@@ -20769,7 +20769,7 @@
       <c r="O197" s="5"/>
       <c r="P197" s="5"/>
       <c r="Q197" s="5">
-        <f>MAX(25, INT(POWER(2.2,J197/45)))</f>
+        <f t="shared" si="9"/>
         <v>548</v>
       </c>
       <c r="R197" s="5">
@@ -20823,7 +20823,7 @@
         <v>58</v>
       </c>
       <c r="J198" s="5">
-        <f>SUM(E198:I198)</f>
+        <f t="shared" si="10"/>
         <v>234</v>
       </c>
       <c r="K198" s="5">
@@ -20841,7 +20841,7 @@
       <c r="O198" s="5"/>
       <c r="P198" s="5"/>
       <c r="Q198" s="5">
-        <f>MAX(25, INT(POWER(2.2,J198/45)))</f>
+        <f t="shared" si="9"/>
         <v>60</v>
       </c>
       <c r="R198" s="5">
@@ -20895,7 +20895,7 @@
         <v>37</v>
       </c>
       <c r="J199" s="5">
-        <f>SUM(E199:I199)</f>
+        <f t="shared" si="10"/>
         <v>182</v>
       </c>
       <c r="K199" s="5">
@@ -20913,7 +20913,7 @@
       <c r="O199" s="5"/>
       <c r="P199" s="5"/>
       <c r="Q199" s="5">
-        <f>MAX(25, INT(POWER(2.2,J199/45)))</f>
+        <f t="shared" si="9"/>
         <v>25</v>
       </c>
       <c r="R199" s="5">
@@ -20967,7 +20967,7 @@
         <v>23</v>
       </c>
       <c r="J200" s="5">
-        <f>SUM(E200:I200)</f>
+        <f t="shared" si="10"/>
         <v>169</v>
       </c>
       <c r="K200" s="5">
@@ -20985,7 +20985,7 @@
       <c r="O200" s="5"/>
       <c r="P200" s="5"/>
       <c r="Q200" s="5">
-        <f>MAX(25, INT(POWER(2.2,J200/45)))</f>
+        <f t="shared" si="9"/>
         <v>25</v>
       </c>
       <c r="R200" s="5">
@@ -21039,7 +21039,7 @@
         <v>69</v>
       </c>
       <c r="J201" s="5">
-        <f>SUM(E201:I201)</f>
+        <f t="shared" si="10"/>
         <v>328</v>
       </c>
       <c r="K201" s="5">
@@ -21057,7 +21057,7 @@
       <c r="O201" s="5"/>
       <c r="P201" s="5"/>
       <c r="Q201" s="5">
-        <f>MAX(25, INT(POWER(2.2,J201/45)))</f>
+        <f t="shared" si="9"/>
         <v>313</v>
       </c>
       <c r="R201" s="5">
@@ -21111,7 +21111,7 @@
         <v>75</v>
       </c>
       <c r="J202" s="5">
-        <f>SUM(E202:I202)</f>
+        <f t="shared" si="10"/>
         <v>312</v>
       </c>
       <c r="K202" s="5">
@@ -21129,7 +21129,7 @@
       <c r="O202" s="5"/>
       <c r="P202" s="5"/>
       <c r="Q202" s="5">
-        <f>MAX(25, INT(POWER(2.2,J202/45)))</f>
+        <f t="shared" si="9"/>
         <v>236</v>
       </c>
       <c r="R202" s="5">
@@ -21183,7 +21183,7 @@
         <v>17</v>
       </c>
       <c r="J203" s="5">
-        <f>SUM(E203:I203)</f>
+        <f t="shared" si="10"/>
         <v>234</v>
       </c>
       <c r="K203" s="5">
@@ -21201,7 +21201,7 @@
       <c r="O203" s="5"/>
       <c r="P203" s="5"/>
       <c r="Q203" s="5">
-        <f>MAX(25, INT(POWER(2.2,J203/45)))</f>
+        <f t="shared" si="9"/>
         <v>60</v>
       </c>
       <c r="R203" s="5">
@@ -21255,7 +21255,7 @@
         <v>73</v>
       </c>
       <c r="J204" s="5">
-        <f>SUM(E204:I204)</f>
+        <f t="shared" si="10"/>
         <v>253</v>
       </c>
       <c r="K204" s="5">
@@ -21273,7 +21273,7 @@
       <c r="O204" s="5"/>
       <c r="P204" s="5"/>
       <c r="Q204" s="5">
-        <f>MAX(25, INT(POWER(2.2,J204/45)))</f>
+        <f t="shared" si="9"/>
         <v>84</v>
       </c>
       <c r="R204" s="5">
@@ -21327,7 +21327,7 @@
         <v>88</v>
       </c>
       <c r="J205" s="5">
-        <f>SUM(E205:I205)</f>
+        <f t="shared" si="10"/>
         <v>359</v>
       </c>
       <c r="K205" s="5">
@@ -21345,7 +21345,7 @@
       <c r="O205" s="5"/>
       <c r="P205" s="5"/>
       <c r="Q205" s="5">
-        <f>MAX(25, INT(POWER(2.2,J205/45)))</f>
+        <f t="shared" si="9"/>
         <v>539</v>
       </c>
       <c r="R205" s="5">
@@ -21399,7 +21399,7 @@
         <v>80</v>
       </c>
       <c r="J206" s="5">
-        <f>SUM(E206:I206)</f>
+        <f t="shared" si="10"/>
         <v>336</v>
       </c>
       <c r="K206" s="5">
@@ -21417,7 +21417,7 @@
       <c r="O206" s="5"/>
       <c r="P206" s="5"/>
       <c r="Q206" s="5">
-        <f>MAX(25, INT(POWER(2.2,J206/45)))</f>
+        <f t="shared" si="9"/>
         <v>360</v>
       </c>
       <c r="R206" s="5">
@@ -21477,7 +21477,7 @@
         <v>71</v>
       </c>
       <c r="J207" s="5">
-        <f>SUM(E207:I207)</f>
+        <f t="shared" si="10"/>
         <v>342</v>
       </c>
       <c r="K207" s="5">
@@ -21495,7 +21495,7 @@
       <c r="O207" s="5"/>
       <c r="P207" s="5"/>
       <c r="Q207" s="5">
-        <f>MAX(25, INT(POWER(2.2,J207/45)))</f>
+        <f t="shared" si="9"/>
         <v>400</v>
       </c>
       <c r="R207" s="5">
@@ -21557,7 +21557,7 @@
         <v>67</v>
       </c>
       <c r="J208" s="5">
-        <f>SUM(E208:I208)</f>
+        <f t="shared" si="10"/>
         <v>360</v>
       </c>
       <c r="K208" s="5">
@@ -21575,7 +21575,7 @@
       <c r="O208" s="5"/>
       <c r="P208" s="5"/>
       <c r="Q208" s="5">
-        <f>MAX(25, INT(POWER(2.2,J208/45)))</f>
+        <f t="shared" si="9"/>
         <v>548</v>
       </c>
       <c r="R208" s="5">
@@ -21635,7 +21635,7 @@
         <v>65</v>
       </c>
       <c r="J209" s="5">
-        <f>SUM(E209:I209)</f>
+        <f t="shared" si="10"/>
         <v>339</v>
       </c>
       <c r="K209" s="5">
@@ -21653,7 +21653,7 @@
       <c r="O209" s="5"/>
       <c r="P209" s="5"/>
       <c r="Q209" s="5">
-        <f>MAX(25, INT(POWER(2.2,J209/45)))</f>
+        <f t="shared" si="9"/>
         <v>379</v>
       </c>
       <c r="R209" s="5">
@@ -21711,7 +21711,7 @@
         <v>54</v>
       </c>
       <c r="J210" s="5">
-        <f>SUM(E210:I210)</f>
+        <f t="shared" si="10"/>
         <v>283</v>
       </c>
       <c r="K210" s="5">
@@ -21729,7 +21729,7 @@
       <c r="O210" s="5"/>
       <c r="P210" s="5"/>
       <c r="Q210" s="5">
-        <f>MAX(25, INT(POWER(2.2,J210/45)))</f>
+        <f t="shared" si="9"/>
         <v>142</v>
       </c>
       <c r="R210" s="5">
@@ -21783,7 +21783,7 @@
         <v>49</v>
       </c>
       <c r="J211" s="5">
-        <f>SUM(E211:I211)</f>
+        <f t="shared" si="10"/>
         <v>254</v>
       </c>
       <c r="K211" s="5">
@@ -21801,7 +21801,7 @@
       <c r="O211" s="5"/>
       <c r="P211" s="5"/>
       <c r="Q211" s="5">
-        <f>MAX(25, INT(POWER(2.2,J211/45)))</f>
+        <f t="shared" si="9"/>
         <v>85</v>
       </c>
       <c r="R211" s="5">
@@ -21855,7 +21855,7 @@
         <v>63</v>
       </c>
       <c r="J212" s="5">
-        <f>SUM(E212:I212)</f>
+        <f t="shared" si="10"/>
         <v>278</v>
       </c>
       <c r="K212" s="5">
@@ -21873,7 +21873,7 @@
       <c r="O212" s="5"/>
       <c r="P212" s="5"/>
       <c r="Q212" s="5">
-        <f>MAX(25, INT(POWER(2.2,J212/45)))</f>
+        <f t="shared" si="9"/>
         <v>130</v>
       </c>
       <c r="R212" s="5">
@@ -21927,7 +21927,7 @@
         <v>35</v>
       </c>
       <c r="J213" s="5">
-        <f>SUM(E213:I213)</f>
+        <f t="shared" si="10"/>
         <v>211</v>
       </c>
       <c r="K213" s="5">
@@ -21945,7 +21945,7 @@
       <c r="O213" s="5"/>
       <c r="P213" s="5"/>
       <c r="Q213" s="5">
-        <f>MAX(25, INT(POWER(2.2,J213/45)))</f>
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
       <c r="R213" s="5">
@@ -21999,7 +21999,7 @@
         <v>57</v>
       </c>
       <c r="J214" s="5">
-        <f>SUM(E214:I214)</f>
+        <f t="shared" si="10"/>
         <v>279</v>
       </c>
       <c r="K214" s="5">
@@ -22017,7 +22017,7 @@
       <c r="O214" s="5"/>
       <c r="P214" s="5"/>
       <c r="Q214" s="5">
-        <f>MAX(25, INT(POWER(2.2,J214/45)))</f>
+        <f t="shared" si="9"/>
         <v>132</v>
       </c>
       <c r="R214" s="5">
@@ -22071,7 +22071,7 @@
         <v>25</v>
       </c>
       <c r="J215" s="5">
-        <f>SUM(E215:I215)</f>
+        <f t="shared" si="10"/>
         <v>186</v>
       </c>
       <c r="K215" s="5">
@@ -22089,7 +22089,7 @@
       <c r="O215" s="5"/>
       <c r="P215" s="5"/>
       <c r="Q215" s="5">
-        <f>MAX(25, INT(POWER(2.2,J215/45)))</f>
+        <f t="shared" si="9"/>
         <v>26</v>
       </c>
       <c r="R215" s="5">
@@ -22143,7 +22143,7 @@
         <v>49</v>
       </c>
       <c r="J216" s="5">
-        <f>SUM(E216:I216)</f>
+        <f t="shared" si="10"/>
         <v>261</v>
       </c>
       <c r="K216" s="5">
@@ -22161,7 +22161,7 @@
       <c r="O216" s="5"/>
       <c r="P216" s="5"/>
       <c r="Q216" s="5">
-        <f>MAX(25, INT(POWER(2.2,J216/45)))</f>
+        <f t="shared" si="9"/>
         <v>96</v>
       </c>
       <c r="R216" s="5">
@@ -22215,7 +22215,7 @@
         <v>40</v>
       </c>
       <c r="J217" s="5">
-        <f>SUM(E217:I217)</f>
+        <f t="shared" si="10"/>
         <v>281</v>
       </c>
       <c r="K217" s="5">
@@ -22233,7 +22233,7 @@
       <c r="O217" s="5"/>
       <c r="P217" s="5"/>
       <c r="Q217" s="5">
-        <f>MAX(25, INT(POWER(2.2,J217/45)))</f>
+        <f t="shared" si="9"/>
         <v>137</v>
       </c>
       <c r="R217" s="5">
@@ -22287,7 +22287,7 @@
         <v>69</v>
       </c>
       <c r="J218" s="5">
-        <f>SUM(E218:I218)</f>
+        <f t="shared" si="10"/>
         <v>344</v>
       </c>
       <c r="K218" s="5">
@@ -22305,7 +22305,7 @@
       <c r="O218" s="5"/>
       <c r="P218" s="5"/>
       <c r="Q218" s="5">
-        <f>MAX(25, INT(POWER(2.2,J218/45)))</f>
+        <f t="shared" si="9"/>
         <v>414</v>
       </c>
       <c r="R218" s="5">
@@ -22359,7 +22359,7 @@
         <v>80</v>
       </c>
       <c r="J219" s="5">
-        <f>SUM(E219:I219)</f>
+        <f t="shared" si="10"/>
         <v>377</v>
       </c>
       <c r="K219" s="5">
@@ -22377,7 +22377,7 @@
       <c r="O219" s="5"/>
       <c r="P219" s="5"/>
       <c r="Q219" s="5">
-        <f>MAX(25, INT(POWER(2.2,J219/45)))</f>
+        <f t="shared" si="9"/>
         <v>739</v>
       </c>
       <c r="R219" s="5">
@@ -22433,7 +22433,7 @@
         <v>80</v>
       </c>
       <c r="J220" s="5">
-        <f>SUM(E220:I220)</f>
+        <f t="shared" si="10"/>
         <v>306</v>
       </c>
       <c r="K220" s="5">
@@ -22508,7 +22508,7 @@
         <v>51</v>
       </c>
       <c r="J221" s="5">
-        <f>SUM(E221:I221)</f>
+        <f t="shared" si="10"/>
         <v>343</v>
       </c>
       <c r="K221" s="5">
@@ -22526,7 +22526,7 @@
       <c r="O221" s="5"/>
       <c r="P221" s="5"/>
       <c r="Q221" s="5">
-        <f>MAX(25, INT(POWER(2.2,J221/45)))</f>
+        <f t="shared" ref="Q221:Q238" si="11">MAX(25, INT(POWER(2.2,J221/45)))</f>
         <v>407</v>
       </c>
       <c r="R221" s="5">
@@ -22588,7 +22588,7 @@
         <v>75</v>
       </c>
       <c r="J222" s="5">
-        <f>SUM(E222:I222)</f>
+        <f t="shared" si="10"/>
         <v>372</v>
       </c>
       <c r="K222" s="5">
@@ -22607,10 +22607,10 @@
         <v>40</v>
       </c>
       <c r="P222" s="5">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q222" s="5">
-        <f>MAX(25, INT(POWER(2.2,J222/45)))</f>
+        <f t="shared" si="11"/>
         <v>677</v>
       </c>
       <c r="R222" s="5">
@@ -22672,7 +22672,7 @@
         <v>66</v>
       </c>
       <c r="J223" s="5">
-        <f>SUM(E223:I223)</f>
+        <f t="shared" si="10"/>
         <v>307</v>
       </c>
       <c r="K223" s="5">
@@ -22690,7 +22690,7 @@
       <c r="O223" s="5"/>
       <c r="P223" s="5"/>
       <c r="Q223" s="5">
-        <f>MAX(25, INT(POWER(2.2,J223/45)))</f>
+        <f t="shared" si="11"/>
         <v>216</v>
       </c>
       <c r="R223" s="5">
@@ -22748,7 +22748,7 @@
         <v>52</v>
       </c>
       <c r="J224" s="5">
-        <f>SUM(E224:I224)</f>
+        <f t="shared" si="10"/>
         <v>219</v>
       </c>
       <c r="K224" s="5">
@@ -22766,7 +22766,7 @@
       <c r="O224" s="5"/>
       <c r="P224" s="5"/>
       <c r="Q224" s="5">
-        <f>MAX(25, INT(POWER(2.2,J224/45)))</f>
+        <f t="shared" si="11"/>
         <v>46</v>
       </c>
       <c r="R224" s="5">
@@ -22824,7 +22824,7 @@
         <v>31</v>
       </c>
       <c r="J225" s="5">
-        <f>SUM(E225:I225)</f>
+        <f t="shared" si="10"/>
         <v>258</v>
       </c>
       <c r="K225" s="5">
@@ -22842,7 +22842,7 @@
       <c r="O225" s="5"/>
       <c r="P225" s="5"/>
       <c r="Q225" s="5">
-        <f>MAX(25, INT(POWER(2.2,J225/45)))</f>
+        <f t="shared" si="11"/>
         <v>91</v>
       </c>
       <c r="R225" s="5">
@@ -22900,7 +22900,7 @@
         <v>61</v>
       </c>
       <c r="J226" s="5">
-        <f>SUM(E226:I226)</f>
+        <f t="shared" si="10"/>
         <v>249</v>
       </c>
       <c r="K226" s="5">
@@ -22918,7 +22918,7 @@
       <c r="O226" s="5"/>
       <c r="P226" s="5"/>
       <c r="Q226" s="5">
-        <f>MAX(25, INT(POWER(2.2,J226/45)))</f>
+        <f t="shared" si="11"/>
         <v>78</v>
       </c>
       <c r="R226" s="5">
@@ -22972,7 +22972,7 @@
         <v>60</v>
       </c>
       <c r="J227" s="5">
-        <f>SUM(E227:I227)</f>
+        <f t="shared" si="10"/>
         <v>308</v>
       </c>
       <c r="K227" s="5">
@@ -22990,7 +22990,7 @@
       <c r="O227" s="5"/>
       <c r="P227" s="5"/>
       <c r="Q227" s="5">
-        <f>MAX(25, INT(POWER(2.2,J227/45)))</f>
+        <f t="shared" si="11"/>
         <v>220</v>
       </c>
       <c r="R227" s="5">
@@ -23044,7 +23044,7 @@
         <v>54</v>
       </c>
       <c r="J228" s="5">
-        <f>SUM(E228:I228)</f>
+        <f t="shared" si="10"/>
         <v>238</v>
       </c>
       <c r="K228" s="5">
@@ -23062,7 +23062,7 @@
       <c r="O228" s="5"/>
       <c r="P228" s="5"/>
       <c r="Q228" s="5">
-        <f>MAX(25, INT(POWER(2.2,J228/45)))</f>
+        <f t="shared" si="11"/>
         <v>64</v>
       </c>
       <c r="R228" s="5">
@@ -23116,7 +23116,7 @@
         <v>53</v>
       </c>
       <c r="J229" s="5">
-        <f>SUM(E229:I229)</f>
+        <f t="shared" si="10"/>
         <v>282</v>
       </c>
       <c r="K229" s="5">
@@ -23134,7 +23134,7 @@
       <c r="O229" s="5"/>
       <c r="P229" s="5"/>
       <c r="Q229" s="5">
-        <f>MAX(25, INT(POWER(2.2,J229/45)))</f>
+        <f t="shared" si="11"/>
         <v>139</v>
       </c>
       <c r="R229" s="5">
@@ -23188,7 +23188,7 @@
         <v>84</v>
       </c>
       <c r="J230" s="5">
-        <f>SUM(E230:I230)</f>
+        <f t="shared" si="10"/>
         <v>303</v>
       </c>
       <c r="K230" s="5">
@@ -23206,7 +23206,7 @@
       <c r="O230" s="5"/>
       <c r="P230" s="5"/>
       <c r="Q230" s="5">
-        <f>MAX(25, INT(POWER(2.2,J230/45)))</f>
+        <f t="shared" si="11"/>
         <v>202</v>
       </c>
       <c r="R230" s="5">
@@ -23260,7 +23260,7 @@
         <v>48</v>
       </c>
       <c r="J231" s="5">
-        <f>SUM(E231:I231)</f>
+        <f t="shared" si="10"/>
         <v>285</v>
       </c>
       <c r="K231" s="5">
@@ -23278,7 +23278,7 @@
       <c r="O231" s="5"/>
       <c r="P231" s="5"/>
       <c r="Q231" s="5">
-        <f>MAX(25, INT(POWER(2.2,J231/45)))</f>
+        <f t="shared" si="11"/>
         <v>147</v>
       </c>
       <c r="R231" s="5">
@@ -23332,7 +23332,7 @@
         <v>71</v>
       </c>
       <c r="J232" s="5">
-        <f>SUM(E232:I232)</f>
+        <f t="shared" si="10"/>
         <v>343</v>
       </c>
       <c r="K232" s="5">
@@ -23350,7 +23350,7 @@
       <c r="O232" s="5"/>
       <c r="P232" s="5"/>
       <c r="Q232" s="5">
-        <f>MAX(25, INT(POWER(2.2,J232/45)))</f>
+        <f t="shared" si="11"/>
         <v>407</v>
       </c>
       <c r="R232" s="5">
@@ -23404,7 +23404,7 @@
         <v>73</v>
       </c>
       <c r="J233" s="5">
-        <f>SUM(E233:I233)</f>
+        <f t="shared" si="10"/>
         <v>318</v>
       </c>
       <c r="K233" s="5">
@@ -23422,7 +23422,7 @@
       <c r="O233" s="5"/>
       <c r="P233" s="5"/>
       <c r="Q233" s="5">
-        <f>MAX(25, INT(POWER(2.2,J233/45)))</f>
+        <f t="shared" si="11"/>
         <v>262</v>
       </c>
       <c r="R233" s="5">
@@ -23476,7 +23476,7 @@
         <v>69</v>
       </c>
       <c r="J234" s="5">
-        <f>SUM(E234:I234)</f>
+        <f t="shared" si="10"/>
         <v>255</v>
       </c>
       <c r="K234" s="5">
@@ -23494,7 +23494,7 @@
       <c r="O234" s="5"/>
       <c r="P234" s="5"/>
       <c r="Q234" s="5">
-        <f>MAX(25, INT(POWER(2.2,J234/45)))</f>
+        <f t="shared" si="11"/>
         <v>87</v>
       </c>
       <c r="R234" s="5">
@@ -23548,7 +23548,7 @@
         <v>42</v>
       </c>
       <c r="J235" s="5">
-        <f>SUM(E235:I235)</f>
+        <f t="shared" si="10"/>
         <v>155</v>
       </c>
       <c r="K235" s="5">
@@ -23566,7 +23566,7 @@
       <c r="O235" s="5"/>
       <c r="P235" s="5"/>
       <c r="Q235" s="5">
-        <f>MAX(25, INT(POWER(2.2,J235/45)))</f>
+        <f t="shared" si="11"/>
         <v>25</v>
       </c>
       <c r="R235" s="5">
@@ -23621,7 +23621,7 @@
         <v>66</v>
       </c>
       <c r="J236" s="5">
-        <f>SUM(E236:I236)</f>
+        <f t="shared" si="10"/>
         <v>208</v>
       </c>
       <c r="K236" s="5">
@@ -23639,7 +23639,7 @@
       <c r="O236" s="5"/>
       <c r="P236" s="5"/>
       <c r="Q236" s="5">
-        <f>MAX(25, INT(POWER(2.2,J236/45)))</f>
+        <f t="shared" si="11"/>
         <v>38</v>
       </c>
       <c r="R236" s="5">
@@ -23693,7 +23693,7 @@
         <v>44</v>
       </c>
       <c r="J237" s="5">
-        <f>SUM(E237:I237)</f>
+        <f t="shared" si="10"/>
         <v>157</v>
       </c>
       <c r="K237" s="5">
@@ -23711,7 +23711,7 @@
       <c r="O237" s="5"/>
       <c r="P237" s="5"/>
       <c r="Q237" s="5">
-        <f>MAX(25, INT(POWER(2.2,J237/45)))</f>
+        <f t="shared" si="11"/>
         <v>25</v>
       </c>
       <c r="R237" s="5">
@@ -23765,7 +23765,7 @@
         <v>62</v>
       </c>
       <c r="J238" s="5">
-        <f>SUM(E238:I238)</f>
+        <f t="shared" si="10"/>
         <v>358</v>
       </c>
       <c r="K238" s="5">
@@ -23783,7 +23783,7 @@
       <c r="O238" s="5"/>
       <c r="P238" s="5"/>
       <c r="Q238" s="5">
-        <f>MAX(25, INT(POWER(2.2,J238/45)))</f>
+        <f t="shared" si="11"/>
         <v>529</v>
       </c>
       <c r="R238" s="5">
@@ -23837,7 +23837,7 @@
         <v>64</v>
       </c>
       <c r="J239" s="5">
-        <f>SUM(E239:I239)</f>
+        <f t="shared" si="10"/>
         <v>128</v>
       </c>
       <c r="K239" s="5">
@@ -23908,7 +23908,7 @@
         <v>79</v>
       </c>
       <c r="J240" s="5">
-        <f>SUM(E240:I240)</f>
+        <f t="shared" si="10"/>
         <v>374</v>
       </c>
       <c r="K240" s="5">
@@ -23926,7 +23926,7 @@
       <c r="O240" s="5"/>
       <c r="P240" s="5"/>
       <c r="Q240" s="5">
-        <f>MAX(25, INT(POWER(2.2,J240/45)))</f>
+        <f t="shared" ref="Q240:Q266" si="12">MAX(25, INT(POWER(2.2,J240/45)))</f>
         <v>701</v>
       </c>
       <c r="R240" s="5">
@@ -23982,7 +23982,7 @@
         <v>50</v>
       </c>
       <c r="J241" s="5">
-        <f>SUM(E241:I241)</f>
+        <f t="shared" si="10"/>
         <v>358</v>
       </c>
       <c r="K241" s="5">
@@ -24000,7 +24000,7 @@
       <c r="O241" s="5"/>
       <c r="P241" s="5"/>
       <c r="Q241" s="5">
-        <f>MAX(25, INT(POWER(2.2,J241/45)))</f>
+        <f t="shared" si="12"/>
         <v>529</v>
       </c>
       <c r="R241" s="5">
@@ -24055,7 +24055,7 @@
         <v>19</v>
       </c>
       <c r="J242" s="5">
-        <f>SUM(E242:I242)</f>
+        <f t="shared" si="10"/>
         <v>211</v>
       </c>
       <c r="K242" s="5">
@@ -24075,7 +24075,7 @@
       </c>
       <c r="P242" s="5"/>
       <c r="Q242" s="5">
-        <f>MAX(25, INT(POWER(2.2,J242/45)))</f>
+        <f t="shared" si="12"/>
         <v>40</v>
       </c>
       <c r="R242" s="5">
@@ -24132,7 +24132,7 @@
         <v>79</v>
       </c>
       <c r="J243" s="5">
-        <f>SUM(E243:I243)</f>
+        <f t="shared" si="10"/>
         <v>383</v>
       </c>
       <c r="K243" s="5">
@@ -24152,7 +24152,7 @@
       </c>
       <c r="P243" s="5"/>
       <c r="Q243" s="5">
-        <f>MAX(25, INT(POWER(2.2,J243/45)))</f>
+        <f t="shared" si="12"/>
         <v>821</v>
       </c>
       <c r="R243" s="5">
@@ -24212,7 +24212,7 @@
         <v>75</v>
       </c>
       <c r="J244" s="5">
-        <f>SUM(E244:I244)</f>
+        <f t="shared" si="10"/>
         <v>355</v>
       </c>
       <c r="K244" s="5">
@@ -24230,7 +24230,7 @@
       <c r="O244" s="5"/>
       <c r="P244" s="5"/>
       <c r="Q244" s="5">
-        <f>MAX(25, INT(POWER(2.2,J244/45)))</f>
+        <f t="shared" si="12"/>
         <v>502</v>
       </c>
       <c r="R244" s="5">
@@ -24290,7 +24290,7 @@
         <v>78</v>
       </c>
       <c r="J245" s="5">
-        <f>SUM(E245:I245)</f>
+        <f t="shared" si="10"/>
         <v>333</v>
       </c>
       <c r="K245" s="5">
@@ -24308,7 +24308,7 @@
       <c r="O245" s="5"/>
       <c r="P245" s="5"/>
       <c r="Q245" s="5">
-        <f>MAX(25, INT(POWER(2.2,J245/45)))</f>
+        <f t="shared" si="12"/>
         <v>341</v>
       </c>
       <c r="R245" s="5">
@@ -24368,7 +24368,7 @@
         <v>55</v>
       </c>
       <c r="J246" s="5">
-        <f>SUM(E246:I246)</f>
+        <f t="shared" si="10"/>
         <v>363</v>
       </c>
       <c r="K246" s="5">
@@ -24388,7 +24388,7 @@
       </c>
       <c r="P246" s="5"/>
       <c r="Q246" s="5">
-        <f>MAX(25, INT(POWER(2.2,J246/45)))</f>
+        <f t="shared" si="12"/>
         <v>578</v>
       </c>
       <c r="R246" s="5">
@@ -24448,7 +24448,7 @@
         <v>78</v>
       </c>
       <c r="J247" s="5">
-        <f>SUM(E247:I247)</f>
+        <f t="shared" si="10"/>
         <v>375</v>
       </c>
       <c r="K247" s="5">
@@ -24466,7 +24466,7 @@
       <c r="O247" s="5"/>
       <c r="P247" s="5"/>
       <c r="Q247" s="5">
-        <f>MAX(25, INT(POWER(2.2,J247/45)))</f>
+        <f t="shared" si="12"/>
         <v>713</v>
       </c>
       <c r="R247" s="5">
@@ -24522,7 +24522,7 @@
         <v>72</v>
       </c>
       <c r="J248" s="5">
-        <f>SUM(E248:I248)</f>
+        <f t="shared" si="10"/>
         <v>361</v>
       </c>
       <c r="K248" s="5">
@@ -24541,10 +24541,10 @@
         <v>40</v>
       </c>
       <c r="P248" s="5">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q248" s="5">
-        <f>MAX(25, INT(POWER(2.2,J248/45)))</f>
+        <f t="shared" si="12"/>
         <v>558</v>
       </c>
       <c r="R248" s="5">
@@ -24600,7 +24600,7 @@
         <v>78</v>
       </c>
       <c r="J249" s="5">
-        <f>SUM(E249:I249)</f>
+        <f t="shared" si="10"/>
         <v>382</v>
       </c>
       <c r="K249" s="5">
@@ -24618,7 +24618,7 @@
       <c r="O249" s="5"/>
       <c r="P249" s="5"/>
       <c r="Q249" s="5">
-        <f>MAX(25, INT(POWER(2.2,J249/45)))</f>
+        <f t="shared" si="12"/>
         <v>806</v>
       </c>
       <c r="R249" s="5">
@@ -24674,7 +24674,7 @@
         <v>76</v>
       </c>
       <c r="J250" s="5">
-        <f>SUM(E250:I250)</f>
+        <f t="shared" si="10"/>
         <v>385</v>
       </c>
       <c r="K250" s="5">
@@ -24693,10 +24693,10 @@
         <v>40</v>
       </c>
       <c r="P250" s="5">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q250" s="5">
-        <f>MAX(25, INT(POWER(2.2,J250/45)))</f>
+        <f t="shared" si="12"/>
         <v>850</v>
       </c>
       <c r="R250" s="5">
@@ -24752,7 +24752,7 @@
         <v>53</v>
       </c>
       <c r="J251" s="5">
-        <f>SUM(E251:I251)</f>
+        <f t="shared" si="10"/>
         <v>288</v>
       </c>
       <c r="K251" s="5">
@@ -24770,7 +24770,7 @@
       <c r="O251" s="5"/>
       <c r="P251" s="5"/>
       <c r="Q251" s="5">
-        <f>MAX(25, INT(POWER(2.2,J251/45)))</f>
+        <f t="shared" si="12"/>
         <v>155</v>
       </c>
       <c r="R251" s="5">
@@ -24824,7 +24824,7 @@
         <v>52</v>
       </c>
       <c r="J252" s="5">
-        <f>SUM(E252:I252)</f>
+        <f t="shared" si="10"/>
         <v>305</v>
       </c>
       <c r="K252" s="5">
@@ -24842,7 +24842,7 @@
       <c r="O252" s="5"/>
       <c r="P252" s="5"/>
       <c r="Q252" s="5">
-        <f>MAX(25, INT(POWER(2.2,J252/45)))</f>
+        <f t="shared" si="12"/>
         <v>209</v>
       </c>
       <c r="R252" s="5">
@@ -24896,7 +24896,7 @@
         <v>53</v>
       </c>
       <c r="J253" s="5">
-        <f>SUM(E253:I253)</f>
+        <f t="shared" si="10"/>
         <v>313</v>
       </c>
       <c r="K253" s="5">
@@ -24914,7 +24914,7 @@
       <c r="O253" s="5"/>
       <c r="P253" s="5"/>
       <c r="Q253" s="5">
-        <f>MAX(25, INT(POWER(2.2,J253/45)))</f>
+        <f t="shared" si="12"/>
         <v>240</v>
       </c>
       <c r="R253" s="5">
@@ -24968,7 +24968,7 @@
         <v>50</v>
       </c>
       <c r="J254" s="5">
-        <f>SUM(E254:I254)</f>
+        <f t="shared" si="10"/>
         <v>263</v>
       </c>
       <c r="K254" s="5">
@@ -24986,7 +24986,7 @@
       <c r="O254" s="5"/>
       <c r="P254" s="5"/>
       <c r="Q254" s="5">
-        <f>MAX(25, INT(POWER(2.2,J254/45)))</f>
+        <f t="shared" si="12"/>
         <v>100</v>
       </c>
       <c r="R254" s="5">
@@ -25040,7 +25040,7 @@
         <v>55</v>
       </c>
       <c r="J255" s="5">
-        <f>SUM(E255:I255)</f>
+        <f t="shared" si="10"/>
         <v>285</v>
       </c>
       <c r="K255" s="5">
@@ -25058,7 +25058,7 @@
       <c r="O255" s="5"/>
       <c r="P255" s="5"/>
       <c r="Q255" s="5">
-        <f>MAX(25, INT(POWER(2.2,J255/45)))</f>
+        <f t="shared" si="12"/>
         <v>147</v>
       </c>
       <c r="R255" s="5">
@@ -25112,7 +25112,7 @@
         <v>73</v>
       </c>
       <c r="J256" s="5">
-        <f>SUM(E256:I256)</f>
+        <f t="shared" si="10"/>
         <v>334</v>
       </c>
       <c r="K256" s="5">
@@ -25130,7 +25130,7 @@
       <c r="O256" s="5"/>
       <c r="P256" s="5"/>
       <c r="Q256" s="5">
-        <f>MAX(25, INT(POWER(2.2,J256/45)))</f>
+        <f t="shared" si="12"/>
         <v>347</v>
       </c>
       <c r="R256" s="5">
@@ -25184,7 +25184,7 @@
         <v>76</v>
       </c>
       <c r="J257" s="5">
-        <f>SUM(E257:I257)</f>
+        <f t="shared" si="10"/>
         <v>329</v>
       </c>
       <c r="K257" s="5">
@@ -25202,7 +25202,7 @@
       <c r="O257" s="5"/>
       <c r="P257" s="5"/>
       <c r="Q257" s="5">
-        <f>MAX(25, INT(POWER(2.2,J257/45)))</f>
+        <f t="shared" si="12"/>
         <v>318</v>
       </c>
       <c r="R257" s="5">
@@ -25256,7 +25256,7 @@
         <v>77</v>
       </c>
       <c r="J258" s="5">
-        <f>SUM(E258:I258)</f>
+        <f t="shared" si="10"/>
         <v>371</v>
       </c>
       <c r="K258" s="5">
@@ -25274,7 +25274,7 @@
       <c r="O258" s="5"/>
       <c r="P258" s="5"/>
       <c r="Q258" s="5">
-        <f>MAX(25, INT(POWER(2.2,J258/45)))</f>
+        <f t="shared" si="12"/>
         <v>665</v>
       </c>
       <c r="R258" s="5">
@@ -25328,7 +25328,7 @@
         <v>66</v>
       </c>
       <c r="J259" s="5">
-        <f>SUM(E259:I259)</f>
+        <f t="shared" si="10"/>
         <v>312</v>
       </c>
       <c r="K259" s="5">
@@ -25346,7 +25346,7 @@
       <c r="O259" s="5"/>
       <c r="P259" s="5"/>
       <c r="Q259" s="5">
-        <f>MAX(25, INT(POWER(2.2,J259/45)))</f>
+        <f t="shared" si="12"/>
         <v>236</v>
       </c>
       <c r="R259" s="5">
@@ -25400,7 +25400,7 @@
         <v>23</v>
       </c>
       <c r="J260" s="5">
-        <f>SUM(E260:I260)</f>
+        <f t="shared" si="10"/>
         <v>281</v>
       </c>
       <c r="K260" s="5">
@@ -25418,7 +25418,7 @@
       <c r="O260" s="5"/>
       <c r="P260" s="5"/>
       <c r="Q260" s="5">
-        <f>MAX(25, INT(POWER(2.2,J260/45)))</f>
+        <f t="shared" si="12"/>
         <v>137</v>
       </c>
       <c r="R260" s="5">
@@ -25472,7 +25472,7 @@
         <v>62</v>
       </c>
       <c r="J261" s="5">
-        <f>SUM(E261:I261)</f>
+        <f t="shared" ref="J261:J324" si="13">SUM(E261:I261)</f>
         <v>316</v>
       </c>
       <c r="K261" s="5">
@@ -25490,7 +25490,7 @@
       <c r="O261" s="5"/>
       <c r="P261" s="5"/>
       <c r="Q261" s="5">
-        <f>MAX(25, INT(POWER(2.2,J261/45)))</f>
+        <f t="shared" si="12"/>
         <v>253</v>
       </c>
       <c r="R261" s="5">
@@ -25544,7 +25544,7 @@
         <v>55</v>
       </c>
       <c r="J262" s="5">
-        <f>SUM(E262:I262)</f>
+        <f t="shared" si="13"/>
         <v>247</v>
       </c>
       <c r="K262" s="5">
@@ -25562,7 +25562,7 @@
       <c r="O262" s="5"/>
       <c r="P262" s="5"/>
       <c r="Q262" s="5">
-        <f>MAX(25, INT(POWER(2.2,J262/45)))</f>
+        <f t="shared" si="12"/>
         <v>75</v>
       </c>
       <c r="R262" s="5">
@@ -25616,7 +25616,7 @@
         <v>73</v>
       </c>
       <c r="J263" s="5">
-        <f>SUM(E263:I263)</f>
+        <f t="shared" si="13"/>
         <v>290</v>
       </c>
       <c r="K263" s="5">
@@ -25634,7 +25634,7 @@
       <c r="O263" s="5"/>
       <c r="P263" s="5"/>
       <c r="Q263" s="5">
-        <f>MAX(25, INT(POWER(2.2,J263/45)))</f>
+        <f t="shared" si="12"/>
         <v>160</v>
       </c>
       <c r="R263" s="5">
@@ -25692,7 +25692,7 @@
         <v>75</v>
       </c>
       <c r="J264" s="5">
-        <f>SUM(E264:I264)</f>
+        <f t="shared" si="13"/>
         <v>244</v>
       </c>
       <c r="K264" s="5">
@@ -25710,7 +25710,7 @@
       <c r="O264" s="5"/>
       <c r="P264" s="5"/>
       <c r="Q264" s="5">
-        <f>MAX(25, INT(POWER(2.2,J264/45)))</f>
+        <f t="shared" si="12"/>
         <v>71</v>
       </c>
       <c r="R264" s="5">
@@ -25768,7 +25768,7 @@
         <v>66</v>
       </c>
       <c r="J265" s="5">
-        <f>SUM(E265:I265)</f>
+        <f t="shared" si="13"/>
         <v>248</v>
       </c>
       <c r="K265" s="5">
@@ -25786,7 +25786,7 @@
       <c r="O265" s="5"/>
       <c r="P265" s="5"/>
       <c r="Q265" s="5">
-        <f>MAX(25, INT(POWER(2.2,J265/45)))</f>
+        <f t="shared" si="12"/>
         <v>77</v>
       </c>
       <c r="R265" s="5">
@@ -25844,7 +25844,7 @@
         <v>65</v>
       </c>
       <c r="J266" s="5">
-        <f>SUM(E266:I266)</f>
+        <f t="shared" si="13"/>
         <v>212</v>
       </c>
       <c r="K266" s="5">
@@ -25862,7 +25862,7 @@
       <c r="O266" s="5"/>
       <c r="P266" s="5"/>
       <c r="Q266" s="5">
-        <f>MAX(25, INT(POWER(2.2,J266/45)))</f>
+        <f t="shared" si="12"/>
         <v>41</v>
       </c>
       <c r="R266" s="5">
@@ -25920,7 +25920,7 @@
         <v>75</v>
       </c>
       <c r="J267" s="5">
-        <f>SUM(E267:I267)</f>
+        <f t="shared" si="13"/>
         <v>304</v>
       </c>
       <c r="K267" s="5">
@@ -25995,7 +25995,7 @@
         <v>58</v>
       </c>
       <c r="J268" s="5">
-        <f>SUM(E268:I268)</f>
+        <f t="shared" si="13"/>
         <v>277</v>
       </c>
       <c r="K268" s="5">
@@ -26013,7 +26013,7 @@
       <c r="O268" s="5"/>
       <c r="P268" s="5"/>
       <c r="Q268" s="5">
-        <f>MAX(25, INT(POWER(2.2,J268/45)))</f>
+        <f t="shared" ref="Q268:Q304" si="14">MAX(25, INT(POWER(2.2,J268/45)))</f>
         <v>128</v>
       </c>
       <c r="R268" s="5">
@@ -26071,7 +26071,7 @@
         <v>54</v>
       </c>
       <c r="J269" s="5">
-        <f>SUM(E269:I269)</f>
+        <f t="shared" si="13"/>
         <v>285</v>
       </c>
       <c r="K269" s="5">
@@ -26089,7 +26089,7 @@
       <c r="O269" s="5"/>
       <c r="P269" s="5"/>
       <c r="Q269" s="5">
-        <f>MAX(25, INT(POWER(2.2,J269/45)))</f>
+        <f t="shared" si="14"/>
         <v>147</v>
       </c>
       <c r="R269" s="5">
@@ -26147,7 +26147,7 @@
         <v>40</v>
       </c>
       <c r="J270" s="5">
-        <f>SUM(E270:I270)</f>
+        <f t="shared" si="13"/>
         <v>243</v>
       </c>
       <c r="K270" s="5">
@@ -26165,7 +26165,7 @@
       <c r="O270" s="5"/>
       <c r="P270" s="5"/>
       <c r="Q270" s="5">
-        <f>MAX(25, INT(POWER(2.2,J270/45)))</f>
+        <f t="shared" si="14"/>
         <v>70</v>
       </c>
       <c r="R270" s="5">
@@ -26223,7 +26223,7 @@
         <v>4</v>
       </c>
       <c r="J271" s="5">
-        <f>SUM(E271:I271)</f>
+        <f t="shared" si="13"/>
         <v>70</v>
       </c>
       <c r="K271" s="5">
@@ -26241,7 +26241,7 @@
       <c r="O271" s="5"/>
       <c r="P271" s="5"/>
       <c r="Q271" s="5">
-        <f>MAX(25, INT(POWER(2.2,J271/45)))</f>
+        <f t="shared" si="14"/>
         <v>25</v>
       </c>
       <c r="R271" s="5">
@@ -26299,7 +26299,7 @@
         <v>20</v>
       </c>
       <c r="J272" s="5">
-        <f>SUM(E272:I272)</f>
+        <f t="shared" si="13"/>
         <v>148</v>
       </c>
       <c r="K272" s="5">
@@ -26317,7 +26317,7 @@
       <c r="O272" s="5"/>
       <c r="P272" s="5"/>
       <c r="Q272" s="5">
-        <f>MAX(25, INT(POWER(2.2,J272/45)))</f>
+        <f t="shared" si="14"/>
         <v>25</v>
       </c>
       <c r="R272" s="5">
@@ -26375,7 +26375,7 @@
         <v>70</v>
       </c>
       <c r="J273" s="5">
-        <f>SUM(E273:I273)</f>
+        <f t="shared" si="13"/>
         <v>286</v>
       </c>
       <c r="K273" s="5">
@@ -26393,7 +26393,7 @@
       <c r="O273" s="5"/>
       <c r="P273" s="5"/>
       <c r="Q273" s="5">
-        <f>MAX(25, INT(POWER(2.2,J273/45)))</f>
+        <f t="shared" si="14"/>
         <v>150</v>
       </c>
       <c r="R273" s="5">
@@ -26451,7 +26451,7 @@
         <v>45</v>
       </c>
       <c r="J274" s="5">
-        <f>SUM(E274:I274)</f>
+        <f t="shared" si="13"/>
         <v>302</v>
       </c>
       <c r="K274" s="5">
@@ -26469,7 +26469,7 @@
       <c r="O274" s="5"/>
       <c r="P274" s="5"/>
       <c r="Q274" s="5">
-        <f>MAX(25, INT(POWER(2.2,J274/45)))</f>
+        <f t="shared" si="14"/>
         <v>198</v>
       </c>
       <c r="R274" s="5">
@@ -26527,7 +26527,7 @@
         <v>47</v>
       </c>
       <c r="J275" s="5">
-        <f>SUM(E275:I275)</f>
+        <f t="shared" si="13"/>
         <v>262</v>
       </c>
       <c r="K275" s="5">
@@ -26545,7 +26545,7 @@
       <c r="O275" s="5"/>
       <c r="P275" s="5"/>
       <c r="Q275" s="5">
-        <f>MAX(25, INT(POWER(2.2,J275/45)))</f>
+        <f t="shared" si="14"/>
         <v>98</v>
       </c>
       <c r="R275" s="5">
@@ -26599,7 +26599,7 @@
         <v>55</v>
       </c>
       <c r="J276" s="5">
-        <f>SUM(E276:I276)</f>
+        <f t="shared" si="13"/>
         <v>315</v>
       </c>
       <c r="K276" s="5">
@@ -26617,7 +26617,7 @@
       <c r="O276" s="5"/>
       <c r="P276" s="5"/>
       <c r="Q276" s="5">
-        <f>MAX(25, INT(POWER(2.2,J276/45)))</f>
+        <f t="shared" si="14"/>
         <v>249</v>
       </c>
       <c r="R276" s="5">
@@ -26671,7 +26671,7 @@
         <v>46</v>
       </c>
       <c r="J277" s="5">
-        <f>SUM(E277:I277)</f>
+        <f t="shared" si="13"/>
         <v>159</v>
       </c>
       <c r="K277" s="5">
@@ -26689,7 +26689,7 @@
       <c r="O277" s="5"/>
       <c r="P277" s="5"/>
       <c r="Q277" s="5">
-        <f>MAX(25, INT(POWER(2.2,J277/45)))</f>
+        <f t="shared" si="14"/>
         <v>25</v>
       </c>
       <c r="R277" s="5">
@@ -26743,7 +26743,7 @@
         <v>83</v>
       </c>
       <c r="J278" s="5">
-        <f>SUM(E278:I278)</f>
+        <f t="shared" si="13"/>
         <v>277</v>
       </c>
       <c r="K278" s="5">
@@ -26761,7 +26761,7 @@
       <c r="O278" s="5"/>
       <c r="P278" s="5"/>
       <c r="Q278" s="5">
-        <f>MAX(25, INT(POWER(2.2,J278/45)))</f>
+        <f t="shared" si="14"/>
         <v>128</v>
       </c>
       <c r="R278" s="5">
@@ -26815,7 +26815,7 @@
         <v>49</v>
       </c>
       <c r="J279" s="5">
-        <f>SUM(E279:I279)</f>
+        <f t="shared" si="13"/>
         <v>220</v>
       </c>
       <c r="K279" s="5">
@@ -26833,7 +26833,7 @@
       <c r="O279" s="5"/>
       <c r="P279" s="5"/>
       <c r="Q279" s="5">
-        <f>MAX(25, INT(POWER(2.2,J279/45)))</f>
+        <f t="shared" si="14"/>
         <v>47</v>
       </c>
       <c r="R279" s="5">
@@ -26887,7 +26887,7 @@
         <v>59</v>
       </c>
       <c r="J280" s="5">
-        <f>SUM(E280:I280)</f>
+        <f t="shared" si="13"/>
         <v>279</v>
       </c>
       <c r="K280" s="5">
@@ -26905,7 +26905,7 @@
       <c r="O280" s="5"/>
       <c r="P280" s="5"/>
       <c r="Q280" s="5">
-        <f>MAX(25, INT(POWER(2.2,J280/45)))</f>
+        <f t="shared" si="14"/>
         <v>132</v>
       </c>
       <c r="R280" s="5">
@@ -26959,7 +26959,7 @@
         <v>46</v>
       </c>
       <c r="J281" s="5">
-        <f>SUM(E281:I281)</f>
+        <f t="shared" si="13"/>
         <v>238</v>
       </c>
       <c r="K281" s="5">
@@ -26977,7 +26977,7 @@
       <c r="O281" s="5"/>
       <c r="P281" s="5"/>
       <c r="Q281" s="5">
-        <f>MAX(25, INT(POWER(2.2,J281/45)))</f>
+        <f t="shared" si="14"/>
         <v>64</v>
       </c>
       <c r="R281" s="5">
@@ -27035,7 +27035,7 @@
         <v>32</v>
       </c>
       <c r="J282" s="5">
-        <f>SUM(E282:I282)</f>
+        <f t="shared" si="13"/>
         <v>246</v>
       </c>
       <c r="K282" s="5">
@@ -27053,7 +27053,7 @@
       <c r="O282" s="5"/>
       <c r="P282" s="5"/>
       <c r="Q282" s="5">
-        <f>MAX(25, INT(POWER(2.2,J282/45)))</f>
+        <f t="shared" si="14"/>
         <v>74</v>
       </c>
       <c r="R282" s="5">
@@ -27107,7 +27107,7 @@
         <v>38</v>
       </c>
       <c r="J283" s="5">
-        <f>SUM(E283:I283)</f>
+        <f t="shared" si="13"/>
         <v>237</v>
       </c>
       <c r="K283" s="5">
@@ -27125,7 +27125,7 @@
       <c r="O283" s="5"/>
       <c r="P283" s="5"/>
       <c r="Q283" s="5">
-        <f>MAX(25, INT(POWER(2.2,J283/45)))</f>
+        <f t="shared" si="14"/>
         <v>63</v>
       </c>
       <c r="R283" s="5">
@@ -27179,7 +27179,7 @@
         <v>45</v>
       </c>
       <c r="J284" s="5">
-        <f>SUM(E284:I284)</f>
+        <f t="shared" si="13"/>
         <v>216</v>
       </c>
       <c r="K284" s="5">
@@ -27197,7 +27197,7 @@
       <c r="O284" s="5"/>
       <c r="P284" s="5"/>
       <c r="Q284" s="5">
-        <f>MAX(25, INT(POWER(2.2,J284/45)))</f>
+        <f t="shared" si="14"/>
         <v>44</v>
       </c>
       <c r="R284" s="5">
@@ -27251,7 +27251,7 @@
         <v>15</v>
       </c>
       <c r="J285" s="5">
-        <f>SUM(E285:I285)</f>
+        <f t="shared" si="13"/>
         <v>194</v>
       </c>
       <c r="K285" s="5">
@@ -27269,7 +27269,7 @@
       <c r="O285" s="5"/>
       <c r="P285" s="5"/>
       <c r="Q285" s="5">
-        <f>MAX(25, INT(POWER(2.2,J285/45)))</f>
+        <f t="shared" si="14"/>
         <v>29</v>
       </c>
       <c r="R285" s="5">
@@ -27323,7 +27323,7 @@
         <v>32</v>
       </c>
       <c r="J286" s="5">
-        <f>SUM(E286:I286)</f>
+        <f t="shared" si="13"/>
         <v>193</v>
       </c>
       <c r="K286" s="5">
@@ -27341,7 +27341,7 @@
       <c r="O286" s="5"/>
       <c r="P286" s="5"/>
       <c r="Q286" s="5">
-        <f>MAX(25, INT(POWER(2.2,J286/45)))</f>
+        <f t="shared" si="14"/>
         <v>29</v>
       </c>
       <c r="R286" s="5">
@@ -27395,7 +27395,7 @@
         <v>53</v>
       </c>
       <c r="J287" s="5">
-        <f>SUM(E287:I287)</f>
+        <f t="shared" si="13"/>
         <v>272</v>
       </c>
       <c r="K287" s="5">
@@ -27413,7 +27413,7 @@
       <c r="O287" s="5"/>
       <c r="P287" s="5"/>
       <c r="Q287" s="5">
-        <f>MAX(25, INT(POWER(2.2,J287/45)))</f>
+        <f t="shared" si="14"/>
         <v>117</v>
       </c>
       <c r="R287" s="5">
@@ -27467,7 +27467,7 @@
         <v>56</v>
       </c>
       <c r="J288" s="5">
-        <f>SUM(E288:I288)</f>
+        <f t="shared" si="13"/>
         <v>262</v>
       </c>
       <c r="K288" s="5">
@@ -27485,7 +27485,7 @@
       <c r="O288" s="5"/>
       <c r="P288" s="5"/>
       <c r="Q288" s="5">
-        <f>MAX(25, INT(POWER(2.2,J288/45)))</f>
+        <f t="shared" si="14"/>
         <v>98</v>
       </c>
       <c r="R288" s="5">
@@ -27539,7 +27539,7 @@
         <v>51</v>
       </c>
       <c r="J289" s="5">
-        <f>SUM(E289:I289)</f>
+        <f t="shared" si="13"/>
         <v>253</v>
       </c>
       <c r="K289" s="5">
@@ -27557,7 +27557,7 @@
       <c r="O289" s="5"/>
       <c r="P289" s="5"/>
       <c r="Q289" s="5">
-        <f>MAX(25, INT(POWER(2.2,J289/45)))</f>
+        <f t="shared" si="14"/>
         <v>84</v>
       </c>
       <c r="R289" s="5">
@@ -27611,7 +27611,7 @@
         <v>44</v>
       </c>
       <c r="J290" s="5">
-        <f>SUM(E290:I290)</f>
+        <f t="shared" si="13"/>
         <v>218</v>
       </c>
       <c r="K290" s="5">
@@ -27629,7 +27629,7 @@
       <c r="O290" s="5"/>
       <c r="P290" s="5"/>
       <c r="Q290" s="5">
-        <f>MAX(25, INT(POWER(2.2,J290/45)))</f>
+        <f t="shared" si="14"/>
         <v>45</v>
       </c>
       <c r="R290" s="5">
@@ -27683,7 +27683,7 @@
         <v>62</v>
       </c>
       <c r="J291" s="5">
-        <f>SUM(E291:I291)</f>
+        <f t="shared" si="13"/>
         <v>359</v>
       </c>
       <c r="K291" s="5">
@@ -27701,7 +27701,7 @@
       <c r="O291" s="5"/>
       <c r="P291" s="5"/>
       <c r="Q291" s="5">
-        <f>MAX(25, INT(POWER(2.2,J291/45)))</f>
+        <f t="shared" si="14"/>
         <v>539</v>
       </c>
       <c r="R291" s="5">
@@ -27755,7 +27755,7 @@
         <v>77</v>
       </c>
       <c r="J292" s="5">
-        <f>SUM(E292:I292)</f>
+        <f t="shared" si="13"/>
         <v>362</v>
       </c>
       <c r="K292" s="5">
@@ -27773,7 +27773,7 @@
       <c r="O292" s="5"/>
       <c r="P292" s="5"/>
       <c r="Q292" s="5">
-        <f>MAX(25, INT(POWER(2.2,J292/45)))</f>
+        <f t="shared" si="14"/>
         <v>568</v>
       </c>
       <c r="R292" s="5">
@@ -27827,7 +27827,7 @@
         <v>61</v>
       </c>
       <c r="J293" s="5">
-        <f>SUM(E293:I293)</f>
+        <f t="shared" si="13"/>
         <v>329</v>
       </c>
       <c r="K293" s="5">
@@ -27845,7 +27845,7 @@
       <c r="O293" s="5"/>
       <c r="P293" s="5"/>
       <c r="Q293" s="5">
-        <f>MAX(25, INT(POWER(2.2,J293/45)))</f>
+        <f t="shared" si="14"/>
         <v>318</v>
       </c>
       <c r="R293" s="5">
@@ -27899,7 +27899,7 @@
         <v>62</v>
       </c>
       <c r="J294" s="5">
-        <f>SUM(E294:I294)</f>
+        <f t="shared" si="13"/>
         <v>293</v>
       </c>
       <c r="K294" s="5">
@@ -27917,7 +27917,7 @@
       <c r="O294" s="5"/>
       <c r="P294" s="5"/>
       <c r="Q294" s="5">
-        <f>MAX(25, INT(POWER(2.2,J294/45)))</f>
+        <f t="shared" si="14"/>
         <v>169</v>
       </c>
       <c r="R294" s="5">
@@ -27971,7 +27971,7 @@
         <v>49</v>
       </c>
       <c r="J295" s="5">
-        <f>SUM(E295:I295)</f>
+        <f t="shared" si="13"/>
         <v>250</v>
       </c>
       <c r="K295" s="5">
@@ -27989,7 +27989,7 @@
       <c r="O295" s="5"/>
       <c r="P295" s="5"/>
       <c r="Q295" s="5">
-        <f>MAX(25, INT(POWER(2.2,J295/45)))</f>
+        <f t="shared" si="14"/>
         <v>79</v>
       </c>
       <c r="R295" s="5">
@@ -28043,7 +28043,7 @@
         <v>72</v>
       </c>
       <c r="J296" s="5">
-        <f>SUM(E296:I296)</f>
+        <f t="shared" si="13"/>
         <v>370</v>
       </c>
       <c r="K296" s="5">
@@ -28061,7 +28061,7 @@
       <c r="O296" s="5"/>
       <c r="P296" s="5"/>
       <c r="Q296" s="5">
-        <f>MAX(25, INT(POWER(2.2,J296/45)))</f>
+        <f t="shared" si="14"/>
         <v>653</v>
       </c>
       <c r="R296" s="5">
@@ -28115,7 +28115,7 @@
         <v>63</v>
       </c>
       <c r="J297" s="5">
-        <f>SUM(E297:I297)</f>
+        <f t="shared" si="13"/>
         <v>313</v>
       </c>
       <c r="K297" s="5">
@@ -28133,7 +28133,7 @@
       <c r="O297" s="5"/>
       <c r="P297" s="5"/>
       <c r="Q297" s="5">
-        <f>MAX(25, INT(POWER(2.2,J297/45)))</f>
+        <f t="shared" si="14"/>
         <v>240</v>
       </c>
       <c r="R297" s="5">
@@ -28187,7 +28187,7 @@
         <v>54</v>
       </c>
       <c r="J298" s="5">
-        <f>SUM(E298:I298)</f>
+        <f t="shared" si="13"/>
         <v>285</v>
       </c>
       <c r="K298" s="5">
@@ -28205,7 +28205,7 @@
       <c r="O298" s="5"/>
       <c r="P298" s="5"/>
       <c r="Q298" s="5">
-        <f>MAX(25, INT(POWER(2.2,J298/45)))</f>
+        <f t="shared" si="14"/>
         <v>147</v>
       </c>
       <c r="R298" s="5">
@@ -28259,7 +28259,7 @@
         <v>38</v>
       </c>
       <c r="J299" s="5">
-        <f>SUM(E299:I299)</f>
+        <f t="shared" si="13"/>
         <v>230</v>
       </c>
       <c r="K299" s="5">
@@ -28277,7 +28277,7 @@
       <c r="O299" s="5"/>
       <c r="P299" s="5"/>
       <c r="Q299" s="5">
-        <f>MAX(25, INT(POWER(2.2,J299/45)))</f>
+        <f t="shared" si="14"/>
         <v>56</v>
       </c>
       <c r="R299" s="5">
@@ -28335,7 +28335,7 @@
         <v>42</v>
       </c>
       <c r="J300" s="5">
-        <f>SUM(E300:I300)</f>
+        <f t="shared" si="13"/>
         <v>267</v>
       </c>
       <c r="K300" s="5">
@@ -28353,7 +28353,7 @@
       <c r="O300" s="5"/>
       <c r="P300" s="5"/>
       <c r="Q300" s="5">
-        <f>MAX(25, INT(POWER(2.2,J300/45)))</f>
+        <f t="shared" si="14"/>
         <v>107</v>
       </c>
       <c r="R300" s="5">
@@ -28411,7 +28411,7 @@
         <v>81</v>
       </c>
       <c r="J301" s="5">
-        <f>SUM(E301:I301)</f>
+        <f t="shared" si="13"/>
         <v>409</v>
       </c>
       <c r="K301" s="5">
@@ -28429,7 +28429,7 @@
       <c r="O301" s="5"/>
       <c r="P301" s="5"/>
       <c r="Q301" s="5">
-        <f>MAX(25, INT(POWER(2.2,J301/45)))</f>
+        <f t="shared" si="14"/>
         <v>1294</v>
       </c>
       <c r="R301" s="5">
@@ -28491,7 +28491,7 @@
         <v>55</v>
       </c>
       <c r="J302" s="5">
-        <f>SUM(E302:I302)</f>
+        <f t="shared" si="13"/>
         <v>310</v>
       </c>
       <c r="K302" s="5">
@@ -28509,7 +28509,7 @@
       <c r="O302" s="5"/>
       <c r="P302" s="5"/>
       <c r="Q302" s="5">
-        <f>MAX(25, INT(POWER(2.2,J302/45)))</f>
+        <f t="shared" si="14"/>
         <v>228</v>
       </c>
       <c r="R302" s="5">
@@ -28567,7 +28567,7 @@
         <v>39</v>
       </c>
       <c r="J303" s="5">
-        <f>SUM(E303:I303)</f>
+        <f t="shared" si="13"/>
         <v>213</v>
       </c>
       <c r="K303" s="5">
@@ -28585,7 +28585,7 @@
       <c r="O303" s="5"/>
       <c r="P303" s="5"/>
       <c r="Q303" s="5">
-        <f>MAX(25, INT(POWER(2.2,J303/45)))</f>
+        <f t="shared" si="14"/>
         <v>41</v>
       </c>
       <c r="R303" s="5">
@@ -28643,7 +28643,7 @@
         <v>53</v>
       </c>
       <c r="J304" s="5">
-        <f>SUM(E304:I304)</f>
+        <f t="shared" si="13"/>
         <v>298</v>
       </c>
       <c r="K304" s="5">
@@ -28661,7 +28661,7 @@
       <c r="O304" s="5"/>
       <c r="P304" s="5"/>
       <c r="Q304" s="5">
-        <f>MAX(25, INT(POWER(2.2,J304/45)))</f>
+        <f t="shared" si="14"/>
         <v>185</v>
       </c>
       <c r="R304" s="5">
@@ -28719,7 +28719,7 @@
         <v>75</v>
       </c>
       <c r="J305" s="5">
-        <f>SUM(E305:I305)</f>
+        <f t="shared" si="13"/>
         <v>365</v>
       </c>
       <c r="K305" s="5">
@@ -28792,7 +28792,7 @@
         <v>75</v>
       </c>
       <c r="J306" s="5">
-        <f>SUM(E306:I306)</f>
+        <f t="shared" si="13"/>
         <v>433</v>
       </c>
       <c r="K306" s="5">
@@ -28808,7 +28808,7 @@
       <c r="O306" s="5"/>
       <c r="P306" s="5"/>
       <c r="Q306" s="5">
-        <f>MAX(25, INT(POWER(2.2,J306/45)))</f>
+        <f t="shared" ref="Q306:Q351" si="15">MAX(25, INT(POWER(2.2,J306/45)))</f>
         <v>1971</v>
       </c>
       <c r="R306" s="5">
@@ -28867,7 +28867,7 @@
         <v>70</v>
       </c>
       <c r="J307" s="5">
-        <f>SUM(E307:I307)</f>
+        <f t="shared" si="13"/>
         <v>386</v>
       </c>
       <c r="K307" s="5">
@@ -28885,7 +28885,7 @@
       </c>
       <c r="P307" s="5"/>
       <c r="Q307" s="5">
-        <f>MAX(25, INT(POWER(2.2,J307/45)))</f>
+        <f t="shared" si="15"/>
         <v>865</v>
       </c>
       <c r="R307" s="5">
@@ -28941,7 +28941,7 @@
         <v>65</v>
       </c>
       <c r="J308" s="5">
-        <f>SUM(E308:I308)</f>
+        <f t="shared" si="13"/>
         <v>371</v>
       </c>
       <c r="K308" s="5">
@@ -28959,7 +28959,7 @@
       </c>
       <c r="P308" s="5"/>
       <c r="Q308" s="5">
-        <f>MAX(25, INT(POWER(2.2,J308/45)))</f>
+        <f t="shared" si="15"/>
         <v>665</v>
       </c>
       <c r="R308" s="5">
@@ -29018,7 +29018,7 @@
         <v>92</v>
       </c>
       <c r="J309" s="5">
-        <f>SUM(E309:I309)</f>
+        <f t="shared" si="13"/>
         <v>420</v>
       </c>
       <c r="K309" s="5">
@@ -29034,7 +29034,7 @@
       <c r="O309" s="5"/>
       <c r="P309" s="5"/>
       <c r="Q309" s="5">
-        <f>MAX(25, INT(POWER(2.2,J309/45)))</f>
+        <f t="shared" si="15"/>
         <v>1570</v>
       </c>
       <c r="R309" s="5">
@@ -29093,7 +29093,7 @@
         <v>65</v>
       </c>
       <c r="J310" s="5">
-        <f>SUM(E310:I310)</f>
+        <f t="shared" si="13"/>
         <v>382</v>
       </c>
       <c r="K310" s="5">
@@ -29111,7 +29111,7 @@
       </c>
       <c r="P310" s="5"/>
       <c r="Q310" s="5">
-        <f>MAX(25, INT(POWER(2.2,J310/45)))</f>
+        <f t="shared" si="15"/>
         <v>806</v>
       </c>
       <c r="R310" s="5">
@@ -29170,7 +29170,7 @@
         <v>71</v>
       </c>
       <c r="J311" s="5">
-        <f>SUM(E311:I311)</f>
+        <f t="shared" si="13"/>
         <v>390</v>
       </c>
       <c r="K311" s="5">
@@ -29186,7 +29186,7 @@
       <c r="O311" s="5"/>
       <c r="P311" s="5"/>
       <c r="Q311" s="5">
-        <f>MAX(25, INT(POWER(2.2,J311/45)))</f>
+        <f t="shared" si="15"/>
         <v>928</v>
       </c>
       <c r="R311" s="5">
@@ -29245,7 +29245,7 @@
         <v>78</v>
       </c>
       <c r="J312" s="5">
-        <f>SUM(E312:I312)</f>
+        <f t="shared" si="13"/>
         <v>366</v>
       </c>
       <c r="K312" s="5">
@@ -29263,7 +29263,7 @@
       </c>
       <c r="P312" s="5"/>
       <c r="Q312" s="5">
-        <f>MAX(25, INT(POWER(2.2,J312/45)))</f>
+        <f t="shared" si="15"/>
         <v>609</v>
       </c>
       <c r="R312" s="5">
@@ -29322,7 +29322,7 @@
         <v>75</v>
       </c>
       <c r="J313" s="5">
-        <f>SUM(E313:I313)</f>
+        <f t="shared" si="13"/>
         <v>368</v>
       </c>
       <c r="K313" s="5">
@@ -29338,7 +29338,7 @@
       <c r="O313" s="5"/>
       <c r="P313" s="5"/>
       <c r="Q313" s="5">
-        <f>MAX(25, INT(POWER(2.2,J313/45)))</f>
+        <f t="shared" si="15"/>
         <v>631</v>
       </c>
       <c r="R313" s="5">
@@ -29397,7 +29397,7 @@
         <v>82</v>
       </c>
       <c r="J314" s="5">
-        <f>SUM(E314:I314)</f>
+        <f t="shared" si="13"/>
         <v>316</v>
       </c>
       <c r="K314" s="5">
@@ -29415,7 +29415,7 @@
       </c>
       <c r="P314" s="5"/>
       <c r="Q314" s="5">
-        <f>MAX(25, INT(POWER(2.2,J314/45)))</f>
+        <f t="shared" si="15"/>
         <v>253</v>
       </c>
       <c r="R314" s="5">
@@ -29474,7 +29474,7 @@
         <v>94</v>
       </c>
       <c r="J315" s="5">
-        <f>SUM(E315:I315)</f>
+        <f t="shared" si="13"/>
         <v>432</v>
       </c>
       <c r="K315" s="5">
@@ -29490,7 +29490,7 @@
       <c r="O315" s="5"/>
       <c r="P315" s="5"/>
       <c r="Q315" s="5">
-        <f>MAX(25, INT(POWER(2.2,J315/45)))</f>
+        <f t="shared" si="15"/>
         <v>1937</v>
       </c>
       <c r="R315" s="5">
@@ -29550,7 +29550,7 @@
         <v>92</v>
       </c>
       <c r="J316" s="5">
-        <f>SUM(E316:I316)</f>
+        <f t="shared" si="13"/>
         <v>434</v>
       </c>
       <c r="K316" s="5">
@@ -29568,7 +29568,7 @@
       </c>
       <c r="P316" s="5"/>
       <c r="Q316" s="5">
-        <f>MAX(25, INT(POWER(2.2,J316/45)))</f>
+        <f t="shared" si="15"/>
         <v>2006</v>
       </c>
       <c r="R316" s="5">
@@ -29630,7 +29630,7 @@
         <v>79</v>
       </c>
       <c r="J317" s="5">
-        <f>SUM(E317:I317)</f>
+        <f t="shared" si="13"/>
         <v>416</v>
       </c>
       <c r="K317" s="5">
@@ -29646,7 +29646,7 @@
       <c r="O317" s="5"/>
       <c r="P317" s="5"/>
       <c r="Q317" s="5">
-        <f>MAX(25, INT(POWER(2.2,J317/45)))</f>
+        <f t="shared" si="15"/>
         <v>1463</v>
       </c>
       <c r="R317" s="5">
@@ -29706,7 +29706,7 @@
         <v>73</v>
       </c>
       <c r="J318" s="5">
-        <f>SUM(E318:I318)</f>
+        <f t="shared" si="13"/>
         <v>354</v>
       </c>
       <c r="K318" s="5">
@@ -29722,7 +29722,7 @@
       <c r="O318" s="5"/>
       <c r="P318" s="5"/>
       <c r="Q318" s="5">
-        <f>MAX(25, INT(POWER(2.2,J318/45)))</f>
+        <f t="shared" si="15"/>
         <v>493</v>
       </c>
       <c r="R318" s="5">
@@ -29781,7 +29781,7 @@
         <v>65</v>
       </c>
       <c r="J319" s="5">
-        <f>SUM(E319:I319)</f>
+        <f t="shared" si="13"/>
         <v>381</v>
       </c>
       <c r="K319" s="5">
@@ -29799,7 +29799,7 @@
       </c>
       <c r="P319" s="5"/>
       <c r="Q319" s="5">
-        <f>MAX(25, INT(POWER(2.2,J319/45)))</f>
+        <f t="shared" si="15"/>
         <v>792</v>
       </c>
       <c r="R319" s="5">
@@ -29861,7 +29861,7 @@
         <v>67</v>
       </c>
       <c r="J320" s="5">
-        <f>SUM(E320:I320)</f>
+        <f t="shared" si="13"/>
         <v>321</v>
       </c>
       <c r="K320" s="5">
@@ -29877,7 +29877,7 @@
       <c r="O320" s="5"/>
       <c r="P320" s="5"/>
       <c r="Q320" s="5">
-        <f>MAX(25, INT(POWER(2.2,J320/45)))</f>
+        <f t="shared" si="15"/>
         <v>277</v>
       </c>
       <c r="R320" s="5">
@@ -29936,7 +29936,7 @@
         <v>72</v>
       </c>
       <c r="J321" s="5">
-        <f>SUM(E321:I321)</f>
+        <f t="shared" si="13"/>
         <v>323</v>
       </c>
       <c r="K321" s="5">
@@ -29953,10 +29953,10 @@
         <v>50</v>
       </c>
       <c r="P321" s="5">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q321" s="5">
-        <f>MAX(25, INT(POWER(2.2,J321/45)))</f>
+        <f t="shared" si="15"/>
         <v>286</v>
       </c>
       <c r="R321" s="5">
@@ -30013,7 +30013,7 @@
         <v>70</v>
       </c>
       <c r="J322" s="5">
-        <f>SUM(E322:I322)</f>
+        <f t="shared" si="13"/>
         <v>333</v>
       </c>
       <c r="K322" s="5">
@@ -30030,10 +30030,10 @@
         <v>26</v>
       </c>
       <c r="P322" s="5">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="Q322" s="5">
-        <f>MAX(25, INT(POWER(2.2,J322/45)))</f>
+        <f t="shared" si="15"/>
         <v>341</v>
       </c>
       <c r="R322" s="5">
@@ -30091,7 +30091,7 @@
         <v>52</v>
       </c>
       <c r="J323" s="5">
-        <f>SUM(E323:I323)</f>
+        <f t="shared" si="13"/>
         <v>146</v>
       </c>
       <c r="K323" s="5">
@@ -30109,7 +30109,7 @@
       </c>
       <c r="P323" s="5"/>
       <c r="Q323" s="5">
-        <f>MAX(25, INT(POWER(2.2,J323/45)))</f>
+        <f t="shared" si="15"/>
         <v>25</v>
       </c>
       <c r="R323" s="5">
@@ -30168,7 +30168,7 @@
         <v>65</v>
       </c>
       <c r="J324" s="5">
-        <f>SUM(E324:I324)</f>
+        <f t="shared" si="13"/>
         <v>285</v>
       </c>
       <c r="K324" s="5">
@@ -30186,7 +30186,7 @@
       </c>
       <c r="P324" s="5"/>
       <c r="Q324" s="5">
-        <f>MAX(25, INT(POWER(2.2,J324/45)))</f>
+        <f t="shared" si="15"/>
         <v>147</v>
       </c>
       <c r="R324" s="5">
@@ -30246,7 +30246,7 @@
         <v>87</v>
       </c>
       <c r="J325" s="5">
-        <f>SUM(E325:I325)</f>
+        <f t="shared" ref="J325:J388" si="16">SUM(E325:I325)</f>
         <v>439</v>
       </c>
       <c r="K325" s="5">
@@ -30264,7 +30264,7 @@
       </c>
       <c r="P325" s="5"/>
       <c r="Q325" s="5">
-        <f>MAX(25, INT(POWER(2.2,J325/45)))</f>
+        <f t="shared" si="15"/>
         <v>2190</v>
       </c>
       <c r="R325" s="5">
@@ -30324,7 +30324,7 @@
         <v>68</v>
       </c>
       <c r="J326" s="5">
-        <f>SUM(E326:I326)</f>
+        <f t="shared" si="16"/>
         <v>349</v>
       </c>
       <c r="K326" s="5">
@@ -30340,7 +30340,7 @@
       <c r="O326" s="5"/>
       <c r="P326" s="5"/>
       <c r="Q326" s="5">
-        <f>MAX(25, INT(POWER(2.2,J326/45)))</f>
+        <f t="shared" si="15"/>
         <v>452</v>
       </c>
       <c r="R326" s="5">
@@ -30400,7 +30400,7 @@
         <v>27</v>
       </c>
       <c r="J327" s="5">
-        <f>SUM(E327:I327)</f>
+        <f t="shared" si="16"/>
         <v>224</v>
       </c>
       <c r="K327" s="5">
@@ -30416,7 +30416,7 @@
       <c r="O327" s="5"/>
       <c r="P327" s="5"/>
       <c r="Q327" s="5">
-        <f>MAX(25, INT(POWER(2.2,J327/45)))</f>
+        <f t="shared" si="15"/>
         <v>50</v>
       </c>
       <c r="R327" s="5">
@@ -30476,7 +30476,7 @@
         <v>68</v>
       </c>
       <c r="J328" s="5">
-        <f>SUM(E328:I328)</f>
+        <f t="shared" si="16"/>
         <v>364</v>
       </c>
       <c r="K328" s="5">
@@ -30493,10 +30493,10 @@
         <v>40</v>
       </c>
       <c r="P328" s="5">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q328" s="5">
-        <f>MAX(25, INT(POWER(2.2,J328/45)))</f>
+        <f t="shared" si="15"/>
         <v>588</v>
       </c>
       <c r="R328" s="5">
@@ -30555,7 +30555,7 @@
         <v>52</v>
       </c>
       <c r="J329" s="5">
-        <f>SUM(E329:I329)</f>
+        <f t="shared" si="16"/>
         <v>309</v>
       </c>
       <c r="K329" s="5">
@@ -30571,7 +30571,7 @@
       <c r="O329" s="5"/>
       <c r="P329" s="5"/>
       <c r="Q329" s="5">
-        <f>MAX(25, INT(POWER(2.2,J329/45)))</f>
+        <f t="shared" si="15"/>
         <v>224</v>
       </c>
       <c r="R329" s="5">
@@ -30631,7 +30631,7 @@
         <v>92</v>
       </c>
       <c r="J330" s="5">
-        <f>SUM(E330:I330)</f>
+        <f t="shared" si="16"/>
         <v>430</v>
       </c>
       <c r="K330" s="5">
@@ -30647,7 +30647,7 @@
       <c r="O330" s="5"/>
       <c r="P330" s="5"/>
       <c r="Q330" s="5">
-        <f>MAX(25, INT(POWER(2.2,J330/45)))</f>
+        <f t="shared" si="15"/>
         <v>1870</v>
       </c>
       <c r="R330" s="5">
@@ -30707,7 +30707,7 @@
         <v>57</v>
       </c>
       <c r="J331" s="5">
-        <f>SUM(E331:I331)</f>
+        <f t="shared" si="16"/>
         <v>346</v>
       </c>
       <c r="K331" s="5">
@@ -30725,7 +30725,7 @@
       </c>
       <c r="P331" s="5"/>
       <c r="Q331" s="5">
-        <f>MAX(25, INT(POWER(2.2,J331/45)))</f>
+        <f t="shared" si="15"/>
         <v>429</v>
       </c>
       <c r="R331" s="5">
@@ -30785,7 +30785,7 @@
         <v>85</v>
       </c>
       <c r="J332" s="5">
-        <f>SUM(E332:I332)</f>
+        <f t="shared" si="16"/>
         <v>326</v>
       </c>
       <c r="K332" s="5">
@@ -30803,7 +30803,7 @@
       </c>
       <c r="P332" s="5"/>
       <c r="Q332" s="5">
-        <f>MAX(25, INT(POWER(2.2,J332/45)))</f>
+        <f t="shared" si="15"/>
         <v>302</v>
       </c>
       <c r="R332" s="5">
@@ -30863,7 +30863,7 @@
         <v>70</v>
       </c>
       <c r="J333" s="5">
-        <f>SUM(E333:I333)</f>
+        <f t="shared" si="16"/>
         <v>296</v>
       </c>
       <c r="K333" s="5">
@@ -30881,7 +30881,7 @@
       </c>
       <c r="P333" s="5"/>
       <c r="Q333" s="5">
-        <f>MAX(25, INT(POWER(2.2,J333/45)))</f>
+        <f t="shared" si="15"/>
         <v>178</v>
       </c>
       <c r="R333" s="5">
@@ -30941,7 +30941,7 @@
         <v>88</v>
       </c>
       <c r="J334" s="5">
-        <f>SUM(E334:I334)</f>
+        <f t="shared" si="16"/>
         <v>372</v>
       </c>
       <c r="K334" s="5">
@@ -30959,7 +30959,7 @@
       </c>
       <c r="P334" s="5"/>
       <c r="Q334" s="5">
-        <f>MAX(25, INT(POWER(2.2,J334/45)))</f>
+        <f t="shared" si="15"/>
         <v>677</v>
       </c>
       <c r="R334" s="5">
@@ -31021,7 +31021,7 @@
         <v>75</v>
       </c>
       <c r="J335" s="5">
-        <f>SUM(E335:I335)</f>
+        <f t="shared" si="16"/>
         <v>388</v>
       </c>
       <c r="K335" s="5">
@@ -31037,7 +31037,7 @@
       <c r="O335" s="5"/>
       <c r="P335" s="5"/>
       <c r="Q335" s="5">
-        <f>MAX(25, INT(POWER(2.2,J335/45)))</f>
+        <f t="shared" si="15"/>
         <v>896</v>
       </c>
       <c r="R335" s="5">
@@ -31097,7 +31097,7 @@
         <v>70</v>
       </c>
       <c r="J336" s="5">
-        <f>SUM(E336:I336)</f>
+        <f t="shared" si="16"/>
         <v>377</v>
       </c>
       <c r="K336" s="5">
@@ -31114,10 +31114,10 @@
         <v>26</v>
       </c>
       <c r="P336" s="5">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="Q336" s="5">
-        <f>MAX(25, INT(POWER(2.2,J336/45)))</f>
+        <f t="shared" si="15"/>
         <v>739</v>
       </c>
       <c r="R336" s="5">
@@ -31175,7 +31175,7 @@
         <v>78</v>
       </c>
       <c r="J337" s="5">
-        <f>SUM(E337:I337)</f>
+        <f t="shared" si="16"/>
         <v>359</v>
       </c>
       <c r="K337" s="5">
@@ -31191,7 +31191,7 @@
       <c r="O337" s="5"/>
       <c r="P337" s="5"/>
       <c r="Q337" s="5">
-        <f>MAX(25, INT(POWER(2.2,J337/45)))</f>
+        <f t="shared" si="15"/>
         <v>539</v>
       </c>
       <c r="R337" s="5">
@@ -31249,7 +31249,7 @@
         <v>82</v>
       </c>
       <c r="J338" s="5">
-        <f>SUM(E338:I338)</f>
+        <f t="shared" si="16"/>
         <v>308</v>
       </c>
       <c r="K338" s="5">
@@ -31267,7 +31267,7 @@
       </c>
       <c r="P338" s="5"/>
       <c r="Q338" s="5">
-        <f>MAX(25, INT(POWER(2.2,J338/45)))</f>
+        <f t="shared" si="15"/>
         <v>220</v>
       </c>
       <c r="R338" s="5">
@@ -31327,7 +31327,7 @@
         <v>65</v>
       </c>
       <c r="J339" s="5">
-        <f>SUM(E339:I339)</f>
+        <f t="shared" si="16"/>
         <v>365</v>
       </c>
       <c r="K339" s="5">
@@ -31345,7 +31345,7 @@
       </c>
       <c r="P339" s="5"/>
       <c r="Q339" s="5">
-        <f>MAX(25, INT(POWER(2.2,J339/45)))</f>
+        <f t="shared" si="15"/>
         <v>599</v>
       </c>
       <c r="R339" s="5">
@@ -31405,7 +31405,7 @@
         <v>86</v>
       </c>
       <c r="J340" s="5">
-        <f>SUM(E340:I340)</f>
+        <f t="shared" si="16"/>
         <v>394</v>
       </c>
       <c r="K340" s="5">
@@ -31423,7 +31423,7 @@
       </c>
       <c r="P340" s="5"/>
       <c r="Q340" s="5">
-        <f>MAX(25, INT(POWER(2.2,J340/45)))</f>
+        <f t="shared" si="15"/>
         <v>995</v>
       </c>
       <c r="R340" s="5">
@@ -31483,7 +31483,7 @@
         <v>81</v>
       </c>
       <c r="J341" s="5">
-        <f>SUM(E341:I341)</f>
+        <f t="shared" si="16"/>
         <v>379</v>
       </c>
       <c r="K341" s="5">
@@ -31501,7 +31501,7 @@
       </c>
       <c r="P341" s="5"/>
       <c r="Q341" s="5">
-        <f>MAX(25, INT(POWER(2.2,J341/45)))</f>
+        <f t="shared" si="15"/>
         <v>765</v>
       </c>
       <c r="R341" s="5">
@@ -31559,7 +31559,7 @@
         <v>83</v>
       </c>
       <c r="J342" s="5">
-        <f>SUM(E342:I342)</f>
+        <f t="shared" si="16"/>
         <v>371</v>
       </c>
       <c r="K342" s="5">
@@ -31577,7 +31577,7 @@
       </c>
       <c r="P342" s="5"/>
       <c r="Q342" s="5">
-        <f>MAX(25, INT(POWER(2.2,J342/45)))</f>
+        <f t="shared" si="15"/>
         <v>665</v>
       </c>
       <c r="R342" s="5">
@@ -31637,7 +31637,7 @@
         <v>75</v>
       </c>
       <c r="J343" s="5">
-        <f>SUM(E343:I343)</f>
+        <f t="shared" si="16"/>
         <v>348</v>
       </c>
       <c r="K343" s="5">
@@ -31655,7 +31655,7 @@
       </c>
       <c r="P343" s="5"/>
       <c r="Q343" s="5">
-        <f>MAX(25, INT(POWER(2.2,J343/45)))</f>
+        <f t="shared" si="15"/>
         <v>444</v>
       </c>
       <c r="R343" s="5">
@@ -31715,7 +31715,7 @@
         <v>87</v>
       </c>
       <c r="J344" s="5">
-        <f>SUM(E344:I344)</f>
+        <f t="shared" si="16"/>
         <v>397</v>
       </c>
       <c r="K344" s="5">
@@ -31731,7 +31731,7 @@
       <c r="O344" s="5"/>
       <c r="P344" s="5"/>
       <c r="Q344" s="5">
-        <f>MAX(25, INT(POWER(2.2,J344/45)))</f>
+        <f t="shared" si="15"/>
         <v>1049</v>
       </c>
       <c r="R344" s="5">
@@ -31791,7 +31791,7 @@
         <v>51</v>
       </c>
       <c r="J345" s="5">
-        <f>SUM(E345:I345)</f>
+        <f t="shared" si="16"/>
         <v>345</v>
       </c>
       <c r="K345" s="5">
@@ -31807,7 +31807,7 @@
       <c r="O345" s="5"/>
       <c r="P345" s="5"/>
       <c r="Q345" s="5">
-        <f>MAX(25, INT(POWER(2.2,J345/45)))</f>
+        <f t="shared" si="15"/>
         <v>421</v>
       </c>
       <c r="R345" s="5">
@@ -31869,7 +31869,7 @@
         <v>86</v>
       </c>
       <c r="J346" s="5">
-        <f>SUM(E346:I346)</f>
+        <f t="shared" si="16"/>
         <v>415</v>
       </c>
       <c r="K346" s="5">
@@ -31886,10 +31886,10 @@
         <v>50</v>
       </c>
       <c r="P346" s="5">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q346" s="5">
-        <f>MAX(25, INT(POWER(2.2,J346/45)))</f>
+        <f t="shared" si="15"/>
         <v>1438</v>
       </c>
       <c r="R346" s="5">
@@ -31949,7 +31949,7 @@
         <v>50</v>
       </c>
       <c r="J347" s="5">
-        <f>SUM(E347:I347)</f>
+        <f t="shared" si="16"/>
         <v>303</v>
       </c>
       <c r="K347" s="5">
@@ -31966,10 +31966,10 @@
         <v>50</v>
       </c>
       <c r="P347" s="5">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q347" s="5">
-        <f>MAX(25, INT(POWER(2.2,J347/45)))</f>
+        <f t="shared" si="15"/>
         <v>202</v>
       </c>
       <c r="R347" s="5">
@@ -32027,7 +32027,7 @@
         <v>76</v>
       </c>
       <c r="J348" s="5">
-        <f>SUM(E348:I348)</f>
+        <f t="shared" si="16"/>
         <v>382</v>
       </c>
       <c r="K348" s="5">
@@ -32043,7 +32043,7 @@
       <c r="O348" s="5"/>
       <c r="P348" s="5"/>
       <c r="Q348" s="5">
-        <f>MAX(25, INT(POWER(2.2,J348/45)))</f>
+        <f t="shared" si="15"/>
         <v>806</v>
       </c>
       <c r="R348" s="5">
@@ -32103,7 +32103,7 @@
         <v>56</v>
       </c>
       <c r="J349" s="5">
-        <f>SUM(E349:I349)</f>
+        <f t="shared" si="16"/>
         <v>271</v>
       </c>
       <c r="K349" s="5">
@@ -32119,7 +32119,7 @@
       <c r="O349" s="5"/>
       <c r="P349" s="5"/>
       <c r="Q349" s="5">
-        <f>MAX(25, INT(POWER(2.2,J349/45)))</f>
+        <f t="shared" si="15"/>
         <v>115</v>
       </c>
       <c r="R349" s="5">
@@ -32177,7 +32177,7 @@
         <v>64</v>
       </c>
       <c r="J350" s="5">
-        <f>SUM(E350:I350)</f>
+        <f t="shared" si="16"/>
         <v>335</v>
       </c>
       <c r="K350" s="5">
@@ -32193,7 +32193,7 @@
       <c r="O350" s="5"/>
       <c r="P350" s="5"/>
       <c r="Q350" s="5">
-        <f>MAX(25, INT(POWER(2.2,J350/45)))</f>
+        <f t="shared" si="15"/>
         <v>354</v>
       </c>
       <c r="R350" s="5">
@@ -32253,7 +32253,7 @@
         <v>70</v>
       </c>
       <c r="J351" s="5">
-        <f>SUM(E351:I351)</f>
+        <f t="shared" si="16"/>
         <v>331</v>
       </c>
       <c r="K351" s="5">
@@ -32269,7 +32269,7 @@
       <c r="O351" s="5"/>
       <c r="P351" s="5"/>
       <c r="Q351" s="5">
-        <f>MAX(25, INT(POWER(2.2,J351/45)))</f>
+        <f t="shared" si="15"/>
         <v>330</v>
       </c>
       <c r="R351" s="5">

--- a/Design/config/HeroConfig.xlsx
+++ b/Design/config/HeroConfig.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2656" uniqueCount="1027">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2656" uniqueCount="1028">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -3837,79 +3837,83 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>荀彧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>马玩</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓟</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>邺</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>程银</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>马超</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>江夏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>张松</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阎象</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>北海</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>襄阳</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>零陵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>邺</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>江夏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>汉中</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>江州</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>BornCity</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>荀彧</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>马玩</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>蓟</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>邺</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>程银</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>马超</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>江夏</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>张松</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>阎象</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>北海</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>襄阳</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>零陵</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>邺</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>江夏</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>汉中</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>江州</t>
+    <t>吴</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6131,7 +6135,7 @@
         <v>607</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>1008</v>
+        <v>1026</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>245</v>
@@ -6214,7 +6218,7 @@
         <v>608</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="N3" s="7" t="s">
         <v>7</v>
@@ -6297,7 +6301,7 @@
         <v>609</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="N4" s="7" t="s">
         <v>6</v>
@@ -6381,7 +6385,7 @@
         <v>696</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="N5" s="5">
         <v>10</v>
@@ -7627,7 +7631,7 @@
         <v>102003</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C21" s="5">
         <v>163</v>
@@ -12914,7 +12918,7 @@
         <v>739</v>
       </c>
       <c r="M88" s="5" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="N88" s="5">
         <v>10</v>
@@ -22121,7 +22125,7 @@
         <v>106001</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C206" s="5">
         <v>176</v>
@@ -22629,7 +22633,7 @@
         <v>611</v>
       </c>
       <c r="M212" s="5" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="N212" s="5">
         <v>10</v>
@@ -22670,7 +22674,7 @@
         <v>106008</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C213" s="5">
         <v>175</v>
@@ -22704,7 +22708,7 @@
         <v>612</v>
       </c>
       <c r="M213" s="5" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="N213" s="5">
         <v>10</v>
@@ -22779,7 +22783,7 @@
         <v>611</v>
       </c>
       <c r="M214" s="5" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="N214" s="5">
         <v>10</v>
@@ -22895,7 +22899,7 @@
         <v>106011</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C216" s="5">
         <v>170</v>
@@ -23004,7 +23008,7 @@
         <v>612</v>
       </c>
       <c r="M217" s="5" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="N217" s="5">
         <v>10</v>
@@ -24692,7 +24696,7 @@
         <v>688</v>
       </c>
       <c r="M239" s="5" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="N239" s="5">
         <v>10</v>
@@ -24885,7 +24889,7 @@
         <v>108003</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C242" s="5">
         <v>165</v>
@@ -28510,7 +28514,7 @@
         <v>110015</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C289" s="5">
         <v>166</v>
@@ -31757,7 +31761,7 @@
       </c>
       <c r="L330" s="5"/>
       <c r="M330" s="5" t="s">
-        <v>1002</v>
+        <v>1027</v>
       </c>
       <c r="N330" s="5">
         <v>10</v>
@@ -31836,7 +31840,7 @@
       </c>
       <c r="L331" s="5"/>
       <c r="M331" s="5" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="N331" s="5">
         <v>10</v>
@@ -32480,7 +32484,7 @@
       </c>
       <c r="L339" s="5"/>
       <c r="M339" s="5" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="N339" s="5">
         <v>99</v>
@@ -32561,7 +32565,7 @@
       </c>
       <c r="L340" s="5"/>
       <c r="M340" s="5" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="N340" s="5">
         <v>99</v>
@@ -32642,7 +32646,7 @@
       </c>
       <c r="L341" s="5"/>
       <c r="M341" s="5" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="N341" s="5">
         <v>10</v>
@@ -32721,7 +32725,7 @@
       </c>
       <c r="L342" s="5"/>
       <c r="M342" s="5" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="N342" s="5">
         <v>10</v>
@@ -32802,7 +32806,7 @@
       </c>
       <c r="L343" s="5"/>
       <c r="M343" s="5" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="N343" s="5">
         <v>10</v>
@@ -32962,7 +32966,7 @@
       </c>
       <c r="L345" s="5"/>
       <c r="M345" s="5" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="N345" s="5">
         <v>10</v>
